--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ255"/>
+  <dimension ref="A1:AZ256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7753,10 +7753,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>96714961</v>
+        <v>136837813</v>
       </c>
       <c r="B69" t="n">
-        <v>90691</v>
+        <v>93395</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7764,37 +7764,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6276</v>
+        <v>6055</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bengttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471372</v>
+        <v>470979</v>
       </c>
       <c r="R69" t="n">
-        <v>6770686</v>
+        <v>6770615</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7818,12 +7818,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7838,24 +7838,24 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714961</t>
+          <t>https://artportalen.se/Sighting/136837813</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>96715014</v>
+        <v>96714961</v>
       </c>
       <c r="B70" t="n">
         <v>90691</v>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>470841</v>
+        <v>471372</v>
       </c>
       <c r="R70" t="n">
-        <v>6770558</v>
+        <v>6770686</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -7951,16 +7951,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715014</t>
+          <t>https://artportalen.se/Sighting/96714961</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>96715007</v>
+        <v>96715014</v>
       </c>
       <c r="B71" t="n">
-        <v>79327</v>
+        <v>90691</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7968,21 +7968,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471383</v>
+        <v>470841</v>
       </c>
       <c r="R71" t="n">
-        <v>6770715</v>
+        <v>6770558</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8053,13 +8053,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715007</t>
+          <t>https://artportalen.se/Sighting/96715014</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129943529</v>
+        <v>96715007</v>
       </c>
       <c r="B72" t="n">
         <v>79327</v>
@@ -8090,17 +8090,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471492</v>
+        <v>471383</v>
       </c>
       <c r="R72" t="n">
-        <v>6770712</v>
+        <v>6770715</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8124,22 +8124,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8154,24 +8144,24 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943529</t>
+          <t>https://artportalen.se/Sighting/96715007</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129943541</v>
+        <v>129943529</v>
       </c>
       <c r="B73" t="n">
         <v>79327</v>
@@ -8206,10 +8196,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471478</v>
+        <v>471492</v>
       </c>
       <c r="R73" t="n">
-        <v>6770707</v>
+        <v>6770712</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8277,13 +8267,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943541</t>
+          <t>https://artportalen.se/Sighting/129943529</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129943580</v>
+        <v>129943541</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8318,10 +8308,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471468</v>
+        <v>471478</v>
       </c>
       <c r="R74" t="n">
-        <v>6770744</v>
+        <v>6770707</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8389,13 +8379,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943580</t>
+          <t>https://artportalen.se/Sighting/129943541</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129943763</v>
+        <v>129943580</v>
       </c>
       <c r="B75" t="n">
         <v>79327</v>
@@ -8430,10 +8420,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471466</v>
+        <v>471468</v>
       </c>
       <c r="R75" t="n">
-        <v>6770713</v>
+        <v>6770744</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8501,13 +8491,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943763</t>
+          <t>https://artportalen.se/Sighting/129943580</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129943809</v>
+        <v>129943763</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -8542,10 +8532,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471447</v>
+        <v>471466</v>
       </c>
       <c r="R76" t="n">
-        <v>6770716</v>
+        <v>6770713</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8613,13 +8603,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943809</t>
+          <t>https://artportalen.se/Sighting/129943763</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129943855</v>
+        <v>129943809</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -8654,10 +8644,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471451</v>
+        <v>471447</v>
       </c>
       <c r="R77" t="n">
-        <v>6770706</v>
+        <v>6770716</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8725,13 +8715,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943855</t>
+          <t>https://artportalen.se/Sighting/129943809</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129943914</v>
+        <v>129943855</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -8766,10 +8756,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471432</v>
+        <v>471451</v>
       </c>
       <c r="R78" t="n">
-        <v>6770701</v>
+        <v>6770706</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8837,13 +8827,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943914</t>
+          <t>https://artportalen.se/Sighting/129943855</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129943999</v>
+        <v>129943914</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -8878,10 +8868,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471428</v>
+        <v>471432</v>
       </c>
       <c r="R79" t="n">
-        <v>6770747</v>
+        <v>6770701</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8949,13 +8939,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943999</t>
+          <t>https://artportalen.se/Sighting/129943914</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129944026</v>
+        <v>129943999</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -8990,10 +8980,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471422</v>
+        <v>471428</v>
       </c>
       <c r="R80" t="n">
-        <v>6770745</v>
+        <v>6770747</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9061,13 +9051,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944026</t>
+          <t>https://artportalen.se/Sighting/129943999</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129944037</v>
+        <v>129944026</v>
       </c>
       <c r="B81" t="n">
         <v>79327</v>
@@ -9102,10 +9092,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471417</v>
+        <v>471422</v>
       </c>
       <c r="R81" t="n">
-        <v>6770738</v>
+        <v>6770745</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9173,13 +9163,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944037</t>
+          <t>https://artportalen.se/Sighting/129944026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129944164</v>
+        <v>129944037</v>
       </c>
       <c r="B82" t="n">
         <v>79327</v>
@@ -9214,10 +9204,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471363</v>
+        <v>471417</v>
       </c>
       <c r="R82" t="n">
-        <v>6770736</v>
+        <v>6770738</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9285,13 +9275,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944164</t>
+          <t>https://artportalen.se/Sighting/129944037</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944178</v>
+        <v>129944164</v>
       </c>
       <c r="B83" t="n">
         <v>79327</v>
@@ -9326,10 +9316,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471372</v>
+        <v>471363</v>
       </c>
       <c r="R83" t="n">
-        <v>6770719</v>
+        <v>6770736</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9397,13 +9387,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944178</t>
+          <t>https://artportalen.se/Sighting/129944164</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944210</v>
+        <v>129944178</v>
       </c>
       <c r="B84" t="n">
         <v>79327</v>
@@ -9438,10 +9428,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471390</v>
+        <v>471372</v>
       </c>
       <c r="R84" t="n">
-        <v>6770705</v>
+        <v>6770719</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9509,13 +9499,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944210</t>
+          <t>https://artportalen.se/Sighting/129944178</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129944228</v>
+        <v>129944210</v>
       </c>
       <c r="B85" t="n">
         <v>79327</v>
@@ -9553,7 +9543,7 @@
         <v>471390</v>
       </c>
       <c r="R85" t="n">
-        <v>6770693</v>
+        <v>6770705</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9621,13 +9611,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944228</t>
+          <t>https://artportalen.se/Sighting/129944210</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129944311</v>
+        <v>129944228</v>
       </c>
       <c r="B86" t="n">
         <v>79327</v>
@@ -9662,10 +9652,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471369</v>
+        <v>471390</v>
       </c>
       <c r="R86" t="n">
-        <v>6770686</v>
+        <v>6770693</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9733,13 +9723,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944311</t>
+          <t>https://artportalen.se/Sighting/129944228</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129944355</v>
+        <v>129944311</v>
       </c>
       <c r="B87" t="n">
         <v>79327</v>
@@ -9774,10 +9764,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471342</v>
+        <v>471369</v>
       </c>
       <c r="R87" t="n">
-        <v>6770682</v>
+        <v>6770686</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9845,13 +9835,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944355</t>
+          <t>https://artportalen.se/Sighting/129944311</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129944466</v>
+        <v>129944355</v>
       </c>
       <c r="B88" t="n">
         <v>79327</v>
@@ -9886,10 +9876,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471322</v>
+        <v>471342</v>
       </c>
       <c r="R88" t="n">
-        <v>6770702</v>
+        <v>6770682</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9957,13 +9947,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944466</t>
+          <t>https://artportalen.se/Sighting/129944355</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129944473</v>
+        <v>129944466</v>
       </c>
       <c r="B89" t="n">
         <v>79327</v>
@@ -9998,10 +9988,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471328</v>
+        <v>471322</v>
       </c>
       <c r="R89" t="n">
-        <v>6770726</v>
+        <v>6770702</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10069,13 +10059,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944473</t>
+          <t>https://artportalen.se/Sighting/129944466</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129944488</v>
+        <v>129944473</v>
       </c>
       <c r="B90" t="n">
         <v>79327</v>
@@ -10110,10 +10100,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471318</v>
+        <v>471328</v>
       </c>
       <c r="R90" t="n">
-        <v>6770729</v>
+        <v>6770726</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10181,13 +10171,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944488</t>
+          <t>https://artportalen.se/Sighting/129944473</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129944495</v>
+        <v>129944488</v>
       </c>
       <c r="B91" t="n">
         <v>79327</v>
@@ -10222,10 +10212,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471288</v>
+        <v>471318</v>
       </c>
       <c r="R91" t="n">
-        <v>6770728</v>
+        <v>6770729</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10293,13 +10283,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944495</t>
+          <t>https://artportalen.se/Sighting/129944488</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129944523</v>
+        <v>129944495</v>
       </c>
       <c r="B92" t="n">
         <v>79327</v>
@@ -10334,10 +10324,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471303</v>
+        <v>471288</v>
       </c>
       <c r="R92" t="n">
-        <v>6770699</v>
+        <v>6770728</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10405,13 +10395,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944523</t>
+          <t>https://artportalen.se/Sighting/129944495</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129944544</v>
+        <v>129944523</v>
       </c>
       <c r="B93" t="n">
         <v>79327</v>
@@ -10446,10 +10436,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471330</v>
+        <v>471303</v>
       </c>
       <c r="R93" t="n">
-        <v>6770712</v>
+        <v>6770699</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10517,13 +10507,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944544</t>
+          <t>https://artportalen.se/Sighting/129944523</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129944592</v>
+        <v>129944544</v>
       </c>
       <c r="B94" t="n">
         <v>79327</v>
@@ -10558,10 +10548,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471313</v>
+        <v>471330</v>
       </c>
       <c r="R94" t="n">
-        <v>6770688</v>
+        <v>6770712</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10629,13 +10619,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944592</t>
+          <t>https://artportalen.se/Sighting/129944544</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129944756</v>
+        <v>129944592</v>
       </c>
       <c r="B95" t="n">
         <v>79327</v>
@@ -10670,10 +10660,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471288</v>
+        <v>471313</v>
       </c>
       <c r="R95" t="n">
-        <v>6770685</v>
+        <v>6770688</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10741,13 +10731,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944756</t>
+          <t>https://artportalen.se/Sighting/129944592</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129944762</v>
+        <v>129944756</v>
       </c>
       <c r="B96" t="n">
         <v>79327</v>
@@ -10782,10 +10772,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471276</v>
+        <v>471288</v>
       </c>
       <c r="R96" t="n">
-        <v>6770703</v>
+        <v>6770685</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10853,13 +10843,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944762</t>
+          <t>https://artportalen.se/Sighting/129944756</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129944804</v>
+        <v>129944762</v>
       </c>
       <c r="B97" t="n">
         <v>79327</v>
@@ -10894,10 +10884,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471271</v>
+        <v>471276</v>
       </c>
       <c r="R97" t="n">
-        <v>6770733</v>
+        <v>6770703</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10965,13 +10955,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944804</t>
+          <t>https://artportalen.se/Sighting/129944762</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129944807</v>
+        <v>129944804</v>
       </c>
       <c r="B98" t="n">
         <v>79327</v>
@@ -11006,10 +10996,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471248</v>
+        <v>471271</v>
       </c>
       <c r="R98" t="n">
-        <v>6770737</v>
+        <v>6770733</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11077,13 +11067,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944807</t>
+          <t>https://artportalen.se/Sighting/129944804</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129944809</v>
+        <v>129944807</v>
       </c>
       <c r="B99" t="n">
         <v>79327</v>
@@ -11118,10 +11108,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471247</v>
+        <v>471248</v>
       </c>
       <c r="R99" t="n">
-        <v>6770726</v>
+        <v>6770737</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11189,13 +11179,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944809</t>
+          <t>https://artportalen.se/Sighting/129944807</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944917</v>
+        <v>129944809</v>
       </c>
       <c r="B100" t="n">
         <v>79327</v>
@@ -11230,10 +11220,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471263</v>
+        <v>471247</v>
       </c>
       <c r="R100" t="n">
-        <v>6770694</v>
+        <v>6770726</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11301,13 +11291,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944917</t>
+          <t>https://artportalen.se/Sighting/129944809</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129944975</v>
+        <v>129944917</v>
       </c>
       <c r="B101" t="n">
         <v>79327</v>
@@ -11342,10 +11332,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471242</v>
+        <v>471263</v>
       </c>
       <c r="R101" t="n">
-        <v>6770682</v>
+        <v>6770694</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11413,13 +11403,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944975</t>
+          <t>https://artportalen.se/Sighting/129944917</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129945066</v>
+        <v>129944975</v>
       </c>
       <c r="B102" t="n">
         <v>79327</v>
@@ -11454,10 +11444,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471239</v>
+        <v>471242</v>
       </c>
       <c r="R102" t="n">
-        <v>6770732</v>
+        <v>6770682</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11525,13 +11515,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945066</t>
+          <t>https://artportalen.se/Sighting/129944975</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129945078</v>
+        <v>129945066</v>
       </c>
       <c r="B103" t="n">
         <v>79327</v>
@@ -11566,10 +11556,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471209</v>
+        <v>471239</v>
       </c>
       <c r="R103" t="n">
-        <v>6770731</v>
+        <v>6770732</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11637,13 +11627,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945078</t>
+          <t>https://artportalen.se/Sighting/129945066</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129945104</v>
+        <v>129945078</v>
       </c>
       <c r="B104" t="n">
         <v>79327</v>
@@ -11678,10 +11668,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471219</v>
+        <v>471209</v>
       </c>
       <c r="R104" t="n">
-        <v>6770720</v>
+        <v>6770731</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11749,13 +11739,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945104</t>
+          <t>https://artportalen.se/Sighting/129945078</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129945451</v>
+        <v>129945104</v>
       </c>
       <c r="B105" t="n">
         <v>79327</v>
@@ -11790,10 +11780,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471189</v>
+        <v>471219</v>
       </c>
       <c r="R105" t="n">
-        <v>6770706</v>
+        <v>6770720</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11861,13 +11851,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945451</t>
+          <t>https://artportalen.se/Sighting/129945104</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129945509</v>
+        <v>129945451</v>
       </c>
       <c r="B106" t="n">
         <v>79327</v>
@@ -11902,10 +11892,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471198</v>
+        <v>471189</v>
       </c>
       <c r="R106" t="n">
-        <v>6770689</v>
+        <v>6770706</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11950,11 +11940,6 @@
           <t>11:17</t>
         </is>
       </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -11978,13 +11963,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945509</t>
+          <t>https://artportalen.se/Sighting/129945451</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129946029</v>
+        <v>129945509</v>
       </c>
       <c r="B107" t="n">
         <v>79327</v>
@@ -12019,10 +12004,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471185</v>
+        <v>471198</v>
       </c>
       <c r="R107" t="n">
-        <v>6770690</v>
+        <v>6770689</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12067,6 +12052,11 @@
           <t>11:17</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12090,13 +12080,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946029</t>
+          <t>https://artportalen.se/Sighting/129945509</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129946053</v>
+        <v>129946029</v>
       </c>
       <c r="B108" t="n">
         <v>79327</v>
@@ -12131,10 +12121,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471161</v>
+        <v>471185</v>
       </c>
       <c r="R108" t="n">
-        <v>6770705</v>
+        <v>6770690</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12202,13 +12192,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946053</t>
+          <t>https://artportalen.se/Sighting/129946029</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129946117</v>
+        <v>129946053</v>
       </c>
       <c r="B109" t="n">
         <v>79327</v>
@@ -12243,10 +12233,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471106</v>
+        <v>471161</v>
       </c>
       <c r="R109" t="n">
-        <v>6770711</v>
+        <v>6770705</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12314,13 +12304,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946117</t>
+          <t>https://artportalen.se/Sighting/129946053</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129946170</v>
+        <v>129946117</v>
       </c>
       <c r="B110" t="n">
         <v>79327</v>
@@ -12355,10 +12345,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471030</v>
+        <v>471106</v>
       </c>
       <c r="R110" t="n">
-        <v>6770688</v>
+        <v>6770711</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12426,13 +12416,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946170</t>
+          <t>https://artportalen.se/Sighting/129946117</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129946182</v>
+        <v>129946170</v>
       </c>
       <c r="B111" t="n">
         <v>79327</v>
@@ -12467,10 +12457,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471000</v>
+        <v>471030</v>
       </c>
       <c r="R111" t="n">
-        <v>6770675</v>
+        <v>6770688</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12538,13 +12528,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946182</t>
+          <t>https://artportalen.se/Sighting/129946170</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129946197</v>
+        <v>129946182</v>
       </c>
       <c r="B112" t="n">
         <v>79327</v>
@@ -12579,10 +12569,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>470971</v>
+        <v>471000</v>
       </c>
       <c r="R112" t="n">
-        <v>6770676</v>
+        <v>6770675</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12650,13 +12640,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946197</t>
+          <t>https://artportalen.se/Sighting/129946182</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129946408</v>
+        <v>129946197</v>
       </c>
       <c r="B113" t="n">
         <v>79327</v>
@@ -12691,10 +12681,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>470921</v>
+        <v>470971</v>
       </c>
       <c r="R113" t="n">
-        <v>6770579</v>
+        <v>6770676</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12762,13 +12752,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946408</t>
+          <t>https://artportalen.se/Sighting/129946197</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129946586</v>
+        <v>129946408</v>
       </c>
       <c r="B114" t="n">
         <v>79327</v>
@@ -12803,10 +12793,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471095</v>
+        <v>470921</v>
       </c>
       <c r="R114" t="n">
-        <v>6770660</v>
+        <v>6770579</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12874,13 +12864,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946586</t>
+          <t>https://artportalen.se/Sighting/129946408</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129946708</v>
+        <v>129946586</v>
       </c>
       <c r="B115" t="n">
         <v>79327</v>
@@ -12915,7 +12905,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471171</v>
+        <v>471095</v>
       </c>
       <c r="R115" t="n">
         <v>6770660</v>
@@ -12986,13 +12976,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946708</t>
+          <t>https://artportalen.se/Sighting/129946586</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129954408</v>
+        <v>129946708</v>
       </c>
       <c r="B116" t="n">
         <v>79327</v>
@@ -13027,10 +13017,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471019</v>
+        <v>471171</v>
       </c>
       <c r="R116" t="n">
-        <v>6770666</v>
+        <v>6770660</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13057,22 +13047,22 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13098,13 +13088,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954408</t>
+          <t>https://artportalen.se/Sighting/129946708</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129954413</v>
+        <v>129954408</v>
       </c>
       <c r="B117" t="n">
         <v>79327</v>
@@ -13139,10 +13129,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471028</v>
+        <v>471019</v>
       </c>
       <c r="R117" t="n">
-        <v>6770675</v>
+        <v>6770666</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13210,13 +13200,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954413</t>
+          <t>https://artportalen.se/Sighting/129954408</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129954442</v>
+        <v>129954413</v>
       </c>
       <c r="B118" t="n">
         <v>79327</v>
@@ -13251,10 +13241,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>471053</v>
+        <v>471028</v>
       </c>
       <c r="R118" t="n">
-        <v>6770682</v>
+        <v>6770675</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13322,13 +13312,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954442</t>
+          <t>https://artportalen.se/Sighting/129954413</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129954452</v>
+        <v>129954442</v>
       </c>
       <c r="B119" t="n">
         <v>79327</v>
@@ -13363,10 +13353,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471058</v>
+        <v>471053</v>
       </c>
       <c r="R119" t="n">
-        <v>6770677</v>
+        <v>6770682</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13434,13 +13424,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954452</t>
+          <t>https://artportalen.se/Sighting/129954442</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129954531</v>
+        <v>129954452</v>
       </c>
       <c r="B120" t="n">
         <v>79327</v>
@@ -13475,10 +13465,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471106</v>
+        <v>471058</v>
       </c>
       <c r="R120" t="n">
-        <v>6770683</v>
+        <v>6770677</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13546,13 +13536,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954531</t>
+          <t>https://artportalen.se/Sighting/129954452</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129954534</v>
+        <v>129954531</v>
       </c>
       <c r="B121" t="n">
         <v>79327</v>
@@ -13587,10 +13577,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471086</v>
+        <v>471106</v>
       </c>
       <c r="R121" t="n">
-        <v>6770684</v>
+        <v>6770683</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13658,13 +13648,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954534</t>
+          <t>https://artportalen.se/Sighting/129954531</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129954584</v>
+        <v>129954534</v>
       </c>
       <c r="B122" t="n">
         <v>79327</v>
@@ -13699,10 +13689,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471062</v>
+        <v>471086</v>
       </c>
       <c r="R122" t="n">
-        <v>6770731</v>
+        <v>6770684</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13770,13 +13760,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954584</t>
+          <t>https://artportalen.se/Sighting/129954534</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129954590</v>
+        <v>129954584</v>
       </c>
       <c r="B123" t="n">
         <v>79327</v>
@@ -13811,10 +13801,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471013</v>
+        <v>471062</v>
       </c>
       <c r="R123" t="n">
-        <v>6770715</v>
+        <v>6770731</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13882,13 +13872,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954590</t>
+          <t>https://artportalen.se/Sighting/129954584</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129954674</v>
+        <v>129954590</v>
       </c>
       <c r="B124" t="n">
         <v>79327</v>
@@ -13923,10 +13913,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>470938</v>
+        <v>471013</v>
       </c>
       <c r="R124" t="n">
-        <v>6770693</v>
+        <v>6770715</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13994,13 +13984,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954674</t>
+          <t>https://artportalen.se/Sighting/129954590</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129955100</v>
+        <v>129954674</v>
       </c>
       <c r="B125" t="n">
         <v>79327</v>
@@ -14035,10 +14025,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470981</v>
+        <v>470938</v>
       </c>
       <c r="R125" t="n">
-        <v>6770691</v>
+        <v>6770693</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14106,13 +14096,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129955100</t>
+          <t>https://artportalen.se/Sighting/129954674</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129955313</v>
+        <v>129955100</v>
       </c>
       <c r="B126" t="n">
         <v>79327</v>
@@ -14147,10 +14137,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470992</v>
+        <v>470981</v>
       </c>
       <c r="R126" t="n">
-        <v>6770702</v>
+        <v>6770691</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14218,13 +14208,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129955313</t>
+          <t>https://artportalen.se/Sighting/129955100</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129956843</v>
+        <v>129955313</v>
       </c>
       <c r="B127" t="n">
         <v>79327</v>
@@ -14259,10 +14249,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470953</v>
+        <v>470992</v>
       </c>
       <c r="R127" t="n">
-        <v>6770692</v>
+        <v>6770702</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14330,13 +14320,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956843</t>
+          <t>https://artportalen.se/Sighting/129955313</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129956851</v>
+        <v>129956843</v>
       </c>
       <c r="B128" t="n">
         <v>79327</v>
@@ -14371,10 +14361,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470928</v>
+        <v>470953</v>
       </c>
       <c r="R128" t="n">
-        <v>6770695</v>
+        <v>6770692</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14442,13 +14432,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956851</t>
+          <t>https://artportalen.se/Sighting/129956843</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129956859</v>
+        <v>129956851</v>
       </c>
       <c r="B129" t="n">
         <v>79327</v>
@@ -14483,10 +14473,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470936</v>
+        <v>470928</v>
       </c>
       <c r="R129" t="n">
-        <v>6770721</v>
+        <v>6770695</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14554,13 +14544,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956859</t>
+          <t>https://artportalen.se/Sighting/129956851</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129957713</v>
+        <v>129956859</v>
       </c>
       <c r="B130" t="n">
         <v>79327</v>
@@ -14595,10 +14585,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470904</v>
+        <v>470936</v>
       </c>
       <c r="R130" t="n">
-        <v>6770718</v>
+        <v>6770721</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14666,13 +14656,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957713</t>
+          <t>https://artportalen.se/Sighting/129956859</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129957969</v>
+        <v>129957713</v>
       </c>
       <c r="B131" t="n">
         <v>79327</v>
@@ -14707,10 +14697,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470911</v>
+        <v>470904</v>
       </c>
       <c r="R131" t="n">
-        <v>6770707</v>
+        <v>6770718</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14778,13 +14768,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957969</t>
+          <t>https://artportalen.se/Sighting/129957713</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129958010</v>
+        <v>129957969</v>
       </c>
       <c r="B132" t="n">
         <v>79327</v>
@@ -14819,10 +14809,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470894</v>
+        <v>470911</v>
       </c>
       <c r="R132" t="n">
-        <v>6770713</v>
+        <v>6770707</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14890,13 +14880,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958010</t>
+          <t>https://artportalen.se/Sighting/129957969</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129958133</v>
+        <v>129958010</v>
       </c>
       <c r="B133" t="n">
         <v>79327</v>
@@ -14931,10 +14921,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>470869</v>
+        <v>470894</v>
       </c>
       <c r="R133" t="n">
-        <v>6770702</v>
+        <v>6770713</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15002,13 +14992,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958133</t>
+          <t>https://artportalen.se/Sighting/129958010</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129958151</v>
+        <v>129958133</v>
       </c>
       <c r="B134" t="n">
         <v>79327</v>
@@ -15043,10 +15033,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>470842</v>
+        <v>470869</v>
       </c>
       <c r="R134" t="n">
-        <v>6770709</v>
+        <v>6770702</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15114,13 +15104,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958151</t>
+          <t>https://artportalen.se/Sighting/129958133</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129958214</v>
+        <v>129958151</v>
       </c>
       <c r="B135" t="n">
         <v>79327</v>
@@ -15155,10 +15145,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470823</v>
+        <v>470842</v>
       </c>
       <c r="R135" t="n">
-        <v>6770705</v>
+        <v>6770709</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15226,13 +15216,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958214</t>
+          <t>https://artportalen.se/Sighting/129958151</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129958228</v>
+        <v>129958214</v>
       </c>
       <c r="B136" t="n">
         <v>79327</v>
@@ -15267,10 +15257,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470813</v>
+        <v>470823</v>
       </c>
       <c r="R136" t="n">
-        <v>6770681</v>
+        <v>6770705</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15338,13 +15328,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958228</t>
+          <t>https://artportalen.se/Sighting/129958214</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129958464</v>
+        <v>129958228</v>
       </c>
       <c r="B137" t="n">
         <v>79327</v>
@@ -15379,10 +15369,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470822</v>
+        <v>470813</v>
       </c>
       <c r="R137" t="n">
-        <v>6770673</v>
+        <v>6770681</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15450,13 +15440,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958464</t>
+          <t>https://artportalen.se/Sighting/129958228</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129958466</v>
+        <v>129958464</v>
       </c>
       <c r="B138" t="n">
         <v>79327</v>
@@ -15491,10 +15481,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470812</v>
+        <v>470822</v>
       </c>
       <c r="R138" t="n">
-        <v>6770670</v>
+        <v>6770673</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15562,13 +15552,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958466</t>
+          <t>https://artportalen.se/Sighting/129958464</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129958499</v>
+        <v>129958466</v>
       </c>
       <c r="B139" t="n">
         <v>79327</v>
@@ -15603,10 +15593,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470850</v>
+        <v>470812</v>
       </c>
       <c r="R139" t="n">
-        <v>6770690</v>
+        <v>6770670</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15674,13 +15664,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958499</t>
+          <t>https://artportalen.se/Sighting/129958466</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129958545</v>
+        <v>129958499</v>
       </c>
       <c r="B140" t="n">
         <v>79327</v>
@@ -15715,10 +15705,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470877</v>
+        <v>470850</v>
       </c>
       <c r="R140" t="n">
-        <v>6770687</v>
+        <v>6770690</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15786,13 +15776,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958545</t>
+          <t>https://artportalen.se/Sighting/129958499</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129958694</v>
+        <v>129958545</v>
       </c>
       <c r="B141" t="n">
         <v>79327</v>
@@ -15827,10 +15817,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>470844</v>
+        <v>470877</v>
       </c>
       <c r="R141" t="n">
-        <v>6770699</v>
+        <v>6770687</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15898,13 +15888,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958694</t>
+          <t>https://artportalen.se/Sighting/129958545</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129958706</v>
+        <v>129958694</v>
       </c>
       <c r="B142" t="n">
         <v>79327</v>
@@ -15939,10 +15929,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>470816</v>
+        <v>470844</v>
       </c>
       <c r="R142" t="n">
-        <v>6770646</v>
+        <v>6770699</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16010,13 +16000,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958706</t>
+          <t>https://artportalen.se/Sighting/129958694</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129958754</v>
+        <v>129958706</v>
       </c>
       <c r="B143" t="n">
         <v>79327</v>
@@ -16051,10 +16041,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>470817</v>
+        <v>470816</v>
       </c>
       <c r="R143" t="n">
-        <v>6770608</v>
+        <v>6770646</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16122,13 +16112,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958754</t>
+          <t>https://artportalen.se/Sighting/129958706</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129958775</v>
+        <v>129958754</v>
       </c>
       <c r="B144" t="n">
         <v>79327</v>
@@ -16163,10 +16153,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>470803</v>
+        <v>470817</v>
       </c>
       <c r="R144" t="n">
-        <v>6770595</v>
+        <v>6770608</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16234,13 +16224,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958775</t>
+          <t>https://artportalen.se/Sighting/129958754</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129958795</v>
+        <v>129958775</v>
       </c>
       <c r="B145" t="n">
         <v>79327</v>
@@ -16275,10 +16265,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>470822</v>
+        <v>470803</v>
       </c>
       <c r="R145" t="n">
-        <v>6770615</v>
+        <v>6770595</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16323,11 +16313,6 @@
           <t>09:55</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
@@ -16351,13 +16336,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958795</t>
+          <t>https://artportalen.se/Sighting/129958775</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129958800</v>
+        <v>129958795</v>
       </c>
       <c r="B146" t="n">
         <v>79327</v>
@@ -16392,10 +16377,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>470858</v>
+        <v>470822</v>
       </c>
       <c r="R146" t="n">
-        <v>6770602</v>
+        <v>6770615</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16440,6 +16425,11 @@
           <t>09:55</t>
         </is>
       </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
@@ -16463,13 +16453,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958800</t>
+          <t>https://artportalen.se/Sighting/129958795</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129958828</v>
+        <v>129958800</v>
       </c>
       <c r="B147" t="n">
         <v>79327</v>
@@ -16504,10 +16494,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470871</v>
+        <v>470858</v>
       </c>
       <c r="R147" t="n">
-        <v>6770635</v>
+        <v>6770602</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16575,13 +16565,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958828</t>
+          <t>https://artportalen.se/Sighting/129958800</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129958841</v>
+        <v>129958828</v>
       </c>
       <c r="B148" t="n">
         <v>79327</v>
@@ -16616,10 +16606,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470828</v>
+        <v>470871</v>
       </c>
       <c r="R148" t="n">
-        <v>6770636</v>
+        <v>6770635</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16687,13 +16677,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958841</t>
+          <t>https://artportalen.se/Sighting/129958828</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129958842</v>
+        <v>129958841</v>
       </c>
       <c r="B149" t="n">
         <v>79327</v>
@@ -16728,10 +16718,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>470820</v>
+        <v>470828</v>
       </c>
       <c r="R149" t="n">
-        <v>6770624</v>
+        <v>6770636</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16799,13 +16789,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958842</t>
+          <t>https://artportalen.se/Sighting/129958841</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129958895</v>
+        <v>129958842</v>
       </c>
       <c r="B150" t="n">
         <v>79327</v>
@@ -16840,10 +16830,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>470887</v>
+        <v>470820</v>
       </c>
       <c r="R150" t="n">
-        <v>6770658</v>
+        <v>6770624</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16911,13 +16901,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958895</t>
+          <t>https://artportalen.se/Sighting/129958842</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129958937</v>
+        <v>129958895</v>
       </c>
       <c r="B151" t="n">
         <v>79327</v>
@@ -16952,10 +16942,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>470897</v>
+        <v>470887</v>
       </c>
       <c r="R151" t="n">
-        <v>6770647</v>
+        <v>6770658</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17023,13 +17013,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958937</t>
+          <t>https://artportalen.se/Sighting/129958895</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129959037</v>
+        <v>129958937</v>
       </c>
       <c r="B152" t="n">
         <v>79327</v>
@@ -17064,10 +17054,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>470908</v>
+        <v>470897</v>
       </c>
       <c r="R152" t="n">
-        <v>6770622</v>
+        <v>6770647</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17135,13 +17125,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959037</t>
+          <t>https://artportalen.se/Sighting/129958937</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129959060</v>
+        <v>129959037</v>
       </c>
       <c r="B153" t="n">
         <v>79327</v>
@@ -17176,10 +17166,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>470926</v>
+        <v>470908</v>
       </c>
       <c r="R153" t="n">
-        <v>6770613</v>
+        <v>6770622</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17247,13 +17237,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959060</t>
+          <t>https://artportalen.se/Sighting/129959037</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129959250</v>
+        <v>129959060</v>
       </c>
       <c r="B154" t="n">
         <v>79327</v>
@@ -17288,10 +17278,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>470943</v>
+        <v>470926</v>
       </c>
       <c r="R154" t="n">
-        <v>6770559</v>
+        <v>6770613</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17359,13 +17349,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959250</t>
+          <t>https://artportalen.se/Sighting/129959060</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129959256</v>
+        <v>129959250</v>
       </c>
       <c r="B155" t="n">
         <v>79327</v>
@@ -17400,10 +17390,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470922</v>
+        <v>470943</v>
       </c>
       <c r="R155" t="n">
-        <v>6770556</v>
+        <v>6770559</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17471,13 +17461,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959256</t>
+          <t>https://artportalen.se/Sighting/129959250</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129959294</v>
+        <v>129959256</v>
       </c>
       <c r="B156" t="n">
         <v>79327</v>
@@ -17512,10 +17502,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>470904</v>
+        <v>470922</v>
       </c>
       <c r="R156" t="n">
-        <v>6770537</v>
+        <v>6770556</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17583,13 +17573,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959294</t>
+          <t>https://artportalen.se/Sighting/129959256</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129959303</v>
+        <v>129959294</v>
       </c>
       <c r="B157" t="n">
         <v>79327</v>
@@ -17624,10 +17614,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>470879</v>
+        <v>470904</v>
       </c>
       <c r="R157" t="n">
-        <v>6770545</v>
+        <v>6770537</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17695,13 +17685,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959303</t>
+          <t>https://artportalen.se/Sighting/129959294</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129959375</v>
+        <v>129959303</v>
       </c>
       <c r="B158" t="n">
         <v>79327</v>
@@ -17736,10 +17726,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470851</v>
+        <v>470879</v>
       </c>
       <c r="R158" t="n">
-        <v>6770520</v>
+        <v>6770545</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17807,13 +17797,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959375</t>
+          <t>https://artportalen.se/Sighting/129959303</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129959389</v>
+        <v>129959375</v>
       </c>
       <c r="B159" t="n">
         <v>79327</v>
@@ -17848,10 +17838,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>470824</v>
+        <v>470851</v>
       </c>
       <c r="R159" t="n">
-        <v>6770523</v>
+        <v>6770520</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17919,13 +17909,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959389</t>
+          <t>https://artportalen.se/Sighting/129959375</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129959479</v>
+        <v>129959389</v>
       </c>
       <c r="B160" t="n">
         <v>79327</v>
@@ -17960,10 +17950,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>470837</v>
+        <v>470824</v>
       </c>
       <c r="R160" t="n">
-        <v>6770498</v>
+        <v>6770523</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18031,13 +18021,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959479</t>
+          <t>https://artportalen.se/Sighting/129959389</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129959501</v>
+        <v>129959479</v>
       </c>
       <c r="B161" t="n">
         <v>79327</v>
@@ -18072,10 +18062,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>470807</v>
+        <v>470837</v>
       </c>
       <c r="R161" t="n">
-        <v>6770491</v>
+        <v>6770498</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18143,13 +18133,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959501</t>
+          <t>https://artportalen.se/Sighting/129959479</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129959519</v>
+        <v>129959501</v>
       </c>
       <c r="B162" t="n">
         <v>79327</v>
@@ -18184,10 +18174,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>470822</v>
+        <v>470807</v>
       </c>
       <c r="R162" t="n">
-        <v>6770452</v>
+        <v>6770491</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18255,13 +18245,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959519</t>
+          <t>https://artportalen.se/Sighting/129959501</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129959692</v>
+        <v>129959519</v>
       </c>
       <c r="B163" t="n">
         <v>79327</v>
@@ -18296,10 +18286,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>470864</v>
+        <v>470822</v>
       </c>
       <c r="R163" t="n">
-        <v>6770438</v>
+        <v>6770452</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18367,13 +18357,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959692</t>
+          <t>https://artportalen.se/Sighting/129959519</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129959740</v>
+        <v>129959692</v>
       </c>
       <c r="B164" t="n">
         <v>79327</v>
@@ -18408,10 +18398,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>470905</v>
+        <v>470864</v>
       </c>
       <c r="R164" t="n">
-        <v>6770435</v>
+        <v>6770438</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18479,13 +18469,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959740</t>
+          <t>https://artportalen.se/Sighting/129959692</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129959772</v>
+        <v>129959740</v>
       </c>
       <c r="B165" t="n">
         <v>79327</v>
@@ -18520,10 +18510,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>470900</v>
+        <v>470905</v>
       </c>
       <c r="R165" t="n">
-        <v>6770473</v>
+        <v>6770435</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18591,13 +18581,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959772</t>
+          <t>https://artportalen.se/Sighting/129959740</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129959808</v>
+        <v>129959772</v>
       </c>
       <c r="B166" t="n">
         <v>79327</v>
@@ -18632,10 +18622,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470942</v>
+        <v>470900</v>
       </c>
       <c r="R166" t="n">
-        <v>6770455</v>
+        <v>6770473</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18703,13 +18693,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959808</t>
+          <t>https://artportalen.se/Sighting/129959772</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129959994</v>
+        <v>129959808</v>
       </c>
       <c r="B167" t="n">
         <v>79327</v>
@@ -18744,10 +18734,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470954</v>
+        <v>470942</v>
       </c>
       <c r="R167" t="n">
-        <v>6770475</v>
+        <v>6770455</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18815,13 +18805,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959994</t>
+          <t>https://artportalen.se/Sighting/129959808</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129960002</v>
+        <v>129959994</v>
       </c>
       <c r="B168" t="n">
         <v>79327</v>
@@ -18856,10 +18846,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>470932</v>
+        <v>470954</v>
       </c>
       <c r="R168" t="n">
-        <v>6770480</v>
+        <v>6770475</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18927,13 +18917,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960002</t>
+          <t>https://artportalen.se/Sighting/129959994</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129960437</v>
+        <v>129960002</v>
       </c>
       <c r="B169" t="n">
         <v>79327</v>
@@ -18968,10 +18958,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>470948</v>
+        <v>470932</v>
       </c>
       <c r="R169" t="n">
-        <v>6770533</v>
+        <v>6770480</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19039,13 +19029,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960437</t>
+          <t>https://artportalen.se/Sighting/129960002</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129960691</v>
+        <v>129960437</v>
       </c>
       <c r="B170" t="n">
         <v>79327</v>
@@ -19080,10 +19070,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>471056</v>
+        <v>470948</v>
       </c>
       <c r="R170" t="n">
-        <v>6770494</v>
+        <v>6770533</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19151,13 +19141,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960691</t>
+          <t>https://artportalen.se/Sighting/129960437</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129960763</v>
+        <v>129960691</v>
       </c>
       <c r="B171" t="n">
         <v>79327</v>
@@ -19192,10 +19182,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>471062</v>
+        <v>471056</v>
       </c>
       <c r="R171" t="n">
-        <v>6770538</v>
+        <v>6770494</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19263,13 +19253,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960763</t>
+          <t>https://artportalen.se/Sighting/129960691</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129960790</v>
+        <v>129960763</v>
       </c>
       <c r="B172" t="n">
         <v>79327</v>
@@ -19304,10 +19294,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>471073</v>
+        <v>471062</v>
       </c>
       <c r="R172" t="n">
-        <v>6770551</v>
+        <v>6770538</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19375,13 +19365,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960790</t>
+          <t>https://artportalen.se/Sighting/129960763</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129960823</v>
+        <v>129960790</v>
       </c>
       <c r="B173" t="n">
         <v>79327</v>
@@ -19416,10 +19406,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471078</v>
+        <v>471073</v>
       </c>
       <c r="R173" t="n">
-        <v>6770561</v>
+        <v>6770551</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19464,11 +19454,6 @@
           <t>09:55</t>
         </is>
       </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD173" t="b">
         <v>0</v>
       </c>
@@ -19492,13 +19477,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960823</t>
+          <t>https://artportalen.se/Sighting/129960790</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129960843</v>
+        <v>129960823</v>
       </c>
       <c r="B174" t="n">
         <v>79327</v>
@@ -19533,7 +19518,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>471097</v>
+        <v>471078</v>
       </c>
       <c r="R174" t="n">
         <v>6770561</v>
@@ -19581,6 +19566,11 @@
           <t>09:55</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -19604,13 +19594,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960843</t>
+          <t>https://artportalen.se/Sighting/129960823</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129960864</v>
+        <v>129960843</v>
       </c>
       <c r="B175" t="n">
         <v>79327</v>
@@ -19645,10 +19635,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471116</v>
+        <v>471097</v>
       </c>
       <c r="R175" t="n">
-        <v>6770565</v>
+        <v>6770561</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19716,13 +19706,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960864</t>
+          <t>https://artportalen.se/Sighting/129960843</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129960884</v>
+        <v>129960864</v>
       </c>
       <c r="B176" t="n">
         <v>79327</v>
@@ -19757,10 +19747,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471129</v>
+        <v>471116</v>
       </c>
       <c r="R176" t="n">
-        <v>6770567</v>
+        <v>6770565</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19828,13 +19818,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960884</t>
+          <t>https://artportalen.se/Sighting/129960864</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129960891</v>
+        <v>129960884</v>
       </c>
       <c r="B177" t="n">
         <v>79327</v>
@@ -19869,10 +19859,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>471147</v>
+        <v>471129</v>
       </c>
       <c r="R177" t="n">
-        <v>6770575</v>
+        <v>6770567</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19940,13 +19930,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960891</t>
+          <t>https://artportalen.se/Sighting/129960884</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129960901</v>
+        <v>129960891</v>
       </c>
       <c r="B178" t="n">
         <v>79327</v>
@@ -19981,10 +19971,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>471185</v>
+        <v>471147</v>
       </c>
       <c r="R178" t="n">
-        <v>6770590</v>
+        <v>6770575</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20052,13 +20042,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960901</t>
+          <t>https://artportalen.se/Sighting/129960891</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129960929</v>
+        <v>129960901</v>
       </c>
       <c r="B179" t="n">
         <v>79327</v>
@@ -20093,10 +20083,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>471159</v>
+        <v>471185</v>
       </c>
       <c r="R179" t="n">
-        <v>6770613</v>
+        <v>6770590</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20164,13 +20154,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960929</t>
+          <t>https://artportalen.se/Sighting/129960901</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129961603</v>
+        <v>129960929</v>
       </c>
       <c r="B180" t="n">
         <v>79327</v>
@@ -20205,10 +20195,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>471262</v>
+        <v>471159</v>
       </c>
       <c r="R180" t="n">
-        <v>6770622</v>
+        <v>6770613</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20276,13 +20266,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961603</t>
+          <t>https://artportalen.se/Sighting/129960929</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129961818</v>
+        <v>129961603</v>
       </c>
       <c r="B181" t="n">
         <v>79327</v>
@@ -20317,10 +20307,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471228</v>
+        <v>471262</v>
       </c>
       <c r="R181" t="n">
-        <v>6770667</v>
+        <v>6770622</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20388,13 +20378,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961818</t>
+          <t>https://artportalen.se/Sighting/129961603</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129961937</v>
+        <v>129961818</v>
       </c>
       <c r="B182" t="n">
         <v>79327</v>
@@ -20429,10 +20419,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471216</v>
+        <v>471228</v>
       </c>
       <c r="R182" t="n">
-        <v>6770650</v>
+        <v>6770667</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20500,13 +20490,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961937</t>
+          <t>https://artportalen.se/Sighting/129961818</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129962073</v>
+        <v>129961937</v>
       </c>
       <c r="B183" t="n">
         <v>79327</v>
@@ -20541,10 +20531,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>471222</v>
+        <v>471216</v>
       </c>
       <c r="R183" t="n">
-        <v>6770635</v>
+        <v>6770650</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20612,13 +20602,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962073</t>
+          <t>https://artportalen.se/Sighting/129961937</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129962119</v>
+        <v>129962073</v>
       </c>
       <c r="B184" t="n">
         <v>79327</v>
@@ -20653,10 +20643,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>471156</v>
+        <v>471222</v>
       </c>
       <c r="R184" t="n">
-        <v>6770665</v>
+        <v>6770635</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20724,13 +20714,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962119</t>
+          <t>https://artportalen.se/Sighting/129962073</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129962224</v>
+        <v>129962119</v>
       </c>
       <c r="B185" t="n">
         <v>79327</v>
@@ -20765,10 +20755,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>471098</v>
+        <v>471156</v>
       </c>
       <c r="R185" t="n">
-        <v>6770634</v>
+        <v>6770665</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20836,13 +20826,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962224</t>
+          <t>https://artportalen.se/Sighting/129962119</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129962243</v>
+        <v>129962224</v>
       </c>
       <c r="B186" t="n">
         <v>79327</v>
@@ -20877,10 +20867,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>471074</v>
+        <v>471098</v>
       </c>
       <c r="R186" t="n">
-        <v>6770617</v>
+        <v>6770634</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20948,13 +20938,13 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962243</t>
+          <t>https://artportalen.se/Sighting/129962224</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129962260</v>
+        <v>129962243</v>
       </c>
       <c r="B187" t="n">
         <v>79327</v>
@@ -20989,10 +20979,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>471044</v>
+        <v>471074</v>
       </c>
       <c r="R187" t="n">
-        <v>6770615</v>
+        <v>6770617</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21060,13 +21050,13 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962260</t>
+          <t>https://artportalen.se/Sighting/129962243</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129962290</v>
+        <v>129962260</v>
       </c>
       <c r="B188" t="n">
         <v>79327</v>
@@ -21101,10 +21091,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>471033</v>
+        <v>471044</v>
       </c>
       <c r="R188" t="n">
-        <v>6770614</v>
+        <v>6770615</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21172,13 +21162,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962290</t>
+          <t>https://artportalen.se/Sighting/129962260</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129962320</v>
+        <v>129962290</v>
       </c>
       <c r="B189" t="n">
         <v>79327</v>
@@ -21213,10 +21203,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>471024</v>
+        <v>471033</v>
       </c>
       <c r="R189" t="n">
-        <v>6770624</v>
+        <v>6770614</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21284,13 +21274,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962320</t>
+          <t>https://artportalen.se/Sighting/129962290</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129962351</v>
+        <v>129962320</v>
       </c>
       <c r="B190" t="n">
         <v>79327</v>
@@ -21325,10 +21315,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>471017</v>
+        <v>471024</v>
       </c>
       <c r="R190" t="n">
-        <v>6770613</v>
+        <v>6770624</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21396,13 +21386,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962351</t>
+          <t>https://artportalen.se/Sighting/129962320</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129962379</v>
+        <v>129962351</v>
       </c>
       <c r="B191" t="n">
         <v>79327</v>
@@ -21437,10 +21427,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>470996</v>
+        <v>471017</v>
       </c>
       <c r="R191" t="n">
-        <v>6770611</v>
+        <v>6770613</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21508,13 +21498,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962379</t>
+          <t>https://artportalen.se/Sighting/129962351</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129962390</v>
+        <v>129962379</v>
       </c>
       <c r="B192" t="n">
         <v>79327</v>
@@ -21549,10 +21539,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>471004</v>
+        <v>470996</v>
       </c>
       <c r="R192" t="n">
-        <v>6770581</v>
+        <v>6770611</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21620,13 +21610,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962390</t>
+          <t>https://artportalen.se/Sighting/129962379</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129962417</v>
+        <v>129962390</v>
       </c>
       <c r="B193" t="n">
         <v>79327</v>
@@ -21661,10 +21651,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>471002</v>
+        <v>471004</v>
       </c>
       <c r="R193" t="n">
-        <v>6770618</v>
+        <v>6770581</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21732,13 +21722,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962417</t>
+          <t>https://artportalen.se/Sighting/129962390</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129962443</v>
+        <v>129962417</v>
       </c>
       <c r="B194" t="n">
         <v>79327</v>
@@ -21773,10 +21763,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>470989</v>
+        <v>471002</v>
       </c>
       <c r="R194" t="n">
-        <v>6770629</v>
+        <v>6770618</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21844,13 +21834,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962443</t>
+          <t>https://artportalen.se/Sighting/129962417</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129962446</v>
+        <v>129962443</v>
       </c>
       <c r="B195" t="n">
         <v>79327</v>
@@ -21885,10 +21875,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>470993</v>
+        <v>470989</v>
       </c>
       <c r="R195" t="n">
-        <v>6770643</v>
+        <v>6770629</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21956,56 +21946,51 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962446</t>
+          <t>https://artportalen.se/Sighting/129962443</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129944452</v>
+        <v>129962446</v>
       </c>
       <c r="B196" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>471330</v>
+        <v>470993</v>
       </c>
       <c r="R196" t="n">
-        <v>6770712</v>
+        <v>6770643</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22032,22 +22017,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22073,13 +22058,13 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944452</t>
+          <t>https://artportalen.se/Sighting/129962446</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129945156</v>
+        <v>129944452</v>
       </c>
       <c r="B197" t="n">
         <v>57950</v>
@@ -22110,7 +22095,7 @@
       <c r="I197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -22119,10 +22104,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>471198</v>
+        <v>471330</v>
       </c>
       <c r="R197" t="n">
-        <v>6770725</v>
+        <v>6770712</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22190,13 +22175,13 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945156</t>
+          <t>https://artportalen.se/Sighting/129944452</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129945440</v>
+        <v>129945156</v>
       </c>
       <c r="B198" t="n">
         <v>57950</v>
@@ -22236,10 +22221,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>471189</v>
+        <v>471198</v>
       </c>
       <c r="R198" t="n">
-        <v>6770706</v>
+        <v>6770725</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22307,13 +22292,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945440</t>
+          <t>https://artportalen.se/Sighting/129945156</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129946321</v>
+        <v>129945440</v>
       </c>
       <c r="B199" t="n">
         <v>57950</v>
@@ -22344,7 +22329,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22353,10 +22338,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>470871</v>
+        <v>471189</v>
       </c>
       <c r="R199" t="n">
-        <v>6770635</v>
+        <v>6770706</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22424,13 +22409,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946321</t>
+          <t>https://artportalen.se/Sighting/129945440</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129946365</v>
+        <v>129946321</v>
       </c>
       <c r="B200" t="n">
         <v>57950</v>
@@ -22461,7 +22446,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22470,10 +22455,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>470910</v>
+        <v>470871</v>
       </c>
       <c r="R200" t="n">
-        <v>6770605</v>
+        <v>6770635</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22541,13 +22526,13 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946365</t>
+          <t>https://artportalen.se/Sighting/129946321</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129946391</v>
+        <v>129946365</v>
       </c>
       <c r="B201" t="n">
         <v>57950</v>
@@ -22587,10 +22572,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>470921</v>
+        <v>470910</v>
       </c>
       <c r="R201" t="n">
-        <v>6770579</v>
+        <v>6770605</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22658,13 +22643,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946391</t>
+          <t>https://artportalen.se/Sighting/129946365</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129946436</v>
+        <v>129946391</v>
       </c>
       <c r="B202" t="n">
         <v>57950</v>
@@ -22695,7 +22680,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22704,10 +22689,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>470971</v>
+        <v>470921</v>
       </c>
       <c r="R202" t="n">
-        <v>6770603</v>
+        <v>6770579</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22775,13 +22760,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946436</t>
+          <t>https://artportalen.se/Sighting/129946391</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129954441</v>
+        <v>129946436</v>
       </c>
       <c r="B203" t="n">
         <v>57950</v>
@@ -22812,7 +22797,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22821,10 +22806,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>471052</v>
+        <v>470971</v>
       </c>
       <c r="R203" t="n">
-        <v>6770696</v>
+        <v>6770603</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22851,22 +22836,22 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22892,13 +22877,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954441</t>
+          <t>https://artportalen.se/Sighting/129946436</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129957253</v>
+        <v>129954441</v>
       </c>
       <c r="B204" t="n">
         <v>57950</v>
@@ -22938,10 +22923,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>470916</v>
+        <v>471052</v>
       </c>
       <c r="R204" t="n">
-        <v>6770721</v>
+        <v>6770696</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23009,13 +22994,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957253</t>
+          <t>https://artportalen.se/Sighting/129954441</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129958691</v>
+        <v>129957253</v>
       </c>
       <c r="B205" t="n">
         <v>57950</v>
@@ -23055,10 +23040,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>470844</v>
+        <v>470916</v>
       </c>
       <c r="R205" t="n">
-        <v>6770699</v>
+        <v>6770721</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23126,13 +23111,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958691</t>
+          <t>https://artportalen.se/Sighting/129957253</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129959434</v>
+        <v>129958691</v>
       </c>
       <c r="B206" t="n">
         <v>57950</v>
@@ -23172,10 +23157,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470824</v>
+        <v>470844</v>
       </c>
       <c r="R206" t="n">
-        <v>6770523</v>
+        <v>6770699</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23243,13 +23228,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959434</t>
+          <t>https://artportalen.se/Sighting/129958691</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129959567</v>
+        <v>129959434</v>
       </c>
       <c r="B207" t="n">
         <v>57950</v>
@@ -23289,10 +23274,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470822</v>
+        <v>470824</v>
       </c>
       <c r="R207" t="n">
-        <v>6770452</v>
+        <v>6770523</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23360,13 +23345,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959567</t>
+          <t>https://artportalen.se/Sighting/129959434</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129959730</v>
+        <v>129959567</v>
       </c>
       <c r="B208" t="n">
         <v>57950</v>
@@ -23397,7 +23382,7 @@
       <c r="I208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -23406,10 +23391,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470868</v>
+        <v>470822</v>
       </c>
       <c r="R208" t="n">
-        <v>6770431</v>
+        <v>6770452</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23477,13 +23462,13 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959730</t>
+          <t>https://artportalen.se/Sighting/129959567</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129959870</v>
+        <v>129959730</v>
       </c>
       <c r="B209" t="n">
         <v>57950</v>
@@ -23523,10 +23508,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>470952</v>
+        <v>470868</v>
       </c>
       <c r="R209" t="n">
-        <v>6770464</v>
+        <v>6770431</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23594,13 +23579,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959870</t>
+          <t>https://artportalen.se/Sighting/129959730</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129960642</v>
+        <v>129959870</v>
       </c>
       <c r="B210" t="n">
         <v>57950</v>
@@ -23640,10 +23625,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>471025</v>
+        <v>470952</v>
       </c>
       <c r="R210" t="n">
-        <v>6770488</v>
+        <v>6770464</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23711,13 +23696,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960642</t>
+          <t>https://artportalen.se/Sighting/129959870</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129962343</v>
+        <v>129960642</v>
       </c>
       <c r="B211" t="n">
         <v>57950</v>
@@ -23748,7 +23733,7 @@
       <c r="I211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -23757,10 +23742,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>471017</v>
+        <v>471025</v>
       </c>
       <c r="R211" t="n">
-        <v>6770613</v>
+        <v>6770488</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23828,13 +23813,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962343</t>
+          <t>https://artportalen.se/Sighting/129960642</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129962374</v>
+        <v>129962343</v>
       </c>
       <c r="B212" t="n">
         <v>57950</v>
@@ -23874,10 +23859,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>470996</v>
+        <v>471017</v>
       </c>
       <c r="R212" t="n">
-        <v>6770611</v>
+        <v>6770613</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23945,13 +23930,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962374</t>
+          <t>https://artportalen.se/Sighting/129962343</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129962430</v>
+        <v>129962374</v>
       </c>
       <c r="B213" t="n">
         <v>57950</v>
@@ -23982,7 +23967,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23991,10 +23976,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>470989</v>
+        <v>470996</v>
       </c>
       <c r="R213" t="n">
-        <v>6770629</v>
+        <v>6770611</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24062,48 +24047,44 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962430</t>
+          <t>https://artportalen.se/Sighting/129962374</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129944878</v>
+        <v>129962430</v>
       </c>
       <c r="B214" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -24112,13 +24093,13 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471258</v>
+        <v>470989</v>
       </c>
       <c r="R214" t="n">
-        <v>6770712</v>
+        <v>6770629</v>
       </c>
       <c r="S214" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -24142,22 +24123,22 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24183,44 +24164,48 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944878</t>
+          <t>https://artportalen.se/Sighting/129962430</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129944062</v>
+        <v>129944878</v>
       </c>
       <c r="B215" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -24229,13 +24214,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471432</v>
+        <v>471258</v>
       </c>
       <c r="R215" t="n">
-        <v>6770716</v>
+        <v>6770712</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24300,13 +24285,13 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944062</t>
+          <t>https://artportalen.se/Sighting/129944878</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129944158</v>
+        <v>129944062</v>
       </c>
       <c r="B216" t="n">
         <v>8455</v>
@@ -24346,10 +24331,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471363</v>
+        <v>471432</v>
       </c>
       <c r="R216" t="n">
-        <v>6770736</v>
+        <v>6770716</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24417,13 +24402,13 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944158</t>
+          <t>https://artportalen.se/Sighting/129944062</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129944454</v>
+        <v>129944158</v>
       </c>
       <c r="B217" t="n">
         <v>8455</v>
@@ -24452,16 +24437,21 @@
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>471330</v>
+        <v>471363</v>
       </c>
       <c r="R217" t="n">
-        <v>6770712</v>
+        <v>6770736</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24529,13 +24519,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944454</t>
+          <t>https://artportalen.se/Sighting/129944158</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129945161</v>
+        <v>129944454</v>
       </c>
       <c r="B218" t="n">
         <v>8455</v>
@@ -24564,21 +24554,16 @@
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>471198</v>
+        <v>471330</v>
       </c>
       <c r="R218" t="n">
-        <v>6770725</v>
+        <v>6770712</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24646,13 +24631,13 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945161</t>
+          <t>https://artportalen.se/Sighting/129944454</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129945444</v>
+        <v>129945161</v>
       </c>
       <c r="B219" t="n">
         <v>8455</v>
@@ -24692,10 +24677,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471189</v>
+        <v>471198</v>
       </c>
       <c r="R219" t="n">
-        <v>6770706</v>
+        <v>6770725</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24763,13 +24748,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945444</t>
+          <t>https://artportalen.se/Sighting/129945161</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129946047</v>
+        <v>129945444</v>
       </c>
       <c r="B220" t="n">
         <v>8455</v>
@@ -24798,16 +24783,21 @@
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>471161</v>
+        <v>471189</v>
       </c>
       <c r="R220" t="n">
-        <v>6770705</v>
+        <v>6770706</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24875,13 +24865,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946047</t>
+          <t>https://artportalen.se/Sighting/129945444</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129946334</v>
+        <v>129946047</v>
       </c>
       <c r="B221" t="n">
         <v>8455</v>
@@ -24910,21 +24900,16 @@
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>470871</v>
+        <v>471161</v>
       </c>
       <c r="R221" t="n">
-        <v>6770635</v>
+        <v>6770705</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24992,13 +24977,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946334</t>
+          <t>https://artportalen.se/Sighting/129946047</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129946444</v>
+        <v>129946334</v>
       </c>
       <c r="B222" t="n">
         <v>8455</v>
@@ -25038,10 +25023,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470971</v>
+        <v>470871</v>
       </c>
       <c r="R222" t="n">
-        <v>6770603</v>
+        <v>6770635</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25109,13 +25094,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946444</t>
+          <t>https://artportalen.se/Sighting/129946334</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129954662</v>
+        <v>129946444</v>
       </c>
       <c r="B223" t="n">
         <v>8455</v>
@@ -25155,10 +25140,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>470941</v>
+        <v>470971</v>
       </c>
       <c r="R223" t="n">
-        <v>6770708</v>
+        <v>6770603</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25185,22 +25170,22 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25226,13 +25211,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954662</t>
+          <t>https://artportalen.se/Sighting/129946444</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129958131</v>
+        <v>129954662</v>
       </c>
       <c r="B224" t="n">
         <v>8455</v>
@@ -25272,10 +25257,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470869</v>
+        <v>470941</v>
       </c>
       <c r="R224" t="n">
-        <v>6770702</v>
+        <v>6770708</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25343,13 +25328,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958131</t>
+          <t>https://artportalen.se/Sighting/129954662</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129958199</v>
+        <v>129958131</v>
       </c>
       <c r="B225" t="n">
         <v>8455</v>
@@ -25389,10 +25374,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470823</v>
+        <v>470869</v>
       </c>
       <c r="R225" t="n">
-        <v>6770705</v>
+        <v>6770702</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25460,13 +25445,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958199</t>
+          <t>https://artportalen.se/Sighting/129958131</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129958686</v>
+        <v>129958199</v>
       </c>
       <c r="B226" t="n">
         <v>8455</v>
@@ -25506,10 +25491,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>470844</v>
+        <v>470823</v>
       </c>
       <c r="R226" t="n">
-        <v>6770699</v>
+        <v>6770705</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25577,13 +25562,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958686</t>
+          <t>https://artportalen.se/Sighting/129958199</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129959110</v>
+        <v>129958686</v>
       </c>
       <c r="B227" t="n">
         <v>8455</v>
@@ -25623,10 +25608,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>470926</v>
+        <v>470844</v>
       </c>
       <c r="R227" t="n">
-        <v>6770613</v>
+        <v>6770699</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25694,13 +25679,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959110</t>
+          <t>https://artportalen.se/Sighting/129958686</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129959223</v>
+        <v>129959110</v>
       </c>
       <c r="B228" t="n">
         <v>8455</v>
@@ -25740,10 +25725,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470921</v>
+        <v>470926</v>
       </c>
       <c r="R228" t="n">
-        <v>6770579</v>
+        <v>6770613</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25811,13 +25796,13 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959223</t>
+          <t>https://artportalen.se/Sighting/129959110</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129959285</v>
+        <v>129959223</v>
       </c>
       <c r="B229" t="n">
         <v>8455</v>
@@ -25857,10 +25842,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>470922</v>
+        <v>470921</v>
       </c>
       <c r="R229" t="n">
-        <v>6770556</v>
+        <v>6770579</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25928,13 +25913,13 @@
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959285</t>
+          <t>https://artportalen.se/Sighting/129959223</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129959441</v>
+        <v>129959285</v>
       </c>
       <c r="B230" t="n">
         <v>8455</v>
@@ -25974,10 +25959,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>470824</v>
+        <v>470922</v>
       </c>
       <c r="R230" t="n">
-        <v>6770523</v>
+        <v>6770556</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26045,13 +26030,13 @@
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959441</t>
+          <t>https://artportalen.se/Sighting/129959285</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129959579</v>
+        <v>129959441</v>
       </c>
       <c r="B231" t="n">
         <v>8455</v>
@@ -26091,10 +26076,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>470822</v>
+        <v>470824</v>
       </c>
       <c r="R231" t="n">
-        <v>6770452</v>
+        <v>6770523</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26162,13 +26147,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959579</t>
+          <t>https://artportalen.se/Sighting/129959441</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129959710</v>
+        <v>129959579</v>
       </c>
       <c r="B232" t="n">
         <v>8455</v>
@@ -26208,10 +26193,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>470864</v>
+        <v>470822</v>
       </c>
       <c r="R232" t="n">
-        <v>6770438</v>
+        <v>6770452</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26279,13 +26264,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959710</t>
+          <t>https://artportalen.se/Sighting/129959579</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129959735</v>
+        <v>129959710</v>
       </c>
       <c r="B233" t="n">
         <v>8455</v>
@@ -26325,10 +26310,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>470868</v>
+        <v>470864</v>
       </c>
       <c r="R233" t="n">
-        <v>6770431</v>
+        <v>6770438</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26396,13 +26381,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959735</t>
+          <t>https://artportalen.se/Sighting/129959710</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129959924</v>
+        <v>129959735</v>
       </c>
       <c r="B234" t="n">
         <v>8455</v>
@@ -26442,10 +26427,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>470944</v>
+        <v>470868</v>
       </c>
       <c r="R234" t="n">
-        <v>6770458</v>
+        <v>6770431</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26513,13 +26498,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959924</t>
+          <t>https://artportalen.se/Sighting/129959735</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129960514</v>
+        <v>129959924</v>
       </c>
       <c r="B235" t="n">
         <v>8455</v>
@@ -26559,13 +26544,13 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>470976</v>
+        <v>470944</v>
       </c>
       <c r="R235" t="n">
-        <v>6770536</v>
+        <v>6770458</v>
       </c>
       <c r="S235" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -26630,13 +26615,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960514</t>
+          <t>https://artportalen.se/Sighting/129959924</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129960657</v>
+        <v>129960514</v>
       </c>
       <c r="B236" t="n">
         <v>8455</v>
@@ -26676,13 +26661,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>471025</v>
+        <v>470976</v>
       </c>
       <c r="R236" t="n">
-        <v>6770488</v>
+        <v>6770536</v>
       </c>
       <c r="S236" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26747,13 +26732,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960657</t>
+          <t>https://artportalen.se/Sighting/129960514</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129960746</v>
+        <v>129960657</v>
       </c>
       <c r="B237" t="n">
         <v>8455</v>
@@ -26793,10 +26778,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>471053</v>
+        <v>471025</v>
       </c>
       <c r="R237" t="n">
-        <v>6770528</v>
+        <v>6770488</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26864,13 +26849,13 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960746</t>
+          <t>https://artportalen.se/Sighting/129960657</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129960827</v>
+        <v>129960746</v>
       </c>
       <c r="B238" t="n">
         <v>8455</v>
@@ -26910,10 +26895,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>471078</v>
+        <v>471053</v>
       </c>
       <c r="R238" t="n">
-        <v>6770561</v>
+        <v>6770528</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26981,13 +26966,13 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960827</t>
+          <t>https://artportalen.se/Sighting/129960746</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129961109</v>
+        <v>129960827</v>
       </c>
       <c r="B239" t="n">
         <v>8455</v>
@@ -27027,10 +27012,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>471175</v>
+        <v>471078</v>
       </c>
       <c r="R239" t="n">
-        <v>6770631</v>
+        <v>6770561</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27098,13 +27083,13 @@
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961109</t>
+          <t>https://artportalen.se/Sighting/129960827</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129962346</v>
+        <v>129961109</v>
       </c>
       <c r="B240" t="n">
         <v>8455</v>
@@ -27144,10 +27129,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>471017</v>
+        <v>471175</v>
       </c>
       <c r="R240" t="n">
-        <v>6770613</v>
+        <v>6770631</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27215,13 +27200,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962346</t>
+          <t>https://artportalen.se/Sighting/129961109</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129962376</v>
+        <v>129962346</v>
       </c>
       <c r="B241" t="n">
         <v>8455</v>
@@ -27261,10 +27246,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>470996</v>
+        <v>471017</v>
       </c>
       <c r="R241" t="n">
-        <v>6770611</v>
+        <v>6770613</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27332,13 +27317,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962376</t>
+          <t>https://artportalen.se/Sighting/129962346</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129962436</v>
+        <v>129962376</v>
       </c>
       <c r="B242" t="n">
         <v>8455</v>
@@ -27378,10 +27363,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>470989</v>
+        <v>470996</v>
       </c>
       <c r="R242" t="n">
-        <v>6770629</v>
+        <v>6770611</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27449,57 +27434,59 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962436</t>
+          <t>https://artportalen.se/Sighting/129962376</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129271581</v>
+        <v>129962436</v>
       </c>
       <c r="B243" t="n">
-        <v>93228</v>
+        <v>8455</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>232140</v>
+        <v>106545</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
-      <c r="K243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>470835</v>
+        <v>470989</v>
       </c>
       <c r="R243" t="n">
-        <v>6770662</v>
+        <v>6770629</v>
       </c>
       <c r="S243" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -27523,12 +27510,22 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27537,69 +27534,71 @@
       <c r="AE243" t="b">
         <v>0</v>
       </c>
-      <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="b">
         <v>0</v>
       </c>
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129271581</t>
+          <t>https://artportalen.se/Sighting/129962436</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>96714923</v>
+        <v>129271581</v>
       </c>
       <c r="B244" t="n">
-        <v>91402</v>
+        <v>93228</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>256703</v>
+        <v>232140</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>470876</v>
+        <v>470835</v>
       </c>
       <c r="R244" t="n">
-        <v>6770446</v>
+        <v>6770662</v>
       </c>
       <c r="S244" t="n">
         <v>25</v>
@@ -27626,12 +27625,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27640,30 +27639,31 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
+      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714923</t>
+          <t>https://artportalen.se/Sighting/129271581</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>96714929</v>
+        <v>96714923</v>
       </c>
       <c r="B245" t="n">
         <v>91402</v>
@@ -27698,10 +27698,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>471113</v>
+        <v>470876</v>
       </c>
       <c r="R245" t="n">
-        <v>6770726</v>
+        <v>6770446</v>
       </c>
       <c r="S245" t="n">
         <v>25</v>
@@ -27759,13 +27759,13 @@
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714929</t>
+          <t>https://artportalen.se/Sighting/96714923</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>96714933</v>
+        <v>96714929</v>
       </c>
       <c r="B246" t="n">
         <v>91402</v>
@@ -27800,10 +27800,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>470806</v>
+        <v>471113</v>
       </c>
       <c r="R246" t="n">
-        <v>6770695</v>
+        <v>6770726</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -27861,13 +27861,13 @@
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714933</t>
+          <t>https://artportalen.se/Sighting/96714929</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>96714941</v>
+        <v>96714933</v>
       </c>
       <c r="B247" t="n">
         <v>91402</v>
@@ -27902,10 +27902,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>471105</v>
+        <v>470806</v>
       </c>
       <c r="R247" t="n">
-        <v>6770716</v>
+        <v>6770695</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -27963,13 +27963,13 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714941</t>
+          <t>https://artportalen.se/Sighting/96714933</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>96714946</v>
+        <v>96714941</v>
       </c>
       <c r="B248" t="n">
         <v>91402</v>
@@ -28004,7 +28004,7 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>471072</v>
+        <v>471105</v>
       </c>
       <c r="R248" t="n">
         <v>6770716</v>
@@ -28065,13 +28065,13 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714946</t>
+          <t>https://artportalen.se/Sighting/96714941</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>96714952</v>
+        <v>96714946</v>
       </c>
       <c r="B249" t="n">
         <v>91402</v>
@@ -28106,10 +28106,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>470920</v>
+        <v>471072</v>
       </c>
       <c r="R249" t="n">
-        <v>6770687</v>
+        <v>6770716</v>
       </c>
       <c r="S249" t="n">
         <v>25</v>
@@ -28167,13 +28167,13 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714952</t>
+          <t>https://artportalen.se/Sighting/96714946</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>96714953</v>
+        <v>96714952</v>
       </c>
       <c r="B250" t="n">
         <v>91402</v>
@@ -28208,10 +28208,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>471086</v>
+        <v>470920</v>
       </c>
       <c r="R250" t="n">
-        <v>6770698</v>
+        <v>6770687</v>
       </c>
       <c r="S250" t="n">
         <v>25</v>
@@ -28269,13 +28269,13 @@
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714953</t>
+          <t>https://artportalen.se/Sighting/96714952</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>96714960</v>
+        <v>96714953</v>
       </c>
       <c r="B251" t="n">
         <v>91402</v>
@@ -28310,10 +28310,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>471091</v>
+        <v>471086</v>
       </c>
       <c r="R251" t="n">
-        <v>6770723</v>
+        <v>6770698</v>
       </c>
       <c r="S251" t="n">
         <v>25</v>
@@ -28371,13 +28371,13 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714960</t>
+          <t>https://artportalen.se/Sighting/96714953</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>96714973</v>
+        <v>96714960</v>
       </c>
       <c r="B252" t="n">
         <v>91402</v>
@@ -28412,10 +28412,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>471080</v>
+        <v>471091</v>
       </c>
       <c r="R252" t="n">
-        <v>6770598</v>
+        <v>6770723</v>
       </c>
       <c r="S252" t="n">
         <v>25</v>
@@ -28473,13 +28473,13 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714973</t>
+          <t>https://artportalen.se/Sighting/96714960</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>96714981</v>
+        <v>96714973</v>
       </c>
       <c r="B253" t="n">
         <v>91402</v>
@@ -28514,10 +28514,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>471483</v>
+        <v>471080</v>
       </c>
       <c r="R253" t="n">
-        <v>6770715</v>
+        <v>6770598</v>
       </c>
       <c r="S253" t="n">
         <v>25</v>
@@ -28575,13 +28575,13 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714981</t>
+          <t>https://artportalen.se/Sighting/96714973</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>96715005</v>
+        <v>96714981</v>
       </c>
       <c r="B254" t="n">
         <v>91402</v>
@@ -28616,10 +28616,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>470830</v>
+        <v>471483</v>
       </c>
       <c r="R254" t="n">
-        <v>6770666</v>
+        <v>6770715</v>
       </c>
       <c r="S254" t="n">
         <v>25</v>
@@ -28677,13 +28677,13 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715005</t>
+          <t>https://artportalen.se/Sighting/96714981</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>96715010</v>
+        <v>96715005</v>
       </c>
       <c r="B255" t="n">
         <v>91402</v>
@@ -28718,10 +28718,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>471253</v>
+        <v>470830</v>
       </c>
       <c r="R255" t="n">
-        <v>6770676</v>
+        <v>6770666</v>
       </c>
       <c r="S255" t="n">
         <v>25</v>
@@ -28778,6 +28778,108 @@
       </c>
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715005</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>96715010</v>
+      </c>
+      <c r="B256" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Bonäsheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>471253</v>
+      </c>
+      <c r="R256" t="n">
+        <v>6770676</v>
+      </c>
+      <c r="S256" t="n">
+        <v>25</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96715010</t>
         </is>
@@ -29039,6 +29141,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ256"/>
+  <dimension ref="A1:AZ258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6997,48 +6997,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>96714971</v>
+        <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93201</v>
+        <v>93413</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bengttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470825</v>
+        <v>470909</v>
       </c>
       <c r="R62" t="n">
-        <v>6770664</v>
+        <v>6770448</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7062,12 +7062,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7082,49 +7092,49 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Uno Skog, Andreas Öster</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714971</t>
+          <t>https://artportalen.se/Sighting/136837910</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>96714979</v>
+        <v>96714971</v>
       </c>
       <c r="B63" t="n">
-        <v>92841</v>
+        <v>93201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7134,10 +7144,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471064</v>
+        <v>470825</v>
       </c>
       <c r="R63" t="n">
-        <v>6770563</v>
+        <v>6770664</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7195,16 +7205,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714979</t>
+          <t>https://artportalen.se/Sighting/96714971</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129943849</v>
+        <v>96714979</v>
       </c>
       <c r="B64" t="n">
-        <v>91930</v>
+        <v>92841</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7212,41 +7222,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>4745</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471451</v>
+        <v>471064</v>
       </c>
       <c r="R64" t="n">
-        <v>6770706</v>
+        <v>6770563</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7270,22 +7276,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7300,24 +7296,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943849</t>
+          <t>https://artportalen.se/Sighting/96714979</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129944262</v>
+        <v>129943849</v>
       </c>
       <c r="B65" t="n">
         <v>91930</v>
@@ -7356,10 +7352,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471369</v>
+        <v>471451</v>
       </c>
       <c r="R65" t="n">
-        <v>6770686</v>
+        <v>6770706</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7427,13 +7423,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944262</t>
+          <t>https://artportalen.se/Sighting/129943849</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129959667</v>
+        <v>129944262</v>
       </c>
       <c r="B66" t="n">
         <v>91930</v>
@@ -7463,7 +7459,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7472,10 +7468,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470864</v>
+        <v>471369</v>
       </c>
       <c r="R66" t="n">
-        <v>6770438</v>
+        <v>6770686</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7502,22 +7498,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7543,16 +7539,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959667</t>
+          <t>https://artportalen.se/Sighting/129944262</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>96714915</v>
+        <v>129959667</v>
       </c>
       <c r="B67" t="n">
-        <v>93235</v>
+        <v>91930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7560,37 +7556,41 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471343</v>
+        <v>470864</v>
       </c>
       <c r="R67" t="n">
-        <v>6770659</v>
+        <v>6770438</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7614,12 +7614,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7634,24 +7644,24 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714915</t>
+          <t>https://artportalen.se/Sighting/129959667</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>96714991</v>
+        <v>96714915</v>
       </c>
       <c r="B68" t="n">
         <v>93235</v>
@@ -7686,10 +7696,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>470824</v>
+        <v>471343</v>
       </c>
       <c r="R68" t="n">
-        <v>6770660</v>
+        <v>6770659</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7747,54 +7757,54 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714991</t>
+          <t>https://artportalen.se/Sighting/96714915</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136837813</v>
+        <v>96714991</v>
       </c>
       <c r="B69" t="n">
-        <v>93395</v>
+        <v>93235</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6055</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bengttjärnen, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470979</v>
+        <v>470824</v>
       </c>
       <c r="R69" t="n">
-        <v>6770615</v>
+        <v>6770660</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7818,12 +7828,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7838,27 +7848,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837813</t>
+          <t>https://artportalen.se/Sighting/96714991</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>96714961</v>
+        <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>90691</v>
+        <v>93397</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7866,37 +7876,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6276</v>
+        <v>6055</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bengttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471372</v>
+        <v>470971</v>
       </c>
       <c r="R70" t="n">
-        <v>6770686</v>
+        <v>6770613</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7920,12 +7930,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7940,27 +7960,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714961</t>
+          <t>https://artportalen.se/Sighting/136836580</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>96715014</v>
+        <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>90691</v>
+        <v>93397</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7968,37 +7988,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6276</v>
+        <v>6055</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bengttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470841</v>
+        <v>470979</v>
       </c>
       <c r="R71" t="n">
-        <v>6770558</v>
+        <v>6770615</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8022,12 +8042,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8042,27 +8062,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715014</t>
+          <t>https://artportalen.se/Sighting/136837813</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>96715007</v>
+        <v>96714961</v>
       </c>
       <c r="B72" t="n">
-        <v>79327</v>
+        <v>90691</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8070,21 +8090,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8094,10 +8114,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471383</v>
+        <v>471372</v>
       </c>
       <c r="R72" t="n">
-        <v>6770715</v>
+        <v>6770686</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8155,16 +8175,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715007</t>
+          <t>https://artportalen.se/Sighting/96714961</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129943529</v>
+        <v>96715014</v>
       </c>
       <c r="B73" t="n">
-        <v>79327</v>
+        <v>90691</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8172,37 +8192,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471492</v>
+        <v>470841</v>
       </c>
       <c r="R73" t="n">
-        <v>6770712</v>
+        <v>6770558</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8226,22 +8246,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8256,24 +8266,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943529</t>
+          <t>https://artportalen.se/Sighting/96715014</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129943541</v>
+        <v>96715007</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8304,17 +8314,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471478</v>
+        <v>471383</v>
       </c>
       <c r="R74" t="n">
-        <v>6770707</v>
+        <v>6770715</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8338,22 +8348,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8368,24 +8368,24 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943541</t>
+          <t>https://artportalen.se/Sighting/96715007</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129943580</v>
+        <v>129943529</v>
       </c>
       <c r="B75" t="n">
         <v>79327</v>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471468</v>
+        <v>471492</v>
       </c>
       <c r="R75" t="n">
-        <v>6770744</v>
+        <v>6770712</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8491,13 +8491,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943580</t>
+          <t>https://artportalen.se/Sighting/129943529</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129943763</v>
+        <v>129943541</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471466</v>
+        <v>471478</v>
       </c>
       <c r="R76" t="n">
-        <v>6770713</v>
+        <v>6770707</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8603,13 +8603,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943763</t>
+          <t>https://artportalen.se/Sighting/129943541</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129943809</v>
+        <v>129943580</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471447</v>
+        <v>471468</v>
       </c>
       <c r="R77" t="n">
-        <v>6770716</v>
+        <v>6770744</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8715,13 +8715,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943809</t>
+          <t>https://artportalen.se/Sighting/129943580</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129943855</v>
+        <v>129943763</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471451</v>
+        <v>471466</v>
       </c>
       <c r="R78" t="n">
-        <v>6770706</v>
+        <v>6770713</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8827,13 +8827,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943855</t>
+          <t>https://artportalen.se/Sighting/129943763</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129943914</v>
+        <v>129943809</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -8868,10 +8868,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471432</v>
+        <v>471447</v>
       </c>
       <c r="R79" t="n">
-        <v>6770701</v>
+        <v>6770716</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8939,13 +8939,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943914</t>
+          <t>https://artportalen.se/Sighting/129943809</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129943999</v>
+        <v>129943855</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471428</v>
+        <v>471451</v>
       </c>
       <c r="R80" t="n">
-        <v>6770747</v>
+        <v>6770706</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9051,13 +9051,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943999</t>
+          <t>https://artportalen.se/Sighting/129943855</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129944026</v>
+        <v>129943914</v>
       </c>
       <c r="B81" t="n">
         <v>79327</v>
@@ -9092,10 +9092,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471422</v>
+        <v>471432</v>
       </c>
       <c r="R81" t="n">
-        <v>6770745</v>
+        <v>6770701</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9163,13 +9163,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944026</t>
+          <t>https://artportalen.se/Sighting/129943914</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129944037</v>
+        <v>129943999</v>
       </c>
       <c r="B82" t="n">
         <v>79327</v>
@@ -9204,10 +9204,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471417</v>
+        <v>471428</v>
       </c>
       <c r="R82" t="n">
-        <v>6770738</v>
+        <v>6770747</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9275,13 +9275,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944037</t>
+          <t>https://artportalen.se/Sighting/129943999</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944164</v>
+        <v>129944026</v>
       </c>
       <c r="B83" t="n">
         <v>79327</v>
@@ -9316,10 +9316,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471363</v>
+        <v>471422</v>
       </c>
       <c r="R83" t="n">
-        <v>6770736</v>
+        <v>6770745</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9387,13 +9387,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944164</t>
+          <t>https://artportalen.se/Sighting/129944026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944178</v>
+        <v>129944037</v>
       </c>
       <c r="B84" t="n">
         <v>79327</v>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471372</v>
+        <v>471417</v>
       </c>
       <c r="R84" t="n">
-        <v>6770719</v>
+        <v>6770738</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9499,13 +9499,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944178</t>
+          <t>https://artportalen.se/Sighting/129944037</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129944210</v>
+        <v>129944164</v>
       </c>
       <c r="B85" t="n">
         <v>79327</v>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471390</v>
+        <v>471363</v>
       </c>
       <c r="R85" t="n">
-        <v>6770705</v>
+        <v>6770736</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,13 +9611,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944210</t>
+          <t>https://artportalen.se/Sighting/129944164</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129944228</v>
+        <v>129944178</v>
       </c>
       <c r="B86" t="n">
         <v>79327</v>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471390</v>
+        <v>471372</v>
       </c>
       <c r="R86" t="n">
-        <v>6770693</v>
+        <v>6770719</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9723,13 +9723,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944228</t>
+          <t>https://artportalen.se/Sighting/129944178</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129944311</v>
+        <v>129944210</v>
       </c>
       <c r="B87" t="n">
         <v>79327</v>
@@ -9764,10 +9764,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471369</v>
+        <v>471390</v>
       </c>
       <c r="R87" t="n">
-        <v>6770686</v>
+        <v>6770705</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9835,13 +9835,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944311</t>
+          <t>https://artportalen.se/Sighting/129944210</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129944355</v>
+        <v>129944228</v>
       </c>
       <c r="B88" t="n">
         <v>79327</v>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471342</v>
+        <v>471390</v>
       </c>
       <c r="R88" t="n">
-        <v>6770682</v>
+        <v>6770693</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9947,13 +9947,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944355</t>
+          <t>https://artportalen.se/Sighting/129944228</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129944466</v>
+        <v>129944311</v>
       </c>
       <c r="B89" t="n">
         <v>79327</v>
@@ -9988,10 +9988,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471322</v>
+        <v>471369</v>
       </c>
       <c r="R89" t="n">
-        <v>6770702</v>
+        <v>6770686</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10059,13 +10059,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944466</t>
+          <t>https://artportalen.se/Sighting/129944311</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129944473</v>
+        <v>129944355</v>
       </c>
       <c r="B90" t="n">
         <v>79327</v>
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471328</v>
+        <v>471342</v>
       </c>
       <c r="R90" t="n">
-        <v>6770726</v>
+        <v>6770682</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10171,13 +10171,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944473</t>
+          <t>https://artportalen.se/Sighting/129944355</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129944488</v>
+        <v>129944466</v>
       </c>
       <c r="B91" t="n">
         <v>79327</v>
@@ -10212,10 +10212,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471318</v>
+        <v>471322</v>
       </c>
       <c r="R91" t="n">
-        <v>6770729</v>
+        <v>6770702</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10283,13 +10283,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944488</t>
+          <t>https://artportalen.se/Sighting/129944466</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129944495</v>
+        <v>129944473</v>
       </c>
       <c r="B92" t="n">
         <v>79327</v>
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471288</v>
+        <v>471328</v>
       </c>
       <c r="R92" t="n">
-        <v>6770728</v>
+        <v>6770726</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10395,13 +10395,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944495</t>
+          <t>https://artportalen.se/Sighting/129944473</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129944523</v>
+        <v>129944488</v>
       </c>
       <c r="B93" t="n">
         <v>79327</v>
@@ -10436,10 +10436,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471303</v>
+        <v>471318</v>
       </c>
       <c r="R93" t="n">
-        <v>6770699</v>
+        <v>6770729</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10507,13 +10507,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944523</t>
+          <t>https://artportalen.se/Sighting/129944488</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129944544</v>
+        <v>129944495</v>
       </c>
       <c r="B94" t="n">
         <v>79327</v>
@@ -10548,10 +10548,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471330</v>
+        <v>471288</v>
       </c>
       <c r="R94" t="n">
-        <v>6770712</v>
+        <v>6770728</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10619,13 +10619,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944544</t>
+          <t>https://artportalen.se/Sighting/129944495</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129944592</v>
+        <v>129944523</v>
       </c>
       <c r="B95" t="n">
         <v>79327</v>
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471313</v>
+        <v>471303</v>
       </c>
       <c r="R95" t="n">
-        <v>6770688</v>
+        <v>6770699</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10731,13 +10731,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944592</t>
+          <t>https://artportalen.se/Sighting/129944523</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129944756</v>
+        <v>129944544</v>
       </c>
       <c r="B96" t="n">
         <v>79327</v>
@@ -10772,10 +10772,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471288</v>
+        <v>471330</v>
       </c>
       <c r="R96" t="n">
-        <v>6770685</v>
+        <v>6770712</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10843,13 +10843,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944756</t>
+          <t>https://artportalen.se/Sighting/129944544</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129944762</v>
+        <v>129944592</v>
       </c>
       <c r="B97" t="n">
         <v>79327</v>
@@ -10884,10 +10884,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471276</v>
+        <v>471313</v>
       </c>
       <c r="R97" t="n">
-        <v>6770703</v>
+        <v>6770688</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10955,13 +10955,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944762</t>
+          <t>https://artportalen.se/Sighting/129944592</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129944804</v>
+        <v>129944756</v>
       </c>
       <c r="B98" t="n">
         <v>79327</v>
@@ -10996,10 +10996,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471271</v>
+        <v>471288</v>
       </c>
       <c r="R98" t="n">
-        <v>6770733</v>
+        <v>6770685</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11067,13 +11067,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944804</t>
+          <t>https://artportalen.se/Sighting/129944756</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129944807</v>
+        <v>129944762</v>
       </c>
       <c r="B99" t="n">
         <v>79327</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471248</v>
+        <v>471276</v>
       </c>
       <c r="R99" t="n">
-        <v>6770737</v>
+        <v>6770703</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11179,13 +11179,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944807</t>
+          <t>https://artportalen.se/Sighting/129944762</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944809</v>
+        <v>129944804</v>
       </c>
       <c r="B100" t="n">
         <v>79327</v>
@@ -11220,10 +11220,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471247</v>
+        <v>471271</v>
       </c>
       <c r="R100" t="n">
-        <v>6770726</v>
+        <v>6770733</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11291,13 +11291,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944809</t>
+          <t>https://artportalen.se/Sighting/129944804</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129944917</v>
+        <v>129944807</v>
       </c>
       <c r="B101" t="n">
         <v>79327</v>
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471263</v>
+        <v>471248</v>
       </c>
       <c r="R101" t="n">
-        <v>6770694</v>
+        <v>6770737</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,13 +11403,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944917</t>
+          <t>https://artportalen.se/Sighting/129944807</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129944975</v>
+        <v>129944809</v>
       </c>
       <c r="B102" t="n">
         <v>79327</v>
@@ -11444,10 +11444,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471242</v>
+        <v>471247</v>
       </c>
       <c r="R102" t="n">
-        <v>6770682</v>
+        <v>6770726</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11515,13 +11515,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944975</t>
+          <t>https://artportalen.se/Sighting/129944809</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129945066</v>
+        <v>129944917</v>
       </c>
       <c r="B103" t="n">
         <v>79327</v>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471239</v>
+        <v>471263</v>
       </c>
       <c r="R103" t="n">
-        <v>6770732</v>
+        <v>6770694</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11627,13 +11627,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945066</t>
+          <t>https://artportalen.se/Sighting/129944917</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129945078</v>
+        <v>129944975</v>
       </c>
       <c r="B104" t="n">
         <v>79327</v>
@@ -11668,10 +11668,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471209</v>
+        <v>471242</v>
       </c>
       <c r="R104" t="n">
-        <v>6770731</v>
+        <v>6770682</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11739,13 +11739,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945078</t>
+          <t>https://artportalen.se/Sighting/129944975</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129945104</v>
+        <v>129945066</v>
       </c>
       <c r="B105" t="n">
         <v>79327</v>
@@ -11780,10 +11780,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471219</v>
+        <v>471239</v>
       </c>
       <c r="R105" t="n">
-        <v>6770720</v>
+        <v>6770732</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11851,13 +11851,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945104</t>
+          <t>https://artportalen.se/Sighting/129945066</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129945451</v>
+        <v>129945078</v>
       </c>
       <c r="B106" t="n">
         <v>79327</v>
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471189</v>
+        <v>471209</v>
       </c>
       <c r="R106" t="n">
-        <v>6770706</v>
+        <v>6770731</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11963,13 +11963,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945451</t>
+          <t>https://artportalen.se/Sighting/129945078</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129945509</v>
+        <v>129945104</v>
       </c>
       <c r="B107" t="n">
         <v>79327</v>
@@ -12004,10 +12004,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471198</v>
+        <v>471219</v>
       </c>
       <c r="R107" t="n">
-        <v>6770689</v>
+        <v>6770720</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12052,11 +12052,6 @@
           <t>11:17</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12080,13 +12075,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945509</t>
+          <t>https://artportalen.se/Sighting/129945104</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129946029</v>
+        <v>129945451</v>
       </c>
       <c r="B108" t="n">
         <v>79327</v>
@@ -12121,10 +12116,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471185</v>
+        <v>471189</v>
       </c>
       <c r="R108" t="n">
-        <v>6770690</v>
+        <v>6770706</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12192,13 +12187,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946029</t>
+          <t>https://artportalen.se/Sighting/129945451</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129946053</v>
+        <v>129945509</v>
       </c>
       <c r="B109" t="n">
         <v>79327</v>
@@ -12233,10 +12228,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471161</v>
+        <v>471198</v>
       </c>
       <c r="R109" t="n">
-        <v>6770705</v>
+        <v>6770689</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12281,6 +12276,11 @@
           <t>11:17</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12304,13 +12304,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946053</t>
+          <t>https://artportalen.se/Sighting/129945509</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129946117</v>
+        <v>129946029</v>
       </c>
       <c r="B110" t="n">
         <v>79327</v>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471106</v>
+        <v>471185</v>
       </c>
       <c r="R110" t="n">
-        <v>6770711</v>
+        <v>6770690</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12416,13 +12416,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946117</t>
+          <t>https://artportalen.se/Sighting/129946029</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129946170</v>
+        <v>129946053</v>
       </c>
       <c r="B111" t="n">
         <v>79327</v>
@@ -12457,10 +12457,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471030</v>
+        <v>471161</v>
       </c>
       <c r="R111" t="n">
-        <v>6770688</v>
+        <v>6770705</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12528,13 +12528,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946170</t>
+          <t>https://artportalen.se/Sighting/129946053</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129946182</v>
+        <v>129946117</v>
       </c>
       <c r="B112" t="n">
         <v>79327</v>
@@ -12569,10 +12569,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471000</v>
+        <v>471106</v>
       </c>
       <c r="R112" t="n">
-        <v>6770675</v>
+        <v>6770711</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12640,13 +12640,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946182</t>
+          <t>https://artportalen.se/Sighting/129946117</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129946197</v>
+        <v>129946170</v>
       </c>
       <c r="B113" t="n">
         <v>79327</v>
@@ -12681,10 +12681,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>470971</v>
+        <v>471030</v>
       </c>
       <c r="R113" t="n">
-        <v>6770676</v>
+        <v>6770688</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12752,13 +12752,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946197</t>
+          <t>https://artportalen.se/Sighting/129946170</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129946408</v>
+        <v>129946182</v>
       </c>
       <c r="B114" t="n">
         <v>79327</v>
@@ -12793,10 +12793,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>470921</v>
+        <v>471000</v>
       </c>
       <c r="R114" t="n">
-        <v>6770579</v>
+        <v>6770675</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12864,13 +12864,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946408</t>
+          <t>https://artportalen.se/Sighting/129946182</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129946586</v>
+        <v>129946197</v>
       </c>
       <c r="B115" t="n">
         <v>79327</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471095</v>
+        <v>470971</v>
       </c>
       <c r="R115" t="n">
-        <v>6770660</v>
+        <v>6770676</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12976,13 +12976,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946586</t>
+          <t>https://artportalen.se/Sighting/129946197</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129946708</v>
+        <v>129946408</v>
       </c>
       <c r="B116" t="n">
         <v>79327</v>
@@ -13017,10 +13017,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471171</v>
+        <v>470921</v>
       </c>
       <c r="R116" t="n">
-        <v>6770660</v>
+        <v>6770579</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13088,13 +13088,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946708</t>
+          <t>https://artportalen.se/Sighting/129946408</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129954408</v>
+        <v>129946586</v>
       </c>
       <c r="B117" t="n">
         <v>79327</v>
@@ -13129,10 +13129,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471019</v>
+        <v>471095</v>
       </c>
       <c r="R117" t="n">
-        <v>6770666</v>
+        <v>6770660</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13159,22 +13159,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13200,13 +13200,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954408</t>
+          <t>https://artportalen.se/Sighting/129946586</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129954413</v>
+        <v>129946708</v>
       </c>
       <c r="B118" t="n">
         <v>79327</v>
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>471028</v>
+        <v>471171</v>
       </c>
       <c r="R118" t="n">
-        <v>6770675</v>
+        <v>6770660</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13271,22 +13271,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13312,13 +13312,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954413</t>
+          <t>https://artportalen.se/Sighting/129946708</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129954442</v>
+        <v>129954408</v>
       </c>
       <c r="B119" t="n">
         <v>79327</v>
@@ -13353,10 +13353,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471053</v>
+        <v>471019</v>
       </c>
       <c r="R119" t="n">
-        <v>6770682</v>
+        <v>6770666</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13424,13 +13424,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954442</t>
+          <t>https://artportalen.se/Sighting/129954408</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129954452</v>
+        <v>129954413</v>
       </c>
       <c r="B120" t="n">
         <v>79327</v>
@@ -13465,10 +13465,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471058</v>
+        <v>471028</v>
       </c>
       <c r="R120" t="n">
-        <v>6770677</v>
+        <v>6770675</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13536,13 +13536,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954452</t>
+          <t>https://artportalen.se/Sighting/129954413</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129954531</v>
+        <v>129954442</v>
       </c>
       <c r="B121" t="n">
         <v>79327</v>
@@ -13577,10 +13577,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471106</v>
+        <v>471053</v>
       </c>
       <c r="R121" t="n">
-        <v>6770683</v>
+        <v>6770682</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13648,13 +13648,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954531</t>
+          <t>https://artportalen.se/Sighting/129954442</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129954534</v>
+        <v>129954452</v>
       </c>
       <c r="B122" t="n">
         <v>79327</v>
@@ -13689,10 +13689,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471086</v>
+        <v>471058</v>
       </c>
       <c r="R122" t="n">
-        <v>6770684</v>
+        <v>6770677</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13760,13 +13760,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954534</t>
+          <t>https://artportalen.se/Sighting/129954452</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129954584</v>
+        <v>129954531</v>
       </c>
       <c r="B123" t="n">
         <v>79327</v>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471062</v>
+        <v>471106</v>
       </c>
       <c r="R123" t="n">
-        <v>6770731</v>
+        <v>6770683</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13872,13 +13872,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954584</t>
+          <t>https://artportalen.se/Sighting/129954531</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129954590</v>
+        <v>129954534</v>
       </c>
       <c r="B124" t="n">
         <v>79327</v>
@@ -13913,10 +13913,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471013</v>
+        <v>471086</v>
       </c>
       <c r="R124" t="n">
-        <v>6770715</v>
+        <v>6770684</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13984,13 +13984,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954590</t>
+          <t>https://artportalen.se/Sighting/129954534</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129954674</v>
+        <v>129954584</v>
       </c>
       <c r="B125" t="n">
         <v>79327</v>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470938</v>
+        <v>471062</v>
       </c>
       <c r="R125" t="n">
-        <v>6770693</v>
+        <v>6770731</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14096,13 +14096,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954674</t>
+          <t>https://artportalen.se/Sighting/129954584</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129955100</v>
+        <v>129954590</v>
       </c>
       <c r="B126" t="n">
         <v>79327</v>
@@ -14137,10 +14137,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470981</v>
+        <v>471013</v>
       </c>
       <c r="R126" t="n">
-        <v>6770691</v>
+        <v>6770715</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14208,13 +14208,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129955100</t>
+          <t>https://artportalen.se/Sighting/129954590</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129955313</v>
+        <v>129954674</v>
       </c>
       <c r="B127" t="n">
         <v>79327</v>
@@ -14249,10 +14249,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470992</v>
+        <v>470938</v>
       </c>
       <c r="R127" t="n">
-        <v>6770702</v>
+        <v>6770693</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14320,13 +14320,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129955313</t>
+          <t>https://artportalen.se/Sighting/129954674</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129956843</v>
+        <v>129955100</v>
       </c>
       <c r="B128" t="n">
         <v>79327</v>
@@ -14361,10 +14361,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470953</v>
+        <v>470981</v>
       </c>
       <c r="R128" t="n">
-        <v>6770692</v>
+        <v>6770691</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14432,13 +14432,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956843</t>
+          <t>https://artportalen.se/Sighting/129955100</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129956851</v>
+        <v>129955313</v>
       </c>
       <c r="B129" t="n">
         <v>79327</v>
@@ -14473,10 +14473,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470928</v>
+        <v>470992</v>
       </c>
       <c r="R129" t="n">
-        <v>6770695</v>
+        <v>6770702</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14544,13 +14544,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956851</t>
+          <t>https://artportalen.se/Sighting/129955313</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129956859</v>
+        <v>129956843</v>
       </c>
       <c r="B130" t="n">
         <v>79327</v>
@@ -14585,10 +14585,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470936</v>
+        <v>470953</v>
       </c>
       <c r="R130" t="n">
-        <v>6770721</v>
+        <v>6770692</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14656,13 +14656,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956859</t>
+          <t>https://artportalen.se/Sighting/129956843</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129957713</v>
+        <v>129956851</v>
       </c>
       <c r="B131" t="n">
         <v>79327</v>
@@ -14697,10 +14697,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470904</v>
+        <v>470928</v>
       </c>
       <c r="R131" t="n">
-        <v>6770718</v>
+        <v>6770695</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14768,13 +14768,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957713</t>
+          <t>https://artportalen.se/Sighting/129956851</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129957969</v>
+        <v>129956859</v>
       </c>
       <c r="B132" t="n">
         <v>79327</v>
@@ -14809,10 +14809,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470911</v>
+        <v>470936</v>
       </c>
       <c r="R132" t="n">
-        <v>6770707</v>
+        <v>6770721</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14880,13 +14880,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957969</t>
+          <t>https://artportalen.se/Sighting/129956859</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129958010</v>
+        <v>129957713</v>
       </c>
       <c r="B133" t="n">
         <v>79327</v>
@@ -14921,10 +14921,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>470894</v>
+        <v>470904</v>
       </c>
       <c r="R133" t="n">
-        <v>6770713</v>
+        <v>6770718</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14992,13 +14992,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958010</t>
+          <t>https://artportalen.se/Sighting/129957713</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129958133</v>
+        <v>129957969</v>
       </c>
       <c r="B134" t="n">
         <v>79327</v>
@@ -15033,10 +15033,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>470869</v>
+        <v>470911</v>
       </c>
       <c r="R134" t="n">
-        <v>6770702</v>
+        <v>6770707</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15104,13 +15104,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958133</t>
+          <t>https://artportalen.se/Sighting/129957969</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129958151</v>
+        <v>129958010</v>
       </c>
       <c r="B135" t="n">
         <v>79327</v>
@@ -15145,10 +15145,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470842</v>
+        <v>470894</v>
       </c>
       <c r="R135" t="n">
-        <v>6770709</v>
+        <v>6770713</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15216,13 +15216,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958151</t>
+          <t>https://artportalen.se/Sighting/129958010</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129958214</v>
+        <v>129958133</v>
       </c>
       <c r="B136" t="n">
         <v>79327</v>
@@ -15257,10 +15257,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470823</v>
+        <v>470869</v>
       </c>
       <c r="R136" t="n">
-        <v>6770705</v>
+        <v>6770702</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15328,13 +15328,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958214</t>
+          <t>https://artportalen.se/Sighting/129958133</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129958228</v>
+        <v>129958151</v>
       </c>
       <c r="B137" t="n">
         <v>79327</v>
@@ -15369,10 +15369,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470813</v>
+        <v>470842</v>
       </c>
       <c r="R137" t="n">
-        <v>6770681</v>
+        <v>6770709</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15440,13 +15440,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958228</t>
+          <t>https://artportalen.se/Sighting/129958151</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129958464</v>
+        <v>129958214</v>
       </c>
       <c r="B138" t="n">
         <v>79327</v>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470822</v>
+        <v>470823</v>
       </c>
       <c r="R138" t="n">
-        <v>6770673</v>
+        <v>6770705</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15552,13 +15552,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958464</t>
+          <t>https://artportalen.se/Sighting/129958214</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129958466</v>
+        <v>129958228</v>
       </c>
       <c r="B139" t="n">
         <v>79327</v>
@@ -15593,10 +15593,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470812</v>
+        <v>470813</v>
       </c>
       <c r="R139" t="n">
-        <v>6770670</v>
+        <v>6770681</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15664,13 +15664,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958466</t>
+          <t>https://artportalen.se/Sighting/129958228</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129958499</v>
+        <v>129958464</v>
       </c>
       <c r="B140" t="n">
         <v>79327</v>
@@ -15705,10 +15705,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470850</v>
+        <v>470822</v>
       </c>
       <c r="R140" t="n">
-        <v>6770690</v>
+        <v>6770673</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15776,13 +15776,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958499</t>
+          <t>https://artportalen.se/Sighting/129958464</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129958545</v>
+        <v>129958466</v>
       </c>
       <c r="B141" t="n">
         <v>79327</v>
@@ -15817,10 +15817,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>470877</v>
+        <v>470812</v>
       </c>
       <c r="R141" t="n">
-        <v>6770687</v>
+        <v>6770670</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15888,13 +15888,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958545</t>
+          <t>https://artportalen.se/Sighting/129958466</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129958694</v>
+        <v>129958499</v>
       </c>
       <c r="B142" t="n">
         <v>79327</v>
@@ -15929,10 +15929,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>470844</v>
+        <v>470850</v>
       </c>
       <c r="R142" t="n">
-        <v>6770699</v>
+        <v>6770690</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16000,13 +16000,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958694</t>
+          <t>https://artportalen.se/Sighting/129958499</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129958706</v>
+        <v>129958545</v>
       </c>
       <c r="B143" t="n">
         <v>79327</v>
@@ -16041,10 +16041,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>470816</v>
+        <v>470877</v>
       </c>
       <c r="R143" t="n">
-        <v>6770646</v>
+        <v>6770687</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16112,13 +16112,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958706</t>
+          <t>https://artportalen.se/Sighting/129958545</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129958754</v>
+        <v>129958694</v>
       </c>
       <c r="B144" t="n">
         <v>79327</v>
@@ -16153,10 +16153,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>470817</v>
+        <v>470844</v>
       </c>
       <c r="R144" t="n">
-        <v>6770608</v>
+        <v>6770699</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16224,13 +16224,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958754</t>
+          <t>https://artportalen.se/Sighting/129958694</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129958775</v>
+        <v>129958706</v>
       </c>
       <c r="B145" t="n">
         <v>79327</v>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>470803</v>
+        <v>470816</v>
       </c>
       <c r="R145" t="n">
-        <v>6770595</v>
+        <v>6770646</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16336,13 +16336,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958775</t>
+          <t>https://artportalen.se/Sighting/129958706</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129958795</v>
+        <v>129958754</v>
       </c>
       <c r="B146" t="n">
         <v>79327</v>
@@ -16377,10 +16377,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>470822</v>
+        <v>470817</v>
       </c>
       <c r="R146" t="n">
-        <v>6770615</v>
+        <v>6770608</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16425,11 +16425,6 @@
           <t>09:55</t>
         </is>
       </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
@@ -16453,13 +16448,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958795</t>
+          <t>https://artportalen.se/Sighting/129958754</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129958800</v>
+        <v>129958775</v>
       </c>
       <c r="B147" t="n">
         <v>79327</v>
@@ -16494,10 +16489,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470858</v>
+        <v>470803</v>
       </c>
       <c r="R147" t="n">
-        <v>6770602</v>
+        <v>6770595</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16565,13 +16560,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958800</t>
+          <t>https://artportalen.se/Sighting/129958775</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129958828</v>
+        <v>129958795</v>
       </c>
       <c r="B148" t="n">
         <v>79327</v>
@@ -16606,10 +16601,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470871</v>
+        <v>470822</v>
       </c>
       <c r="R148" t="n">
-        <v>6770635</v>
+        <v>6770615</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16654,6 +16649,11 @@
           <t>09:55</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -16677,13 +16677,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958828</t>
+          <t>https://artportalen.se/Sighting/129958795</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129958841</v>
+        <v>129958800</v>
       </c>
       <c r="B149" t="n">
         <v>79327</v>
@@ -16718,10 +16718,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>470828</v>
+        <v>470858</v>
       </c>
       <c r="R149" t="n">
-        <v>6770636</v>
+        <v>6770602</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16789,13 +16789,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958841</t>
+          <t>https://artportalen.se/Sighting/129958800</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129958842</v>
+        <v>129958828</v>
       </c>
       <c r="B150" t="n">
         <v>79327</v>
@@ -16830,10 +16830,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>470820</v>
+        <v>470871</v>
       </c>
       <c r="R150" t="n">
-        <v>6770624</v>
+        <v>6770635</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16901,13 +16901,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958842</t>
+          <t>https://artportalen.se/Sighting/129958828</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129958895</v>
+        <v>129958841</v>
       </c>
       <c r="B151" t="n">
         <v>79327</v>
@@ -16942,10 +16942,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>470887</v>
+        <v>470828</v>
       </c>
       <c r="R151" t="n">
-        <v>6770658</v>
+        <v>6770636</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17013,13 +17013,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958895</t>
+          <t>https://artportalen.se/Sighting/129958841</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129958937</v>
+        <v>129958842</v>
       </c>
       <c r="B152" t="n">
         <v>79327</v>
@@ -17054,10 +17054,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>470897</v>
+        <v>470820</v>
       </c>
       <c r="R152" t="n">
-        <v>6770647</v>
+        <v>6770624</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17125,13 +17125,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958937</t>
+          <t>https://artportalen.se/Sighting/129958842</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129959037</v>
+        <v>129958895</v>
       </c>
       <c r="B153" t="n">
         <v>79327</v>
@@ -17166,10 +17166,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>470908</v>
+        <v>470887</v>
       </c>
       <c r="R153" t="n">
-        <v>6770622</v>
+        <v>6770658</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17237,13 +17237,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959037</t>
+          <t>https://artportalen.se/Sighting/129958895</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129959060</v>
+        <v>129958937</v>
       </c>
       <c r="B154" t="n">
         <v>79327</v>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>470926</v>
+        <v>470897</v>
       </c>
       <c r="R154" t="n">
-        <v>6770613</v>
+        <v>6770647</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17349,13 +17349,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959060</t>
+          <t>https://artportalen.se/Sighting/129958937</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129959250</v>
+        <v>129959037</v>
       </c>
       <c r="B155" t="n">
         <v>79327</v>
@@ -17390,10 +17390,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470943</v>
+        <v>470908</v>
       </c>
       <c r="R155" t="n">
-        <v>6770559</v>
+        <v>6770622</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17461,13 +17461,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959250</t>
+          <t>https://artportalen.se/Sighting/129959037</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129959256</v>
+        <v>129959060</v>
       </c>
       <c r="B156" t="n">
         <v>79327</v>
@@ -17502,10 +17502,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>470922</v>
+        <v>470926</v>
       </c>
       <c r="R156" t="n">
-        <v>6770556</v>
+        <v>6770613</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17573,13 +17573,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959256</t>
+          <t>https://artportalen.se/Sighting/129959060</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129959294</v>
+        <v>129959250</v>
       </c>
       <c r="B157" t="n">
         <v>79327</v>
@@ -17614,10 +17614,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>470904</v>
+        <v>470943</v>
       </c>
       <c r="R157" t="n">
-        <v>6770537</v>
+        <v>6770559</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17685,13 +17685,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959294</t>
+          <t>https://artportalen.se/Sighting/129959250</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129959303</v>
+        <v>129959256</v>
       </c>
       <c r="B158" t="n">
         <v>79327</v>
@@ -17726,10 +17726,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470879</v>
+        <v>470922</v>
       </c>
       <c r="R158" t="n">
-        <v>6770545</v>
+        <v>6770556</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17797,13 +17797,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959303</t>
+          <t>https://artportalen.se/Sighting/129959256</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129959375</v>
+        <v>129959294</v>
       </c>
       <c r="B159" t="n">
         <v>79327</v>
@@ -17838,10 +17838,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>470851</v>
+        <v>470904</v>
       </c>
       <c r="R159" t="n">
-        <v>6770520</v>
+        <v>6770537</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17909,13 +17909,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959375</t>
+          <t>https://artportalen.se/Sighting/129959294</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129959389</v>
+        <v>129959303</v>
       </c>
       <c r="B160" t="n">
         <v>79327</v>
@@ -17950,10 +17950,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>470824</v>
+        <v>470879</v>
       </c>
       <c r="R160" t="n">
-        <v>6770523</v>
+        <v>6770545</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18021,13 +18021,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959389</t>
+          <t>https://artportalen.se/Sighting/129959303</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129959479</v>
+        <v>129959375</v>
       </c>
       <c r="B161" t="n">
         <v>79327</v>
@@ -18062,10 +18062,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>470837</v>
+        <v>470851</v>
       </c>
       <c r="R161" t="n">
-        <v>6770498</v>
+        <v>6770520</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18133,13 +18133,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959479</t>
+          <t>https://artportalen.se/Sighting/129959375</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129959501</v>
+        <v>129959389</v>
       </c>
       <c r="B162" t="n">
         <v>79327</v>
@@ -18174,10 +18174,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>470807</v>
+        <v>470824</v>
       </c>
       <c r="R162" t="n">
-        <v>6770491</v>
+        <v>6770523</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18245,13 +18245,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959501</t>
+          <t>https://artportalen.se/Sighting/129959389</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129959519</v>
+        <v>129959479</v>
       </c>
       <c r="B163" t="n">
         <v>79327</v>
@@ -18286,10 +18286,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>470822</v>
+        <v>470837</v>
       </c>
       <c r="R163" t="n">
-        <v>6770452</v>
+        <v>6770498</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18357,13 +18357,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959519</t>
+          <t>https://artportalen.se/Sighting/129959479</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129959692</v>
+        <v>129959501</v>
       </c>
       <c r="B164" t="n">
         <v>79327</v>
@@ -18398,10 +18398,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>470864</v>
+        <v>470807</v>
       </c>
       <c r="R164" t="n">
-        <v>6770438</v>
+        <v>6770491</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18469,13 +18469,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959692</t>
+          <t>https://artportalen.se/Sighting/129959501</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129959740</v>
+        <v>129959519</v>
       </c>
       <c r="B165" t="n">
         <v>79327</v>
@@ -18510,10 +18510,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>470905</v>
+        <v>470822</v>
       </c>
       <c r="R165" t="n">
-        <v>6770435</v>
+        <v>6770452</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18581,13 +18581,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959740</t>
+          <t>https://artportalen.se/Sighting/129959519</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129959772</v>
+        <v>129959692</v>
       </c>
       <c r="B166" t="n">
         <v>79327</v>
@@ -18622,10 +18622,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470900</v>
+        <v>470864</v>
       </c>
       <c r="R166" t="n">
-        <v>6770473</v>
+        <v>6770438</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18693,13 +18693,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959772</t>
+          <t>https://artportalen.se/Sighting/129959692</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129959808</v>
+        <v>129959740</v>
       </c>
       <c r="B167" t="n">
         <v>79327</v>
@@ -18734,10 +18734,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470942</v>
+        <v>470905</v>
       </c>
       <c r="R167" t="n">
-        <v>6770455</v>
+        <v>6770435</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18805,13 +18805,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959808</t>
+          <t>https://artportalen.se/Sighting/129959740</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129959994</v>
+        <v>129959772</v>
       </c>
       <c r="B168" t="n">
         <v>79327</v>
@@ -18846,10 +18846,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>470954</v>
+        <v>470900</v>
       </c>
       <c r="R168" t="n">
-        <v>6770475</v>
+        <v>6770473</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18917,13 +18917,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959994</t>
+          <t>https://artportalen.se/Sighting/129959772</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129960002</v>
+        <v>129959808</v>
       </c>
       <c r="B169" t="n">
         <v>79327</v>
@@ -18958,10 +18958,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>470932</v>
+        <v>470942</v>
       </c>
       <c r="R169" t="n">
-        <v>6770480</v>
+        <v>6770455</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19029,13 +19029,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960002</t>
+          <t>https://artportalen.se/Sighting/129959808</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129960437</v>
+        <v>129959994</v>
       </c>
       <c r="B170" t="n">
         <v>79327</v>
@@ -19070,10 +19070,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>470948</v>
+        <v>470954</v>
       </c>
       <c r="R170" t="n">
-        <v>6770533</v>
+        <v>6770475</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19141,13 +19141,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960437</t>
+          <t>https://artportalen.se/Sighting/129959994</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129960691</v>
+        <v>129960002</v>
       </c>
       <c r="B171" t="n">
         <v>79327</v>
@@ -19182,10 +19182,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>471056</v>
+        <v>470932</v>
       </c>
       <c r="R171" t="n">
-        <v>6770494</v>
+        <v>6770480</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19253,13 +19253,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960691</t>
+          <t>https://artportalen.se/Sighting/129960002</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129960763</v>
+        <v>129960437</v>
       </c>
       <c r="B172" t="n">
         <v>79327</v>
@@ -19294,10 +19294,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>471062</v>
+        <v>470948</v>
       </c>
       <c r="R172" t="n">
-        <v>6770538</v>
+        <v>6770533</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19365,13 +19365,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960763</t>
+          <t>https://artportalen.se/Sighting/129960437</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129960790</v>
+        <v>129960691</v>
       </c>
       <c r="B173" t="n">
         <v>79327</v>
@@ -19406,10 +19406,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471073</v>
+        <v>471056</v>
       </c>
       <c r="R173" t="n">
-        <v>6770551</v>
+        <v>6770494</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19477,13 +19477,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960790</t>
+          <t>https://artportalen.se/Sighting/129960691</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129960823</v>
+        <v>129960763</v>
       </c>
       <c r="B174" t="n">
         <v>79327</v>
@@ -19518,10 +19518,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>471078</v>
+        <v>471062</v>
       </c>
       <c r="R174" t="n">
-        <v>6770561</v>
+        <v>6770538</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19566,11 +19566,6 @@
           <t>09:55</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -19594,13 +19589,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960823</t>
+          <t>https://artportalen.se/Sighting/129960763</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129960843</v>
+        <v>129960790</v>
       </c>
       <c r="B175" t="n">
         <v>79327</v>
@@ -19635,10 +19630,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471097</v>
+        <v>471073</v>
       </c>
       <c r="R175" t="n">
-        <v>6770561</v>
+        <v>6770551</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19706,13 +19701,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960843</t>
+          <t>https://artportalen.se/Sighting/129960790</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129960864</v>
+        <v>129960823</v>
       </c>
       <c r="B176" t="n">
         <v>79327</v>
@@ -19747,10 +19742,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471116</v>
+        <v>471078</v>
       </c>
       <c r="R176" t="n">
-        <v>6770565</v>
+        <v>6770561</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19795,6 +19790,11 @@
           <t>09:55</t>
         </is>
       </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
@@ -19818,13 +19818,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960864</t>
+          <t>https://artportalen.se/Sighting/129960823</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129960884</v>
+        <v>129960843</v>
       </c>
       <c r="B177" t="n">
         <v>79327</v>
@@ -19859,10 +19859,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>471129</v>
+        <v>471097</v>
       </c>
       <c r="R177" t="n">
-        <v>6770567</v>
+        <v>6770561</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19930,13 +19930,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960884</t>
+          <t>https://artportalen.se/Sighting/129960843</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129960891</v>
+        <v>129960864</v>
       </c>
       <c r="B178" t="n">
         <v>79327</v>
@@ -19971,10 +19971,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>471147</v>
+        <v>471116</v>
       </c>
       <c r="R178" t="n">
-        <v>6770575</v>
+        <v>6770565</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20042,13 +20042,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960891</t>
+          <t>https://artportalen.se/Sighting/129960864</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129960901</v>
+        <v>129960884</v>
       </c>
       <c r="B179" t="n">
         <v>79327</v>
@@ -20083,10 +20083,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>471185</v>
+        <v>471129</v>
       </c>
       <c r="R179" t="n">
-        <v>6770590</v>
+        <v>6770567</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20154,13 +20154,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960901</t>
+          <t>https://artportalen.se/Sighting/129960884</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129960929</v>
+        <v>129960891</v>
       </c>
       <c r="B180" t="n">
         <v>79327</v>
@@ -20195,10 +20195,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>471159</v>
+        <v>471147</v>
       </c>
       <c r="R180" t="n">
-        <v>6770613</v>
+        <v>6770575</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20266,13 +20266,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960929</t>
+          <t>https://artportalen.se/Sighting/129960891</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129961603</v>
+        <v>129960901</v>
       </c>
       <c r="B181" t="n">
         <v>79327</v>
@@ -20307,10 +20307,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471262</v>
+        <v>471185</v>
       </c>
       <c r="R181" t="n">
-        <v>6770622</v>
+        <v>6770590</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20378,13 +20378,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961603</t>
+          <t>https://artportalen.se/Sighting/129960901</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129961818</v>
+        <v>129960929</v>
       </c>
       <c r="B182" t="n">
         <v>79327</v>
@@ -20419,10 +20419,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471228</v>
+        <v>471159</v>
       </c>
       <c r="R182" t="n">
-        <v>6770667</v>
+        <v>6770613</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20490,13 +20490,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961818</t>
+          <t>https://artportalen.se/Sighting/129960929</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129961937</v>
+        <v>129961603</v>
       </c>
       <c r="B183" t="n">
         <v>79327</v>
@@ -20531,10 +20531,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>471216</v>
+        <v>471262</v>
       </c>
       <c r="R183" t="n">
-        <v>6770650</v>
+        <v>6770622</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20602,13 +20602,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961937</t>
+          <t>https://artportalen.se/Sighting/129961603</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129962073</v>
+        <v>129961818</v>
       </c>
       <c r="B184" t="n">
         <v>79327</v>
@@ -20643,10 +20643,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>471222</v>
+        <v>471228</v>
       </c>
       <c r="R184" t="n">
-        <v>6770635</v>
+        <v>6770667</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20714,13 +20714,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962073</t>
+          <t>https://artportalen.se/Sighting/129961818</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129962119</v>
+        <v>129961937</v>
       </c>
       <c r="B185" t="n">
         <v>79327</v>
@@ -20755,10 +20755,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>471156</v>
+        <v>471216</v>
       </c>
       <c r="R185" t="n">
-        <v>6770665</v>
+        <v>6770650</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20826,13 +20826,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962119</t>
+          <t>https://artportalen.se/Sighting/129961937</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129962224</v>
+        <v>129962073</v>
       </c>
       <c r="B186" t="n">
         <v>79327</v>
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>471098</v>
+        <v>471222</v>
       </c>
       <c r="R186" t="n">
-        <v>6770634</v>
+        <v>6770635</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20938,13 +20938,13 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962224</t>
+          <t>https://artportalen.se/Sighting/129962073</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129962243</v>
+        <v>129962119</v>
       </c>
       <c r="B187" t="n">
         <v>79327</v>
@@ -20979,10 +20979,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>471074</v>
+        <v>471156</v>
       </c>
       <c r="R187" t="n">
-        <v>6770617</v>
+        <v>6770665</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21050,13 +21050,13 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962243</t>
+          <t>https://artportalen.se/Sighting/129962119</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129962260</v>
+        <v>129962224</v>
       </c>
       <c r="B188" t="n">
         <v>79327</v>
@@ -21091,10 +21091,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>471044</v>
+        <v>471098</v>
       </c>
       <c r="R188" t="n">
-        <v>6770615</v>
+        <v>6770634</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21162,13 +21162,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962260</t>
+          <t>https://artportalen.se/Sighting/129962224</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129962290</v>
+        <v>129962243</v>
       </c>
       <c r="B189" t="n">
         <v>79327</v>
@@ -21203,10 +21203,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>471033</v>
+        <v>471074</v>
       </c>
       <c r="R189" t="n">
-        <v>6770614</v>
+        <v>6770617</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21274,13 +21274,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962290</t>
+          <t>https://artportalen.se/Sighting/129962243</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129962320</v>
+        <v>129962260</v>
       </c>
       <c r="B190" t="n">
         <v>79327</v>
@@ -21315,10 +21315,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>471024</v>
+        <v>471044</v>
       </c>
       <c r="R190" t="n">
-        <v>6770624</v>
+        <v>6770615</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21386,13 +21386,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962320</t>
+          <t>https://artportalen.se/Sighting/129962260</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129962351</v>
+        <v>129962290</v>
       </c>
       <c r="B191" t="n">
         <v>79327</v>
@@ -21427,10 +21427,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>471017</v>
+        <v>471033</v>
       </c>
       <c r="R191" t="n">
-        <v>6770613</v>
+        <v>6770614</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21498,13 +21498,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962351</t>
+          <t>https://artportalen.se/Sighting/129962290</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129962379</v>
+        <v>129962320</v>
       </c>
       <c r="B192" t="n">
         <v>79327</v>
@@ -21539,10 +21539,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>470996</v>
+        <v>471024</v>
       </c>
       <c r="R192" t="n">
-        <v>6770611</v>
+        <v>6770624</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21610,13 +21610,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962379</t>
+          <t>https://artportalen.se/Sighting/129962320</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129962390</v>
+        <v>129962351</v>
       </c>
       <c r="B193" t="n">
         <v>79327</v>
@@ -21651,10 +21651,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>471004</v>
+        <v>471017</v>
       </c>
       <c r="R193" t="n">
-        <v>6770581</v>
+        <v>6770613</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21722,13 +21722,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962390</t>
+          <t>https://artportalen.se/Sighting/129962351</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129962417</v>
+        <v>129962379</v>
       </c>
       <c r="B194" t="n">
         <v>79327</v>
@@ -21763,10 +21763,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>471002</v>
+        <v>470996</v>
       </c>
       <c r="R194" t="n">
-        <v>6770618</v>
+        <v>6770611</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21834,13 +21834,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962417</t>
+          <t>https://artportalen.se/Sighting/129962379</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129962443</v>
+        <v>129962390</v>
       </c>
       <c r="B195" t="n">
         <v>79327</v>
@@ -21875,10 +21875,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>470989</v>
+        <v>471004</v>
       </c>
       <c r="R195" t="n">
-        <v>6770629</v>
+        <v>6770581</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21946,13 +21946,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962443</t>
+          <t>https://artportalen.se/Sighting/129962390</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129962446</v>
+        <v>129962417</v>
       </c>
       <c r="B196" t="n">
         <v>79327</v>
@@ -21987,10 +21987,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>470993</v>
+        <v>471002</v>
       </c>
       <c r="R196" t="n">
-        <v>6770643</v>
+        <v>6770618</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22058,56 +22058,51 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962446</t>
+          <t>https://artportalen.se/Sighting/129962417</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129944452</v>
+        <v>129962443</v>
       </c>
       <c r="B197" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>471330</v>
+        <v>470989</v>
       </c>
       <c r="R197" t="n">
-        <v>6770712</v>
+        <v>6770629</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22134,22 +22129,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22175,56 +22170,51 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944452</t>
+          <t>https://artportalen.se/Sighting/129962443</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129945156</v>
+        <v>129962446</v>
       </c>
       <c r="B198" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>471198</v>
+        <v>470993</v>
       </c>
       <c r="R198" t="n">
-        <v>6770725</v>
+        <v>6770643</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22251,22 +22241,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22292,13 +22282,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945156</t>
+          <t>https://artportalen.se/Sighting/129962446</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129945440</v>
+        <v>129944452</v>
       </c>
       <c r="B199" t="n">
         <v>57950</v>
@@ -22329,7 +22319,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22338,10 +22328,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471189</v>
+        <v>471330</v>
       </c>
       <c r="R199" t="n">
-        <v>6770706</v>
+        <v>6770712</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22409,13 +22399,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945440</t>
+          <t>https://artportalen.se/Sighting/129944452</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129946321</v>
+        <v>129945156</v>
       </c>
       <c r="B200" t="n">
         <v>57950</v>
@@ -22446,7 +22436,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22455,10 +22445,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>470871</v>
+        <v>471198</v>
       </c>
       <c r="R200" t="n">
-        <v>6770635</v>
+        <v>6770725</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22526,13 +22516,13 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946321</t>
+          <t>https://artportalen.se/Sighting/129945156</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129946365</v>
+        <v>129945440</v>
       </c>
       <c r="B201" t="n">
         <v>57950</v>
@@ -22572,10 +22562,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>470910</v>
+        <v>471189</v>
       </c>
       <c r="R201" t="n">
-        <v>6770605</v>
+        <v>6770706</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22643,13 +22633,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946365</t>
+          <t>https://artportalen.se/Sighting/129945440</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129946391</v>
+        <v>129946321</v>
       </c>
       <c r="B202" t="n">
         <v>57950</v>
@@ -22680,7 +22670,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22689,10 +22679,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>470921</v>
+        <v>470871</v>
       </c>
       <c r="R202" t="n">
-        <v>6770579</v>
+        <v>6770635</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22760,13 +22750,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946391</t>
+          <t>https://artportalen.se/Sighting/129946321</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129946436</v>
+        <v>129946365</v>
       </c>
       <c r="B203" t="n">
         <v>57950</v>
@@ -22797,7 +22787,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22806,10 +22796,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>470971</v>
+        <v>470910</v>
       </c>
       <c r="R203" t="n">
-        <v>6770603</v>
+        <v>6770605</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22877,13 +22867,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946436</t>
+          <t>https://artportalen.se/Sighting/129946365</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129954441</v>
+        <v>129946391</v>
       </c>
       <c r="B204" t="n">
         <v>57950</v>
@@ -22923,10 +22913,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>471052</v>
+        <v>470921</v>
       </c>
       <c r="R204" t="n">
-        <v>6770696</v>
+        <v>6770579</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22953,22 +22943,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22994,13 +22984,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954441</t>
+          <t>https://artportalen.se/Sighting/129946391</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129957253</v>
+        <v>129946436</v>
       </c>
       <c r="B205" t="n">
         <v>57950</v>
@@ -23031,7 +23021,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -23040,10 +23030,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>470916</v>
+        <v>470971</v>
       </c>
       <c r="R205" t="n">
-        <v>6770721</v>
+        <v>6770603</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23070,22 +23060,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23111,13 +23101,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957253</t>
+          <t>https://artportalen.se/Sighting/129946436</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129958691</v>
+        <v>129954441</v>
       </c>
       <c r="B206" t="n">
         <v>57950</v>
@@ -23157,10 +23147,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470844</v>
+        <v>471052</v>
       </c>
       <c r="R206" t="n">
-        <v>6770699</v>
+        <v>6770696</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23228,13 +23218,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958691</t>
+          <t>https://artportalen.se/Sighting/129954441</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129959434</v>
+        <v>129957253</v>
       </c>
       <c r="B207" t="n">
         <v>57950</v>
@@ -23274,10 +23264,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470824</v>
+        <v>470916</v>
       </c>
       <c r="R207" t="n">
-        <v>6770523</v>
+        <v>6770721</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23345,13 +23335,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959434</t>
+          <t>https://artportalen.se/Sighting/129957253</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129959567</v>
+        <v>129958691</v>
       </c>
       <c r="B208" t="n">
         <v>57950</v>
@@ -23391,10 +23381,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470822</v>
+        <v>470844</v>
       </c>
       <c r="R208" t="n">
-        <v>6770452</v>
+        <v>6770699</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23462,13 +23452,13 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959567</t>
+          <t>https://artportalen.se/Sighting/129958691</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129959730</v>
+        <v>129959434</v>
       </c>
       <c r="B209" t="n">
         <v>57950</v>
@@ -23499,7 +23489,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -23508,10 +23498,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>470868</v>
+        <v>470824</v>
       </c>
       <c r="R209" t="n">
-        <v>6770431</v>
+        <v>6770523</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23579,13 +23569,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959730</t>
+          <t>https://artportalen.se/Sighting/129959434</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129959870</v>
+        <v>129959567</v>
       </c>
       <c r="B210" t="n">
         <v>57950</v>
@@ -23616,7 +23606,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -23625,10 +23615,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>470952</v>
+        <v>470822</v>
       </c>
       <c r="R210" t="n">
-        <v>6770464</v>
+        <v>6770452</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23696,13 +23686,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959870</t>
+          <t>https://artportalen.se/Sighting/129959567</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129960642</v>
+        <v>129959730</v>
       </c>
       <c r="B211" t="n">
         <v>57950</v>
@@ -23742,10 +23732,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>471025</v>
+        <v>470868</v>
       </c>
       <c r="R211" t="n">
-        <v>6770488</v>
+        <v>6770431</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23813,13 +23803,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960642</t>
+          <t>https://artportalen.se/Sighting/129959730</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129962343</v>
+        <v>129959870</v>
       </c>
       <c r="B212" t="n">
         <v>57950</v>
@@ -23850,7 +23840,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -23859,10 +23849,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>471017</v>
+        <v>470952</v>
       </c>
       <c r="R212" t="n">
-        <v>6770613</v>
+        <v>6770464</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23930,13 +23920,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962343</t>
+          <t>https://artportalen.se/Sighting/129959870</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129962374</v>
+        <v>129960642</v>
       </c>
       <c r="B213" t="n">
         <v>57950</v>
@@ -23967,7 +23957,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23976,10 +23966,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>470996</v>
+        <v>471025</v>
       </c>
       <c r="R213" t="n">
-        <v>6770611</v>
+        <v>6770488</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24047,13 +24037,13 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962374</t>
+          <t>https://artportalen.se/Sighting/129960642</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129962430</v>
+        <v>129962343</v>
       </c>
       <c r="B214" t="n">
         <v>57950</v>
@@ -24084,7 +24074,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -24093,10 +24083,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>470989</v>
+        <v>471017</v>
       </c>
       <c r="R214" t="n">
-        <v>6770629</v>
+        <v>6770613</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24164,48 +24154,44 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962430</t>
+          <t>https://artportalen.se/Sighting/129962343</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129944878</v>
+        <v>129962374</v>
       </c>
       <c r="B215" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -24214,13 +24200,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471258</v>
+        <v>470996</v>
       </c>
       <c r="R215" t="n">
-        <v>6770712</v>
+        <v>6770611</v>
       </c>
       <c r="S215" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24244,22 +24230,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24285,16 +24271,16 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944878</t>
+          <t>https://artportalen.se/Sighting/129962374</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129944062</v>
+        <v>129962430</v>
       </c>
       <c r="B216" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24302,27 +24288,27 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -24331,10 +24317,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471432</v>
+        <v>470989</v>
       </c>
       <c r="R216" t="n">
-        <v>6770716</v>
+        <v>6770629</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24361,22 +24347,22 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24402,44 +24388,48 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944062</t>
+          <t>https://artportalen.se/Sighting/129962430</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129944158</v>
+        <v>129944878</v>
       </c>
       <c r="B217" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -24448,13 +24438,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>471363</v>
+        <v>471258</v>
       </c>
       <c r="R217" t="n">
-        <v>6770736</v>
+        <v>6770712</v>
       </c>
       <c r="S217" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -24519,13 +24509,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944158</t>
+          <t>https://artportalen.se/Sighting/129944878</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129944454</v>
+        <v>129944062</v>
       </c>
       <c r="B218" t="n">
         <v>8455</v>
@@ -24554,16 +24544,21 @@
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>471330</v>
+        <v>471432</v>
       </c>
       <c r="R218" t="n">
-        <v>6770712</v>
+        <v>6770716</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24631,13 +24626,13 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944454</t>
+          <t>https://artportalen.se/Sighting/129944062</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129945161</v>
+        <v>129944158</v>
       </c>
       <c r="B219" t="n">
         <v>8455</v>
@@ -24677,10 +24672,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471198</v>
+        <v>471363</v>
       </c>
       <c r="R219" t="n">
-        <v>6770725</v>
+        <v>6770736</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24748,13 +24743,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945161</t>
+          <t>https://artportalen.se/Sighting/129944158</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129945444</v>
+        <v>129944454</v>
       </c>
       <c r="B220" t="n">
         <v>8455</v>
@@ -24783,21 +24778,16 @@
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>471189</v>
+        <v>471330</v>
       </c>
       <c r="R220" t="n">
-        <v>6770706</v>
+        <v>6770712</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24865,13 +24855,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945444</t>
+          <t>https://artportalen.se/Sighting/129944454</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129946047</v>
+        <v>129945161</v>
       </c>
       <c r="B221" t="n">
         <v>8455</v>
@@ -24900,16 +24890,21 @@
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>471161</v>
+        <v>471198</v>
       </c>
       <c r="R221" t="n">
-        <v>6770705</v>
+        <v>6770725</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24977,13 +24972,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946047</t>
+          <t>https://artportalen.se/Sighting/129945161</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129946334</v>
+        <v>129945444</v>
       </c>
       <c r="B222" t="n">
         <v>8455</v>
@@ -25023,10 +25018,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470871</v>
+        <v>471189</v>
       </c>
       <c r="R222" t="n">
-        <v>6770635</v>
+        <v>6770706</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25094,13 +25089,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946334</t>
+          <t>https://artportalen.se/Sighting/129945444</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129946444</v>
+        <v>129946047</v>
       </c>
       <c r="B223" t="n">
         <v>8455</v>
@@ -25129,21 +25124,16 @@
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>470971</v>
+        <v>471161</v>
       </c>
       <c r="R223" t="n">
-        <v>6770603</v>
+        <v>6770705</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25211,13 +25201,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946444</t>
+          <t>https://artportalen.se/Sighting/129946047</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129954662</v>
+        <v>129946334</v>
       </c>
       <c r="B224" t="n">
         <v>8455</v>
@@ -25257,10 +25247,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470941</v>
+        <v>470871</v>
       </c>
       <c r="R224" t="n">
-        <v>6770708</v>
+        <v>6770635</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25287,22 +25277,22 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25328,13 +25318,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954662</t>
+          <t>https://artportalen.se/Sighting/129946334</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129958131</v>
+        <v>129946444</v>
       </c>
       <c r="B225" t="n">
         <v>8455</v>
@@ -25374,10 +25364,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470869</v>
+        <v>470971</v>
       </c>
       <c r="R225" t="n">
-        <v>6770702</v>
+        <v>6770603</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25404,22 +25394,22 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25445,13 +25435,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958131</t>
+          <t>https://artportalen.se/Sighting/129946444</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129958199</v>
+        <v>129954662</v>
       </c>
       <c r="B226" t="n">
         <v>8455</v>
@@ -25491,10 +25481,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>470823</v>
+        <v>470941</v>
       </c>
       <c r="R226" t="n">
-        <v>6770705</v>
+        <v>6770708</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25562,13 +25552,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958199</t>
+          <t>https://artportalen.se/Sighting/129954662</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129958686</v>
+        <v>129958131</v>
       </c>
       <c r="B227" t="n">
         <v>8455</v>
@@ -25608,10 +25598,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>470844</v>
+        <v>470869</v>
       </c>
       <c r="R227" t="n">
-        <v>6770699</v>
+        <v>6770702</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25679,13 +25669,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958686</t>
+          <t>https://artportalen.se/Sighting/129958131</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129959110</v>
+        <v>129958199</v>
       </c>
       <c r="B228" t="n">
         <v>8455</v>
@@ -25725,10 +25715,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470926</v>
+        <v>470823</v>
       </c>
       <c r="R228" t="n">
-        <v>6770613</v>
+        <v>6770705</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25796,13 +25786,13 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959110</t>
+          <t>https://artportalen.se/Sighting/129958199</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129959223</v>
+        <v>129958686</v>
       </c>
       <c r="B229" t="n">
         <v>8455</v>
@@ -25842,10 +25832,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>470921</v>
+        <v>470844</v>
       </c>
       <c r="R229" t="n">
-        <v>6770579</v>
+        <v>6770699</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25913,13 +25903,13 @@
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959223</t>
+          <t>https://artportalen.se/Sighting/129958686</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129959285</v>
+        <v>129959110</v>
       </c>
       <c r="B230" t="n">
         <v>8455</v>
@@ -25959,10 +25949,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>470922</v>
+        <v>470926</v>
       </c>
       <c r="R230" t="n">
-        <v>6770556</v>
+        <v>6770613</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26030,13 +26020,13 @@
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959285</t>
+          <t>https://artportalen.se/Sighting/129959110</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129959441</v>
+        <v>129959223</v>
       </c>
       <c r="B231" t="n">
         <v>8455</v>
@@ -26076,10 +26066,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>470824</v>
+        <v>470921</v>
       </c>
       <c r="R231" t="n">
-        <v>6770523</v>
+        <v>6770579</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26147,13 +26137,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959441</t>
+          <t>https://artportalen.se/Sighting/129959223</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129959579</v>
+        <v>129959285</v>
       </c>
       <c r="B232" t="n">
         <v>8455</v>
@@ -26193,10 +26183,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>470822</v>
+        <v>470922</v>
       </c>
       <c r="R232" t="n">
-        <v>6770452</v>
+        <v>6770556</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26264,13 +26254,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959579</t>
+          <t>https://artportalen.se/Sighting/129959285</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129959710</v>
+        <v>129959441</v>
       </c>
       <c r="B233" t="n">
         <v>8455</v>
@@ -26310,10 +26300,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>470864</v>
+        <v>470824</v>
       </c>
       <c r="R233" t="n">
-        <v>6770438</v>
+        <v>6770523</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26381,13 +26371,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959710</t>
+          <t>https://artportalen.se/Sighting/129959441</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129959735</v>
+        <v>129959579</v>
       </c>
       <c r="B234" t="n">
         <v>8455</v>
@@ -26427,10 +26417,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>470868</v>
+        <v>470822</v>
       </c>
       <c r="R234" t="n">
-        <v>6770431</v>
+        <v>6770452</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26498,13 +26488,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959735</t>
+          <t>https://artportalen.se/Sighting/129959579</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129959924</v>
+        <v>129959710</v>
       </c>
       <c r="B235" t="n">
         <v>8455</v>
@@ -26544,10 +26534,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>470944</v>
+        <v>470864</v>
       </c>
       <c r="R235" t="n">
-        <v>6770458</v>
+        <v>6770438</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26615,13 +26605,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959924</t>
+          <t>https://artportalen.se/Sighting/129959710</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129960514</v>
+        <v>129959735</v>
       </c>
       <c r="B236" t="n">
         <v>8455</v>
@@ -26661,13 +26651,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>470976</v>
+        <v>470868</v>
       </c>
       <c r="R236" t="n">
-        <v>6770536</v>
+        <v>6770431</v>
       </c>
       <c r="S236" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26732,13 +26722,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960514</t>
+          <t>https://artportalen.se/Sighting/129959735</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129960657</v>
+        <v>129959924</v>
       </c>
       <c r="B237" t="n">
         <v>8455</v>
@@ -26778,10 +26768,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>471025</v>
+        <v>470944</v>
       </c>
       <c r="R237" t="n">
-        <v>6770488</v>
+        <v>6770458</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26849,13 +26839,13 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960657</t>
+          <t>https://artportalen.se/Sighting/129959924</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129960746</v>
+        <v>129960514</v>
       </c>
       <c r="B238" t="n">
         <v>8455</v>
@@ -26895,13 +26885,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>471053</v>
+        <v>470976</v>
       </c>
       <c r="R238" t="n">
-        <v>6770528</v>
+        <v>6770536</v>
       </c>
       <c r="S238" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -26966,13 +26956,13 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960746</t>
+          <t>https://artportalen.se/Sighting/129960514</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129960827</v>
+        <v>129960657</v>
       </c>
       <c r="B239" t="n">
         <v>8455</v>
@@ -27012,10 +27002,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>471078</v>
+        <v>471025</v>
       </c>
       <c r="R239" t="n">
-        <v>6770561</v>
+        <v>6770488</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27083,13 +27073,13 @@
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960827</t>
+          <t>https://artportalen.se/Sighting/129960657</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129961109</v>
+        <v>129960746</v>
       </c>
       <c r="B240" t="n">
         <v>8455</v>
@@ -27129,10 +27119,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>471175</v>
+        <v>471053</v>
       </c>
       <c r="R240" t="n">
-        <v>6770631</v>
+        <v>6770528</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27200,13 +27190,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961109</t>
+          <t>https://artportalen.se/Sighting/129960746</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129962346</v>
+        <v>129960827</v>
       </c>
       <c r="B241" t="n">
         <v>8455</v>
@@ -27246,10 +27236,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>471017</v>
+        <v>471078</v>
       </c>
       <c r="R241" t="n">
-        <v>6770613</v>
+        <v>6770561</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27317,13 +27307,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962346</t>
+          <t>https://artportalen.se/Sighting/129960827</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129962376</v>
+        <v>129961109</v>
       </c>
       <c r="B242" t="n">
         <v>8455</v>
@@ -27363,10 +27353,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>470996</v>
+        <v>471175</v>
       </c>
       <c r="R242" t="n">
-        <v>6770611</v>
+        <v>6770631</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27434,13 +27424,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962376</t>
+          <t>https://artportalen.se/Sighting/129961109</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129962436</v>
+        <v>129962346</v>
       </c>
       <c r="B243" t="n">
         <v>8455</v>
@@ -27480,10 +27470,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>470989</v>
+        <v>471017</v>
       </c>
       <c r="R243" t="n">
-        <v>6770629</v>
+        <v>6770613</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27551,57 +27541,59 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962436</t>
+          <t>https://artportalen.se/Sighting/129962346</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129271581</v>
+        <v>129962376</v>
       </c>
       <c r="B244" t="n">
-        <v>93228</v>
+        <v>8455</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>232140</v>
+        <v>106545</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>470835</v>
+        <v>470996</v>
       </c>
       <c r="R244" t="n">
-        <v>6770662</v>
+        <v>6770611</v>
       </c>
       <c r="S244" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27625,12 +27617,22 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27639,72 +27641,76 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
-      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129271581</t>
+          <t>https://artportalen.se/Sighting/129962376</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>96714923</v>
+        <v>129962436</v>
       </c>
       <c r="B245" t="n">
-        <v>91402</v>
+        <v>8455</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>256703</v>
+        <v>106545</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>470876</v>
+        <v>470989</v>
       </c>
       <c r="R245" t="n">
-        <v>6770446</v>
+        <v>6770629</v>
       </c>
       <c r="S245" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27728,12 +27734,22 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27748,62 +27764,65 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714923</t>
+          <t>https://artportalen.se/Sighting/129962436</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>96714929</v>
+        <v>129271581</v>
       </c>
       <c r="B246" t="n">
-        <v>91402</v>
+        <v>93228</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>256703</v>
+        <v>232140</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>471113</v>
+        <v>470835</v>
       </c>
       <c r="R246" t="n">
-        <v>6770726</v>
+        <v>6770662</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -27830,12 +27849,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -27844,30 +27863,31 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714929</t>
+          <t>https://artportalen.se/Sighting/129271581</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>96714933</v>
+        <v>96714923</v>
       </c>
       <c r="B247" t="n">
         <v>91402</v>
@@ -27902,10 +27922,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>470806</v>
+        <v>470876</v>
       </c>
       <c r="R247" t="n">
-        <v>6770695</v>
+        <v>6770446</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -27963,13 +27983,13 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714933</t>
+          <t>https://artportalen.se/Sighting/96714923</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>96714941</v>
+        <v>96714929</v>
       </c>
       <c r="B248" t="n">
         <v>91402</v>
@@ -28004,10 +28024,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>471105</v>
+        <v>471113</v>
       </c>
       <c r="R248" t="n">
-        <v>6770716</v>
+        <v>6770726</v>
       </c>
       <c r="S248" t="n">
         <v>25</v>
@@ -28065,13 +28085,13 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714941</t>
+          <t>https://artportalen.se/Sighting/96714929</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>96714946</v>
+        <v>96714933</v>
       </c>
       <c r="B249" t="n">
         <v>91402</v>
@@ -28106,10 +28126,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>471072</v>
+        <v>470806</v>
       </c>
       <c r="R249" t="n">
-        <v>6770716</v>
+        <v>6770695</v>
       </c>
       <c r="S249" t="n">
         <v>25</v>
@@ -28167,13 +28187,13 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714946</t>
+          <t>https://artportalen.se/Sighting/96714933</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>96714952</v>
+        <v>96714941</v>
       </c>
       <c r="B250" t="n">
         <v>91402</v>
@@ -28208,10 +28228,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>470920</v>
+        <v>471105</v>
       </c>
       <c r="R250" t="n">
-        <v>6770687</v>
+        <v>6770716</v>
       </c>
       <c r="S250" t="n">
         <v>25</v>
@@ -28269,13 +28289,13 @@
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714952</t>
+          <t>https://artportalen.se/Sighting/96714941</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>96714953</v>
+        <v>96714946</v>
       </c>
       <c r="B251" t="n">
         <v>91402</v>
@@ -28310,10 +28330,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>471086</v>
+        <v>471072</v>
       </c>
       <c r="R251" t="n">
-        <v>6770698</v>
+        <v>6770716</v>
       </c>
       <c r="S251" t="n">
         <v>25</v>
@@ -28371,13 +28391,13 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714953</t>
+          <t>https://artportalen.se/Sighting/96714946</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>96714960</v>
+        <v>96714952</v>
       </c>
       <c r="B252" t="n">
         <v>91402</v>
@@ -28412,10 +28432,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>471091</v>
+        <v>470920</v>
       </c>
       <c r="R252" t="n">
-        <v>6770723</v>
+        <v>6770687</v>
       </c>
       <c r="S252" t="n">
         <v>25</v>
@@ -28473,13 +28493,13 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714960</t>
+          <t>https://artportalen.se/Sighting/96714952</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>96714973</v>
+        <v>96714953</v>
       </c>
       <c r="B253" t="n">
         <v>91402</v>
@@ -28514,10 +28534,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>471080</v>
+        <v>471086</v>
       </c>
       <c r="R253" t="n">
-        <v>6770598</v>
+        <v>6770698</v>
       </c>
       <c r="S253" t="n">
         <v>25</v>
@@ -28575,13 +28595,13 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714973</t>
+          <t>https://artportalen.se/Sighting/96714953</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>96714981</v>
+        <v>96714960</v>
       </c>
       <c r="B254" t="n">
         <v>91402</v>
@@ -28616,10 +28636,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>471483</v>
+        <v>471091</v>
       </c>
       <c r="R254" t="n">
-        <v>6770715</v>
+        <v>6770723</v>
       </c>
       <c r="S254" t="n">
         <v>25</v>
@@ -28677,13 +28697,13 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714981</t>
+          <t>https://artportalen.se/Sighting/96714960</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>96715005</v>
+        <v>96714973</v>
       </c>
       <c r="B255" t="n">
         <v>91402</v>
@@ -28718,10 +28738,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>470830</v>
+        <v>471080</v>
       </c>
       <c r="R255" t="n">
-        <v>6770666</v>
+        <v>6770598</v>
       </c>
       <c r="S255" t="n">
         <v>25</v>
@@ -28779,13 +28799,13 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715005</t>
+          <t>https://artportalen.se/Sighting/96714973</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>96715010</v>
+        <v>96714981</v>
       </c>
       <c r="B256" t="n">
         <v>91402</v>
@@ -28820,10 +28840,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>471253</v>
+        <v>471483</v>
       </c>
       <c r="R256" t="n">
-        <v>6770676</v>
+        <v>6770715</v>
       </c>
       <c r="S256" t="n">
         <v>25</v>
@@ -28880,6 +28900,210 @@
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714981</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>96715005</v>
+      </c>
+      <c r="B257" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Bonäsheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>470830</v>
+      </c>
+      <c r="R257" t="n">
+        <v>6770666</v>
+      </c>
+      <c r="S257" t="n">
+        <v>25</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715005</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>96715010</v>
+      </c>
+      <c r="B258" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Bonäsheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>471253</v>
+      </c>
+      <c r="R258" t="n">
+        <v>6770676</v>
+      </c>
+      <c r="S258" t="n">
+        <v>25</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96715010</t>
         </is>
@@ -29142,6 +29366,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ258"/>
+  <dimension ref="A1:AZ256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6997,48 +6997,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136837910</v>
+        <v>96714971</v>
       </c>
       <c r="B62" t="n">
-        <v>93416</v>
+        <v>93201</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bengttjärnen, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470909</v>
+        <v>470825</v>
       </c>
       <c r="R62" t="n">
-        <v>6770448</v>
+        <v>6770664</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7062,22 +7062,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7092,49 +7082,49 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Uno Skog, Andreas Öster</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837910</t>
+          <t>https://artportalen.se/Sighting/96714971</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>96714971</v>
+        <v>96714979</v>
       </c>
       <c r="B63" t="n">
-        <v>93201</v>
+        <v>92841</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4365</v>
+        <v>4745</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7144,10 +7134,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>470825</v>
+        <v>471064</v>
       </c>
       <c r="R63" t="n">
-        <v>6770664</v>
+        <v>6770563</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7205,16 +7195,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714971</t>
+          <t>https://artportalen.se/Sighting/96714979</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>96714979</v>
+        <v>129943849</v>
       </c>
       <c r="B64" t="n">
-        <v>92841</v>
+        <v>91930</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7222,37 +7212,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4745</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471064</v>
+        <v>471451</v>
       </c>
       <c r="R64" t="n">
-        <v>6770563</v>
+        <v>6770706</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7276,12 +7270,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7296,24 +7300,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714979</t>
+          <t>https://artportalen.se/Sighting/129943849</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129943849</v>
+        <v>129944262</v>
       </c>
       <c r="B65" t="n">
         <v>91930</v>
@@ -7352,10 +7356,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471451</v>
+        <v>471369</v>
       </c>
       <c r="R65" t="n">
-        <v>6770706</v>
+        <v>6770686</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7423,13 +7427,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943849</t>
+          <t>https://artportalen.se/Sighting/129944262</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129944262</v>
+        <v>129959667</v>
       </c>
       <c r="B66" t="n">
         <v>91930</v>
@@ -7459,7 +7463,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7468,10 +7472,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471369</v>
+        <v>470864</v>
       </c>
       <c r="R66" t="n">
-        <v>6770686</v>
+        <v>6770438</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7498,22 +7502,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7539,16 +7543,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944262</t>
+          <t>https://artportalen.se/Sighting/129959667</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129959667</v>
+        <v>96714915</v>
       </c>
       <c r="B67" t="n">
-        <v>91930</v>
+        <v>93235</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7556,41 +7560,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>470864</v>
+        <v>471343</v>
       </c>
       <c r="R67" t="n">
-        <v>6770438</v>
+        <v>6770659</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7614,22 +7614,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7644,24 +7634,24 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959667</t>
+          <t>https://artportalen.se/Sighting/96714915</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>96714915</v>
+        <v>96714991</v>
       </c>
       <c r="B68" t="n">
         <v>93235</v>
@@ -7696,10 +7686,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471343</v>
+        <v>470824</v>
       </c>
       <c r="R68" t="n">
-        <v>6770659</v>
+        <v>6770660</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7757,54 +7747,54 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714915</t>
+          <t>https://artportalen.se/Sighting/96714991</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>96714991</v>
+        <v>136837813</v>
       </c>
       <c r="B69" t="n">
-        <v>93235</v>
+        <v>93400</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>6055</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bengttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470824</v>
+        <v>470979</v>
       </c>
       <c r="R69" t="n">
-        <v>6770660</v>
+        <v>6770615</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7828,12 +7818,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7848,27 +7838,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714991</t>
+          <t>https://artportalen.se/Sighting/136837813</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136836580</v>
+        <v>96714961</v>
       </c>
       <c r="B70" t="n">
-        <v>93400</v>
+        <v>90691</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7876,37 +7866,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6055</v>
+        <v>6276</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bengttjärnen, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>470971</v>
+        <v>471372</v>
       </c>
       <c r="R70" t="n">
-        <v>6770613</v>
+        <v>6770686</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7930,22 +7920,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7960,27 +7940,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136836580</t>
+          <t>https://artportalen.se/Sighting/96714961</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136837813</v>
+        <v>96715014</v>
       </c>
       <c r="B71" t="n">
-        <v>93400</v>
+        <v>90691</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7988,37 +7968,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6055</v>
+        <v>6276</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bengttjärnen, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470979</v>
+        <v>470841</v>
       </c>
       <c r="R71" t="n">
-        <v>6770615</v>
+        <v>6770558</v>
       </c>
       <c r="S71" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8042,12 +8022,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8062,27 +8042,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837813</t>
+          <t>https://artportalen.se/Sighting/96715014</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>96714961</v>
+        <v>96715007</v>
       </c>
       <c r="B72" t="n">
-        <v>90691</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8090,21 +8070,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6276</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8114,10 +8094,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471372</v>
+        <v>471383</v>
       </c>
       <c r="R72" t="n">
-        <v>6770686</v>
+        <v>6770715</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8175,16 +8155,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714961</t>
+          <t>https://artportalen.se/Sighting/96715007</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>96715014</v>
+        <v>129943529</v>
       </c>
       <c r="B73" t="n">
-        <v>90691</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8192,37 +8172,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6276</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470841</v>
+        <v>471492</v>
       </c>
       <c r="R73" t="n">
-        <v>6770558</v>
+        <v>6770712</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8246,12 +8226,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8266,24 +8256,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715014</t>
+          <t>https://artportalen.se/Sighting/129943529</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>96715007</v>
+        <v>129943541</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8314,17 +8304,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471383</v>
+        <v>471478</v>
       </c>
       <c r="R74" t="n">
-        <v>6770715</v>
+        <v>6770707</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8348,12 +8338,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8368,24 +8368,24 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715007</t>
+          <t>https://artportalen.se/Sighting/129943541</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129943529</v>
+        <v>129943580</v>
       </c>
       <c r="B75" t="n">
         <v>79327</v>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471492</v>
+        <v>471468</v>
       </c>
       <c r="R75" t="n">
-        <v>6770712</v>
+        <v>6770744</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8491,13 +8491,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943529</t>
+          <t>https://artportalen.se/Sighting/129943580</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129943541</v>
+        <v>129943763</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471478</v>
+        <v>471466</v>
       </c>
       <c r="R76" t="n">
-        <v>6770707</v>
+        <v>6770713</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8603,13 +8603,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943541</t>
+          <t>https://artportalen.se/Sighting/129943763</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129943580</v>
+        <v>129943809</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471468</v>
+        <v>471447</v>
       </c>
       <c r="R77" t="n">
-        <v>6770744</v>
+        <v>6770716</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8715,13 +8715,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943580</t>
+          <t>https://artportalen.se/Sighting/129943809</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129943763</v>
+        <v>129943855</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471466</v>
+        <v>471451</v>
       </c>
       <c r="R78" t="n">
-        <v>6770713</v>
+        <v>6770706</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8827,13 +8827,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943763</t>
+          <t>https://artportalen.se/Sighting/129943855</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129943809</v>
+        <v>129943914</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -8868,10 +8868,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471447</v>
+        <v>471432</v>
       </c>
       <c r="R79" t="n">
-        <v>6770716</v>
+        <v>6770701</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8939,13 +8939,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943809</t>
+          <t>https://artportalen.se/Sighting/129943914</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129943855</v>
+        <v>129943999</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471451</v>
+        <v>471428</v>
       </c>
       <c r="R80" t="n">
-        <v>6770706</v>
+        <v>6770747</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9051,13 +9051,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943855</t>
+          <t>https://artportalen.se/Sighting/129943999</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129943914</v>
+        <v>129944026</v>
       </c>
       <c r="B81" t="n">
         <v>79327</v>
@@ -9092,10 +9092,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471432</v>
+        <v>471422</v>
       </c>
       <c r="R81" t="n">
-        <v>6770701</v>
+        <v>6770745</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9163,13 +9163,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943914</t>
+          <t>https://artportalen.se/Sighting/129944026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129943999</v>
+        <v>129944037</v>
       </c>
       <c r="B82" t="n">
         <v>79327</v>
@@ -9204,10 +9204,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471428</v>
+        <v>471417</v>
       </c>
       <c r="R82" t="n">
-        <v>6770747</v>
+        <v>6770738</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9275,13 +9275,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943999</t>
+          <t>https://artportalen.se/Sighting/129944037</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944026</v>
+        <v>129944164</v>
       </c>
       <c r="B83" t="n">
         <v>79327</v>
@@ -9316,10 +9316,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471422</v>
+        <v>471363</v>
       </c>
       <c r="R83" t="n">
-        <v>6770745</v>
+        <v>6770736</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9387,13 +9387,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944026</t>
+          <t>https://artportalen.se/Sighting/129944164</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944037</v>
+        <v>129944178</v>
       </c>
       <c r="B84" t="n">
         <v>79327</v>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471417</v>
+        <v>471372</v>
       </c>
       <c r="R84" t="n">
-        <v>6770738</v>
+        <v>6770719</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9499,13 +9499,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944037</t>
+          <t>https://artportalen.se/Sighting/129944178</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129944164</v>
+        <v>129944210</v>
       </c>
       <c r="B85" t="n">
         <v>79327</v>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471363</v>
+        <v>471390</v>
       </c>
       <c r="R85" t="n">
-        <v>6770736</v>
+        <v>6770705</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,13 +9611,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944164</t>
+          <t>https://artportalen.se/Sighting/129944210</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129944178</v>
+        <v>129944228</v>
       </c>
       <c r="B86" t="n">
         <v>79327</v>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471372</v>
+        <v>471390</v>
       </c>
       <c r="R86" t="n">
-        <v>6770719</v>
+        <v>6770693</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9723,13 +9723,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944178</t>
+          <t>https://artportalen.se/Sighting/129944228</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129944210</v>
+        <v>129944311</v>
       </c>
       <c r="B87" t="n">
         <v>79327</v>
@@ -9764,10 +9764,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471390</v>
+        <v>471369</v>
       </c>
       <c r="R87" t="n">
-        <v>6770705</v>
+        <v>6770686</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9835,13 +9835,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944210</t>
+          <t>https://artportalen.se/Sighting/129944311</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129944228</v>
+        <v>129944355</v>
       </c>
       <c r="B88" t="n">
         <v>79327</v>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471390</v>
+        <v>471342</v>
       </c>
       <c r="R88" t="n">
-        <v>6770693</v>
+        <v>6770682</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9947,13 +9947,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944228</t>
+          <t>https://artportalen.se/Sighting/129944355</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129944311</v>
+        <v>129944466</v>
       </c>
       <c r="B89" t="n">
         <v>79327</v>
@@ -9988,10 +9988,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471369</v>
+        <v>471322</v>
       </c>
       <c r="R89" t="n">
-        <v>6770686</v>
+        <v>6770702</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10059,13 +10059,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944311</t>
+          <t>https://artportalen.se/Sighting/129944466</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129944355</v>
+        <v>129944473</v>
       </c>
       <c r="B90" t="n">
         <v>79327</v>
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471342</v>
+        <v>471328</v>
       </c>
       <c r="R90" t="n">
-        <v>6770682</v>
+        <v>6770726</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10171,13 +10171,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944355</t>
+          <t>https://artportalen.se/Sighting/129944473</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129944466</v>
+        <v>129944488</v>
       </c>
       <c r="B91" t="n">
         <v>79327</v>
@@ -10212,10 +10212,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471322</v>
+        <v>471318</v>
       </c>
       <c r="R91" t="n">
-        <v>6770702</v>
+        <v>6770729</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10283,13 +10283,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944466</t>
+          <t>https://artportalen.se/Sighting/129944488</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129944473</v>
+        <v>129944495</v>
       </c>
       <c r="B92" t="n">
         <v>79327</v>
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471328</v>
+        <v>471288</v>
       </c>
       <c r="R92" t="n">
-        <v>6770726</v>
+        <v>6770728</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10395,13 +10395,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944473</t>
+          <t>https://artportalen.se/Sighting/129944495</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129944488</v>
+        <v>129944523</v>
       </c>
       <c r="B93" t="n">
         <v>79327</v>
@@ -10436,10 +10436,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471318</v>
+        <v>471303</v>
       </c>
       <c r="R93" t="n">
-        <v>6770729</v>
+        <v>6770699</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10507,13 +10507,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944488</t>
+          <t>https://artportalen.se/Sighting/129944523</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129944495</v>
+        <v>129944544</v>
       </c>
       <c r="B94" t="n">
         <v>79327</v>
@@ -10548,10 +10548,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471288</v>
+        <v>471330</v>
       </c>
       <c r="R94" t="n">
-        <v>6770728</v>
+        <v>6770712</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10619,13 +10619,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944495</t>
+          <t>https://artportalen.se/Sighting/129944544</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129944523</v>
+        <v>129944592</v>
       </c>
       <c r="B95" t="n">
         <v>79327</v>
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471303</v>
+        <v>471313</v>
       </c>
       <c r="R95" t="n">
-        <v>6770699</v>
+        <v>6770688</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10731,13 +10731,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944523</t>
+          <t>https://artportalen.se/Sighting/129944592</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129944544</v>
+        <v>129944756</v>
       </c>
       <c r="B96" t="n">
         <v>79327</v>
@@ -10772,10 +10772,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471330</v>
+        <v>471288</v>
       </c>
       <c r="R96" t="n">
-        <v>6770712</v>
+        <v>6770685</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10843,13 +10843,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944544</t>
+          <t>https://artportalen.se/Sighting/129944756</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129944592</v>
+        <v>129944762</v>
       </c>
       <c r="B97" t="n">
         <v>79327</v>
@@ -10884,10 +10884,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471313</v>
+        <v>471276</v>
       </c>
       <c r="R97" t="n">
-        <v>6770688</v>
+        <v>6770703</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10955,13 +10955,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944592</t>
+          <t>https://artportalen.se/Sighting/129944762</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129944756</v>
+        <v>129944804</v>
       </c>
       <c r="B98" t="n">
         <v>79327</v>
@@ -10996,10 +10996,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471288</v>
+        <v>471271</v>
       </c>
       <c r="R98" t="n">
-        <v>6770685</v>
+        <v>6770733</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11067,13 +11067,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944756</t>
+          <t>https://artportalen.se/Sighting/129944804</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129944762</v>
+        <v>129944807</v>
       </c>
       <c r="B99" t="n">
         <v>79327</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471276</v>
+        <v>471248</v>
       </c>
       <c r="R99" t="n">
-        <v>6770703</v>
+        <v>6770737</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11179,13 +11179,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944762</t>
+          <t>https://artportalen.se/Sighting/129944807</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944804</v>
+        <v>129944809</v>
       </c>
       <c r="B100" t="n">
         <v>79327</v>
@@ -11220,10 +11220,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471271</v>
+        <v>471247</v>
       </c>
       <c r="R100" t="n">
-        <v>6770733</v>
+        <v>6770726</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11291,13 +11291,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944804</t>
+          <t>https://artportalen.se/Sighting/129944809</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129944807</v>
+        <v>129944917</v>
       </c>
       <c r="B101" t="n">
         <v>79327</v>
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471248</v>
+        <v>471263</v>
       </c>
       <c r="R101" t="n">
-        <v>6770737</v>
+        <v>6770694</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,13 +11403,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944807</t>
+          <t>https://artportalen.se/Sighting/129944917</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129944809</v>
+        <v>129944975</v>
       </c>
       <c r="B102" t="n">
         <v>79327</v>
@@ -11444,10 +11444,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471247</v>
+        <v>471242</v>
       </c>
       <c r="R102" t="n">
-        <v>6770726</v>
+        <v>6770682</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11515,13 +11515,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944809</t>
+          <t>https://artportalen.se/Sighting/129944975</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129944917</v>
+        <v>129945066</v>
       </c>
       <c r="B103" t="n">
         <v>79327</v>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471263</v>
+        <v>471239</v>
       </c>
       <c r="R103" t="n">
-        <v>6770694</v>
+        <v>6770732</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11627,13 +11627,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944917</t>
+          <t>https://artportalen.se/Sighting/129945066</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129944975</v>
+        <v>129945078</v>
       </c>
       <c r="B104" t="n">
         <v>79327</v>
@@ -11668,10 +11668,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471242</v>
+        <v>471209</v>
       </c>
       <c r="R104" t="n">
-        <v>6770682</v>
+        <v>6770731</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11739,13 +11739,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944975</t>
+          <t>https://artportalen.se/Sighting/129945078</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129945066</v>
+        <v>129945104</v>
       </c>
       <c r="B105" t="n">
         <v>79327</v>
@@ -11780,10 +11780,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471239</v>
+        <v>471219</v>
       </c>
       <c r="R105" t="n">
-        <v>6770732</v>
+        <v>6770720</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11851,13 +11851,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945066</t>
+          <t>https://artportalen.se/Sighting/129945104</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129945078</v>
+        <v>129945451</v>
       </c>
       <c r="B106" t="n">
         <v>79327</v>
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471209</v>
+        <v>471189</v>
       </c>
       <c r="R106" t="n">
-        <v>6770731</v>
+        <v>6770706</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11963,13 +11963,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945078</t>
+          <t>https://artportalen.se/Sighting/129945451</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129945104</v>
+        <v>129945509</v>
       </c>
       <c r="B107" t="n">
         <v>79327</v>
@@ -12004,10 +12004,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471219</v>
+        <v>471198</v>
       </c>
       <c r="R107" t="n">
-        <v>6770720</v>
+        <v>6770689</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12052,6 +12052,11 @@
           <t>11:17</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12075,13 +12080,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945104</t>
+          <t>https://artportalen.se/Sighting/129945509</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129945451</v>
+        <v>129946029</v>
       </c>
       <c r="B108" t="n">
         <v>79327</v>
@@ -12116,10 +12121,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471189</v>
+        <v>471185</v>
       </c>
       <c r="R108" t="n">
-        <v>6770706</v>
+        <v>6770690</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12187,13 +12192,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945451</t>
+          <t>https://artportalen.se/Sighting/129946029</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129945509</v>
+        <v>129946053</v>
       </c>
       <c r="B109" t="n">
         <v>79327</v>
@@ -12228,10 +12233,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471198</v>
+        <v>471161</v>
       </c>
       <c r="R109" t="n">
-        <v>6770689</v>
+        <v>6770705</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12276,11 +12281,6 @@
           <t>11:17</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12304,13 +12304,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945509</t>
+          <t>https://artportalen.se/Sighting/129946053</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129946029</v>
+        <v>129946117</v>
       </c>
       <c r="B110" t="n">
         <v>79327</v>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471185</v>
+        <v>471106</v>
       </c>
       <c r="R110" t="n">
-        <v>6770690</v>
+        <v>6770711</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12416,13 +12416,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946029</t>
+          <t>https://artportalen.se/Sighting/129946117</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129946053</v>
+        <v>129946170</v>
       </c>
       <c r="B111" t="n">
         <v>79327</v>
@@ -12457,10 +12457,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471161</v>
+        <v>471030</v>
       </c>
       <c r="R111" t="n">
-        <v>6770705</v>
+        <v>6770688</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12528,13 +12528,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946053</t>
+          <t>https://artportalen.se/Sighting/129946170</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129946117</v>
+        <v>129946182</v>
       </c>
       <c r="B112" t="n">
         <v>79327</v>
@@ -12569,10 +12569,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471106</v>
+        <v>471000</v>
       </c>
       <c r="R112" t="n">
-        <v>6770711</v>
+        <v>6770675</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12640,13 +12640,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946117</t>
+          <t>https://artportalen.se/Sighting/129946182</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129946170</v>
+        <v>129946197</v>
       </c>
       <c r="B113" t="n">
         <v>79327</v>
@@ -12681,10 +12681,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471030</v>
+        <v>470971</v>
       </c>
       <c r="R113" t="n">
-        <v>6770688</v>
+        <v>6770676</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12752,13 +12752,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946170</t>
+          <t>https://artportalen.se/Sighting/129946197</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129946182</v>
+        <v>129946408</v>
       </c>
       <c r="B114" t="n">
         <v>79327</v>
@@ -12793,10 +12793,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471000</v>
+        <v>470921</v>
       </c>
       <c r="R114" t="n">
-        <v>6770675</v>
+        <v>6770579</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12864,13 +12864,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946182</t>
+          <t>https://artportalen.se/Sighting/129946408</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129946197</v>
+        <v>129946586</v>
       </c>
       <c r="B115" t="n">
         <v>79327</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>470971</v>
+        <v>471095</v>
       </c>
       <c r="R115" t="n">
-        <v>6770676</v>
+        <v>6770660</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12976,13 +12976,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946197</t>
+          <t>https://artportalen.se/Sighting/129946586</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129946408</v>
+        <v>129946708</v>
       </c>
       <c r="B116" t="n">
         <v>79327</v>
@@ -13017,10 +13017,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>470921</v>
+        <v>471171</v>
       </c>
       <c r="R116" t="n">
-        <v>6770579</v>
+        <v>6770660</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13088,13 +13088,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946408</t>
+          <t>https://artportalen.se/Sighting/129946708</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129946586</v>
+        <v>129954408</v>
       </c>
       <c r="B117" t="n">
         <v>79327</v>
@@ -13129,10 +13129,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471095</v>
+        <v>471019</v>
       </c>
       <c r="R117" t="n">
-        <v>6770660</v>
+        <v>6770666</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13159,22 +13159,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13200,13 +13200,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946586</t>
+          <t>https://artportalen.se/Sighting/129954408</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129946708</v>
+        <v>129954413</v>
       </c>
       <c r="B118" t="n">
         <v>79327</v>
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>471171</v>
+        <v>471028</v>
       </c>
       <c r="R118" t="n">
-        <v>6770660</v>
+        <v>6770675</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13271,22 +13271,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13312,13 +13312,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946708</t>
+          <t>https://artportalen.se/Sighting/129954413</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129954408</v>
+        <v>129954442</v>
       </c>
       <c r="B119" t="n">
         <v>79327</v>
@@ -13353,10 +13353,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471019</v>
+        <v>471053</v>
       </c>
       <c r="R119" t="n">
-        <v>6770666</v>
+        <v>6770682</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13424,13 +13424,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954408</t>
+          <t>https://artportalen.se/Sighting/129954442</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129954413</v>
+        <v>129954452</v>
       </c>
       <c r="B120" t="n">
         <v>79327</v>
@@ -13465,10 +13465,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471028</v>
+        <v>471058</v>
       </c>
       <c r="R120" t="n">
-        <v>6770675</v>
+        <v>6770677</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13536,13 +13536,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954413</t>
+          <t>https://artportalen.se/Sighting/129954452</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129954442</v>
+        <v>129954531</v>
       </c>
       <c r="B121" t="n">
         <v>79327</v>
@@ -13577,10 +13577,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471053</v>
+        <v>471106</v>
       </c>
       <c r="R121" t="n">
-        <v>6770682</v>
+        <v>6770683</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13648,13 +13648,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954442</t>
+          <t>https://artportalen.se/Sighting/129954531</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129954452</v>
+        <v>129954534</v>
       </c>
       <c r="B122" t="n">
         <v>79327</v>
@@ -13689,10 +13689,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471058</v>
+        <v>471086</v>
       </c>
       <c r="R122" t="n">
-        <v>6770677</v>
+        <v>6770684</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13760,13 +13760,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954452</t>
+          <t>https://artportalen.se/Sighting/129954534</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129954531</v>
+        <v>129954584</v>
       </c>
       <c r="B123" t="n">
         <v>79327</v>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471106</v>
+        <v>471062</v>
       </c>
       <c r="R123" t="n">
-        <v>6770683</v>
+        <v>6770731</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13872,13 +13872,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954531</t>
+          <t>https://artportalen.se/Sighting/129954584</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129954534</v>
+        <v>129954590</v>
       </c>
       <c r="B124" t="n">
         <v>79327</v>
@@ -13913,10 +13913,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471086</v>
+        <v>471013</v>
       </c>
       <c r="R124" t="n">
-        <v>6770684</v>
+        <v>6770715</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13984,13 +13984,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954534</t>
+          <t>https://artportalen.se/Sighting/129954590</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129954584</v>
+        <v>129954674</v>
       </c>
       <c r="B125" t="n">
         <v>79327</v>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>471062</v>
+        <v>470938</v>
       </c>
       <c r="R125" t="n">
-        <v>6770731</v>
+        <v>6770693</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14096,13 +14096,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954584</t>
+          <t>https://artportalen.se/Sighting/129954674</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129954590</v>
+        <v>129955100</v>
       </c>
       <c r="B126" t="n">
         <v>79327</v>
@@ -14137,10 +14137,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>471013</v>
+        <v>470981</v>
       </c>
       <c r="R126" t="n">
-        <v>6770715</v>
+        <v>6770691</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14208,13 +14208,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954590</t>
+          <t>https://artportalen.se/Sighting/129955100</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129954674</v>
+        <v>129955313</v>
       </c>
       <c r="B127" t="n">
         <v>79327</v>
@@ -14249,10 +14249,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470938</v>
+        <v>470992</v>
       </c>
       <c r="R127" t="n">
-        <v>6770693</v>
+        <v>6770702</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14320,13 +14320,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954674</t>
+          <t>https://artportalen.se/Sighting/129955313</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129955100</v>
+        <v>129956843</v>
       </c>
       <c r="B128" t="n">
         <v>79327</v>
@@ -14361,10 +14361,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470981</v>
+        <v>470953</v>
       </c>
       <c r="R128" t="n">
-        <v>6770691</v>
+        <v>6770692</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14432,13 +14432,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129955100</t>
+          <t>https://artportalen.se/Sighting/129956843</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129955313</v>
+        <v>129956851</v>
       </c>
       <c r="B129" t="n">
         <v>79327</v>
@@ -14473,10 +14473,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470992</v>
+        <v>470928</v>
       </c>
       <c r="R129" t="n">
-        <v>6770702</v>
+        <v>6770695</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14544,13 +14544,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129955313</t>
+          <t>https://artportalen.se/Sighting/129956851</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129956843</v>
+        <v>129956859</v>
       </c>
       <c r="B130" t="n">
         <v>79327</v>
@@ -14585,10 +14585,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470953</v>
+        <v>470936</v>
       </c>
       <c r="R130" t="n">
-        <v>6770692</v>
+        <v>6770721</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14656,13 +14656,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956843</t>
+          <t>https://artportalen.se/Sighting/129956859</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129956851</v>
+        <v>129957713</v>
       </c>
       <c r="B131" t="n">
         <v>79327</v>
@@ -14697,10 +14697,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470928</v>
+        <v>470904</v>
       </c>
       <c r="R131" t="n">
-        <v>6770695</v>
+        <v>6770718</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14768,13 +14768,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956851</t>
+          <t>https://artportalen.se/Sighting/129957713</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129956859</v>
+        <v>129957969</v>
       </c>
       <c r="B132" t="n">
         <v>79327</v>
@@ -14809,10 +14809,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470936</v>
+        <v>470911</v>
       </c>
       <c r="R132" t="n">
-        <v>6770721</v>
+        <v>6770707</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14880,13 +14880,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956859</t>
+          <t>https://artportalen.se/Sighting/129957969</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129957713</v>
+        <v>129958010</v>
       </c>
       <c r="B133" t="n">
         <v>79327</v>
@@ -14921,10 +14921,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>470904</v>
+        <v>470894</v>
       </c>
       <c r="R133" t="n">
-        <v>6770718</v>
+        <v>6770713</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14992,13 +14992,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957713</t>
+          <t>https://artportalen.se/Sighting/129958010</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129957969</v>
+        <v>129958133</v>
       </c>
       <c r="B134" t="n">
         <v>79327</v>
@@ -15033,10 +15033,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>470911</v>
+        <v>470869</v>
       </c>
       <c r="R134" t="n">
-        <v>6770707</v>
+        <v>6770702</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15104,13 +15104,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957969</t>
+          <t>https://artportalen.se/Sighting/129958133</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129958010</v>
+        <v>129958151</v>
       </c>
       <c r="B135" t="n">
         <v>79327</v>
@@ -15145,10 +15145,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470894</v>
+        <v>470842</v>
       </c>
       <c r="R135" t="n">
-        <v>6770713</v>
+        <v>6770709</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15216,13 +15216,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958010</t>
+          <t>https://artportalen.se/Sighting/129958151</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129958133</v>
+        <v>129958214</v>
       </c>
       <c r="B136" t="n">
         <v>79327</v>
@@ -15257,10 +15257,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470869</v>
+        <v>470823</v>
       </c>
       <c r="R136" t="n">
-        <v>6770702</v>
+        <v>6770705</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15328,13 +15328,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958133</t>
+          <t>https://artportalen.se/Sighting/129958214</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129958151</v>
+        <v>129958228</v>
       </c>
       <c r="B137" t="n">
         <v>79327</v>
@@ -15369,10 +15369,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470842</v>
+        <v>470813</v>
       </c>
       <c r="R137" t="n">
-        <v>6770709</v>
+        <v>6770681</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15440,13 +15440,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958151</t>
+          <t>https://artportalen.se/Sighting/129958228</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129958214</v>
+        <v>129958464</v>
       </c>
       <c r="B138" t="n">
         <v>79327</v>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470823</v>
+        <v>470822</v>
       </c>
       <c r="R138" t="n">
-        <v>6770705</v>
+        <v>6770673</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15552,13 +15552,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958214</t>
+          <t>https://artportalen.se/Sighting/129958464</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129958228</v>
+        <v>129958466</v>
       </c>
       <c r="B139" t="n">
         <v>79327</v>
@@ -15593,10 +15593,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470813</v>
+        <v>470812</v>
       </c>
       <c r="R139" t="n">
-        <v>6770681</v>
+        <v>6770670</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15664,13 +15664,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958228</t>
+          <t>https://artportalen.se/Sighting/129958466</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129958464</v>
+        <v>129958499</v>
       </c>
       <c r="B140" t="n">
         <v>79327</v>
@@ -15705,10 +15705,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470822</v>
+        <v>470850</v>
       </c>
       <c r="R140" t="n">
-        <v>6770673</v>
+        <v>6770690</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15776,13 +15776,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958464</t>
+          <t>https://artportalen.se/Sighting/129958499</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129958466</v>
+        <v>129958545</v>
       </c>
       <c r="B141" t="n">
         <v>79327</v>
@@ -15817,10 +15817,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>470812</v>
+        <v>470877</v>
       </c>
       <c r="R141" t="n">
-        <v>6770670</v>
+        <v>6770687</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15888,13 +15888,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958466</t>
+          <t>https://artportalen.se/Sighting/129958545</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129958499</v>
+        <v>129958694</v>
       </c>
       <c r="B142" t="n">
         <v>79327</v>
@@ -15929,10 +15929,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>470850</v>
+        <v>470844</v>
       </c>
       <c r="R142" t="n">
-        <v>6770690</v>
+        <v>6770699</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16000,13 +16000,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958499</t>
+          <t>https://artportalen.se/Sighting/129958694</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129958545</v>
+        <v>129958706</v>
       </c>
       <c r="B143" t="n">
         <v>79327</v>
@@ -16041,10 +16041,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>470877</v>
+        <v>470816</v>
       </c>
       <c r="R143" t="n">
-        <v>6770687</v>
+        <v>6770646</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16112,13 +16112,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958545</t>
+          <t>https://artportalen.se/Sighting/129958706</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129958694</v>
+        <v>129958754</v>
       </c>
       <c r="B144" t="n">
         <v>79327</v>
@@ -16153,10 +16153,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>470844</v>
+        <v>470817</v>
       </c>
       <c r="R144" t="n">
-        <v>6770699</v>
+        <v>6770608</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16224,13 +16224,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958694</t>
+          <t>https://artportalen.se/Sighting/129958754</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129958706</v>
+        <v>129958775</v>
       </c>
       <c r="B145" t="n">
         <v>79327</v>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>470816</v>
+        <v>470803</v>
       </c>
       <c r="R145" t="n">
-        <v>6770646</v>
+        <v>6770595</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16336,13 +16336,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958706</t>
+          <t>https://artportalen.se/Sighting/129958775</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129958754</v>
+        <v>129958795</v>
       </c>
       <c r="B146" t="n">
         <v>79327</v>
@@ -16377,10 +16377,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>470817</v>
+        <v>470822</v>
       </c>
       <c r="R146" t="n">
-        <v>6770608</v>
+        <v>6770615</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16425,6 +16425,11 @@
           <t>09:55</t>
         </is>
       </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
@@ -16448,13 +16453,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958754</t>
+          <t>https://artportalen.se/Sighting/129958795</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129958775</v>
+        <v>129958800</v>
       </c>
       <c r="B147" t="n">
         <v>79327</v>
@@ -16489,10 +16494,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470803</v>
+        <v>470858</v>
       </c>
       <c r="R147" t="n">
-        <v>6770595</v>
+        <v>6770602</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16560,13 +16565,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958775</t>
+          <t>https://artportalen.se/Sighting/129958800</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129958795</v>
+        <v>129958828</v>
       </c>
       <c r="B148" t="n">
         <v>79327</v>
@@ -16601,10 +16606,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470822</v>
+        <v>470871</v>
       </c>
       <c r="R148" t="n">
-        <v>6770615</v>
+        <v>6770635</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16649,11 +16654,6 @@
           <t>09:55</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -16677,13 +16677,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958795</t>
+          <t>https://artportalen.se/Sighting/129958828</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129958800</v>
+        <v>129958841</v>
       </c>
       <c r="B149" t="n">
         <v>79327</v>
@@ -16718,10 +16718,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>470858</v>
+        <v>470828</v>
       </c>
       <c r="R149" t="n">
-        <v>6770602</v>
+        <v>6770636</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16789,13 +16789,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958800</t>
+          <t>https://artportalen.se/Sighting/129958841</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129958828</v>
+        <v>129958842</v>
       </c>
       <c r="B150" t="n">
         <v>79327</v>
@@ -16830,10 +16830,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>470871</v>
+        <v>470820</v>
       </c>
       <c r="R150" t="n">
-        <v>6770635</v>
+        <v>6770624</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16901,13 +16901,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958828</t>
+          <t>https://artportalen.se/Sighting/129958842</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129958841</v>
+        <v>129958895</v>
       </c>
       <c r="B151" t="n">
         <v>79327</v>
@@ -16942,10 +16942,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>470828</v>
+        <v>470887</v>
       </c>
       <c r="R151" t="n">
-        <v>6770636</v>
+        <v>6770658</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17013,13 +17013,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958841</t>
+          <t>https://artportalen.se/Sighting/129958895</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129958842</v>
+        <v>129958937</v>
       </c>
       <c r="B152" t="n">
         <v>79327</v>
@@ -17054,10 +17054,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>470820</v>
+        <v>470897</v>
       </c>
       <c r="R152" t="n">
-        <v>6770624</v>
+        <v>6770647</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17125,13 +17125,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958842</t>
+          <t>https://artportalen.se/Sighting/129958937</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129958895</v>
+        <v>129959037</v>
       </c>
       <c r="B153" t="n">
         <v>79327</v>
@@ -17166,10 +17166,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>470887</v>
+        <v>470908</v>
       </c>
       <c r="R153" t="n">
-        <v>6770658</v>
+        <v>6770622</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17237,13 +17237,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958895</t>
+          <t>https://artportalen.se/Sighting/129959037</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129958937</v>
+        <v>129959060</v>
       </c>
       <c r="B154" t="n">
         <v>79327</v>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>470897</v>
+        <v>470926</v>
       </c>
       <c r="R154" t="n">
-        <v>6770647</v>
+        <v>6770613</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17349,13 +17349,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958937</t>
+          <t>https://artportalen.se/Sighting/129959060</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129959037</v>
+        <v>129959250</v>
       </c>
       <c r="B155" t="n">
         <v>79327</v>
@@ -17390,10 +17390,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470908</v>
+        <v>470943</v>
       </c>
       <c r="R155" t="n">
-        <v>6770622</v>
+        <v>6770559</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17461,13 +17461,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959037</t>
+          <t>https://artportalen.se/Sighting/129959250</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129959060</v>
+        <v>129959256</v>
       </c>
       <c r="B156" t="n">
         <v>79327</v>
@@ -17502,10 +17502,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>470926</v>
+        <v>470922</v>
       </c>
       <c r="R156" t="n">
-        <v>6770613</v>
+        <v>6770556</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17573,13 +17573,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959060</t>
+          <t>https://artportalen.se/Sighting/129959256</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129959250</v>
+        <v>129959294</v>
       </c>
       <c r="B157" t="n">
         <v>79327</v>
@@ -17614,10 +17614,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>470943</v>
+        <v>470904</v>
       </c>
       <c r="R157" t="n">
-        <v>6770559</v>
+        <v>6770537</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17685,13 +17685,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959250</t>
+          <t>https://artportalen.se/Sighting/129959294</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129959256</v>
+        <v>129959303</v>
       </c>
       <c r="B158" t="n">
         <v>79327</v>
@@ -17726,10 +17726,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470922</v>
+        <v>470879</v>
       </c>
       <c r="R158" t="n">
-        <v>6770556</v>
+        <v>6770545</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17797,13 +17797,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959256</t>
+          <t>https://artportalen.se/Sighting/129959303</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129959294</v>
+        <v>129959375</v>
       </c>
       <c r="B159" t="n">
         <v>79327</v>
@@ -17838,10 +17838,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>470904</v>
+        <v>470851</v>
       </c>
       <c r="R159" t="n">
-        <v>6770537</v>
+        <v>6770520</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17909,13 +17909,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959294</t>
+          <t>https://artportalen.se/Sighting/129959375</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129959303</v>
+        <v>129959389</v>
       </c>
       <c r="B160" t="n">
         <v>79327</v>
@@ -17950,10 +17950,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>470879</v>
+        <v>470824</v>
       </c>
       <c r="R160" t="n">
-        <v>6770545</v>
+        <v>6770523</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18021,13 +18021,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959303</t>
+          <t>https://artportalen.se/Sighting/129959389</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129959375</v>
+        <v>129959479</v>
       </c>
       <c r="B161" t="n">
         <v>79327</v>
@@ -18062,10 +18062,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>470851</v>
+        <v>470837</v>
       </c>
       <c r="R161" t="n">
-        <v>6770520</v>
+        <v>6770498</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18133,13 +18133,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959375</t>
+          <t>https://artportalen.se/Sighting/129959479</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129959389</v>
+        <v>129959501</v>
       </c>
       <c r="B162" t="n">
         <v>79327</v>
@@ -18174,10 +18174,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>470824</v>
+        <v>470807</v>
       </c>
       <c r="R162" t="n">
-        <v>6770523</v>
+        <v>6770491</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18245,13 +18245,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959389</t>
+          <t>https://artportalen.se/Sighting/129959501</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129959479</v>
+        <v>129959519</v>
       </c>
       <c r="B163" t="n">
         <v>79327</v>
@@ -18286,10 +18286,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>470837</v>
+        <v>470822</v>
       </c>
       <c r="R163" t="n">
-        <v>6770498</v>
+        <v>6770452</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18357,13 +18357,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959479</t>
+          <t>https://artportalen.se/Sighting/129959519</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129959501</v>
+        <v>129959692</v>
       </c>
       <c r="B164" t="n">
         <v>79327</v>
@@ -18398,10 +18398,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>470807</v>
+        <v>470864</v>
       </c>
       <c r="R164" t="n">
-        <v>6770491</v>
+        <v>6770438</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18469,13 +18469,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959501</t>
+          <t>https://artportalen.se/Sighting/129959692</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129959519</v>
+        <v>129959740</v>
       </c>
       <c r="B165" t="n">
         <v>79327</v>
@@ -18510,10 +18510,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>470822</v>
+        <v>470905</v>
       </c>
       <c r="R165" t="n">
-        <v>6770452</v>
+        <v>6770435</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18581,13 +18581,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959519</t>
+          <t>https://artportalen.se/Sighting/129959740</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129959692</v>
+        <v>129959772</v>
       </c>
       <c r="B166" t="n">
         <v>79327</v>
@@ -18622,10 +18622,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470864</v>
+        <v>470900</v>
       </c>
       <c r="R166" t="n">
-        <v>6770438</v>
+        <v>6770473</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18693,13 +18693,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959692</t>
+          <t>https://artportalen.se/Sighting/129959772</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129959740</v>
+        <v>129959808</v>
       </c>
       <c r="B167" t="n">
         <v>79327</v>
@@ -18734,10 +18734,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470905</v>
+        <v>470942</v>
       </c>
       <c r="R167" t="n">
-        <v>6770435</v>
+        <v>6770455</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18805,13 +18805,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959740</t>
+          <t>https://artportalen.se/Sighting/129959808</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129959772</v>
+        <v>129959994</v>
       </c>
       <c r="B168" t="n">
         <v>79327</v>
@@ -18846,10 +18846,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>470900</v>
+        <v>470954</v>
       </c>
       <c r="R168" t="n">
-        <v>6770473</v>
+        <v>6770475</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18917,13 +18917,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959772</t>
+          <t>https://artportalen.se/Sighting/129959994</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129959808</v>
+        <v>129960002</v>
       </c>
       <c r="B169" t="n">
         <v>79327</v>
@@ -18958,10 +18958,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>470942</v>
+        <v>470932</v>
       </c>
       <c r="R169" t="n">
-        <v>6770455</v>
+        <v>6770480</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19029,13 +19029,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959808</t>
+          <t>https://artportalen.se/Sighting/129960002</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129959994</v>
+        <v>129960437</v>
       </c>
       <c r="B170" t="n">
         <v>79327</v>
@@ -19070,10 +19070,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>470954</v>
+        <v>470948</v>
       </c>
       <c r="R170" t="n">
-        <v>6770475</v>
+        <v>6770533</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19141,13 +19141,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959994</t>
+          <t>https://artportalen.se/Sighting/129960437</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129960002</v>
+        <v>129960691</v>
       </c>
       <c r="B171" t="n">
         <v>79327</v>
@@ -19182,10 +19182,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>470932</v>
+        <v>471056</v>
       </c>
       <c r="R171" t="n">
-        <v>6770480</v>
+        <v>6770494</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19253,13 +19253,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960002</t>
+          <t>https://artportalen.se/Sighting/129960691</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129960437</v>
+        <v>129960763</v>
       </c>
       <c r="B172" t="n">
         <v>79327</v>
@@ -19294,10 +19294,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>470948</v>
+        <v>471062</v>
       </c>
       <c r="R172" t="n">
-        <v>6770533</v>
+        <v>6770538</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19365,13 +19365,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960437</t>
+          <t>https://artportalen.se/Sighting/129960763</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129960691</v>
+        <v>129960790</v>
       </c>
       <c r="B173" t="n">
         <v>79327</v>
@@ -19406,10 +19406,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471056</v>
+        <v>471073</v>
       </c>
       <c r="R173" t="n">
-        <v>6770494</v>
+        <v>6770551</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19477,13 +19477,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960691</t>
+          <t>https://artportalen.se/Sighting/129960790</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129960763</v>
+        <v>129960823</v>
       </c>
       <c r="B174" t="n">
         <v>79327</v>
@@ -19518,10 +19518,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>471062</v>
+        <v>471078</v>
       </c>
       <c r="R174" t="n">
-        <v>6770538</v>
+        <v>6770561</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19566,6 +19566,11 @@
           <t>09:55</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -19589,13 +19594,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960763</t>
+          <t>https://artportalen.se/Sighting/129960823</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129960790</v>
+        <v>129960843</v>
       </c>
       <c r="B175" t="n">
         <v>79327</v>
@@ -19630,10 +19635,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471073</v>
+        <v>471097</v>
       </c>
       <c r="R175" t="n">
-        <v>6770551</v>
+        <v>6770561</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19701,13 +19706,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960790</t>
+          <t>https://artportalen.se/Sighting/129960843</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129960823</v>
+        <v>129960864</v>
       </c>
       <c r="B176" t="n">
         <v>79327</v>
@@ -19742,10 +19747,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471078</v>
+        <v>471116</v>
       </c>
       <c r="R176" t="n">
-        <v>6770561</v>
+        <v>6770565</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19790,11 +19795,6 @@
           <t>09:55</t>
         </is>
       </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
@@ -19818,13 +19818,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960823</t>
+          <t>https://artportalen.se/Sighting/129960864</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129960843</v>
+        <v>129960884</v>
       </c>
       <c r="B177" t="n">
         <v>79327</v>
@@ -19859,10 +19859,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>471097</v>
+        <v>471129</v>
       </c>
       <c r="R177" t="n">
-        <v>6770561</v>
+        <v>6770567</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19930,13 +19930,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960843</t>
+          <t>https://artportalen.se/Sighting/129960884</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129960864</v>
+        <v>129960891</v>
       </c>
       <c r="B178" t="n">
         <v>79327</v>
@@ -19971,10 +19971,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>471116</v>
+        <v>471147</v>
       </c>
       <c r="R178" t="n">
-        <v>6770565</v>
+        <v>6770575</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20042,13 +20042,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960864</t>
+          <t>https://artportalen.se/Sighting/129960891</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129960884</v>
+        <v>129960901</v>
       </c>
       <c r="B179" t="n">
         <v>79327</v>
@@ -20083,10 +20083,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>471129</v>
+        <v>471185</v>
       </c>
       <c r="R179" t="n">
-        <v>6770567</v>
+        <v>6770590</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20154,13 +20154,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960884</t>
+          <t>https://artportalen.se/Sighting/129960901</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129960891</v>
+        <v>129960929</v>
       </c>
       <c r="B180" t="n">
         <v>79327</v>
@@ -20195,10 +20195,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>471147</v>
+        <v>471159</v>
       </c>
       <c r="R180" t="n">
-        <v>6770575</v>
+        <v>6770613</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20266,13 +20266,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960891</t>
+          <t>https://artportalen.se/Sighting/129960929</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129960901</v>
+        <v>129961603</v>
       </c>
       <c r="B181" t="n">
         <v>79327</v>
@@ -20307,10 +20307,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471185</v>
+        <v>471262</v>
       </c>
       <c r="R181" t="n">
-        <v>6770590</v>
+        <v>6770622</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20378,13 +20378,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960901</t>
+          <t>https://artportalen.se/Sighting/129961603</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129960929</v>
+        <v>129961818</v>
       </c>
       <c r="B182" t="n">
         <v>79327</v>
@@ -20419,10 +20419,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471159</v>
+        <v>471228</v>
       </c>
       <c r="R182" t="n">
-        <v>6770613</v>
+        <v>6770667</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20490,13 +20490,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960929</t>
+          <t>https://artportalen.se/Sighting/129961818</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129961603</v>
+        <v>129961937</v>
       </c>
       <c r="B183" t="n">
         <v>79327</v>
@@ -20531,10 +20531,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>471262</v>
+        <v>471216</v>
       </c>
       <c r="R183" t="n">
-        <v>6770622</v>
+        <v>6770650</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20602,13 +20602,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961603</t>
+          <t>https://artportalen.se/Sighting/129961937</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129961818</v>
+        <v>129962073</v>
       </c>
       <c r="B184" t="n">
         <v>79327</v>
@@ -20643,10 +20643,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>471228</v>
+        <v>471222</v>
       </c>
       <c r="R184" t="n">
-        <v>6770667</v>
+        <v>6770635</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20714,13 +20714,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961818</t>
+          <t>https://artportalen.se/Sighting/129962073</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129961937</v>
+        <v>129962119</v>
       </c>
       <c r="B185" t="n">
         <v>79327</v>
@@ -20755,10 +20755,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>471216</v>
+        <v>471156</v>
       </c>
       <c r="R185" t="n">
-        <v>6770650</v>
+        <v>6770665</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20826,13 +20826,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961937</t>
+          <t>https://artportalen.se/Sighting/129962119</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129962073</v>
+        <v>129962224</v>
       </c>
       <c r="B186" t="n">
         <v>79327</v>
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>471222</v>
+        <v>471098</v>
       </c>
       <c r="R186" t="n">
-        <v>6770635</v>
+        <v>6770634</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20938,13 +20938,13 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962073</t>
+          <t>https://artportalen.se/Sighting/129962224</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129962119</v>
+        <v>129962243</v>
       </c>
       <c r="B187" t="n">
         <v>79327</v>
@@ -20979,10 +20979,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>471156</v>
+        <v>471074</v>
       </c>
       <c r="R187" t="n">
-        <v>6770665</v>
+        <v>6770617</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21050,13 +21050,13 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962119</t>
+          <t>https://artportalen.se/Sighting/129962243</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129962224</v>
+        <v>129962260</v>
       </c>
       <c r="B188" t="n">
         <v>79327</v>
@@ -21091,10 +21091,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>471098</v>
+        <v>471044</v>
       </c>
       <c r="R188" t="n">
-        <v>6770634</v>
+        <v>6770615</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21162,13 +21162,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962224</t>
+          <t>https://artportalen.se/Sighting/129962260</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129962243</v>
+        <v>129962290</v>
       </c>
       <c r="B189" t="n">
         <v>79327</v>
@@ -21203,10 +21203,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>471074</v>
+        <v>471033</v>
       </c>
       <c r="R189" t="n">
-        <v>6770617</v>
+        <v>6770614</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21274,13 +21274,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962243</t>
+          <t>https://artportalen.se/Sighting/129962290</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129962260</v>
+        <v>129962320</v>
       </c>
       <c r="B190" t="n">
         <v>79327</v>
@@ -21315,10 +21315,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>471044</v>
+        <v>471024</v>
       </c>
       <c r="R190" t="n">
-        <v>6770615</v>
+        <v>6770624</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21386,13 +21386,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962260</t>
+          <t>https://artportalen.se/Sighting/129962320</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129962290</v>
+        <v>129962351</v>
       </c>
       <c r="B191" t="n">
         <v>79327</v>
@@ -21427,10 +21427,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>471033</v>
+        <v>471017</v>
       </c>
       <c r="R191" t="n">
-        <v>6770614</v>
+        <v>6770613</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21498,13 +21498,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962290</t>
+          <t>https://artportalen.se/Sighting/129962351</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129962320</v>
+        <v>129962379</v>
       </c>
       <c r="B192" t="n">
         <v>79327</v>
@@ -21539,10 +21539,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>471024</v>
+        <v>470996</v>
       </c>
       <c r="R192" t="n">
-        <v>6770624</v>
+        <v>6770611</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21610,13 +21610,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962320</t>
+          <t>https://artportalen.se/Sighting/129962379</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129962351</v>
+        <v>129962390</v>
       </c>
       <c r="B193" t="n">
         <v>79327</v>
@@ -21651,10 +21651,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>471017</v>
+        <v>471004</v>
       </c>
       <c r="R193" t="n">
-        <v>6770613</v>
+        <v>6770581</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21722,13 +21722,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962351</t>
+          <t>https://artportalen.se/Sighting/129962390</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129962379</v>
+        <v>129962417</v>
       </c>
       <c r="B194" t="n">
         <v>79327</v>
@@ -21763,10 +21763,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>470996</v>
+        <v>471002</v>
       </c>
       <c r="R194" t="n">
-        <v>6770611</v>
+        <v>6770618</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21834,13 +21834,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962379</t>
+          <t>https://artportalen.se/Sighting/129962417</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129962390</v>
+        <v>129962443</v>
       </c>
       <c r="B195" t="n">
         <v>79327</v>
@@ -21875,10 +21875,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>471004</v>
+        <v>470989</v>
       </c>
       <c r="R195" t="n">
-        <v>6770581</v>
+        <v>6770629</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21946,13 +21946,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962390</t>
+          <t>https://artportalen.se/Sighting/129962443</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129962417</v>
+        <v>129962446</v>
       </c>
       <c r="B196" t="n">
         <v>79327</v>
@@ -21987,10 +21987,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>471002</v>
+        <v>470993</v>
       </c>
       <c r="R196" t="n">
-        <v>6770618</v>
+        <v>6770643</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22058,51 +22058,56 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962417</t>
+          <t>https://artportalen.se/Sighting/129962446</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129962443</v>
+        <v>129944452</v>
       </c>
       <c r="B197" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>470989</v>
+        <v>471330</v>
       </c>
       <c r="R197" t="n">
-        <v>6770629</v>
+        <v>6770712</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22129,22 +22134,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22170,51 +22175,56 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962443</t>
+          <t>https://artportalen.se/Sighting/129944452</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129962446</v>
+        <v>129945156</v>
       </c>
       <c r="B198" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>470993</v>
+        <v>471198</v>
       </c>
       <c r="R198" t="n">
-        <v>6770643</v>
+        <v>6770725</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22241,22 +22251,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22282,13 +22292,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962446</t>
+          <t>https://artportalen.se/Sighting/129945156</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129944452</v>
+        <v>129945440</v>
       </c>
       <c r="B199" t="n">
         <v>57950</v>
@@ -22319,7 +22329,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22328,10 +22338,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471330</v>
+        <v>471189</v>
       </c>
       <c r="R199" t="n">
-        <v>6770712</v>
+        <v>6770706</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22399,13 +22409,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944452</t>
+          <t>https://artportalen.se/Sighting/129945440</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129945156</v>
+        <v>129946321</v>
       </c>
       <c r="B200" t="n">
         <v>57950</v>
@@ -22436,7 +22446,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22445,10 +22455,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>471198</v>
+        <v>470871</v>
       </c>
       <c r="R200" t="n">
-        <v>6770725</v>
+        <v>6770635</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22516,13 +22526,13 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945156</t>
+          <t>https://artportalen.se/Sighting/129946321</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129945440</v>
+        <v>129946365</v>
       </c>
       <c r="B201" t="n">
         <v>57950</v>
@@ -22562,10 +22572,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>471189</v>
+        <v>470910</v>
       </c>
       <c r="R201" t="n">
-        <v>6770706</v>
+        <v>6770605</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22633,13 +22643,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945440</t>
+          <t>https://artportalen.se/Sighting/129946365</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129946321</v>
+        <v>129946391</v>
       </c>
       <c r="B202" t="n">
         <v>57950</v>
@@ -22670,7 +22680,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22679,10 +22689,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>470871</v>
+        <v>470921</v>
       </c>
       <c r="R202" t="n">
-        <v>6770635</v>
+        <v>6770579</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22750,13 +22760,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946321</t>
+          <t>https://artportalen.se/Sighting/129946391</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129946365</v>
+        <v>129946436</v>
       </c>
       <c r="B203" t="n">
         <v>57950</v>
@@ -22787,7 +22797,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22796,10 +22806,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>470910</v>
+        <v>470971</v>
       </c>
       <c r="R203" t="n">
-        <v>6770605</v>
+        <v>6770603</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22867,13 +22877,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946365</t>
+          <t>https://artportalen.se/Sighting/129946436</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129946391</v>
+        <v>129954441</v>
       </c>
       <c r="B204" t="n">
         <v>57950</v>
@@ -22913,10 +22923,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>470921</v>
+        <v>471052</v>
       </c>
       <c r="R204" t="n">
-        <v>6770579</v>
+        <v>6770696</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22943,22 +22953,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22984,13 +22994,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946391</t>
+          <t>https://artportalen.se/Sighting/129954441</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129946436</v>
+        <v>129957253</v>
       </c>
       <c r="B205" t="n">
         <v>57950</v>
@@ -23021,7 +23031,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -23030,10 +23040,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>470971</v>
+        <v>470916</v>
       </c>
       <c r="R205" t="n">
-        <v>6770603</v>
+        <v>6770721</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23060,22 +23070,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23101,13 +23111,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946436</t>
+          <t>https://artportalen.se/Sighting/129957253</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129954441</v>
+        <v>129958691</v>
       </c>
       <c r="B206" t="n">
         <v>57950</v>
@@ -23147,10 +23157,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>471052</v>
+        <v>470844</v>
       </c>
       <c r="R206" t="n">
-        <v>6770696</v>
+        <v>6770699</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23218,13 +23228,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954441</t>
+          <t>https://artportalen.se/Sighting/129958691</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129957253</v>
+        <v>129959434</v>
       </c>
       <c r="B207" t="n">
         <v>57950</v>
@@ -23264,10 +23274,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470916</v>
+        <v>470824</v>
       </c>
       <c r="R207" t="n">
-        <v>6770721</v>
+        <v>6770523</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23335,13 +23345,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957253</t>
+          <t>https://artportalen.se/Sighting/129959434</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129958691</v>
+        <v>129959567</v>
       </c>
       <c r="B208" t="n">
         <v>57950</v>
@@ -23381,10 +23391,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470844</v>
+        <v>470822</v>
       </c>
       <c r="R208" t="n">
-        <v>6770699</v>
+        <v>6770452</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23452,13 +23462,13 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958691</t>
+          <t>https://artportalen.se/Sighting/129959567</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129959434</v>
+        <v>129959730</v>
       </c>
       <c r="B209" t="n">
         <v>57950</v>
@@ -23489,7 +23499,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -23498,10 +23508,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>470824</v>
+        <v>470868</v>
       </c>
       <c r="R209" t="n">
-        <v>6770523</v>
+        <v>6770431</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23569,13 +23579,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959434</t>
+          <t>https://artportalen.se/Sighting/129959730</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129959567</v>
+        <v>129959870</v>
       </c>
       <c r="B210" t="n">
         <v>57950</v>
@@ -23606,7 +23616,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -23615,10 +23625,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>470822</v>
+        <v>470952</v>
       </c>
       <c r="R210" t="n">
-        <v>6770452</v>
+        <v>6770464</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23686,13 +23696,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959567</t>
+          <t>https://artportalen.se/Sighting/129959870</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129959730</v>
+        <v>129960642</v>
       </c>
       <c r="B211" t="n">
         <v>57950</v>
@@ -23732,10 +23742,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>470868</v>
+        <v>471025</v>
       </c>
       <c r="R211" t="n">
-        <v>6770431</v>
+        <v>6770488</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23803,13 +23813,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959730</t>
+          <t>https://artportalen.se/Sighting/129960642</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129959870</v>
+        <v>129962343</v>
       </c>
       <c r="B212" t="n">
         <v>57950</v>
@@ -23840,7 +23850,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -23849,10 +23859,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>470952</v>
+        <v>471017</v>
       </c>
       <c r="R212" t="n">
-        <v>6770464</v>
+        <v>6770613</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23920,13 +23930,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959870</t>
+          <t>https://artportalen.se/Sighting/129962343</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129960642</v>
+        <v>129962374</v>
       </c>
       <c r="B213" t="n">
         <v>57950</v>
@@ -23957,7 +23967,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23966,10 +23976,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>471025</v>
+        <v>470996</v>
       </c>
       <c r="R213" t="n">
-        <v>6770488</v>
+        <v>6770611</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24037,13 +24047,13 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960642</t>
+          <t>https://artportalen.se/Sighting/129962374</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129962343</v>
+        <v>129962430</v>
       </c>
       <c r="B214" t="n">
         <v>57950</v>
@@ -24074,7 +24084,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -24083,10 +24093,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471017</v>
+        <v>470989</v>
       </c>
       <c r="R214" t="n">
-        <v>6770613</v>
+        <v>6770629</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24154,44 +24164,48 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962343</t>
+          <t>https://artportalen.se/Sighting/129962430</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129962374</v>
+        <v>129944878</v>
       </c>
       <c r="B215" t="n">
-        <v>57950</v>
+        <v>58114</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -24200,13 +24214,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>470996</v>
+        <v>471258</v>
       </c>
       <c r="R215" t="n">
-        <v>6770611</v>
+        <v>6770712</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24230,22 +24244,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24271,16 +24285,16 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962374</t>
+          <t>https://artportalen.se/Sighting/129944878</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129962430</v>
+        <v>129944062</v>
       </c>
       <c r="B216" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24288,27 +24302,27 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -24317,10 +24331,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>470989</v>
+        <v>471432</v>
       </c>
       <c r="R216" t="n">
-        <v>6770629</v>
+        <v>6770716</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24347,22 +24361,22 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24388,48 +24402,44 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962430</t>
+          <t>https://artportalen.se/Sighting/129944062</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129944878</v>
+        <v>129944158</v>
       </c>
       <c r="B217" t="n">
-        <v>58114</v>
+        <v>8455</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="M217" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -24438,13 +24448,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>471258</v>
+        <v>471363</v>
       </c>
       <c r="R217" t="n">
-        <v>6770712</v>
+        <v>6770736</v>
       </c>
       <c r="S217" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -24509,13 +24519,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944878</t>
+          <t>https://artportalen.se/Sighting/129944158</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129944062</v>
+        <v>129944454</v>
       </c>
       <c r="B218" t="n">
         <v>8455</v>
@@ -24544,21 +24554,16 @@
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>471432</v>
+        <v>471330</v>
       </c>
       <c r="R218" t="n">
-        <v>6770716</v>
+        <v>6770712</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24626,13 +24631,13 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944062</t>
+          <t>https://artportalen.se/Sighting/129944454</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129944158</v>
+        <v>129945161</v>
       </c>
       <c r="B219" t="n">
         <v>8455</v>
@@ -24672,10 +24677,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471363</v>
+        <v>471198</v>
       </c>
       <c r="R219" t="n">
-        <v>6770736</v>
+        <v>6770725</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24743,13 +24748,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944158</t>
+          <t>https://artportalen.se/Sighting/129945161</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129944454</v>
+        <v>129945444</v>
       </c>
       <c r="B220" t="n">
         <v>8455</v>
@@ -24778,16 +24783,21 @@
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>471330</v>
+        <v>471189</v>
       </c>
       <c r="R220" t="n">
-        <v>6770712</v>
+        <v>6770706</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24855,13 +24865,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944454</t>
+          <t>https://artportalen.se/Sighting/129945444</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129945161</v>
+        <v>129946047</v>
       </c>
       <c r="B221" t="n">
         <v>8455</v>
@@ -24890,21 +24900,16 @@
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>471198</v>
+        <v>471161</v>
       </c>
       <c r="R221" t="n">
-        <v>6770725</v>
+        <v>6770705</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24972,13 +24977,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945161</t>
+          <t>https://artportalen.se/Sighting/129946047</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129945444</v>
+        <v>129946334</v>
       </c>
       <c r="B222" t="n">
         <v>8455</v>
@@ -25018,10 +25023,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>471189</v>
+        <v>470871</v>
       </c>
       <c r="R222" t="n">
-        <v>6770706</v>
+        <v>6770635</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25089,13 +25094,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945444</t>
+          <t>https://artportalen.se/Sighting/129946334</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129946047</v>
+        <v>129946444</v>
       </c>
       <c r="B223" t="n">
         <v>8455</v>
@@ -25124,16 +25129,21 @@
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>471161</v>
+        <v>470971</v>
       </c>
       <c r="R223" t="n">
-        <v>6770705</v>
+        <v>6770603</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25201,13 +25211,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946047</t>
+          <t>https://artportalen.se/Sighting/129946444</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129946334</v>
+        <v>129954662</v>
       </c>
       <c r="B224" t="n">
         <v>8455</v>
@@ -25247,10 +25257,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470871</v>
+        <v>470941</v>
       </c>
       <c r="R224" t="n">
-        <v>6770635</v>
+        <v>6770708</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25277,22 +25287,22 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25318,13 +25328,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946334</t>
+          <t>https://artportalen.se/Sighting/129954662</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129946444</v>
+        <v>129958131</v>
       </c>
       <c r="B225" t="n">
         <v>8455</v>
@@ -25364,10 +25374,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470971</v>
+        <v>470869</v>
       </c>
       <c r="R225" t="n">
-        <v>6770603</v>
+        <v>6770702</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25394,22 +25404,22 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25435,13 +25445,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946444</t>
+          <t>https://artportalen.se/Sighting/129958131</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129954662</v>
+        <v>129958199</v>
       </c>
       <c r="B226" t="n">
         <v>8455</v>
@@ -25481,10 +25491,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>470941</v>
+        <v>470823</v>
       </c>
       <c r="R226" t="n">
-        <v>6770708</v>
+        <v>6770705</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25552,13 +25562,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954662</t>
+          <t>https://artportalen.se/Sighting/129958199</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129958131</v>
+        <v>129958686</v>
       </c>
       <c r="B227" t="n">
         <v>8455</v>
@@ -25598,10 +25608,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>470869</v>
+        <v>470844</v>
       </c>
       <c r="R227" t="n">
-        <v>6770702</v>
+        <v>6770699</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25669,13 +25679,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958131</t>
+          <t>https://artportalen.se/Sighting/129958686</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129958199</v>
+        <v>129959110</v>
       </c>
       <c r="B228" t="n">
         <v>8455</v>
@@ -25715,10 +25725,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470823</v>
+        <v>470926</v>
       </c>
       <c r="R228" t="n">
-        <v>6770705</v>
+        <v>6770613</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25786,13 +25796,13 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958199</t>
+          <t>https://artportalen.se/Sighting/129959110</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129958686</v>
+        <v>129959223</v>
       </c>
       <c r="B229" t="n">
         <v>8455</v>
@@ -25832,10 +25842,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>470844</v>
+        <v>470921</v>
       </c>
       <c r="R229" t="n">
-        <v>6770699</v>
+        <v>6770579</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25903,13 +25913,13 @@
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958686</t>
+          <t>https://artportalen.se/Sighting/129959223</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129959110</v>
+        <v>129959285</v>
       </c>
       <c r="B230" t="n">
         <v>8455</v>
@@ -25949,10 +25959,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>470926</v>
+        <v>470922</v>
       </c>
       <c r="R230" t="n">
-        <v>6770613</v>
+        <v>6770556</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26020,13 +26030,13 @@
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959110</t>
+          <t>https://artportalen.se/Sighting/129959285</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129959223</v>
+        <v>129959441</v>
       </c>
       <c r="B231" t="n">
         <v>8455</v>
@@ -26066,10 +26076,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>470921</v>
+        <v>470824</v>
       </c>
       <c r="R231" t="n">
-        <v>6770579</v>
+        <v>6770523</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26137,13 +26147,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959223</t>
+          <t>https://artportalen.se/Sighting/129959441</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129959285</v>
+        <v>129959579</v>
       </c>
       <c r="B232" t="n">
         <v>8455</v>
@@ -26183,10 +26193,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>470922</v>
+        <v>470822</v>
       </c>
       <c r="R232" t="n">
-        <v>6770556</v>
+        <v>6770452</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26254,13 +26264,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959285</t>
+          <t>https://artportalen.se/Sighting/129959579</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129959441</v>
+        <v>129959710</v>
       </c>
       <c r="B233" t="n">
         <v>8455</v>
@@ -26300,10 +26310,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>470824</v>
+        <v>470864</v>
       </c>
       <c r="R233" t="n">
-        <v>6770523</v>
+        <v>6770438</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26371,13 +26381,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959441</t>
+          <t>https://artportalen.se/Sighting/129959710</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129959579</v>
+        <v>129959735</v>
       </c>
       <c r="B234" t="n">
         <v>8455</v>
@@ -26417,10 +26427,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>470822</v>
+        <v>470868</v>
       </c>
       <c r="R234" t="n">
-        <v>6770452</v>
+        <v>6770431</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26488,13 +26498,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959579</t>
+          <t>https://artportalen.se/Sighting/129959735</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129959710</v>
+        <v>129959924</v>
       </c>
       <c r="B235" t="n">
         <v>8455</v>
@@ -26534,10 +26544,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>470864</v>
+        <v>470944</v>
       </c>
       <c r="R235" t="n">
-        <v>6770438</v>
+        <v>6770458</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26605,13 +26615,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959710</t>
+          <t>https://artportalen.se/Sighting/129959924</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129959735</v>
+        <v>129960514</v>
       </c>
       <c r="B236" t="n">
         <v>8455</v>
@@ -26651,13 +26661,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>470868</v>
+        <v>470976</v>
       </c>
       <c r="R236" t="n">
-        <v>6770431</v>
+        <v>6770536</v>
       </c>
       <c r="S236" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26722,13 +26732,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959735</t>
+          <t>https://artportalen.se/Sighting/129960514</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129959924</v>
+        <v>129960657</v>
       </c>
       <c r="B237" t="n">
         <v>8455</v>
@@ -26768,10 +26778,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>470944</v>
+        <v>471025</v>
       </c>
       <c r="R237" t="n">
-        <v>6770458</v>
+        <v>6770488</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26839,13 +26849,13 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959924</t>
+          <t>https://artportalen.se/Sighting/129960657</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129960514</v>
+        <v>129960746</v>
       </c>
       <c r="B238" t="n">
         <v>8455</v>
@@ -26885,13 +26895,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>470976</v>
+        <v>471053</v>
       </c>
       <c r="R238" t="n">
-        <v>6770536</v>
+        <v>6770528</v>
       </c>
       <c r="S238" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -26956,13 +26966,13 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960514</t>
+          <t>https://artportalen.se/Sighting/129960746</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129960657</v>
+        <v>129960827</v>
       </c>
       <c r="B239" t="n">
         <v>8455</v>
@@ -27002,10 +27012,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>471025</v>
+        <v>471078</v>
       </c>
       <c r="R239" t="n">
-        <v>6770488</v>
+        <v>6770561</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27073,13 +27083,13 @@
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960657</t>
+          <t>https://artportalen.se/Sighting/129960827</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129960746</v>
+        <v>129961109</v>
       </c>
       <c r="B240" t="n">
         <v>8455</v>
@@ -27119,10 +27129,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>471053</v>
+        <v>471175</v>
       </c>
       <c r="R240" t="n">
-        <v>6770528</v>
+        <v>6770631</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27190,13 +27200,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960746</t>
+          <t>https://artportalen.se/Sighting/129961109</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129960827</v>
+        <v>129962346</v>
       </c>
       <c r="B241" t="n">
         <v>8455</v>
@@ -27236,10 +27246,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>471078</v>
+        <v>471017</v>
       </c>
       <c r="R241" t="n">
-        <v>6770561</v>
+        <v>6770613</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27307,13 +27317,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960827</t>
+          <t>https://artportalen.se/Sighting/129962346</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129961109</v>
+        <v>129962376</v>
       </c>
       <c r="B242" t="n">
         <v>8455</v>
@@ -27353,10 +27363,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>471175</v>
+        <v>470996</v>
       </c>
       <c r="R242" t="n">
-        <v>6770631</v>
+        <v>6770611</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27424,13 +27434,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961109</t>
+          <t>https://artportalen.se/Sighting/129962376</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129962346</v>
+        <v>129962436</v>
       </c>
       <c r="B243" t="n">
         <v>8455</v>
@@ -27470,10 +27480,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>471017</v>
+        <v>470989</v>
       </c>
       <c r="R243" t="n">
-        <v>6770613</v>
+        <v>6770629</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27541,59 +27551,57 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962346</t>
+          <t>https://artportalen.se/Sighting/129962436</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129962376</v>
+        <v>129271581</v>
       </c>
       <c r="B244" t="n">
-        <v>8455</v>
+        <v>93228</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>106545</v>
+        <v>232140</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>470996</v>
+        <v>470835</v>
       </c>
       <c r="R244" t="n">
-        <v>6770611</v>
+        <v>6770662</v>
       </c>
       <c r="S244" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27617,22 +27625,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27641,76 +27639,72 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
+      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962376</t>
+          <t>https://artportalen.se/Sighting/129271581</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129962436</v>
+        <v>96714923</v>
       </c>
       <c r="B245" t="n">
-        <v>8455</v>
+        <v>91402</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>106545</v>
+        <v>256703</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>470989</v>
+        <v>470876</v>
       </c>
       <c r="R245" t="n">
-        <v>6770629</v>
+        <v>6770446</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27734,22 +27728,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27764,65 +27748,62 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962436</t>
+          <t>https://artportalen.se/Sighting/96714923</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129271581</v>
+        <v>96714929</v>
       </c>
       <c r="B246" t="n">
-        <v>93228</v>
+        <v>91402</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>232140</v>
+        <v>256703</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>470835</v>
+        <v>471113</v>
       </c>
       <c r="R246" t="n">
-        <v>6770662</v>
+        <v>6770726</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -27849,12 +27830,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -27863,31 +27844,30 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129271581</t>
+          <t>https://artportalen.se/Sighting/96714929</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>96714923</v>
+        <v>96714933</v>
       </c>
       <c r="B247" t="n">
         <v>91402</v>
@@ -27922,10 +27902,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>470876</v>
+        <v>470806</v>
       </c>
       <c r="R247" t="n">
-        <v>6770446</v>
+        <v>6770695</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -27983,13 +27963,13 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714923</t>
+          <t>https://artportalen.se/Sighting/96714933</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>96714929</v>
+        <v>96714941</v>
       </c>
       <c r="B248" t="n">
         <v>91402</v>
@@ -28024,10 +28004,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>471113</v>
+        <v>471105</v>
       </c>
       <c r="R248" t="n">
-        <v>6770726</v>
+        <v>6770716</v>
       </c>
       <c r="S248" t="n">
         <v>25</v>
@@ -28085,13 +28065,13 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714929</t>
+          <t>https://artportalen.se/Sighting/96714941</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>96714933</v>
+        <v>96714946</v>
       </c>
       <c r="B249" t="n">
         <v>91402</v>
@@ -28126,10 +28106,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>470806</v>
+        <v>471072</v>
       </c>
       <c r="R249" t="n">
-        <v>6770695</v>
+        <v>6770716</v>
       </c>
       <c r="S249" t="n">
         <v>25</v>
@@ -28187,13 +28167,13 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714933</t>
+          <t>https://artportalen.se/Sighting/96714946</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>96714941</v>
+        <v>96714952</v>
       </c>
       <c r="B250" t="n">
         <v>91402</v>
@@ -28228,10 +28208,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>471105</v>
+        <v>470920</v>
       </c>
       <c r="R250" t="n">
-        <v>6770716</v>
+        <v>6770687</v>
       </c>
       <c r="S250" t="n">
         <v>25</v>
@@ -28289,13 +28269,13 @@
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714941</t>
+          <t>https://artportalen.se/Sighting/96714952</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>96714946</v>
+        <v>96714953</v>
       </c>
       <c r="B251" t="n">
         <v>91402</v>
@@ -28330,10 +28310,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>471072</v>
+        <v>471086</v>
       </c>
       <c r="R251" t="n">
-        <v>6770716</v>
+        <v>6770698</v>
       </c>
       <c r="S251" t="n">
         <v>25</v>
@@ -28391,13 +28371,13 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714946</t>
+          <t>https://artportalen.se/Sighting/96714953</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>96714952</v>
+        <v>96714960</v>
       </c>
       <c r="B252" t="n">
         <v>91402</v>
@@ -28432,10 +28412,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>470920</v>
+        <v>471091</v>
       </c>
       <c r="R252" t="n">
-        <v>6770687</v>
+        <v>6770723</v>
       </c>
       <c r="S252" t="n">
         <v>25</v>
@@ -28493,13 +28473,13 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714952</t>
+          <t>https://artportalen.se/Sighting/96714960</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>96714953</v>
+        <v>96714973</v>
       </c>
       <c r="B253" t="n">
         <v>91402</v>
@@ -28534,10 +28514,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>471086</v>
+        <v>471080</v>
       </c>
       <c r="R253" t="n">
-        <v>6770698</v>
+        <v>6770598</v>
       </c>
       <c r="S253" t="n">
         <v>25</v>
@@ -28595,13 +28575,13 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714953</t>
+          <t>https://artportalen.se/Sighting/96714973</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>96714960</v>
+        <v>96714981</v>
       </c>
       <c r="B254" t="n">
         <v>91402</v>
@@ -28636,10 +28616,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>471091</v>
+        <v>471483</v>
       </c>
       <c r="R254" t="n">
-        <v>6770723</v>
+        <v>6770715</v>
       </c>
       <c r="S254" t="n">
         <v>25</v>
@@ -28697,13 +28677,13 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714960</t>
+          <t>https://artportalen.se/Sighting/96714981</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>96714973</v>
+        <v>96715005</v>
       </c>
       <c r="B255" t="n">
         <v>91402</v>
@@ -28738,10 +28718,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>471080</v>
+        <v>470830</v>
       </c>
       <c r="R255" t="n">
-        <v>6770598</v>
+        <v>6770666</v>
       </c>
       <c r="S255" t="n">
         <v>25</v>
@@ -28799,13 +28779,13 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714973</t>
+          <t>https://artportalen.se/Sighting/96715005</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>96714981</v>
+        <v>96715010</v>
       </c>
       <c r="B256" t="n">
         <v>91402</v>
@@ -28840,10 +28820,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>471483</v>
+        <v>471253</v>
       </c>
       <c r="R256" t="n">
-        <v>6770715</v>
+        <v>6770676</v>
       </c>
       <c r="S256" t="n">
         <v>25</v>
@@ -28900,210 +28880,6 @@
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/96714981</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
-        <v>96715005</v>
-      </c>
-      <c r="B257" t="n">
-        <v>91402</v>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E257" t="n">
-        <v>256703</v>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>Tallfingersvamp</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>Ramaria eosanguinea</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr"/>
-      <c r="P257" t="inlineStr">
-        <is>
-          <t>Bonäsheden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q257" t="n">
-        <v>470830</v>
-      </c>
-      <c r="R257" t="n">
-        <v>6770666</v>
-      </c>
-      <c r="S257" t="n">
-        <v>25</v>
-      </c>
-      <c r="T257" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="AA257" t="inlineStr">
-        <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AD257" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE257" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG257" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT257" t="inlineStr"/>
-      <c r="AW257" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AX257" t="inlineStr">
-        <is>
-          <t>Andreas Öster, Maria Hindemo</t>
-        </is>
-      </c>
-      <c r="AY257" t="inlineStr"/>
-      <c r="AZ257" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/96715005</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
-        <v>96715010</v>
-      </c>
-      <c r="B258" t="n">
-        <v>91402</v>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E258" t="n">
-        <v>256703</v>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>Tallfingersvamp</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>Ramaria eosanguinea</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr"/>
-      <c r="P258" t="inlineStr">
-        <is>
-          <t>Bonäsheden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q258" t="n">
-        <v>471253</v>
-      </c>
-      <c r="R258" t="n">
-        <v>6770676</v>
-      </c>
-      <c r="S258" t="n">
-        <v>25</v>
-      </c>
-      <c r="T258" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AD258" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE258" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG258" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT258" t="inlineStr"/>
-      <c r="AW258" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AX258" t="inlineStr">
-        <is>
-          <t>Andreas Öster, Maria Hindemo</t>
-        </is>
-      </c>
-      <c r="AY258" t="inlineStr"/>
-      <c r="AZ258" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96715010</t>
         </is>
@@ -29366,8 +29142,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7756,7 +7756,7 @@
         <v>136837813</v>
       </c>
       <c r="B69" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ256"/>
+  <dimension ref="A1:AZ258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6997,48 +6997,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>96714971</v>
+        <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93201</v>
+        <v>93426</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bengttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470825</v>
+        <v>470909</v>
       </c>
       <c r="R62" t="n">
-        <v>6770664</v>
+        <v>6770448</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7062,12 +7062,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7082,49 +7092,49 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Uno Skog, Andreas Öster</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714971</t>
+          <t>https://artportalen.se/Sighting/136837910</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>96714979</v>
+        <v>96714971</v>
       </c>
       <c r="B63" t="n">
-        <v>92841</v>
+        <v>93201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7134,10 +7144,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471064</v>
+        <v>470825</v>
       </c>
       <c r="R63" t="n">
-        <v>6770563</v>
+        <v>6770664</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7195,16 +7205,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714979</t>
+          <t>https://artportalen.se/Sighting/96714971</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129943849</v>
+        <v>96714979</v>
       </c>
       <c r="B64" t="n">
-        <v>91930</v>
+        <v>92841</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7212,41 +7222,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>4745</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471451</v>
+        <v>471064</v>
       </c>
       <c r="R64" t="n">
-        <v>6770706</v>
+        <v>6770563</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7270,22 +7276,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7300,24 +7296,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943849</t>
+          <t>https://artportalen.se/Sighting/96714979</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129944262</v>
+        <v>129943849</v>
       </c>
       <c r="B65" t="n">
         <v>91930</v>
@@ -7356,10 +7352,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471369</v>
+        <v>471451</v>
       </c>
       <c r="R65" t="n">
-        <v>6770686</v>
+        <v>6770706</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7427,13 +7423,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944262</t>
+          <t>https://artportalen.se/Sighting/129943849</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129959667</v>
+        <v>129944262</v>
       </c>
       <c r="B66" t="n">
         <v>91930</v>
@@ -7463,7 +7459,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7472,10 +7468,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470864</v>
+        <v>471369</v>
       </c>
       <c r="R66" t="n">
-        <v>6770438</v>
+        <v>6770686</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7502,22 +7498,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7543,16 +7539,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959667</t>
+          <t>https://artportalen.se/Sighting/129944262</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>96714915</v>
+        <v>129959667</v>
       </c>
       <c r="B67" t="n">
-        <v>93235</v>
+        <v>91930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7560,37 +7556,41 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471343</v>
+        <v>470864</v>
       </c>
       <c r="R67" t="n">
-        <v>6770659</v>
+        <v>6770438</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7614,12 +7614,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7634,24 +7644,24 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714915</t>
+          <t>https://artportalen.se/Sighting/129959667</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>96714991</v>
+        <v>96714915</v>
       </c>
       <c r="B68" t="n">
         <v>93235</v>
@@ -7686,10 +7696,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>470824</v>
+        <v>471343</v>
       </c>
       <c r="R68" t="n">
-        <v>6770660</v>
+        <v>6770659</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7747,54 +7757,54 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714991</t>
+          <t>https://artportalen.se/Sighting/96714915</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136837813</v>
+        <v>96714991</v>
       </c>
       <c r="B69" t="n">
-        <v>93406</v>
+        <v>93235</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6055</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bengttjärnen, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470979</v>
+        <v>470824</v>
       </c>
       <c r="R69" t="n">
-        <v>6770615</v>
+        <v>6770660</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7818,12 +7828,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7838,27 +7848,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837813</t>
+          <t>https://artportalen.se/Sighting/96714991</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>96714961</v>
+        <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>90691</v>
+        <v>93410</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7866,37 +7876,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6276</v>
+        <v>6055</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bengttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471372</v>
+        <v>470971</v>
       </c>
       <c r="R70" t="n">
-        <v>6770686</v>
+        <v>6770613</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7920,12 +7930,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7940,27 +7960,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714961</t>
+          <t>https://artportalen.se/Sighting/136836580</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>96715014</v>
+        <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>90691</v>
+        <v>93410</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7968,37 +7988,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6276</v>
+        <v>6055</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bengttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470841</v>
+        <v>470979</v>
       </c>
       <c r="R71" t="n">
-        <v>6770558</v>
+        <v>6770615</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8022,12 +8042,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8042,27 +8062,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715014</t>
+          <t>https://artportalen.se/Sighting/136837813</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>96715007</v>
+        <v>96714961</v>
       </c>
       <c r="B72" t="n">
-        <v>79327</v>
+        <v>90691</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8070,21 +8090,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8094,10 +8114,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471383</v>
+        <v>471372</v>
       </c>
       <c r="R72" t="n">
-        <v>6770715</v>
+        <v>6770686</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8155,16 +8175,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715007</t>
+          <t>https://artportalen.se/Sighting/96714961</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129943529</v>
+        <v>96715014</v>
       </c>
       <c r="B73" t="n">
-        <v>79327</v>
+        <v>90691</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8172,37 +8192,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471492</v>
+        <v>470841</v>
       </c>
       <c r="R73" t="n">
-        <v>6770712</v>
+        <v>6770558</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8226,22 +8246,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8256,24 +8266,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943529</t>
+          <t>https://artportalen.se/Sighting/96715014</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129943541</v>
+        <v>96715007</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8304,17 +8314,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471478</v>
+        <v>471383</v>
       </c>
       <c r="R74" t="n">
-        <v>6770707</v>
+        <v>6770715</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8338,22 +8348,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8368,24 +8368,24 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943541</t>
+          <t>https://artportalen.se/Sighting/96715007</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129943580</v>
+        <v>129943529</v>
       </c>
       <c r="B75" t="n">
         <v>79327</v>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471468</v>
+        <v>471492</v>
       </c>
       <c r="R75" t="n">
-        <v>6770744</v>
+        <v>6770712</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8491,13 +8491,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943580</t>
+          <t>https://artportalen.se/Sighting/129943529</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129943763</v>
+        <v>129943541</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471466</v>
+        <v>471478</v>
       </c>
       <c r="R76" t="n">
-        <v>6770713</v>
+        <v>6770707</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8603,13 +8603,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943763</t>
+          <t>https://artportalen.se/Sighting/129943541</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129943809</v>
+        <v>129943580</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471447</v>
+        <v>471468</v>
       </c>
       <c r="R77" t="n">
-        <v>6770716</v>
+        <v>6770744</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8715,13 +8715,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943809</t>
+          <t>https://artportalen.se/Sighting/129943580</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129943855</v>
+        <v>129943763</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471451</v>
+        <v>471466</v>
       </c>
       <c r="R78" t="n">
-        <v>6770706</v>
+        <v>6770713</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8827,13 +8827,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943855</t>
+          <t>https://artportalen.se/Sighting/129943763</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129943914</v>
+        <v>129943809</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -8868,10 +8868,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471432</v>
+        <v>471447</v>
       </c>
       <c r="R79" t="n">
-        <v>6770701</v>
+        <v>6770716</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8939,13 +8939,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943914</t>
+          <t>https://artportalen.se/Sighting/129943809</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129943999</v>
+        <v>129943855</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471428</v>
+        <v>471451</v>
       </c>
       <c r="R80" t="n">
-        <v>6770747</v>
+        <v>6770706</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9051,13 +9051,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943999</t>
+          <t>https://artportalen.se/Sighting/129943855</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129944026</v>
+        <v>129943914</v>
       </c>
       <c r="B81" t="n">
         <v>79327</v>
@@ -9092,10 +9092,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471422</v>
+        <v>471432</v>
       </c>
       <c r="R81" t="n">
-        <v>6770745</v>
+        <v>6770701</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9163,13 +9163,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944026</t>
+          <t>https://artportalen.se/Sighting/129943914</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129944037</v>
+        <v>129943999</v>
       </c>
       <c r="B82" t="n">
         <v>79327</v>
@@ -9204,10 +9204,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471417</v>
+        <v>471428</v>
       </c>
       <c r="R82" t="n">
-        <v>6770738</v>
+        <v>6770747</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9275,13 +9275,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944037</t>
+          <t>https://artportalen.se/Sighting/129943999</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944164</v>
+        <v>129944026</v>
       </c>
       <c r="B83" t="n">
         <v>79327</v>
@@ -9316,10 +9316,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471363</v>
+        <v>471422</v>
       </c>
       <c r="R83" t="n">
-        <v>6770736</v>
+        <v>6770745</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9387,13 +9387,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944164</t>
+          <t>https://artportalen.se/Sighting/129944026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944178</v>
+        <v>129944037</v>
       </c>
       <c r="B84" t="n">
         <v>79327</v>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471372</v>
+        <v>471417</v>
       </c>
       <c r="R84" t="n">
-        <v>6770719</v>
+        <v>6770738</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9499,13 +9499,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944178</t>
+          <t>https://artportalen.se/Sighting/129944037</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129944210</v>
+        <v>129944164</v>
       </c>
       <c r="B85" t="n">
         <v>79327</v>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471390</v>
+        <v>471363</v>
       </c>
       <c r="R85" t="n">
-        <v>6770705</v>
+        <v>6770736</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,13 +9611,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944210</t>
+          <t>https://artportalen.se/Sighting/129944164</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129944228</v>
+        <v>129944178</v>
       </c>
       <c r="B86" t="n">
         <v>79327</v>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471390</v>
+        <v>471372</v>
       </c>
       <c r="R86" t="n">
-        <v>6770693</v>
+        <v>6770719</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9723,13 +9723,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944228</t>
+          <t>https://artportalen.se/Sighting/129944178</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129944311</v>
+        <v>129944210</v>
       </c>
       <c r="B87" t="n">
         <v>79327</v>
@@ -9764,10 +9764,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471369</v>
+        <v>471390</v>
       </c>
       <c r="R87" t="n">
-        <v>6770686</v>
+        <v>6770705</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9835,13 +9835,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944311</t>
+          <t>https://artportalen.se/Sighting/129944210</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129944355</v>
+        <v>129944228</v>
       </c>
       <c r="B88" t="n">
         <v>79327</v>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471342</v>
+        <v>471390</v>
       </c>
       <c r="R88" t="n">
-        <v>6770682</v>
+        <v>6770693</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9947,13 +9947,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944355</t>
+          <t>https://artportalen.se/Sighting/129944228</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129944466</v>
+        <v>129944311</v>
       </c>
       <c r="B89" t="n">
         <v>79327</v>
@@ -9988,10 +9988,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471322</v>
+        <v>471369</v>
       </c>
       <c r="R89" t="n">
-        <v>6770702</v>
+        <v>6770686</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10059,13 +10059,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944466</t>
+          <t>https://artportalen.se/Sighting/129944311</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129944473</v>
+        <v>129944355</v>
       </c>
       <c r="B90" t="n">
         <v>79327</v>
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471328</v>
+        <v>471342</v>
       </c>
       <c r="R90" t="n">
-        <v>6770726</v>
+        <v>6770682</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10171,13 +10171,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944473</t>
+          <t>https://artportalen.se/Sighting/129944355</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129944488</v>
+        <v>129944466</v>
       </c>
       <c r="B91" t="n">
         <v>79327</v>
@@ -10212,10 +10212,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471318</v>
+        <v>471322</v>
       </c>
       <c r="R91" t="n">
-        <v>6770729</v>
+        <v>6770702</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10283,13 +10283,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944488</t>
+          <t>https://artportalen.se/Sighting/129944466</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129944495</v>
+        <v>129944473</v>
       </c>
       <c r="B92" t="n">
         <v>79327</v>
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471288</v>
+        <v>471328</v>
       </c>
       <c r="R92" t="n">
-        <v>6770728</v>
+        <v>6770726</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10395,13 +10395,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944495</t>
+          <t>https://artportalen.se/Sighting/129944473</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129944523</v>
+        <v>129944488</v>
       </c>
       <c r="B93" t="n">
         <v>79327</v>
@@ -10436,10 +10436,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471303</v>
+        <v>471318</v>
       </c>
       <c r="R93" t="n">
-        <v>6770699</v>
+        <v>6770729</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10507,13 +10507,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944523</t>
+          <t>https://artportalen.se/Sighting/129944488</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129944544</v>
+        <v>129944495</v>
       </c>
       <c r="B94" t="n">
         <v>79327</v>
@@ -10548,10 +10548,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471330</v>
+        <v>471288</v>
       </c>
       <c r="R94" t="n">
-        <v>6770712</v>
+        <v>6770728</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10619,13 +10619,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944544</t>
+          <t>https://artportalen.se/Sighting/129944495</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129944592</v>
+        <v>129944523</v>
       </c>
       <c r="B95" t="n">
         <v>79327</v>
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471313</v>
+        <v>471303</v>
       </c>
       <c r="R95" t="n">
-        <v>6770688</v>
+        <v>6770699</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10731,13 +10731,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944592</t>
+          <t>https://artportalen.se/Sighting/129944523</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129944756</v>
+        <v>129944544</v>
       </c>
       <c r="B96" t="n">
         <v>79327</v>
@@ -10772,10 +10772,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471288</v>
+        <v>471330</v>
       </c>
       <c r="R96" t="n">
-        <v>6770685</v>
+        <v>6770712</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10843,13 +10843,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944756</t>
+          <t>https://artportalen.se/Sighting/129944544</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129944762</v>
+        <v>129944592</v>
       </c>
       <c r="B97" t="n">
         <v>79327</v>
@@ -10884,10 +10884,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471276</v>
+        <v>471313</v>
       </c>
       <c r="R97" t="n">
-        <v>6770703</v>
+        <v>6770688</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10955,13 +10955,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944762</t>
+          <t>https://artportalen.se/Sighting/129944592</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129944804</v>
+        <v>129944756</v>
       </c>
       <c r="B98" t="n">
         <v>79327</v>
@@ -10996,10 +10996,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471271</v>
+        <v>471288</v>
       </c>
       <c r="R98" t="n">
-        <v>6770733</v>
+        <v>6770685</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11067,13 +11067,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944804</t>
+          <t>https://artportalen.se/Sighting/129944756</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129944807</v>
+        <v>129944762</v>
       </c>
       <c r="B99" t="n">
         <v>79327</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471248</v>
+        <v>471276</v>
       </c>
       <c r="R99" t="n">
-        <v>6770737</v>
+        <v>6770703</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11179,13 +11179,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944807</t>
+          <t>https://artportalen.se/Sighting/129944762</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944809</v>
+        <v>129944804</v>
       </c>
       <c r="B100" t="n">
         <v>79327</v>
@@ -11220,10 +11220,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471247</v>
+        <v>471271</v>
       </c>
       <c r="R100" t="n">
-        <v>6770726</v>
+        <v>6770733</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11291,13 +11291,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944809</t>
+          <t>https://artportalen.se/Sighting/129944804</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129944917</v>
+        <v>129944807</v>
       </c>
       <c r="B101" t="n">
         <v>79327</v>
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471263</v>
+        <v>471248</v>
       </c>
       <c r="R101" t="n">
-        <v>6770694</v>
+        <v>6770737</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,13 +11403,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944917</t>
+          <t>https://artportalen.se/Sighting/129944807</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129944975</v>
+        <v>129944809</v>
       </c>
       <c r="B102" t="n">
         <v>79327</v>
@@ -11444,10 +11444,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471242</v>
+        <v>471247</v>
       </c>
       <c r="R102" t="n">
-        <v>6770682</v>
+        <v>6770726</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11515,13 +11515,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944975</t>
+          <t>https://artportalen.se/Sighting/129944809</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129945066</v>
+        <v>129944917</v>
       </c>
       <c r="B103" t="n">
         <v>79327</v>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471239</v>
+        <v>471263</v>
       </c>
       <c r="R103" t="n">
-        <v>6770732</v>
+        <v>6770694</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11627,13 +11627,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945066</t>
+          <t>https://artportalen.se/Sighting/129944917</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129945078</v>
+        <v>129944975</v>
       </c>
       <c r="B104" t="n">
         <v>79327</v>
@@ -11668,10 +11668,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471209</v>
+        <v>471242</v>
       </c>
       <c r="R104" t="n">
-        <v>6770731</v>
+        <v>6770682</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11739,13 +11739,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945078</t>
+          <t>https://artportalen.se/Sighting/129944975</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129945104</v>
+        <v>129945066</v>
       </c>
       <c r="B105" t="n">
         <v>79327</v>
@@ -11780,10 +11780,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471219</v>
+        <v>471239</v>
       </c>
       <c r="R105" t="n">
-        <v>6770720</v>
+        <v>6770732</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11851,13 +11851,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945104</t>
+          <t>https://artportalen.se/Sighting/129945066</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129945451</v>
+        <v>129945078</v>
       </c>
       <c r="B106" t="n">
         <v>79327</v>
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471189</v>
+        <v>471209</v>
       </c>
       <c r="R106" t="n">
-        <v>6770706</v>
+        <v>6770731</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11963,13 +11963,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945451</t>
+          <t>https://artportalen.se/Sighting/129945078</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129945509</v>
+        <v>129945104</v>
       </c>
       <c r="B107" t="n">
         <v>79327</v>
@@ -12004,10 +12004,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471198</v>
+        <v>471219</v>
       </c>
       <c r="R107" t="n">
-        <v>6770689</v>
+        <v>6770720</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12052,11 +12052,6 @@
           <t>11:17</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12080,13 +12075,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945509</t>
+          <t>https://artportalen.se/Sighting/129945104</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129946029</v>
+        <v>129945451</v>
       </c>
       <c r="B108" t="n">
         <v>79327</v>
@@ -12121,10 +12116,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471185</v>
+        <v>471189</v>
       </c>
       <c r="R108" t="n">
-        <v>6770690</v>
+        <v>6770706</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12192,13 +12187,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946029</t>
+          <t>https://artportalen.se/Sighting/129945451</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129946053</v>
+        <v>129945509</v>
       </c>
       <c r="B109" t="n">
         <v>79327</v>
@@ -12233,10 +12228,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471161</v>
+        <v>471198</v>
       </c>
       <c r="R109" t="n">
-        <v>6770705</v>
+        <v>6770689</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12281,6 +12276,11 @@
           <t>11:17</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12304,13 +12304,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946053</t>
+          <t>https://artportalen.se/Sighting/129945509</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129946117</v>
+        <v>129946029</v>
       </c>
       <c r="B110" t="n">
         <v>79327</v>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471106</v>
+        <v>471185</v>
       </c>
       <c r="R110" t="n">
-        <v>6770711</v>
+        <v>6770690</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12416,13 +12416,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946117</t>
+          <t>https://artportalen.se/Sighting/129946029</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129946170</v>
+        <v>129946053</v>
       </c>
       <c r="B111" t="n">
         <v>79327</v>
@@ -12457,10 +12457,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471030</v>
+        <v>471161</v>
       </c>
       <c r="R111" t="n">
-        <v>6770688</v>
+        <v>6770705</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12528,13 +12528,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946170</t>
+          <t>https://artportalen.se/Sighting/129946053</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129946182</v>
+        <v>129946117</v>
       </c>
       <c r="B112" t="n">
         <v>79327</v>
@@ -12569,10 +12569,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471000</v>
+        <v>471106</v>
       </c>
       <c r="R112" t="n">
-        <v>6770675</v>
+        <v>6770711</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12640,13 +12640,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946182</t>
+          <t>https://artportalen.se/Sighting/129946117</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129946197</v>
+        <v>129946170</v>
       </c>
       <c r="B113" t="n">
         <v>79327</v>
@@ -12681,10 +12681,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>470971</v>
+        <v>471030</v>
       </c>
       <c r="R113" t="n">
-        <v>6770676</v>
+        <v>6770688</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12752,13 +12752,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946197</t>
+          <t>https://artportalen.se/Sighting/129946170</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129946408</v>
+        <v>129946182</v>
       </c>
       <c r="B114" t="n">
         <v>79327</v>
@@ -12793,10 +12793,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>470921</v>
+        <v>471000</v>
       </c>
       <c r="R114" t="n">
-        <v>6770579</v>
+        <v>6770675</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12864,13 +12864,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946408</t>
+          <t>https://artportalen.se/Sighting/129946182</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129946586</v>
+        <v>129946197</v>
       </c>
       <c r="B115" t="n">
         <v>79327</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471095</v>
+        <v>470971</v>
       </c>
       <c r="R115" t="n">
-        <v>6770660</v>
+        <v>6770676</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12976,13 +12976,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946586</t>
+          <t>https://artportalen.se/Sighting/129946197</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129946708</v>
+        <v>129946408</v>
       </c>
       <c r="B116" t="n">
         <v>79327</v>
@@ -13017,10 +13017,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471171</v>
+        <v>470921</v>
       </c>
       <c r="R116" t="n">
-        <v>6770660</v>
+        <v>6770579</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13088,13 +13088,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946708</t>
+          <t>https://artportalen.se/Sighting/129946408</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129954408</v>
+        <v>129946586</v>
       </c>
       <c r="B117" t="n">
         <v>79327</v>
@@ -13129,10 +13129,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471019</v>
+        <v>471095</v>
       </c>
       <c r="R117" t="n">
-        <v>6770666</v>
+        <v>6770660</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13159,22 +13159,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13200,13 +13200,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954408</t>
+          <t>https://artportalen.se/Sighting/129946586</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129954413</v>
+        <v>129946708</v>
       </c>
       <c r="B118" t="n">
         <v>79327</v>
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>471028</v>
+        <v>471171</v>
       </c>
       <c r="R118" t="n">
-        <v>6770675</v>
+        <v>6770660</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13271,22 +13271,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13312,13 +13312,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954413</t>
+          <t>https://artportalen.se/Sighting/129946708</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129954442</v>
+        <v>129954408</v>
       </c>
       <c r="B119" t="n">
         <v>79327</v>
@@ -13353,10 +13353,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471053</v>
+        <v>471019</v>
       </c>
       <c r="R119" t="n">
-        <v>6770682</v>
+        <v>6770666</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13424,13 +13424,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954442</t>
+          <t>https://artportalen.se/Sighting/129954408</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129954452</v>
+        <v>129954413</v>
       </c>
       <c r="B120" t="n">
         <v>79327</v>
@@ -13465,10 +13465,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471058</v>
+        <v>471028</v>
       </c>
       <c r="R120" t="n">
-        <v>6770677</v>
+        <v>6770675</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13536,13 +13536,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954452</t>
+          <t>https://artportalen.se/Sighting/129954413</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129954531</v>
+        <v>129954442</v>
       </c>
       <c r="B121" t="n">
         <v>79327</v>
@@ -13577,10 +13577,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471106</v>
+        <v>471053</v>
       </c>
       <c r="R121" t="n">
-        <v>6770683</v>
+        <v>6770682</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13648,13 +13648,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954531</t>
+          <t>https://artportalen.se/Sighting/129954442</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129954534</v>
+        <v>129954452</v>
       </c>
       <c r="B122" t="n">
         <v>79327</v>
@@ -13689,10 +13689,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471086</v>
+        <v>471058</v>
       </c>
       <c r="R122" t="n">
-        <v>6770684</v>
+        <v>6770677</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13760,13 +13760,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954534</t>
+          <t>https://artportalen.se/Sighting/129954452</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129954584</v>
+        <v>129954531</v>
       </c>
       <c r="B123" t="n">
         <v>79327</v>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471062</v>
+        <v>471106</v>
       </c>
       <c r="R123" t="n">
-        <v>6770731</v>
+        <v>6770683</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13872,13 +13872,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954584</t>
+          <t>https://artportalen.se/Sighting/129954531</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129954590</v>
+        <v>129954534</v>
       </c>
       <c r="B124" t="n">
         <v>79327</v>
@@ -13913,10 +13913,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471013</v>
+        <v>471086</v>
       </c>
       <c r="R124" t="n">
-        <v>6770715</v>
+        <v>6770684</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13984,13 +13984,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954590</t>
+          <t>https://artportalen.se/Sighting/129954534</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129954674</v>
+        <v>129954584</v>
       </c>
       <c r="B125" t="n">
         <v>79327</v>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470938</v>
+        <v>471062</v>
       </c>
       <c r="R125" t="n">
-        <v>6770693</v>
+        <v>6770731</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14096,13 +14096,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954674</t>
+          <t>https://artportalen.se/Sighting/129954584</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129955100</v>
+        <v>129954590</v>
       </c>
       <c r="B126" t="n">
         <v>79327</v>
@@ -14137,10 +14137,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470981</v>
+        <v>471013</v>
       </c>
       <c r="R126" t="n">
-        <v>6770691</v>
+        <v>6770715</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14208,13 +14208,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129955100</t>
+          <t>https://artportalen.se/Sighting/129954590</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129955313</v>
+        <v>129954674</v>
       </c>
       <c r="B127" t="n">
         <v>79327</v>
@@ -14249,10 +14249,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470992</v>
+        <v>470938</v>
       </c>
       <c r="R127" t="n">
-        <v>6770702</v>
+        <v>6770693</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14320,13 +14320,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129955313</t>
+          <t>https://artportalen.se/Sighting/129954674</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129956843</v>
+        <v>129955100</v>
       </c>
       <c r="B128" t="n">
         <v>79327</v>
@@ -14361,10 +14361,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470953</v>
+        <v>470981</v>
       </c>
       <c r="R128" t="n">
-        <v>6770692</v>
+        <v>6770691</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14432,13 +14432,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956843</t>
+          <t>https://artportalen.se/Sighting/129955100</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129956851</v>
+        <v>129955313</v>
       </c>
       <c r="B129" t="n">
         <v>79327</v>
@@ -14473,10 +14473,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470928</v>
+        <v>470992</v>
       </c>
       <c r="R129" t="n">
-        <v>6770695</v>
+        <v>6770702</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14544,13 +14544,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956851</t>
+          <t>https://artportalen.se/Sighting/129955313</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129956859</v>
+        <v>129956843</v>
       </c>
       <c r="B130" t="n">
         <v>79327</v>
@@ -14585,10 +14585,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470936</v>
+        <v>470953</v>
       </c>
       <c r="R130" t="n">
-        <v>6770721</v>
+        <v>6770692</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14656,13 +14656,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956859</t>
+          <t>https://artportalen.se/Sighting/129956843</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129957713</v>
+        <v>129956851</v>
       </c>
       <c r="B131" t="n">
         <v>79327</v>
@@ -14697,10 +14697,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470904</v>
+        <v>470928</v>
       </c>
       <c r="R131" t="n">
-        <v>6770718</v>
+        <v>6770695</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14768,13 +14768,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957713</t>
+          <t>https://artportalen.se/Sighting/129956851</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129957969</v>
+        <v>129956859</v>
       </c>
       <c r="B132" t="n">
         <v>79327</v>
@@ -14809,10 +14809,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470911</v>
+        <v>470936</v>
       </c>
       <c r="R132" t="n">
-        <v>6770707</v>
+        <v>6770721</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14880,13 +14880,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957969</t>
+          <t>https://artportalen.se/Sighting/129956859</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129958010</v>
+        <v>129957713</v>
       </c>
       <c r="B133" t="n">
         <v>79327</v>
@@ -14921,10 +14921,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>470894</v>
+        <v>470904</v>
       </c>
       <c r="R133" t="n">
-        <v>6770713</v>
+        <v>6770718</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14992,13 +14992,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958010</t>
+          <t>https://artportalen.se/Sighting/129957713</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129958133</v>
+        <v>129957969</v>
       </c>
       <c r="B134" t="n">
         <v>79327</v>
@@ -15033,10 +15033,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>470869</v>
+        <v>470911</v>
       </c>
       <c r="R134" t="n">
-        <v>6770702</v>
+        <v>6770707</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15104,13 +15104,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958133</t>
+          <t>https://artportalen.se/Sighting/129957969</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129958151</v>
+        <v>129958010</v>
       </c>
       <c r="B135" t="n">
         <v>79327</v>
@@ -15145,10 +15145,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470842</v>
+        <v>470894</v>
       </c>
       <c r="R135" t="n">
-        <v>6770709</v>
+        <v>6770713</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15216,13 +15216,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958151</t>
+          <t>https://artportalen.se/Sighting/129958010</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129958214</v>
+        <v>129958133</v>
       </c>
       <c r="B136" t="n">
         <v>79327</v>
@@ -15257,10 +15257,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470823</v>
+        <v>470869</v>
       </c>
       <c r="R136" t="n">
-        <v>6770705</v>
+        <v>6770702</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15328,13 +15328,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958214</t>
+          <t>https://artportalen.se/Sighting/129958133</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129958228</v>
+        <v>129958151</v>
       </c>
       <c r="B137" t="n">
         <v>79327</v>
@@ -15369,10 +15369,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470813</v>
+        <v>470842</v>
       </c>
       <c r="R137" t="n">
-        <v>6770681</v>
+        <v>6770709</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15440,13 +15440,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958228</t>
+          <t>https://artportalen.se/Sighting/129958151</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129958464</v>
+        <v>129958214</v>
       </c>
       <c r="B138" t="n">
         <v>79327</v>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470822</v>
+        <v>470823</v>
       </c>
       <c r="R138" t="n">
-        <v>6770673</v>
+        <v>6770705</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15552,13 +15552,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958464</t>
+          <t>https://artportalen.se/Sighting/129958214</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129958466</v>
+        <v>129958228</v>
       </c>
       <c r="B139" t="n">
         <v>79327</v>
@@ -15593,10 +15593,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470812</v>
+        <v>470813</v>
       </c>
       <c r="R139" t="n">
-        <v>6770670</v>
+        <v>6770681</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15664,13 +15664,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958466</t>
+          <t>https://artportalen.se/Sighting/129958228</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129958499</v>
+        <v>129958464</v>
       </c>
       <c r="B140" t="n">
         <v>79327</v>
@@ -15705,10 +15705,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470850</v>
+        <v>470822</v>
       </c>
       <c r="R140" t="n">
-        <v>6770690</v>
+        <v>6770673</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15776,13 +15776,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958499</t>
+          <t>https://artportalen.se/Sighting/129958464</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129958545</v>
+        <v>129958466</v>
       </c>
       <c r="B141" t="n">
         <v>79327</v>
@@ -15817,10 +15817,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>470877</v>
+        <v>470812</v>
       </c>
       <c r="R141" t="n">
-        <v>6770687</v>
+        <v>6770670</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15888,13 +15888,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958545</t>
+          <t>https://artportalen.se/Sighting/129958466</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129958694</v>
+        <v>129958499</v>
       </c>
       <c r="B142" t="n">
         <v>79327</v>
@@ -15929,10 +15929,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>470844</v>
+        <v>470850</v>
       </c>
       <c r="R142" t="n">
-        <v>6770699</v>
+        <v>6770690</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16000,13 +16000,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958694</t>
+          <t>https://artportalen.se/Sighting/129958499</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129958706</v>
+        <v>129958545</v>
       </c>
       <c r="B143" t="n">
         <v>79327</v>
@@ -16041,10 +16041,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>470816</v>
+        <v>470877</v>
       </c>
       <c r="R143" t="n">
-        <v>6770646</v>
+        <v>6770687</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16112,13 +16112,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958706</t>
+          <t>https://artportalen.se/Sighting/129958545</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129958754</v>
+        <v>129958694</v>
       </c>
       <c r="B144" t="n">
         <v>79327</v>
@@ -16153,10 +16153,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>470817</v>
+        <v>470844</v>
       </c>
       <c r="R144" t="n">
-        <v>6770608</v>
+        <v>6770699</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16224,13 +16224,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958754</t>
+          <t>https://artportalen.se/Sighting/129958694</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129958775</v>
+        <v>129958706</v>
       </c>
       <c r="B145" t="n">
         <v>79327</v>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>470803</v>
+        <v>470816</v>
       </c>
       <c r="R145" t="n">
-        <v>6770595</v>
+        <v>6770646</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16336,13 +16336,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958775</t>
+          <t>https://artportalen.se/Sighting/129958706</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129958795</v>
+        <v>129958754</v>
       </c>
       <c r="B146" t="n">
         <v>79327</v>
@@ -16377,10 +16377,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>470822</v>
+        <v>470817</v>
       </c>
       <c r="R146" t="n">
-        <v>6770615</v>
+        <v>6770608</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16425,11 +16425,6 @@
           <t>09:55</t>
         </is>
       </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
@@ -16453,13 +16448,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958795</t>
+          <t>https://artportalen.se/Sighting/129958754</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129958800</v>
+        <v>129958775</v>
       </c>
       <c r="B147" t="n">
         <v>79327</v>
@@ -16494,10 +16489,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470858</v>
+        <v>470803</v>
       </c>
       <c r="R147" t="n">
-        <v>6770602</v>
+        <v>6770595</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16565,13 +16560,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958800</t>
+          <t>https://artportalen.se/Sighting/129958775</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129958828</v>
+        <v>129958795</v>
       </c>
       <c r="B148" t="n">
         <v>79327</v>
@@ -16606,10 +16601,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470871</v>
+        <v>470822</v>
       </c>
       <c r="R148" t="n">
-        <v>6770635</v>
+        <v>6770615</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16654,6 +16649,11 @@
           <t>09:55</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -16677,13 +16677,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958828</t>
+          <t>https://artportalen.se/Sighting/129958795</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129958841</v>
+        <v>129958800</v>
       </c>
       <c r="B149" t="n">
         <v>79327</v>
@@ -16718,10 +16718,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>470828</v>
+        <v>470858</v>
       </c>
       <c r="R149" t="n">
-        <v>6770636</v>
+        <v>6770602</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16789,13 +16789,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958841</t>
+          <t>https://artportalen.se/Sighting/129958800</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129958842</v>
+        <v>129958828</v>
       </c>
       <c r="B150" t="n">
         <v>79327</v>
@@ -16830,10 +16830,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>470820</v>
+        <v>470871</v>
       </c>
       <c r="R150" t="n">
-        <v>6770624</v>
+        <v>6770635</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16901,13 +16901,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958842</t>
+          <t>https://artportalen.se/Sighting/129958828</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129958895</v>
+        <v>129958841</v>
       </c>
       <c r="B151" t="n">
         <v>79327</v>
@@ -16942,10 +16942,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>470887</v>
+        <v>470828</v>
       </c>
       <c r="R151" t="n">
-        <v>6770658</v>
+        <v>6770636</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17013,13 +17013,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958895</t>
+          <t>https://artportalen.se/Sighting/129958841</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129958937</v>
+        <v>129958842</v>
       </c>
       <c r="B152" t="n">
         <v>79327</v>
@@ -17054,10 +17054,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>470897</v>
+        <v>470820</v>
       </c>
       <c r="R152" t="n">
-        <v>6770647</v>
+        <v>6770624</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17125,13 +17125,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958937</t>
+          <t>https://artportalen.se/Sighting/129958842</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129959037</v>
+        <v>129958895</v>
       </c>
       <c r="B153" t="n">
         <v>79327</v>
@@ -17166,10 +17166,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>470908</v>
+        <v>470887</v>
       </c>
       <c r="R153" t="n">
-        <v>6770622</v>
+        <v>6770658</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17237,13 +17237,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959037</t>
+          <t>https://artportalen.se/Sighting/129958895</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129959060</v>
+        <v>129958937</v>
       </c>
       <c r="B154" t="n">
         <v>79327</v>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>470926</v>
+        <v>470897</v>
       </c>
       <c r="R154" t="n">
-        <v>6770613</v>
+        <v>6770647</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17349,13 +17349,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959060</t>
+          <t>https://artportalen.se/Sighting/129958937</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129959250</v>
+        <v>129959037</v>
       </c>
       <c r="B155" t="n">
         <v>79327</v>
@@ -17390,10 +17390,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470943</v>
+        <v>470908</v>
       </c>
       <c r="R155" t="n">
-        <v>6770559</v>
+        <v>6770622</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17461,13 +17461,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959250</t>
+          <t>https://artportalen.se/Sighting/129959037</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129959256</v>
+        <v>129959060</v>
       </c>
       <c r="B156" t="n">
         <v>79327</v>
@@ -17502,10 +17502,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>470922</v>
+        <v>470926</v>
       </c>
       <c r="R156" t="n">
-        <v>6770556</v>
+        <v>6770613</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17573,13 +17573,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959256</t>
+          <t>https://artportalen.se/Sighting/129959060</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129959294</v>
+        <v>129959250</v>
       </c>
       <c r="B157" t="n">
         <v>79327</v>
@@ -17614,10 +17614,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>470904</v>
+        <v>470943</v>
       </c>
       <c r="R157" t="n">
-        <v>6770537</v>
+        <v>6770559</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17685,13 +17685,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959294</t>
+          <t>https://artportalen.se/Sighting/129959250</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129959303</v>
+        <v>129959256</v>
       </c>
       <c r="B158" t="n">
         <v>79327</v>
@@ -17726,10 +17726,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470879</v>
+        <v>470922</v>
       </c>
       <c r="R158" t="n">
-        <v>6770545</v>
+        <v>6770556</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17797,13 +17797,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959303</t>
+          <t>https://artportalen.se/Sighting/129959256</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129959375</v>
+        <v>129959294</v>
       </c>
       <c r="B159" t="n">
         <v>79327</v>
@@ -17838,10 +17838,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>470851</v>
+        <v>470904</v>
       </c>
       <c r="R159" t="n">
-        <v>6770520</v>
+        <v>6770537</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17909,13 +17909,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959375</t>
+          <t>https://artportalen.se/Sighting/129959294</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129959389</v>
+        <v>129959303</v>
       </c>
       <c r="B160" t="n">
         <v>79327</v>
@@ -17950,10 +17950,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>470824</v>
+        <v>470879</v>
       </c>
       <c r="R160" t="n">
-        <v>6770523</v>
+        <v>6770545</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18021,13 +18021,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959389</t>
+          <t>https://artportalen.se/Sighting/129959303</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129959479</v>
+        <v>129959375</v>
       </c>
       <c r="B161" t="n">
         <v>79327</v>
@@ -18062,10 +18062,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>470837</v>
+        <v>470851</v>
       </c>
       <c r="R161" t="n">
-        <v>6770498</v>
+        <v>6770520</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18133,13 +18133,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959479</t>
+          <t>https://artportalen.se/Sighting/129959375</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129959501</v>
+        <v>129959389</v>
       </c>
       <c r="B162" t="n">
         <v>79327</v>
@@ -18174,10 +18174,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>470807</v>
+        <v>470824</v>
       </c>
       <c r="R162" t="n">
-        <v>6770491</v>
+        <v>6770523</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18245,13 +18245,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959501</t>
+          <t>https://artportalen.se/Sighting/129959389</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129959519</v>
+        <v>129959479</v>
       </c>
       <c r="B163" t="n">
         <v>79327</v>
@@ -18286,10 +18286,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>470822</v>
+        <v>470837</v>
       </c>
       <c r="R163" t="n">
-        <v>6770452</v>
+        <v>6770498</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18357,13 +18357,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959519</t>
+          <t>https://artportalen.se/Sighting/129959479</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129959692</v>
+        <v>129959501</v>
       </c>
       <c r="B164" t="n">
         <v>79327</v>
@@ -18398,10 +18398,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>470864</v>
+        <v>470807</v>
       </c>
       <c r="R164" t="n">
-        <v>6770438</v>
+        <v>6770491</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18469,13 +18469,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959692</t>
+          <t>https://artportalen.se/Sighting/129959501</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129959740</v>
+        <v>129959519</v>
       </c>
       <c r="B165" t="n">
         <v>79327</v>
@@ -18510,10 +18510,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>470905</v>
+        <v>470822</v>
       </c>
       <c r="R165" t="n">
-        <v>6770435</v>
+        <v>6770452</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18581,13 +18581,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959740</t>
+          <t>https://artportalen.se/Sighting/129959519</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129959772</v>
+        <v>129959692</v>
       </c>
       <c r="B166" t="n">
         <v>79327</v>
@@ -18622,10 +18622,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470900</v>
+        <v>470864</v>
       </c>
       <c r="R166" t="n">
-        <v>6770473</v>
+        <v>6770438</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18693,13 +18693,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959772</t>
+          <t>https://artportalen.se/Sighting/129959692</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129959808</v>
+        <v>129959740</v>
       </c>
       <c r="B167" t="n">
         <v>79327</v>
@@ -18734,10 +18734,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470942</v>
+        <v>470905</v>
       </c>
       <c r="R167" t="n">
-        <v>6770455</v>
+        <v>6770435</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18805,13 +18805,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959808</t>
+          <t>https://artportalen.se/Sighting/129959740</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129959994</v>
+        <v>129959772</v>
       </c>
       <c r="B168" t="n">
         <v>79327</v>
@@ -18846,10 +18846,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>470954</v>
+        <v>470900</v>
       </c>
       <c r="R168" t="n">
-        <v>6770475</v>
+        <v>6770473</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18917,13 +18917,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959994</t>
+          <t>https://artportalen.se/Sighting/129959772</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129960002</v>
+        <v>129959808</v>
       </c>
       <c r="B169" t="n">
         <v>79327</v>
@@ -18958,10 +18958,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>470932</v>
+        <v>470942</v>
       </c>
       <c r="R169" t="n">
-        <v>6770480</v>
+        <v>6770455</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19029,13 +19029,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960002</t>
+          <t>https://artportalen.se/Sighting/129959808</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129960437</v>
+        <v>129959994</v>
       </c>
       <c r="B170" t="n">
         <v>79327</v>
@@ -19070,10 +19070,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>470948</v>
+        <v>470954</v>
       </c>
       <c r="R170" t="n">
-        <v>6770533</v>
+        <v>6770475</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19141,13 +19141,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960437</t>
+          <t>https://artportalen.se/Sighting/129959994</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129960691</v>
+        <v>129960002</v>
       </c>
       <c r="B171" t="n">
         <v>79327</v>
@@ -19182,10 +19182,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>471056</v>
+        <v>470932</v>
       </c>
       <c r="R171" t="n">
-        <v>6770494</v>
+        <v>6770480</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19253,13 +19253,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960691</t>
+          <t>https://artportalen.se/Sighting/129960002</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129960763</v>
+        <v>129960437</v>
       </c>
       <c r="B172" t="n">
         <v>79327</v>
@@ -19294,10 +19294,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>471062</v>
+        <v>470948</v>
       </c>
       <c r="R172" t="n">
-        <v>6770538</v>
+        <v>6770533</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19365,13 +19365,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960763</t>
+          <t>https://artportalen.se/Sighting/129960437</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129960790</v>
+        <v>129960691</v>
       </c>
       <c r="B173" t="n">
         <v>79327</v>
@@ -19406,10 +19406,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471073</v>
+        <v>471056</v>
       </c>
       <c r="R173" t="n">
-        <v>6770551</v>
+        <v>6770494</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19477,13 +19477,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960790</t>
+          <t>https://artportalen.se/Sighting/129960691</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129960823</v>
+        <v>129960763</v>
       </c>
       <c r="B174" t="n">
         <v>79327</v>
@@ -19518,10 +19518,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>471078</v>
+        <v>471062</v>
       </c>
       <c r="R174" t="n">
-        <v>6770561</v>
+        <v>6770538</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19566,11 +19566,6 @@
           <t>09:55</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -19594,13 +19589,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960823</t>
+          <t>https://artportalen.se/Sighting/129960763</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129960843</v>
+        <v>129960790</v>
       </c>
       <c r="B175" t="n">
         <v>79327</v>
@@ -19635,10 +19630,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471097</v>
+        <v>471073</v>
       </c>
       <c r="R175" t="n">
-        <v>6770561</v>
+        <v>6770551</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19706,13 +19701,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960843</t>
+          <t>https://artportalen.se/Sighting/129960790</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129960864</v>
+        <v>129960823</v>
       </c>
       <c r="B176" t="n">
         <v>79327</v>
@@ -19747,10 +19742,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471116</v>
+        <v>471078</v>
       </c>
       <c r="R176" t="n">
-        <v>6770565</v>
+        <v>6770561</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19795,6 +19790,11 @@
           <t>09:55</t>
         </is>
       </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
@@ -19818,13 +19818,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960864</t>
+          <t>https://artportalen.se/Sighting/129960823</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129960884</v>
+        <v>129960843</v>
       </c>
       <c r="B177" t="n">
         <v>79327</v>
@@ -19859,10 +19859,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>471129</v>
+        <v>471097</v>
       </c>
       <c r="R177" t="n">
-        <v>6770567</v>
+        <v>6770561</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19930,13 +19930,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960884</t>
+          <t>https://artportalen.se/Sighting/129960843</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129960891</v>
+        <v>129960864</v>
       </c>
       <c r="B178" t="n">
         <v>79327</v>
@@ -19971,10 +19971,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>471147</v>
+        <v>471116</v>
       </c>
       <c r="R178" t="n">
-        <v>6770575</v>
+        <v>6770565</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20042,13 +20042,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960891</t>
+          <t>https://artportalen.se/Sighting/129960864</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129960901</v>
+        <v>129960884</v>
       </c>
       <c r="B179" t="n">
         <v>79327</v>
@@ -20083,10 +20083,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>471185</v>
+        <v>471129</v>
       </c>
       <c r="R179" t="n">
-        <v>6770590</v>
+        <v>6770567</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20154,13 +20154,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960901</t>
+          <t>https://artportalen.se/Sighting/129960884</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129960929</v>
+        <v>129960891</v>
       </c>
       <c r="B180" t="n">
         <v>79327</v>
@@ -20195,10 +20195,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>471159</v>
+        <v>471147</v>
       </c>
       <c r="R180" t="n">
-        <v>6770613</v>
+        <v>6770575</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20266,13 +20266,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960929</t>
+          <t>https://artportalen.se/Sighting/129960891</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129961603</v>
+        <v>129960901</v>
       </c>
       <c r="B181" t="n">
         <v>79327</v>
@@ -20307,10 +20307,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471262</v>
+        <v>471185</v>
       </c>
       <c r="R181" t="n">
-        <v>6770622</v>
+        <v>6770590</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20378,13 +20378,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961603</t>
+          <t>https://artportalen.se/Sighting/129960901</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129961818</v>
+        <v>129960929</v>
       </c>
       <c r="B182" t="n">
         <v>79327</v>
@@ -20419,10 +20419,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471228</v>
+        <v>471159</v>
       </c>
       <c r="R182" t="n">
-        <v>6770667</v>
+        <v>6770613</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20490,13 +20490,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961818</t>
+          <t>https://artportalen.se/Sighting/129960929</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129961937</v>
+        <v>129961603</v>
       </c>
       <c r="B183" t="n">
         <v>79327</v>
@@ -20531,10 +20531,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>471216</v>
+        <v>471262</v>
       </c>
       <c r="R183" t="n">
-        <v>6770650</v>
+        <v>6770622</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20602,13 +20602,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961937</t>
+          <t>https://artportalen.se/Sighting/129961603</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129962073</v>
+        <v>129961818</v>
       </c>
       <c r="B184" t="n">
         <v>79327</v>
@@ -20643,10 +20643,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>471222</v>
+        <v>471228</v>
       </c>
       <c r="R184" t="n">
-        <v>6770635</v>
+        <v>6770667</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20714,13 +20714,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962073</t>
+          <t>https://artportalen.se/Sighting/129961818</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129962119</v>
+        <v>129961937</v>
       </c>
       <c r="B185" t="n">
         <v>79327</v>
@@ -20755,10 +20755,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>471156</v>
+        <v>471216</v>
       </c>
       <c r="R185" t="n">
-        <v>6770665</v>
+        <v>6770650</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20826,13 +20826,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962119</t>
+          <t>https://artportalen.se/Sighting/129961937</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129962224</v>
+        <v>129962073</v>
       </c>
       <c r="B186" t="n">
         <v>79327</v>
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>471098</v>
+        <v>471222</v>
       </c>
       <c r="R186" t="n">
-        <v>6770634</v>
+        <v>6770635</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20938,13 +20938,13 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962224</t>
+          <t>https://artportalen.se/Sighting/129962073</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129962243</v>
+        <v>129962119</v>
       </c>
       <c r="B187" t="n">
         <v>79327</v>
@@ -20979,10 +20979,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>471074</v>
+        <v>471156</v>
       </c>
       <c r="R187" t="n">
-        <v>6770617</v>
+        <v>6770665</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21050,13 +21050,13 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962243</t>
+          <t>https://artportalen.se/Sighting/129962119</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129962260</v>
+        <v>129962224</v>
       </c>
       <c r="B188" t="n">
         <v>79327</v>
@@ -21091,10 +21091,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>471044</v>
+        <v>471098</v>
       </c>
       <c r="R188" t="n">
-        <v>6770615</v>
+        <v>6770634</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21162,13 +21162,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962260</t>
+          <t>https://artportalen.se/Sighting/129962224</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129962290</v>
+        <v>129962243</v>
       </c>
       <c r="B189" t="n">
         <v>79327</v>
@@ -21203,10 +21203,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>471033</v>
+        <v>471074</v>
       </c>
       <c r="R189" t="n">
-        <v>6770614</v>
+        <v>6770617</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21274,13 +21274,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962290</t>
+          <t>https://artportalen.se/Sighting/129962243</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129962320</v>
+        <v>129962260</v>
       </c>
       <c r="B190" t="n">
         <v>79327</v>
@@ -21315,10 +21315,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>471024</v>
+        <v>471044</v>
       </c>
       <c r="R190" t="n">
-        <v>6770624</v>
+        <v>6770615</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21386,13 +21386,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962320</t>
+          <t>https://artportalen.se/Sighting/129962260</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129962351</v>
+        <v>129962290</v>
       </c>
       <c r="B191" t="n">
         <v>79327</v>
@@ -21427,10 +21427,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>471017</v>
+        <v>471033</v>
       </c>
       <c r="R191" t="n">
-        <v>6770613</v>
+        <v>6770614</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21498,13 +21498,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962351</t>
+          <t>https://artportalen.se/Sighting/129962290</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129962379</v>
+        <v>129962320</v>
       </c>
       <c r="B192" t="n">
         <v>79327</v>
@@ -21539,10 +21539,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>470996</v>
+        <v>471024</v>
       </c>
       <c r="R192" t="n">
-        <v>6770611</v>
+        <v>6770624</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21610,13 +21610,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962379</t>
+          <t>https://artportalen.se/Sighting/129962320</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129962390</v>
+        <v>129962351</v>
       </c>
       <c r="B193" t="n">
         <v>79327</v>
@@ -21651,10 +21651,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>471004</v>
+        <v>471017</v>
       </c>
       <c r="R193" t="n">
-        <v>6770581</v>
+        <v>6770613</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21722,13 +21722,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962390</t>
+          <t>https://artportalen.se/Sighting/129962351</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129962417</v>
+        <v>129962379</v>
       </c>
       <c r="B194" t="n">
         <v>79327</v>
@@ -21763,10 +21763,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>471002</v>
+        <v>470996</v>
       </c>
       <c r="R194" t="n">
-        <v>6770618</v>
+        <v>6770611</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21834,13 +21834,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962417</t>
+          <t>https://artportalen.se/Sighting/129962379</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129962443</v>
+        <v>129962390</v>
       </c>
       <c r="B195" t="n">
         <v>79327</v>
@@ -21875,10 +21875,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>470989</v>
+        <v>471004</v>
       </c>
       <c r="R195" t="n">
-        <v>6770629</v>
+        <v>6770581</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21946,13 +21946,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962443</t>
+          <t>https://artportalen.se/Sighting/129962390</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129962446</v>
+        <v>129962417</v>
       </c>
       <c r="B196" t="n">
         <v>79327</v>
@@ -21987,10 +21987,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>470993</v>
+        <v>471002</v>
       </c>
       <c r="R196" t="n">
-        <v>6770643</v>
+        <v>6770618</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22058,56 +22058,51 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962446</t>
+          <t>https://artportalen.se/Sighting/129962417</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129944452</v>
+        <v>129962443</v>
       </c>
       <c r="B197" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>471330</v>
+        <v>470989</v>
       </c>
       <c r="R197" t="n">
-        <v>6770712</v>
+        <v>6770629</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22134,22 +22129,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22175,56 +22170,51 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944452</t>
+          <t>https://artportalen.se/Sighting/129962443</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129945156</v>
+        <v>129962446</v>
       </c>
       <c r="B198" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>471198</v>
+        <v>470993</v>
       </c>
       <c r="R198" t="n">
-        <v>6770725</v>
+        <v>6770643</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22251,22 +22241,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22292,13 +22282,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945156</t>
+          <t>https://artportalen.se/Sighting/129962446</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129945440</v>
+        <v>129944452</v>
       </c>
       <c r="B199" t="n">
         <v>57950</v>
@@ -22329,7 +22319,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22338,10 +22328,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471189</v>
+        <v>471330</v>
       </c>
       <c r="R199" t="n">
-        <v>6770706</v>
+        <v>6770712</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22409,13 +22399,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945440</t>
+          <t>https://artportalen.se/Sighting/129944452</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129946321</v>
+        <v>129945156</v>
       </c>
       <c r="B200" t="n">
         <v>57950</v>
@@ -22446,7 +22436,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22455,10 +22445,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>470871</v>
+        <v>471198</v>
       </c>
       <c r="R200" t="n">
-        <v>6770635</v>
+        <v>6770725</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22526,13 +22516,13 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946321</t>
+          <t>https://artportalen.se/Sighting/129945156</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129946365</v>
+        <v>129945440</v>
       </c>
       <c r="B201" t="n">
         <v>57950</v>
@@ -22572,10 +22562,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>470910</v>
+        <v>471189</v>
       </c>
       <c r="R201" t="n">
-        <v>6770605</v>
+        <v>6770706</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22643,13 +22633,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946365</t>
+          <t>https://artportalen.se/Sighting/129945440</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129946391</v>
+        <v>129946321</v>
       </c>
       <c r="B202" t="n">
         <v>57950</v>
@@ -22680,7 +22670,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22689,10 +22679,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>470921</v>
+        <v>470871</v>
       </c>
       <c r="R202" t="n">
-        <v>6770579</v>
+        <v>6770635</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22760,13 +22750,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946391</t>
+          <t>https://artportalen.se/Sighting/129946321</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129946436</v>
+        <v>129946365</v>
       </c>
       <c r="B203" t="n">
         <v>57950</v>
@@ -22797,7 +22787,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22806,10 +22796,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>470971</v>
+        <v>470910</v>
       </c>
       <c r="R203" t="n">
-        <v>6770603</v>
+        <v>6770605</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22877,13 +22867,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946436</t>
+          <t>https://artportalen.se/Sighting/129946365</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129954441</v>
+        <v>129946391</v>
       </c>
       <c r="B204" t="n">
         <v>57950</v>
@@ -22923,10 +22913,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>471052</v>
+        <v>470921</v>
       </c>
       <c r="R204" t="n">
-        <v>6770696</v>
+        <v>6770579</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22953,22 +22943,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22994,13 +22984,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954441</t>
+          <t>https://artportalen.se/Sighting/129946391</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129957253</v>
+        <v>129946436</v>
       </c>
       <c r="B205" t="n">
         <v>57950</v>
@@ -23031,7 +23021,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -23040,10 +23030,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>470916</v>
+        <v>470971</v>
       </c>
       <c r="R205" t="n">
-        <v>6770721</v>
+        <v>6770603</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23070,22 +23060,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23111,13 +23101,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957253</t>
+          <t>https://artportalen.se/Sighting/129946436</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129958691</v>
+        <v>129954441</v>
       </c>
       <c r="B206" t="n">
         <v>57950</v>
@@ -23157,10 +23147,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470844</v>
+        <v>471052</v>
       </c>
       <c r="R206" t="n">
-        <v>6770699</v>
+        <v>6770696</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23228,13 +23218,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958691</t>
+          <t>https://artportalen.se/Sighting/129954441</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129959434</v>
+        <v>129957253</v>
       </c>
       <c r="B207" t="n">
         <v>57950</v>
@@ -23274,10 +23264,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470824</v>
+        <v>470916</v>
       </c>
       <c r="R207" t="n">
-        <v>6770523</v>
+        <v>6770721</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23345,13 +23335,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959434</t>
+          <t>https://artportalen.se/Sighting/129957253</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129959567</v>
+        <v>129958691</v>
       </c>
       <c r="B208" t="n">
         <v>57950</v>
@@ -23391,10 +23381,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470822</v>
+        <v>470844</v>
       </c>
       <c r="R208" t="n">
-        <v>6770452</v>
+        <v>6770699</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23462,13 +23452,13 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959567</t>
+          <t>https://artportalen.se/Sighting/129958691</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129959730</v>
+        <v>129959434</v>
       </c>
       <c r="B209" t="n">
         <v>57950</v>
@@ -23499,7 +23489,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -23508,10 +23498,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>470868</v>
+        <v>470824</v>
       </c>
       <c r="R209" t="n">
-        <v>6770431</v>
+        <v>6770523</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23579,13 +23569,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959730</t>
+          <t>https://artportalen.se/Sighting/129959434</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129959870</v>
+        <v>129959567</v>
       </c>
       <c r="B210" t="n">
         <v>57950</v>
@@ -23616,7 +23606,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -23625,10 +23615,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>470952</v>
+        <v>470822</v>
       </c>
       <c r="R210" t="n">
-        <v>6770464</v>
+        <v>6770452</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23696,13 +23686,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959870</t>
+          <t>https://artportalen.se/Sighting/129959567</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129960642</v>
+        <v>129959730</v>
       </c>
       <c r="B211" t="n">
         <v>57950</v>
@@ -23742,10 +23732,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>471025</v>
+        <v>470868</v>
       </c>
       <c r="R211" t="n">
-        <v>6770488</v>
+        <v>6770431</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23813,13 +23803,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960642</t>
+          <t>https://artportalen.se/Sighting/129959730</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129962343</v>
+        <v>129959870</v>
       </c>
       <c r="B212" t="n">
         <v>57950</v>
@@ -23850,7 +23840,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -23859,10 +23849,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>471017</v>
+        <v>470952</v>
       </c>
       <c r="R212" t="n">
-        <v>6770613</v>
+        <v>6770464</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23930,13 +23920,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962343</t>
+          <t>https://artportalen.se/Sighting/129959870</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129962374</v>
+        <v>129960642</v>
       </c>
       <c r="B213" t="n">
         <v>57950</v>
@@ -23967,7 +23957,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23976,10 +23966,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>470996</v>
+        <v>471025</v>
       </c>
       <c r="R213" t="n">
-        <v>6770611</v>
+        <v>6770488</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24047,13 +24037,13 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962374</t>
+          <t>https://artportalen.se/Sighting/129960642</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129962430</v>
+        <v>129962343</v>
       </c>
       <c r="B214" t="n">
         <v>57950</v>
@@ -24084,7 +24074,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -24093,10 +24083,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>470989</v>
+        <v>471017</v>
       </c>
       <c r="R214" t="n">
-        <v>6770629</v>
+        <v>6770613</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24164,48 +24154,44 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962430</t>
+          <t>https://artportalen.se/Sighting/129962343</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129944878</v>
+        <v>129962374</v>
       </c>
       <c r="B215" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -24214,13 +24200,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471258</v>
+        <v>470996</v>
       </c>
       <c r="R215" t="n">
-        <v>6770712</v>
+        <v>6770611</v>
       </c>
       <c r="S215" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24244,22 +24230,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24285,16 +24271,16 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944878</t>
+          <t>https://artportalen.se/Sighting/129962374</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129944062</v>
+        <v>129962430</v>
       </c>
       <c r="B216" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24302,27 +24288,27 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -24331,10 +24317,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471432</v>
+        <v>470989</v>
       </c>
       <c r="R216" t="n">
-        <v>6770716</v>
+        <v>6770629</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24361,22 +24347,22 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24402,44 +24388,48 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944062</t>
+          <t>https://artportalen.se/Sighting/129962430</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129944158</v>
+        <v>129944878</v>
       </c>
       <c r="B217" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -24448,13 +24438,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>471363</v>
+        <v>471258</v>
       </c>
       <c r="R217" t="n">
-        <v>6770736</v>
+        <v>6770712</v>
       </c>
       <c r="S217" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -24519,13 +24509,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944158</t>
+          <t>https://artportalen.se/Sighting/129944878</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129944454</v>
+        <v>129944062</v>
       </c>
       <c r="B218" t="n">
         <v>8455</v>
@@ -24554,16 +24544,21 @@
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>471330</v>
+        <v>471432</v>
       </c>
       <c r="R218" t="n">
-        <v>6770712</v>
+        <v>6770716</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24631,13 +24626,13 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944454</t>
+          <t>https://artportalen.se/Sighting/129944062</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129945161</v>
+        <v>129944158</v>
       </c>
       <c r="B219" t="n">
         <v>8455</v>
@@ -24677,10 +24672,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471198</v>
+        <v>471363</v>
       </c>
       <c r="R219" t="n">
-        <v>6770725</v>
+        <v>6770736</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24748,13 +24743,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945161</t>
+          <t>https://artportalen.se/Sighting/129944158</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129945444</v>
+        <v>129944454</v>
       </c>
       <c r="B220" t="n">
         <v>8455</v>
@@ -24783,21 +24778,16 @@
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>471189</v>
+        <v>471330</v>
       </c>
       <c r="R220" t="n">
-        <v>6770706</v>
+        <v>6770712</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24865,13 +24855,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945444</t>
+          <t>https://artportalen.se/Sighting/129944454</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129946047</v>
+        <v>129945161</v>
       </c>
       <c r="B221" t="n">
         <v>8455</v>
@@ -24900,16 +24890,21 @@
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>471161</v>
+        <v>471198</v>
       </c>
       <c r="R221" t="n">
-        <v>6770705</v>
+        <v>6770725</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24977,13 +24972,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946047</t>
+          <t>https://artportalen.se/Sighting/129945161</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129946334</v>
+        <v>129945444</v>
       </c>
       <c r="B222" t="n">
         <v>8455</v>
@@ -25023,10 +25018,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470871</v>
+        <v>471189</v>
       </c>
       <c r="R222" t="n">
-        <v>6770635</v>
+        <v>6770706</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25094,13 +25089,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946334</t>
+          <t>https://artportalen.se/Sighting/129945444</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129946444</v>
+        <v>129946047</v>
       </c>
       <c r="B223" t="n">
         <v>8455</v>
@@ -25129,21 +25124,16 @@
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>470971</v>
+        <v>471161</v>
       </c>
       <c r="R223" t="n">
-        <v>6770603</v>
+        <v>6770705</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25211,13 +25201,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946444</t>
+          <t>https://artportalen.se/Sighting/129946047</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129954662</v>
+        <v>129946334</v>
       </c>
       <c r="B224" t="n">
         <v>8455</v>
@@ -25257,10 +25247,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470941</v>
+        <v>470871</v>
       </c>
       <c r="R224" t="n">
-        <v>6770708</v>
+        <v>6770635</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25287,22 +25277,22 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25328,13 +25318,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954662</t>
+          <t>https://artportalen.se/Sighting/129946334</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129958131</v>
+        <v>129946444</v>
       </c>
       <c r="B225" t="n">
         <v>8455</v>
@@ -25374,10 +25364,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470869</v>
+        <v>470971</v>
       </c>
       <c r="R225" t="n">
-        <v>6770702</v>
+        <v>6770603</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25404,22 +25394,22 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25445,13 +25435,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958131</t>
+          <t>https://artportalen.se/Sighting/129946444</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129958199</v>
+        <v>129954662</v>
       </c>
       <c r="B226" t="n">
         <v>8455</v>
@@ -25491,10 +25481,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>470823</v>
+        <v>470941</v>
       </c>
       <c r="R226" t="n">
-        <v>6770705</v>
+        <v>6770708</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25562,13 +25552,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958199</t>
+          <t>https://artportalen.se/Sighting/129954662</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129958686</v>
+        <v>129958131</v>
       </c>
       <c r="B227" t="n">
         <v>8455</v>
@@ -25608,10 +25598,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>470844</v>
+        <v>470869</v>
       </c>
       <c r="R227" t="n">
-        <v>6770699</v>
+        <v>6770702</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25679,13 +25669,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958686</t>
+          <t>https://artportalen.se/Sighting/129958131</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129959110</v>
+        <v>129958199</v>
       </c>
       <c r="B228" t="n">
         <v>8455</v>
@@ -25725,10 +25715,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470926</v>
+        <v>470823</v>
       </c>
       <c r="R228" t="n">
-        <v>6770613</v>
+        <v>6770705</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25796,13 +25786,13 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959110</t>
+          <t>https://artportalen.se/Sighting/129958199</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129959223</v>
+        <v>129958686</v>
       </c>
       <c r="B229" t="n">
         <v>8455</v>
@@ -25842,10 +25832,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>470921</v>
+        <v>470844</v>
       </c>
       <c r="R229" t="n">
-        <v>6770579</v>
+        <v>6770699</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25913,13 +25903,13 @@
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959223</t>
+          <t>https://artportalen.se/Sighting/129958686</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129959285</v>
+        <v>129959110</v>
       </c>
       <c r="B230" t="n">
         <v>8455</v>
@@ -25959,10 +25949,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>470922</v>
+        <v>470926</v>
       </c>
       <c r="R230" t="n">
-        <v>6770556</v>
+        <v>6770613</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26030,13 +26020,13 @@
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959285</t>
+          <t>https://artportalen.se/Sighting/129959110</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129959441</v>
+        <v>129959223</v>
       </c>
       <c r="B231" t="n">
         <v>8455</v>
@@ -26076,10 +26066,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>470824</v>
+        <v>470921</v>
       </c>
       <c r="R231" t="n">
-        <v>6770523</v>
+        <v>6770579</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26147,13 +26137,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959441</t>
+          <t>https://artportalen.se/Sighting/129959223</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129959579</v>
+        <v>129959285</v>
       </c>
       <c r="B232" t="n">
         <v>8455</v>
@@ -26193,10 +26183,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>470822</v>
+        <v>470922</v>
       </c>
       <c r="R232" t="n">
-        <v>6770452</v>
+        <v>6770556</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26264,13 +26254,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959579</t>
+          <t>https://artportalen.se/Sighting/129959285</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129959710</v>
+        <v>129959441</v>
       </c>
       <c r="B233" t="n">
         <v>8455</v>
@@ -26310,10 +26300,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>470864</v>
+        <v>470824</v>
       </c>
       <c r="R233" t="n">
-        <v>6770438</v>
+        <v>6770523</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26381,13 +26371,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959710</t>
+          <t>https://artportalen.se/Sighting/129959441</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129959735</v>
+        <v>129959579</v>
       </c>
       <c r="B234" t="n">
         <v>8455</v>
@@ -26427,10 +26417,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>470868</v>
+        <v>470822</v>
       </c>
       <c r="R234" t="n">
-        <v>6770431</v>
+        <v>6770452</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26498,13 +26488,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959735</t>
+          <t>https://artportalen.se/Sighting/129959579</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129959924</v>
+        <v>129959710</v>
       </c>
       <c r="B235" t="n">
         <v>8455</v>
@@ -26544,10 +26534,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>470944</v>
+        <v>470864</v>
       </c>
       <c r="R235" t="n">
-        <v>6770458</v>
+        <v>6770438</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26615,13 +26605,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959924</t>
+          <t>https://artportalen.se/Sighting/129959710</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129960514</v>
+        <v>129959735</v>
       </c>
       <c r="B236" t="n">
         <v>8455</v>
@@ -26661,13 +26651,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>470976</v>
+        <v>470868</v>
       </c>
       <c r="R236" t="n">
-        <v>6770536</v>
+        <v>6770431</v>
       </c>
       <c r="S236" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26732,13 +26722,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960514</t>
+          <t>https://artportalen.se/Sighting/129959735</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129960657</v>
+        <v>129959924</v>
       </c>
       <c r="B237" t="n">
         <v>8455</v>
@@ -26778,10 +26768,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>471025</v>
+        <v>470944</v>
       </c>
       <c r="R237" t="n">
-        <v>6770488</v>
+        <v>6770458</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26849,13 +26839,13 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960657</t>
+          <t>https://artportalen.se/Sighting/129959924</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129960746</v>
+        <v>129960514</v>
       </c>
       <c r="B238" t="n">
         <v>8455</v>
@@ -26895,13 +26885,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>471053</v>
+        <v>470976</v>
       </c>
       <c r="R238" t="n">
-        <v>6770528</v>
+        <v>6770536</v>
       </c>
       <c r="S238" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -26966,13 +26956,13 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960746</t>
+          <t>https://artportalen.se/Sighting/129960514</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129960827</v>
+        <v>129960657</v>
       </c>
       <c r="B239" t="n">
         <v>8455</v>
@@ -27012,10 +27002,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>471078</v>
+        <v>471025</v>
       </c>
       <c r="R239" t="n">
-        <v>6770561</v>
+        <v>6770488</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27083,13 +27073,13 @@
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960827</t>
+          <t>https://artportalen.se/Sighting/129960657</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129961109</v>
+        <v>129960746</v>
       </c>
       <c r="B240" t="n">
         <v>8455</v>
@@ -27129,10 +27119,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>471175</v>
+        <v>471053</v>
       </c>
       <c r="R240" t="n">
-        <v>6770631</v>
+        <v>6770528</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27200,13 +27190,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961109</t>
+          <t>https://artportalen.se/Sighting/129960746</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129962346</v>
+        <v>129960827</v>
       </c>
       <c r="B241" t="n">
         <v>8455</v>
@@ -27246,10 +27236,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>471017</v>
+        <v>471078</v>
       </c>
       <c r="R241" t="n">
-        <v>6770613</v>
+        <v>6770561</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27317,13 +27307,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962346</t>
+          <t>https://artportalen.se/Sighting/129960827</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129962376</v>
+        <v>129961109</v>
       </c>
       <c r="B242" t="n">
         <v>8455</v>
@@ -27363,10 +27353,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>470996</v>
+        <v>471175</v>
       </c>
       <c r="R242" t="n">
-        <v>6770611</v>
+        <v>6770631</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27434,13 +27424,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962376</t>
+          <t>https://artportalen.se/Sighting/129961109</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129962436</v>
+        <v>129962346</v>
       </c>
       <c r="B243" t="n">
         <v>8455</v>
@@ -27480,10 +27470,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>470989</v>
+        <v>471017</v>
       </c>
       <c r="R243" t="n">
-        <v>6770629</v>
+        <v>6770613</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27551,57 +27541,59 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962436</t>
+          <t>https://artportalen.se/Sighting/129962346</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129271581</v>
+        <v>129962376</v>
       </c>
       <c r="B244" t="n">
-        <v>93228</v>
+        <v>8455</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>232140</v>
+        <v>106545</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>470835</v>
+        <v>470996</v>
       </c>
       <c r="R244" t="n">
-        <v>6770662</v>
+        <v>6770611</v>
       </c>
       <c r="S244" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27625,12 +27617,22 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27639,72 +27641,76 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
-      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129271581</t>
+          <t>https://artportalen.se/Sighting/129962376</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>96714923</v>
+        <v>129962436</v>
       </c>
       <c r="B245" t="n">
-        <v>91402</v>
+        <v>8455</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>256703</v>
+        <v>106545</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>470876</v>
+        <v>470989</v>
       </c>
       <c r="R245" t="n">
-        <v>6770446</v>
+        <v>6770629</v>
       </c>
       <c r="S245" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27728,12 +27734,22 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27748,62 +27764,65 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714923</t>
+          <t>https://artportalen.se/Sighting/129962436</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>96714929</v>
+        <v>129271581</v>
       </c>
       <c r="B246" t="n">
-        <v>91402</v>
+        <v>93228</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>256703</v>
+        <v>232140</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>471113</v>
+        <v>470835</v>
       </c>
       <c r="R246" t="n">
-        <v>6770726</v>
+        <v>6770662</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -27830,12 +27849,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -27844,30 +27863,31 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714929</t>
+          <t>https://artportalen.se/Sighting/129271581</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>96714933</v>
+        <v>96714923</v>
       </c>
       <c r="B247" t="n">
         <v>91402</v>
@@ -27902,10 +27922,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>470806</v>
+        <v>470876</v>
       </c>
       <c r="R247" t="n">
-        <v>6770695</v>
+        <v>6770446</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -27963,13 +27983,13 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714933</t>
+          <t>https://artportalen.se/Sighting/96714923</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>96714941</v>
+        <v>96714929</v>
       </c>
       <c r="B248" t="n">
         <v>91402</v>
@@ -28004,10 +28024,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>471105</v>
+        <v>471113</v>
       </c>
       <c r="R248" t="n">
-        <v>6770716</v>
+        <v>6770726</v>
       </c>
       <c r="S248" t="n">
         <v>25</v>
@@ -28065,13 +28085,13 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714941</t>
+          <t>https://artportalen.se/Sighting/96714929</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>96714946</v>
+        <v>96714933</v>
       </c>
       <c r="B249" t="n">
         <v>91402</v>
@@ -28106,10 +28126,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>471072</v>
+        <v>470806</v>
       </c>
       <c r="R249" t="n">
-        <v>6770716</v>
+        <v>6770695</v>
       </c>
       <c r="S249" t="n">
         <v>25</v>
@@ -28167,13 +28187,13 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714946</t>
+          <t>https://artportalen.se/Sighting/96714933</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>96714952</v>
+        <v>96714941</v>
       </c>
       <c r="B250" t="n">
         <v>91402</v>
@@ -28208,10 +28228,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>470920</v>
+        <v>471105</v>
       </c>
       <c r="R250" t="n">
-        <v>6770687</v>
+        <v>6770716</v>
       </c>
       <c r="S250" t="n">
         <v>25</v>
@@ -28269,13 +28289,13 @@
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714952</t>
+          <t>https://artportalen.se/Sighting/96714941</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>96714953</v>
+        <v>96714946</v>
       </c>
       <c r="B251" t="n">
         <v>91402</v>
@@ -28310,10 +28330,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>471086</v>
+        <v>471072</v>
       </c>
       <c r="R251" t="n">
-        <v>6770698</v>
+        <v>6770716</v>
       </c>
       <c r="S251" t="n">
         <v>25</v>
@@ -28371,13 +28391,13 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714953</t>
+          <t>https://artportalen.se/Sighting/96714946</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>96714960</v>
+        <v>96714952</v>
       </c>
       <c r="B252" t="n">
         <v>91402</v>
@@ -28412,10 +28432,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>471091</v>
+        <v>470920</v>
       </c>
       <c r="R252" t="n">
-        <v>6770723</v>
+        <v>6770687</v>
       </c>
       <c r="S252" t="n">
         <v>25</v>
@@ -28473,13 +28493,13 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714960</t>
+          <t>https://artportalen.se/Sighting/96714952</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>96714973</v>
+        <v>96714953</v>
       </c>
       <c r="B253" t="n">
         <v>91402</v>
@@ -28514,10 +28534,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>471080</v>
+        <v>471086</v>
       </c>
       <c r="R253" t="n">
-        <v>6770598</v>
+        <v>6770698</v>
       </c>
       <c r="S253" t="n">
         <v>25</v>
@@ -28575,13 +28595,13 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714973</t>
+          <t>https://artportalen.se/Sighting/96714953</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>96714981</v>
+        <v>96714960</v>
       </c>
       <c r="B254" t="n">
         <v>91402</v>
@@ -28616,10 +28636,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>471483</v>
+        <v>471091</v>
       </c>
       <c r="R254" t="n">
-        <v>6770715</v>
+        <v>6770723</v>
       </c>
       <c r="S254" t="n">
         <v>25</v>
@@ -28677,13 +28697,13 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714981</t>
+          <t>https://artportalen.se/Sighting/96714960</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>96715005</v>
+        <v>96714973</v>
       </c>
       <c r="B255" t="n">
         <v>91402</v>
@@ -28718,10 +28738,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>470830</v>
+        <v>471080</v>
       </c>
       <c r="R255" t="n">
-        <v>6770666</v>
+        <v>6770598</v>
       </c>
       <c r="S255" t="n">
         <v>25</v>
@@ -28779,13 +28799,13 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715005</t>
+          <t>https://artportalen.se/Sighting/96714973</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>96715010</v>
+        <v>96714981</v>
       </c>
       <c r="B256" t="n">
         <v>91402</v>
@@ -28820,10 +28840,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>471253</v>
+        <v>471483</v>
       </c>
       <c r="R256" t="n">
-        <v>6770676</v>
+        <v>6770715</v>
       </c>
       <c r="S256" t="n">
         <v>25</v>
@@ -28880,6 +28900,210 @@
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714981</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>96715005</v>
+      </c>
+      <c r="B257" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Bonäsheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>470830</v>
+      </c>
+      <c r="R257" t="n">
+        <v>6770666</v>
+      </c>
+      <c r="S257" t="n">
+        <v>25</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715005</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>96715010</v>
+      </c>
+      <c r="B258" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Bonäsheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>471253</v>
+      </c>
+      <c r="R258" t="n">
+        <v>6770676</v>
+      </c>
+      <c r="S258" t="n">
+        <v>25</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96715010</t>
         </is>
@@ -29142,6 +29366,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ258"/>
+  <dimension ref="A1:AZ256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6997,48 +6997,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136837910</v>
+        <v>96714971</v>
       </c>
       <c r="B62" t="n">
-        <v>93426</v>
+        <v>93201</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bengttjärnen, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470909</v>
+        <v>470825</v>
       </c>
       <c r="R62" t="n">
-        <v>6770448</v>
+        <v>6770664</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7062,22 +7062,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7092,49 +7082,49 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Uno Skog, Andreas Öster</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837910</t>
+          <t>https://artportalen.se/Sighting/96714971</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>96714971</v>
+        <v>96714979</v>
       </c>
       <c r="B63" t="n">
-        <v>93201</v>
+        <v>92841</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4365</v>
+        <v>4745</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7144,10 +7134,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>470825</v>
+        <v>471064</v>
       </c>
       <c r="R63" t="n">
-        <v>6770664</v>
+        <v>6770563</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7205,16 +7195,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714971</t>
+          <t>https://artportalen.se/Sighting/96714979</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>96714979</v>
+        <v>129943849</v>
       </c>
       <c r="B64" t="n">
-        <v>92841</v>
+        <v>91930</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7222,37 +7212,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4745</v>
+        <v>5442</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471064</v>
+        <v>471451</v>
       </c>
       <c r="R64" t="n">
-        <v>6770563</v>
+        <v>6770706</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7276,12 +7270,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7296,24 +7300,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714979</t>
+          <t>https://artportalen.se/Sighting/129943849</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129943849</v>
+        <v>129944262</v>
       </c>
       <c r="B65" t="n">
         <v>91930</v>
@@ -7352,10 +7356,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471451</v>
+        <v>471369</v>
       </c>
       <c r="R65" t="n">
-        <v>6770706</v>
+        <v>6770686</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7423,13 +7427,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943849</t>
+          <t>https://artportalen.se/Sighting/129944262</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129944262</v>
+        <v>129959667</v>
       </c>
       <c r="B66" t="n">
         <v>91930</v>
@@ -7459,7 +7463,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7468,10 +7472,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>471369</v>
+        <v>470864</v>
       </c>
       <c r="R66" t="n">
-        <v>6770686</v>
+        <v>6770438</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7498,22 +7502,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7539,16 +7543,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944262</t>
+          <t>https://artportalen.se/Sighting/129959667</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129959667</v>
+        <v>96714915</v>
       </c>
       <c r="B67" t="n">
-        <v>91930</v>
+        <v>93235</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7556,41 +7560,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>470864</v>
+        <v>471343</v>
       </c>
       <c r="R67" t="n">
-        <v>6770438</v>
+        <v>6770659</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7614,22 +7614,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7644,24 +7634,24 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959667</t>
+          <t>https://artportalen.se/Sighting/96714915</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>96714915</v>
+        <v>96714991</v>
       </c>
       <c r="B68" t="n">
         <v>93235</v>
@@ -7696,10 +7686,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471343</v>
+        <v>470824</v>
       </c>
       <c r="R68" t="n">
-        <v>6770659</v>
+        <v>6770660</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7757,54 +7747,54 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714915</t>
+          <t>https://artportalen.se/Sighting/96714991</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>96714991</v>
+        <v>136837813</v>
       </c>
       <c r="B69" t="n">
-        <v>93235</v>
+        <v>93410</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5966</v>
+        <v>6055</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bengttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470824</v>
+        <v>470979</v>
       </c>
       <c r="R69" t="n">
-        <v>6770660</v>
+        <v>6770615</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7828,12 +7818,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7848,27 +7838,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714991</t>
+          <t>https://artportalen.se/Sighting/136837813</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136836580</v>
+        <v>96714961</v>
       </c>
       <c r="B70" t="n">
-        <v>93410</v>
+        <v>90691</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7876,37 +7866,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6055</v>
+        <v>6276</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bengttjärnen, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>470971</v>
+        <v>471372</v>
       </c>
       <c r="R70" t="n">
-        <v>6770613</v>
+        <v>6770686</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7930,22 +7920,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7960,27 +7940,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136836580</t>
+          <t>https://artportalen.se/Sighting/96714961</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136837813</v>
+        <v>96715014</v>
       </c>
       <c r="B71" t="n">
-        <v>93410</v>
+        <v>90691</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7988,37 +7968,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6055</v>
+        <v>6276</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bengttjärnen, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470979</v>
+        <v>470841</v>
       </c>
       <c r="R71" t="n">
-        <v>6770615</v>
+        <v>6770558</v>
       </c>
       <c r="S71" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8042,12 +8022,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8062,27 +8042,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837813</t>
+          <t>https://artportalen.se/Sighting/96715014</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>96714961</v>
+        <v>96715007</v>
       </c>
       <c r="B72" t="n">
-        <v>90691</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8090,21 +8070,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6276</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8114,10 +8094,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471372</v>
+        <v>471383</v>
       </c>
       <c r="R72" t="n">
-        <v>6770686</v>
+        <v>6770715</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8175,16 +8155,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714961</t>
+          <t>https://artportalen.se/Sighting/96715007</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>96715014</v>
+        <v>129943529</v>
       </c>
       <c r="B73" t="n">
-        <v>90691</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8192,37 +8172,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6276</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470841</v>
+        <v>471492</v>
       </c>
       <c r="R73" t="n">
-        <v>6770558</v>
+        <v>6770712</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8246,12 +8226,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8266,24 +8256,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715014</t>
+          <t>https://artportalen.se/Sighting/129943529</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>96715007</v>
+        <v>129943541</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8314,17 +8304,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471383</v>
+        <v>471478</v>
       </c>
       <c r="R74" t="n">
-        <v>6770715</v>
+        <v>6770707</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8348,12 +8338,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8368,24 +8368,24 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715007</t>
+          <t>https://artportalen.se/Sighting/129943541</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129943529</v>
+        <v>129943580</v>
       </c>
       <c r="B75" t="n">
         <v>79327</v>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471492</v>
+        <v>471468</v>
       </c>
       <c r="R75" t="n">
-        <v>6770712</v>
+        <v>6770744</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8491,13 +8491,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943529</t>
+          <t>https://artportalen.se/Sighting/129943580</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129943541</v>
+        <v>129943763</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471478</v>
+        <v>471466</v>
       </c>
       <c r="R76" t="n">
-        <v>6770707</v>
+        <v>6770713</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8603,13 +8603,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943541</t>
+          <t>https://artportalen.se/Sighting/129943763</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129943580</v>
+        <v>129943809</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471468</v>
+        <v>471447</v>
       </c>
       <c r="R77" t="n">
-        <v>6770744</v>
+        <v>6770716</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8715,13 +8715,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943580</t>
+          <t>https://artportalen.se/Sighting/129943809</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129943763</v>
+        <v>129943855</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471466</v>
+        <v>471451</v>
       </c>
       <c r="R78" t="n">
-        <v>6770713</v>
+        <v>6770706</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8827,13 +8827,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943763</t>
+          <t>https://artportalen.se/Sighting/129943855</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129943809</v>
+        <v>129943914</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -8868,10 +8868,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471447</v>
+        <v>471432</v>
       </c>
       <c r="R79" t="n">
-        <v>6770716</v>
+        <v>6770701</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8939,13 +8939,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943809</t>
+          <t>https://artportalen.se/Sighting/129943914</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129943855</v>
+        <v>129943999</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471451</v>
+        <v>471428</v>
       </c>
       <c r="R80" t="n">
-        <v>6770706</v>
+        <v>6770747</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9051,13 +9051,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943855</t>
+          <t>https://artportalen.se/Sighting/129943999</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129943914</v>
+        <v>129944026</v>
       </c>
       <c r="B81" t="n">
         <v>79327</v>
@@ -9092,10 +9092,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471432</v>
+        <v>471422</v>
       </c>
       <c r="R81" t="n">
-        <v>6770701</v>
+        <v>6770745</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9163,13 +9163,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943914</t>
+          <t>https://artportalen.se/Sighting/129944026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129943999</v>
+        <v>129944037</v>
       </c>
       <c r="B82" t="n">
         <v>79327</v>
@@ -9204,10 +9204,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471428</v>
+        <v>471417</v>
       </c>
       <c r="R82" t="n">
-        <v>6770747</v>
+        <v>6770738</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9275,13 +9275,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943999</t>
+          <t>https://artportalen.se/Sighting/129944037</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944026</v>
+        <v>129944164</v>
       </c>
       <c r="B83" t="n">
         <v>79327</v>
@@ -9316,10 +9316,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471422</v>
+        <v>471363</v>
       </c>
       <c r="R83" t="n">
-        <v>6770745</v>
+        <v>6770736</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9387,13 +9387,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944026</t>
+          <t>https://artportalen.se/Sighting/129944164</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944037</v>
+        <v>129944178</v>
       </c>
       <c r="B84" t="n">
         <v>79327</v>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471417</v>
+        <v>471372</v>
       </c>
       <c r="R84" t="n">
-        <v>6770738</v>
+        <v>6770719</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9499,13 +9499,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944037</t>
+          <t>https://artportalen.se/Sighting/129944178</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129944164</v>
+        <v>129944210</v>
       </c>
       <c r="B85" t="n">
         <v>79327</v>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471363</v>
+        <v>471390</v>
       </c>
       <c r="R85" t="n">
-        <v>6770736</v>
+        <v>6770705</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,13 +9611,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944164</t>
+          <t>https://artportalen.se/Sighting/129944210</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129944178</v>
+        <v>129944228</v>
       </c>
       <c r="B86" t="n">
         <v>79327</v>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471372</v>
+        <v>471390</v>
       </c>
       <c r="R86" t="n">
-        <v>6770719</v>
+        <v>6770693</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9723,13 +9723,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944178</t>
+          <t>https://artportalen.se/Sighting/129944228</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129944210</v>
+        <v>129944311</v>
       </c>
       <c r="B87" t="n">
         <v>79327</v>
@@ -9764,10 +9764,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471390</v>
+        <v>471369</v>
       </c>
       <c r="R87" t="n">
-        <v>6770705</v>
+        <v>6770686</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9835,13 +9835,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944210</t>
+          <t>https://artportalen.se/Sighting/129944311</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129944228</v>
+        <v>129944355</v>
       </c>
       <c r="B88" t="n">
         <v>79327</v>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471390</v>
+        <v>471342</v>
       </c>
       <c r="R88" t="n">
-        <v>6770693</v>
+        <v>6770682</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9947,13 +9947,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944228</t>
+          <t>https://artportalen.se/Sighting/129944355</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129944311</v>
+        <v>129944466</v>
       </c>
       <c r="B89" t="n">
         <v>79327</v>
@@ -9988,10 +9988,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471369</v>
+        <v>471322</v>
       </c>
       <c r="R89" t="n">
-        <v>6770686</v>
+        <v>6770702</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10059,13 +10059,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944311</t>
+          <t>https://artportalen.se/Sighting/129944466</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129944355</v>
+        <v>129944473</v>
       </c>
       <c r="B90" t="n">
         <v>79327</v>
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471342</v>
+        <v>471328</v>
       </c>
       <c r="R90" t="n">
-        <v>6770682</v>
+        <v>6770726</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10171,13 +10171,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944355</t>
+          <t>https://artportalen.se/Sighting/129944473</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129944466</v>
+        <v>129944488</v>
       </c>
       <c r="B91" t="n">
         <v>79327</v>
@@ -10212,10 +10212,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471322</v>
+        <v>471318</v>
       </c>
       <c r="R91" t="n">
-        <v>6770702</v>
+        <v>6770729</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10283,13 +10283,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944466</t>
+          <t>https://artportalen.se/Sighting/129944488</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129944473</v>
+        <v>129944495</v>
       </c>
       <c r="B92" t="n">
         <v>79327</v>
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471328</v>
+        <v>471288</v>
       </c>
       <c r="R92" t="n">
-        <v>6770726</v>
+        <v>6770728</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10395,13 +10395,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944473</t>
+          <t>https://artportalen.se/Sighting/129944495</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129944488</v>
+        <v>129944523</v>
       </c>
       <c r="B93" t="n">
         <v>79327</v>
@@ -10436,10 +10436,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471318</v>
+        <v>471303</v>
       </c>
       <c r="R93" t="n">
-        <v>6770729</v>
+        <v>6770699</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10507,13 +10507,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944488</t>
+          <t>https://artportalen.se/Sighting/129944523</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129944495</v>
+        <v>129944544</v>
       </c>
       <c r="B94" t="n">
         <v>79327</v>
@@ -10548,10 +10548,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471288</v>
+        <v>471330</v>
       </c>
       <c r="R94" t="n">
-        <v>6770728</v>
+        <v>6770712</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10619,13 +10619,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944495</t>
+          <t>https://artportalen.se/Sighting/129944544</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129944523</v>
+        <v>129944592</v>
       </c>
       <c r="B95" t="n">
         <v>79327</v>
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471303</v>
+        <v>471313</v>
       </c>
       <c r="R95" t="n">
-        <v>6770699</v>
+        <v>6770688</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10731,13 +10731,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944523</t>
+          <t>https://artportalen.se/Sighting/129944592</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129944544</v>
+        <v>129944756</v>
       </c>
       <c r="B96" t="n">
         <v>79327</v>
@@ -10772,10 +10772,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471330</v>
+        <v>471288</v>
       </c>
       <c r="R96" t="n">
-        <v>6770712</v>
+        <v>6770685</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10843,13 +10843,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944544</t>
+          <t>https://artportalen.se/Sighting/129944756</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129944592</v>
+        <v>129944762</v>
       </c>
       <c r="B97" t="n">
         <v>79327</v>
@@ -10884,10 +10884,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471313</v>
+        <v>471276</v>
       </c>
       <c r="R97" t="n">
-        <v>6770688</v>
+        <v>6770703</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10955,13 +10955,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944592</t>
+          <t>https://artportalen.se/Sighting/129944762</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129944756</v>
+        <v>129944804</v>
       </c>
       <c r="B98" t="n">
         <v>79327</v>
@@ -10996,10 +10996,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471288</v>
+        <v>471271</v>
       </c>
       <c r="R98" t="n">
-        <v>6770685</v>
+        <v>6770733</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11067,13 +11067,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944756</t>
+          <t>https://artportalen.se/Sighting/129944804</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129944762</v>
+        <v>129944807</v>
       </c>
       <c r="B99" t="n">
         <v>79327</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471276</v>
+        <v>471248</v>
       </c>
       <c r="R99" t="n">
-        <v>6770703</v>
+        <v>6770737</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11179,13 +11179,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944762</t>
+          <t>https://artportalen.se/Sighting/129944807</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944804</v>
+        <v>129944809</v>
       </c>
       <c r="B100" t="n">
         <v>79327</v>
@@ -11220,10 +11220,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471271</v>
+        <v>471247</v>
       </c>
       <c r="R100" t="n">
-        <v>6770733</v>
+        <v>6770726</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11291,13 +11291,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944804</t>
+          <t>https://artportalen.se/Sighting/129944809</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129944807</v>
+        <v>129944917</v>
       </c>
       <c r="B101" t="n">
         <v>79327</v>
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471248</v>
+        <v>471263</v>
       </c>
       <c r="R101" t="n">
-        <v>6770737</v>
+        <v>6770694</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,13 +11403,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944807</t>
+          <t>https://artportalen.se/Sighting/129944917</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129944809</v>
+        <v>129944975</v>
       </c>
       <c r="B102" t="n">
         <v>79327</v>
@@ -11444,10 +11444,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471247</v>
+        <v>471242</v>
       </c>
       <c r="R102" t="n">
-        <v>6770726</v>
+        <v>6770682</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11515,13 +11515,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944809</t>
+          <t>https://artportalen.se/Sighting/129944975</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129944917</v>
+        <v>129945066</v>
       </c>
       <c r="B103" t="n">
         <v>79327</v>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471263</v>
+        <v>471239</v>
       </c>
       <c r="R103" t="n">
-        <v>6770694</v>
+        <v>6770732</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11627,13 +11627,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944917</t>
+          <t>https://artportalen.se/Sighting/129945066</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129944975</v>
+        <v>129945078</v>
       </c>
       <c r="B104" t="n">
         <v>79327</v>
@@ -11668,10 +11668,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471242</v>
+        <v>471209</v>
       </c>
       <c r="R104" t="n">
-        <v>6770682</v>
+        <v>6770731</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11739,13 +11739,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944975</t>
+          <t>https://artportalen.se/Sighting/129945078</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129945066</v>
+        <v>129945104</v>
       </c>
       <c r="B105" t="n">
         <v>79327</v>
@@ -11780,10 +11780,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471239</v>
+        <v>471219</v>
       </c>
       <c r="R105" t="n">
-        <v>6770732</v>
+        <v>6770720</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11851,13 +11851,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945066</t>
+          <t>https://artportalen.se/Sighting/129945104</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129945078</v>
+        <v>129945451</v>
       </c>
       <c r="B106" t="n">
         <v>79327</v>
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471209</v>
+        <v>471189</v>
       </c>
       <c r="R106" t="n">
-        <v>6770731</v>
+        <v>6770706</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11963,13 +11963,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945078</t>
+          <t>https://artportalen.se/Sighting/129945451</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129945104</v>
+        <v>129945509</v>
       </c>
       <c r="B107" t="n">
         <v>79327</v>
@@ -12004,10 +12004,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471219</v>
+        <v>471198</v>
       </c>
       <c r="R107" t="n">
-        <v>6770720</v>
+        <v>6770689</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12052,6 +12052,11 @@
           <t>11:17</t>
         </is>
       </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12075,13 +12080,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945104</t>
+          <t>https://artportalen.se/Sighting/129945509</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129945451</v>
+        <v>129946029</v>
       </c>
       <c r="B108" t="n">
         <v>79327</v>
@@ -12116,10 +12121,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471189</v>
+        <v>471185</v>
       </c>
       <c r="R108" t="n">
-        <v>6770706</v>
+        <v>6770690</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12187,13 +12192,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945451</t>
+          <t>https://artportalen.se/Sighting/129946029</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129945509</v>
+        <v>129946053</v>
       </c>
       <c r="B109" t="n">
         <v>79327</v>
@@ -12228,10 +12233,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471198</v>
+        <v>471161</v>
       </c>
       <c r="R109" t="n">
-        <v>6770689</v>
+        <v>6770705</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12276,11 +12281,6 @@
           <t>11:17</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12304,13 +12304,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945509</t>
+          <t>https://artportalen.se/Sighting/129946053</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129946029</v>
+        <v>129946117</v>
       </c>
       <c r="B110" t="n">
         <v>79327</v>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471185</v>
+        <v>471106</v>
       </c>
       <c r="R110" t="n">
-        <v>6770690</v>
+        <v>6770711</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12416,13 +12416,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946029</t>
+          <t>https://artportalen.se/Sighting/129946117</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129946053</v>
+        <v>129946170</v>
       </c>
       <c r="B111" t="n">
         <v>79327</v>
@@ -12457,10 +12457,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471161</v>
+        <v>471030</v>
       </c>
       <c r="R111" t="n">
-        <v>6770705</v>
+        <v>6770688</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12528,13 +12528,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946053</t>
+          <t>https://artportalen.se/Sighting/129946170</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129946117</v>
+        <v>129946182</v>
       </c>
       <c r="B112" t="n">
         <v>79327</v>
@@ -12569,10 +12569,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471106</v>
+        <v>471000</v>
       </c>
       <c r="R112" t="n">
-        <v>6770711</v>
+        <v>6770675</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12640,13 +12640,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946117</t>
+          <t>https://artportalen.se/Sighting/129946182</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129946170</v>
+        <v>129946197</v>
       </c>
       <c r="B113" t="n">
         <v>79327</v>
@@ -12681,10 +12681,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471030</v>
+        <v>470971</v>
       </c>
       <c r="R113" t="n">
-        <v>6770688</v>
+        <v>6770676</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12752,13 +12752,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946170</t>
+          <t>https://artportalen.se/Sighting/129946197</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129946182</v>
+        <v>129946408</v>
       </c>
       <c r="B114" t="n">
         <v>79327</v>
@@ -12793,10 +12793,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>471000</v>
+        <v>470921</v>
       </c>
       <c r="R114" t="n">
-        <v>6770675</v>
+        <v>6770579</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12864,13 +12864,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946182</t>
+          <t>https://artportalen.se/Sighting/129946408</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129946197</v>
+        <v>129946586</v>
       </c>
       <c r="B115" t="n">
         <v>79327</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>470971</v>
+        <v>471095</v>
       </c>
       <c r="R115" t="n">
-        <v>6770676</v>
+        <v>6770660</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12976,13 +12976,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946197</t>
+          <t>https://artportalen.se/Sighting/129946586</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129946408</v>
+        <v>129946708</v>
       </c>
       <c r="B116" t="n">
         <v>79327</v>
@@ -13017,10 +13017,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>470921</v>
+        <v>471171</v>
       </c>
       <c r="R116" t="n">
-        <v>6770579</v>
+        <v>6770660</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13088,13 +13088,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946408</t>
+          <t>https://artportalen.se/Sighting/129946708</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129946586</v>
+        <v>129954408</v>
       </c>
       <c r="B117" t="n">
         <v>79327</v>
@@ -13129,10 +13129,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471095</v>
+        <v>471019</v>
       </c>
       <c r="R117" t="n">
-        <v>6770660</v>
+        <v>6770666</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13159,22 +13159,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13200,13 +13200,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946586</t>
+          <t>https://artportalen.se/Sighting/129954408</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129946708</v>
+        <v>129954413</v>
       </c>
       <c r="B118" t="n">
         <v>79327</v>
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>471171</v>
+        <v>471028</v>
       </c>
       <c r="R118" t="n">
-        <v>6770660</v>
+        <v>6770675</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13271,22 +13271,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13312,13 +13312,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946708</t>
+          <t>https://artportalen.se/Sighting/129954413</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129954408</v>
+        <v>129954442</v>
       </c>
       <c r="B119" t="n">
         <v>79327</v>
@@ -13353,10 +13353,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471019</v>
+        <v>471053</v>
       </c>
       <c r="R119" t="n">
-        <v>6770666</v>
+        <v>6770682</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13424,13 +13424,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954408</t>
+          <t>https://artportalen.se/Sighting/129954442</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129954413</v>
+        <v>129954452</v>
       </c>
       <c r="B120" t="n">
         <v>79327</v>
@@ -13465,10 +13465,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471028</v>
+        <v>471058</v>
       </c>
       <c r="R120" t="n">
-        <v>6770675</v>
+        <v>6770677</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13536,13 +13536,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954413</t>
+          <t>https://artportalen.se/Sighting/129954452</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129954442</v>
+        <v>129954531</v>
       </c>
       <c r="B121" t="n">
         <v>79327</v>
@@ -13577,10 +13577,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471053</v>
+        <v>471106</v>
       </c>
       <c r="R121" t="n">
-        <v>6770682</v>
+        <v>6770683</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13648,13 +13648,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954442</t>
+          <t>https://artportalen.se/Sighting/129954531</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129954452</v>
+        <v>129954534</v>
       </c>
       <c r="B122" t="n">
         <v>79327</v>
@@ -13689,10 +13689,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471058</v>
+        <v>471086</v>
       </c>
       <c r="R122" t="n">
-        <v>6770677</v>
+        <v>6770684</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13760,13 +13760,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954452</t>
+          <t>https://artportalen.se/Sighting/129954534</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129954531</v>
+        <v>129954584</v>
       </c>
       <c r="B123" t="n">
         <v>79327</v>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471106</v>
+        <v>471062</v>
       </c>
       <c r="R123" t="n">
-        <v>6770683</v>
+        <v>6770731</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13872,13 +13872,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954531</t>
+          <t>https://artportalen.se/Sighting/129954584</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129954534</v>
+        <v>129954590</v>
       </c>
       <c r="B124" t="n">
         <v>79327</v>
@@ -13913,10 +13913,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471086</v>
+        <v>471013</v>
       </c>
       <c r="R124" t="n">
-        <v>6770684</v>
+        <v>6770715</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13984,13 +13984,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954534</t>
+          <t>https://artportalen.se/Sighting/129954590</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129954584</v>
+        <v>129954674</v>
       </c>
       <c r="B125" t="n">
         <v>79327</v>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>471062</v>
+        <v>470938</v>
       </c>
       <c r="R125" t="n">
-        <v>6770731</v>
+        <v>6770693</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14096,13 +14096,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954584</t>
+          <t>https://artportalen.se/Sighting/129954674</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129954590</v>
+        <v>129955100</v>
       </c>
       <c r="B126" t="n">
         <v>79327</v>
@@ -14137,10 +14137,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>471013</v>
+        <v>470981</v>
       </c>
       <c r="R126" t="n">
-        <v>6770715</v>
+        <v>6770691</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14208,13 +14208,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954590</t>
+          <t>https://artportalen.se/Sighting/129955100</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129954674</v>
+        <v>129955313</v>
       </c>
       <c r="B127" t="n">
         <v>79327</v>
@@ -14249,10 +14249,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470938</v>
+        <v>470992</v>
       </c>
       <c r="R127" t="n">
-        <v>6770693</v>
+        <v>6770702</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14320,13 +14320,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954674</t>
+          <t>https://artportalen.se/Sighting/129955313</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129955100</v>
+        <v>129956843</v>
       </c>
       <c r="B128" t="n">
         <v>79327</v>
@@ -14361,10 +14361,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470981</v>
+        <v>470953</v>
       </c>
       <c r="R128" t="n">
-        <v>6770691</v>
+        <v>6770692</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14432,13 +14432,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129955100</t>
+          <t>https://artportalen.se/Sighting/129956843</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129955313</v>
+        <v>129956851</v>
       </c>
       <c r="B129" t="n">
         <v>79327</v>
@@ -14473,10 +14473,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470992</v>
+        <v>470928</v>
       </c>
       <c r="R129" t="n">
-        <v>6770702</v>
+        <v>6770695</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14544,13 +14544,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129955313</t>
+          <t>https://artportalen.se/Sighting/129956851</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129956843</v>
+        <v>129956859</v>
       </c>
       <c r="B130" t="n">
         <v>79327</v>
@@ -14585,10 +14585,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470953</v>
+        <v>470936</v>
       </c>
       <c r="R130" t="n">
-        <v>6770692</v>
+        <v>6770721</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14656,13 +14656,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956843</t>
+          <t>https://artportalen.se/Sighting/129956859</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129956851</v>
+        <v>129957713</v>
       </c>
       <c r="B131" t="n">
         <v>79327</v>
@@ -14697,10 +14697,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470928</v>
+        <v>470904</v>
       </c>
       <c r="R131" t="n">
-        <v>6770695</v>
+        <v>6770718</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14768,13 +14768,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956851</t>
+          <t>https://artportalen.se/Sighting/129957713</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129956859</v>
+        <v>129957969</v>
       </c>
       <c r="B132" t="n">
         <v>79327</v>
@@ -14809,10 +14809,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470936</v>
+        <v>470911</v>
       </c>
       <c r="R132" t="n">
-        <v>6770721</v>
+        <v>6770707</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14880,13 +14880,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956859</t>
+          <t>https://artportalen.se/Sighting/129957969</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129957713</v>
+        <v>129958010</v>
       </c>
       <c r="B133" t="n">
         <v>79327</v>
@@ -14921,10 +14921,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>470904</v>
+        <v>470894</v>
       </c>
       <c r="R133" t="n">
-        <v>6770718</v>
+        <v>6770713</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14992,13 +14992,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957713</t>
+          <t>https://artportalen.se/Sighting/129958010</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129957969</v>
+        <v>129958133</v>
       </c>
       <c r="B134" t="n">
         <v>79327</v>
@@ -15033,10 +15033,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>470911</v>
+        <v>470869</v>
       </c>
       <c r="R134" t="n">
-        <v>6770707</v>
+        <v>6770702</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15104,13 +15104,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957969</t>
+          <t>https://artportalen.se/Sighting/129958133</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129958010</v>
+        <v>129958151</v>
       </c>
       <c r="B135" t="n">
         <v>79327</v>
@@ -15145,10 +15145,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470894</v>
+        <v>470842</v>
       </c>
       <c r="R135" t="n">
-        <v>6770713</v>
+        <v>6770709</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15216,13 +15216,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958010</t>
+          <t>https://artportalen.se/Sighting/129958151</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129958133</v>
+        <v>129958214</v>
       </c>
       <c r="B136" t="n">
         <v>79327</v>
@@ -15257,10 +15257,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470869</v>
+        <v>470823</v>
       </c>
       <c r="R136" t="n">
-        <v>6770702</v>
+        <v>6770705</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15328,13 +15328,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958133</t>
+          <t>https://artportalen.se/Sighting/129958214</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129958151</v>
+        <v>129958228</v>
       </c>
       <c r="B137" t="n">
         <v>79327</v>
@@ -15369,10 +15369,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470842</v>
+        <v>470813</v>
       </c>
       <c r="R137" t="n">
-        <v>6770709</v>
+        <v>6770681</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15440,13 +15440,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958151</t>
+          <t>https://artportalen.se/Sighting/129958228</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129958214</v>
+        <v>129958464</v>
       </c>
       <c r="B138" t="n">
         <v>79327</v>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470823</v>
+        <v>470822</v>
       </c>
       <c r="R138" t="n">
-        <v>6770705</v>
+        <v>6770673</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15552,13 +15552,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958214</t>
+          <t>https://artportalen.se/Sighting/129958464</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129958228</v>
+        <v>129958466</v>
       </c>
       <c r="B139" t="n">
         <v>79327</v>
@@ -15593,10 +15593,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470813</v>
+        <v>470812</v>
       </c>
       <c r="R139" t="n">
-        <v>6770681</v>
+        <v>6770670</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15664,13 +15664,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958228</t>
+          <t>https://artportalen.se/Sighting/129958466</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129958464</v>
+        <v>129958499</v>
       </c>
       <c r="B140" t="n">
         <v>79327</v>
@@ -15705,10 +15705,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470822</v>
+        <v>470850</v>
       </c>
       <c r="R140" t="n">
-        <v>6770673</v>
+        <v>6770690</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15776,13 +15776,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958464</t>
+          <t>https://artportalen.se/Sighting/129958499</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129958466</v>
+        <v>129958545</v>
       </c>
       <c r="B141" t="n">
         <v>79327</v>
@@ -15817,10 +15817,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>470812</v>
+        <v>470877</v>
       </c>
       <c r="R141" t="n">
-        <v>6770670</v>
+        <v>6770687</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15888,13 +15888,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958466</t>
+          <t>https://artportalen.se/Sighting/129958545</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129958499</v>
+        <v>129958694</v>
       </c>
       <c r="B142" t="n">
         <v>79327</v>
@@ -15929,10 +15929,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>470850</v>
+        <v>470844</v>
       </c>
       <c r="R142" t="n">
-        <v>6770690</v>
+        <v>6770699</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16000,13 +16000,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958499</t>
+          <t>https://artportalen.se/Sighting/129958694</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129958545</v>
+        <v>129958706</v>
       </c>
       <c r="B143" t="n">
         <v>79327</v>
@@ -16041,10 +16041,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>470877</v>
+        <v>470816</v>
       </c>
       <c r="R143" t="n">
-        <v>6770687</v>
+        <v>6770646</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16112,13 +16112,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958545</t>
+          <t>https://artportalen.se/Sighting/129958706</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129958694</v>
+        <v>129958754</v>
       </c>
       <c r="B144" t="n">
         <v>79327</v>
@@ -16153,10 +16153,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>470844</v>
+        <v>470817</v>
       </c>
       <c r="R144" t="n">
-        <v>6770699</v>
+        <v>6770608</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16224,13 +16224,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958694</t>
+          <t>https://artportalen.se/Sighting/129958754</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129958706</v>
+        <v>129958775</v>
       </c>
       <c r="B145" t="n">
         <v>79327</v>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>470816</v>
+        <v>470803</v>
       </c>
       <c r="R145" t="n">
-        <v>6770646</v>
+        <v>6770595</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16336,13 +16336,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958706</t>
+          <t>https://artportalen.se/Sighting/129958775</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129958754</v>
+        <v>129958795</v>
       </c>
       <c r="B146" t="n">
         <v>79327</v>
@@ -16377,10 +16377,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>470817</v>
+        <v>470822</v>
       </c>
       <c r="R146" t="n">
-        <v>6770608</v>
+        <v>6770615</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16425,6 +16425,11 @@
           <t>09:55</t>
         </is>
       </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
@@ -16448,13 +16453,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958754</t>
+          <t>https://artportalen.se/Sighting/129958795</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129958775</v>
+        <v>129958800</v>
       </c>
       <c r="B147" t="n">
         <v>79327</v>
@@ -16489,10 +16494,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470803</v>
+        <v>470858</v>
       </c>
       <c r="R147" t="n">
-        <v>6770595</v>
+        <v>6770602</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16560,13 +16565,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958775</t>
+          <t>https://artportalen.se/Sighting/129958800</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129958795</v>
+        <v>129958828</v>
       </c>
       <c r="B148" t="n">
         <v>79327</v>
@@ -16601,10 +16606,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470822</v>
+        <v>470871</v>
       </c>
       <c r="R148" t="n">
-        <v>6770615</v>
+        <v>6770635</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16649,11 +16654,6 @@
           <t>09:55</t>
         </is>
       </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -16677,13 +16677,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958795</t>
+          <t>https://artportalen.se/Sighting/129958828</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129958800</v>
+        <v>129958841</v>
       </c>
       <c r="B149" t="n">
         <v>79327</v>
@@ -16718,10 +16718,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>470858</v>
+        <v>470828</v>
       </c>
       <c r="R149" t="n">
-        <v>6770602</v>
+        <v>6770636</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16789,13 +16789,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958800</t>
+          <t>https://artportalen.se/Sighting/129958841</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129958828</v>
+        <v>129958842</v>
       </c>
       <c r="B150" t="n">
         <v>79327</v>
@@ -16830,10 +16830,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>470871</v>
+        <v>470820</v>
       </c>
       <c r="R150" t="n">
-        <v>6770635</v>
+        <v>6770624</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16901,13 +16901,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958828</t>
+          <t>https://artportalen.se/Sighting/129958842</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129958841</v>
+        <v>129958895</v>
       </c>
       <c r="B151" t="n">
         <v>79327</v>
@@ -16942,10 +16942,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>470828</v>
+        <v>470887</v>
       </c>
       <c r="R151" t="n">
-        <v>6770636</v>
+        <v>6770658</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17013,13 +17013,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958841</t>
+          <t>https://artportalen.se/Sighting/129958895</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129958842</v>
+        <v>129958937</v>
       </c>
       <c r="B152" t="n">
         <v>79327</v>
@@ -17054,10 +17054,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>470820</v>
+        <v>470897</v>
       </c>
       <c r="R152" t="n">
-        <v>6770624</v>
+        <v>6770647</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17125,13 +17125,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958842</t>
+          <t>https://artportalen.se/Sighting/129958937</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129958895</v>
+        <v>129959037</v>
       </c>
       <c r="B153" t="n">
         <v>79327</v>
@@ -17166,10 +17166,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>470887</v>
+        <v>470908</v>
       </c>
       <c r="R153" t="n">
-        <v>6770658</v>
+        <v>6770622</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17237,13 +17237,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958895</t>
+          <t>https://artportalen.se/Sighting/129959037</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129958937</v>
+        <v>129959060</v>
       </c>
       <c r="B154" t="n">
         <v>79327</v>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>470897</v>
+        <v>470926</v>
       </c>
       <c r="R154" t="n">
-        <v>6770647</v>
+        <v>6770613</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17349,13 +17349,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958937</t>
+          <t>https://artportalen.se/Sighting/129959060</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129959037</v>
+        <v>129959250</v>
       </c>
       <c r="B155" t="n">
         <v>79327</v>
@@ -17390,10 +17390,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470908</v>
+        <v>470943</v>
       </c>
       <c r="R155" t="n">
-        <v>6770622</v>
+        <v>6770559</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17461,13 +17461,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959037</t>
+          <t>https://artportalen.se/Sighting/129959250</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129959060</v>
+        <v>129959256</v>
       </c>
       <c r="B156" t="n">
         <v>79327</v>
@@ -17502,10 +17502,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>470926</v>
+        <v>470922</v>
       </c>
       <c r="R156" t="n">
-        <v>6770613</v>
+        <v>6770556</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17573,13 +17573,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959060</t>
+          <t>https://artportalen.se/Sighting/129959256</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129959250</v>
+        <v>129959294</v>
       </c>
       <c r="B157" t="n">
         <v>79327</v>
@@ -17614,10 +17614,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>470943</v>
+        <v>470904</v>
       </c>
       <c r="R157" t="n">
-        <v>6770559</v>
+        <v>6770537</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17685,13 +17685,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959250</t>
+          <t>https://artportalen.se/Sighting/129959294</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129959256</v>
+        <v>129959303</v>
       </c>
       <c r="B158" t="n">
         <v>79327</v>
@@ -17726,10 +17726,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470922</v>
+        <v>470879</v>
       </c>
       <c r="R158" t="n">
-        <v>6770556</v>
+        <v>6770545</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17797,13 +17797,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959256</t>
+          <t>https://artportalen.se/Sighting/129959303</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129959294</v>
+        <v>129959375</v>
       </c>
       <c r="B159" t="n">
         <v>79327</v>
@@ -17838,10 +17838,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>470904</v>
+        <v>470851</v>
       </c>
       <c r="R159" t="n">
-        <v>6770537</v>
+        <v>6770520</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17909,13 +17909,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959294</t>
+          <t>https://artportalen.se/Sighting/129959375</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129959303</v>
+        <v>129959389</v>
       </c>
       <c r="B160" t="n">
         <v>79327</v>
@@ -17950,10 +17950,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>470879</v>
+        <v>470824</v>
       </c>
       <c r="R160" t="n">
-        <v>6770545</v>
+        <v>6770523</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18021,13 +18021,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959303</t>
+          <t>https://artportalen.se/Sighting/129959389</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129959375</v>
+        <v>129959479</v>
       </c>
       <c r="B161" t="n">
         <v>79327</v>
@@ -18062,10 +18062,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>470851</v>
+        <v>470837</v>
       </c>
       <c r="R161" t="n">
-        <v>6770520</v>
+        <v>6770498</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18133,13 +18133,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959375</t>
+          <t>https://artportalen.se/Sighting/129959479</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129959389</v>
+        <v>129959501</v>
       </c>
       <c r="B162" t="n">
         <v>79327</v>
@@ -18174,10 +18174,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>470824</v>
+        <v>470807</v>
       </c>
       <c r="R162" t="n">
-        <v>6770523</v>
+        <v>6770491</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18245,13 +18245,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959389</t>
+          <t>https://artportalen.se/Sighting/129959501</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129959479</v>
+        <v>129959519</v>
       </c>
       <c r="B163" t="n">
         <v>79327</v>
@@ -18286,10 +18286,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>470837</v>
+        <v>470822</v>
       </c>
       <c r="R163" t="n">
-        <v>6770498</v>
+        <v>6770452</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18357,13 +18357,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959479</t>
+          <t>https://artportalen.se/Sighting/129959519</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129959501</v>
+        <v>129959692</v>
       </c>
       <c r="B164" t="n">
         <v>79327</v>
@@ -18398,10 +18398,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>470807</v>
+        <v>470864</v>
       </c>
       <c r="R164" t="n">
-        <v>6770491</v>
+        <v>6770438</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18469,13 +18469,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959501</t>
+          <t>https://artportalen.se/Sighting/129959692</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129959519</v>
+        <v>129959740</v>
       </c>
       <c r="B165" t="n">
         <v>79327</v>
@@ -18510,10 +18510,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>470822</v>
+        <v>470905</v>
       </c>
       <c r="R165" t="n">
-        <v>6770452</v>
+        <v>6770435</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18581,13 +18581,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959519</t>
+          <t>https://artportalen.se/Sighting/129959740</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129959692</v>
+        <v>129959772</v>
       </c>
       <c r="B166" t="n">
         <v>79327</v>
@@ -18622,10 +18622,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470864</v>
+        <v>470900</v>
       </c>
       <c r="R166" t="n">
-        <v>6770438</v>
+        <v>6770473</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18693,13 +18693,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959692</t>
+          <t>https://artportalen.se/Sighting/129959772</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129959740</v>
+        <v>129959808</v>
       </c>
       <c r="B167" t="n">
         <v>79327</v>
@@ -18734,10 +18734,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470905</v>
+        <v>470942</v>
       </c>
       <c r="R167" t="n">
-        <v>6770435</v>
+        <v>6770455</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18805,13 +18805,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959740</t>
+          <t>https://artportalen.se/Sighting/129959808</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129959772</v>
+        <v>129959994</v>
       </c>
       <c r="B168" t="n">
         <v>79327</v>
@@ -18846,10 +18846,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>470900</v>
+        <v>470954</v>
       </c>
       <c r="R168" t="n">
-        <v>6770473</v>
+        <v>6770475</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18917,13 +18917,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959772</t>
+          <t>https://artportalen.se/Sighting/129959994</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129959808</v>
+        <v>129960002</v>
       </c>
       <c r="B169" t="n">
         <v>79327</v>
@@ -18958,10 +18958,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>470942</v>
+        <v>470932</v>
       </c>
       <c r="R169" t="n">
-        <v>6770455</v>
+        <v>6770480</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19029,13 +19029,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959808</t>
+          <t>https://artportalen.se/Sighting/129960002</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129959994</v>
+        <v>129960437</v>
       </c>
       <c r="B170" t="n">
         <v>79327</v>
@@ -19070,10 +19070,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>470954</v>
+        <v>470948</v>
       </c>
       <c r="R170" t="n">
-        <v>6770475</v>
+        <v>6770533</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19141,13 +19141,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959994</t>
+          <t>https://artportalen.se/Sighting/129960437</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129960002</v>
+        <v>129960691</v>
       </c>
       <c r="B171" t="n">
         <v>79327</v>
@@ -19182,10 +19182,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>470932</v>
+        <v>471056</v>
       </c>
       <c r="R171" t="n">
-        <v>6770480</v>
+        <v>6770494</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19253,13 +19253,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960002</t>
+          <t>https://artportalen.se/Sighting/129960691</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129960437</v>
+        <v>129960763</v>
       </c>
       <c r="B172" t="n">
         <v>79327</v>
@@ -19294,10 +19294,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>470948</v>
+        <v>471062</v>
       </c>
       <c r="R172" t="n">
-        <v>6770533</v>
+        <v>6770538</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19365,13 +19365,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960437</t>
+          <t>https://artportalen.se/Sighting/129960763</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129960691</v>
+        <v>129960790</v>
       </c>
       <c r="B173" t="n">
         <v>79327</v>
@@ -19406,10 +19406,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471056</v>
+        <v>471073</v>
       </c>
       <c r="R173" t="n">
-        <v>6770494</v>
+        <v>6770551</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19477,13 +19477,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960691</t>
+          <t>https://artportalen.se/Sighting/129960790</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129960763</v>
+        <v>129960823</v>
       </c>
       <c r="B174" t="n">
         <v>79327</v>
@@ -19518,10 +19518,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>471062</v>
+        <v>471078</v>
       </c>
       <c r="R174" t="n">
-        <v>6770538</v>
+        <v>6770561</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19566,6 +19566,11 @@
           <t>09:55</t>
         </is>
       </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -19589,13 +19594,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960763</t>
+          <t>https://artportalen.se/Sighting/129960823</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129960790</v>
+        <v>129960843</v>
       </c>
       <c r="B175" t="n">
         <v>79327</v>
@@ -19630,10 +19635,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471073</v>
+        <v>471097</v>
       </c>
       <c r="R175" t="n">
-        <v>6770551</v>
+        <v>6770561</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19701,13 +19706,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960790</t>
+          <t>https://artportalen.se/Sighting/129960843</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129960823</v>
+        <v>129960864</v>
       </c>
       <c r="B176" t="n">
         <v>79327</v>
@@ -19742,10 +19747,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471078</v>
+        <v>471116</v>
       </c>
       <c r="R176" t="n">
-        <v>6770561</v>
+        <v>6770565</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19790,11 +19795,6 @@
           <t>09:55</t>
         </is>
       </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
@@ -19818,13 +19818,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960823</t>
+          <t>https://artportalen.se/Sighting/129960864</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129960843</v>
+        <v>129960884</v>
       </c>
       <c r="B177" t="n">
         <v>79327</v>
@@ -19859,10 +19859,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>471097</v>
+        <v>471129</v>
       </c>
       <c r="R177" t="n">
-        <v>6770561</v>
+        <v>6770567</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19930,13 +19930,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960843</t>
+          <t>https://artportalen.se/Sighting/129960884</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129960864</v>
+        <v>129960891</v>
       </c>
       <c r="B178" t="n">
         <v>79327</v>
@@ -19971,10 +19971,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>471116</v>
+        <v>471147</v>
       </c>
       <c r="R178" t="n">
-        <v>6770565</v>
+        <v>6770575</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20042,13 +20042,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960864</t>
+          <t>https://artportalen.se/Sighting/129960891</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129960884</v>
+        <v>129960901</v>
       </c>
       <c r="B179" t="n">
         <v>79327</v>
@@ -20083,10 +20083,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>471129</v>
+        <v>471185</v>
       </c>
       <c r="R179" t="n">
-        <v>6770567</v>
+        <v>6770590</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20154,13 +20154,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960884</t>
+          <t>https://artportalen.se/Sighting/129960901</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129960891</v>
+        <v>129960929</v>
       </c>
       <c r="B180" t="n">
         <v>79327</v>
@@ -20195,10 +20195,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>471147</v>
+        <v>471159</v>
       </c>
       <c r="R180" t="n">
-        <v>6770575</v>
+        <v>6770613</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20266,13 +20266,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960891</t>
+          <t>https://artportalen.se/Sighting/129960929</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129960901</v>
+        <v>129961603</v>
       </c>
       <c r="B181" t="n">
         <v>79327</v>
@@ -20307,10 +20307,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471185</v>
+        <v>471262</v>
       </c>
       <c r="R181" t="n">
-        <v>6770590</v>
+        <v>6770622</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20378,13 +20378,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960901</t>
+          <t>https://artportalen.se/Sighting/129961603</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129960929</v>
+        <v>129961818</v>
       </c>
       <c r="B182" t="n">
         <v>79327</v>
@@ -20419,10 +20419,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471159</v>
+        <v>471228</v>
       </c>
       <c r="R182" t="n">
-        <v>6770613</v>
+        <v>6770667</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20490,13 +20490,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960929</t>
+          <t>https://artportalen.se/Sighting/129961818</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129961603</v>
+        <v>129961937</v>
       </c>
       <c r="B183" t="n">
         <v>79327</v>
@@ -20531,10 +20531,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>471262</v>
+        <v>471216</v>
       </c>
       <c r="R183" t="n">
-        <v>6770622</v>
+        <v>6770650</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20602,13 +20602,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961603</t>
+          <t>https://artportalen.se/Sighting/129961937</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129961818</v>
+        <v>129962073</v>
       </c>
       <c r="B184" t="n">
         <v>79327</v>
@@ -20643,10 +20643,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>471228</v>
+        <v>471222</v>
       </c>
       <c r="R184" t="n">
-        <v>6770667</v>
+        <v>6770635</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20714,13 +20714,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961818</t>
+          <t>https://artportalen.se/Sighting/129962073</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129961937</v>
+        <v>129962119</v>
       </c>
       <c r="B185" t="n">
         <v>79327</v>
@@ -20755,10 +20755,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>471216</v>
+        <v>471156</v>
       </c>
       <c r="R185" t="n">
-        <v>6770650</v>
+        <v>6770665</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20826,13 +20826,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961937</t>
+          <t>https://artportalen.se/Sighting/129962119</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129962073</v>
+        <v>129962224</v>
       </c>
       <c r="B186" t="n">
         <v>79327</v>
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>471222</v>
+        <v>471098</v>
       </c>
       <c r="R186" t="n">
-        <v>6770635</v>
+        <v>6770634</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20938,13 +20938,13 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962073</t>
+          <t>https://artportalen.se/Sighting/129962224</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129962119</v>
+        <v>129962243</v>
       </c>
       <c r="B187" t="n">
         <v>79327</v>
@@ -20979,10 +20979,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>471156</v>
+        <v>471074</v>
       </c>
       <c r="R187" t="n">
-        <v>6770665</v>
+        <v>6770617</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21050,13 +21050,13 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962119</t>
+          <t>https://artportalen.se/Sighting/129962243</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129962224</v>
+        <v>129962260</v>
       </c>
       <c r="B188" t="n">
         <v>79327</v>
@@ -21091,10 +21091,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>471098</v>
+        <v>471044</v>
       </c>
       <c r="R188" t="n">
-        <v>6770634</v>
+        <v>6770615</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21162,13 +21162,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962224</t>
+          <t>https://artportalen.se/Sighting/129962260</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129962243</v>
+        <v>129962290</v>
       </c>
       <c r="B189" t="n">
         <v>79327</v>
@@ -21203,10 +21203,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>471074</v>
+        <v>471033</v>
       </c>
       <c r="R189" t="n">
-        <v>6770617</v>
+        <v>6770614</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21274,13 +21274,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962243</t>
+          <t>https://artportalen.se/Sighting/129962290</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129962260</v>
+        <v>129962320</v>
       </c>
       <c r="B190" t="n">
         <v>79327</v>
@@ -21315,10 +21315,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>471044</v>
+        <v>471024</v>
       </c>
       <c r="R190" t="n">
-        <v>6770615</v>
+        <v>6770624</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21386,13 +21386,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962260</t>
+          <t>https://artportalen.se/Sighting/129962320</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129962290</v>
+        <v>129962351</v>
       </c>
       <c r="B191" t="n">
         <v>79327</v>
@@ -21427,10 +21427,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>471033</v>
+        <v>471017</v>
       </c>
       <c r="R191" t="n">
-        <v>6770614</v>
+        <v>6770613</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21498,13 +21498,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962290</t>
+          <t>https://artportalen.se/Sighting/129962351</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129962320</v>
+        <v>129962379</v>
       </c>
       <c r="B192" t="n">
         <v>79327</v>
@@ -21539,10 +21539,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>471024</v>
+        <v>470996</v>
       </c>
       <c r="R192" t="n">
-        <v>6770624</v>
+        <v>6770611</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21610,13 +21610,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962320</t>
+          <t>https://artportalen.se/Sighting/129962379</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129962351</v>
+        <v>129962390</v>
       </c>
       <c r="B193" t="n">
         <v>79327</v>
@@ -21651,10 +21651,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>471017</v>
+        <v>471004</v>
       </c>
       <c r="R193" t="n">
-        <v>6770613</v>
+        <v>6770581</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21722,13 +21722,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962351</t>
+          <t>https://artportalen.se/Sighting/129962390</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129962379</v>
+        <v>129962417</v>
       </c>
       <c r="B194" t="n">
         <v>79327</v>
@@ -21763,10 +21763,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>470996</v>
+        <v>471002</v>
       </c>
       <c r="R194" t="n">
-        <v>6770611</v>
+        <v>6770618</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21834,13 +21834,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962379</t>
+          <t>https://artportalen.se/Sighting/129962417</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129962390</v>
+        <v>129962443</v>
       </c>
       <c r="B195" t="n">
         <v>79327</v>
@@ -21875,10 +21875,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>471004</v>
+        <v>470989</v>
       </c>
       <c r="R195" t="n">
-        <v>6770581</v>
+        <v>6770629</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21946,13 +21946,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962390</t>
+          <t>https://artportalen.se/Sighting/129962443</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129962417</v>
+        <v>129962446</v>
       </c>
       <c r="B196" t="n">
         <v>79327</v>
@@ -21987,10 +21987,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>471002</v>
+        <v>470993</v>
       </c>
       <c r="R196" t="n">
-        <v>6770618</v>
+        <v>6770643</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22058,51 +22058,56 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962417</t>
+          <t>https://artportalen.se/Sighting/129962446</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129962443</v>
+        <v>129944452</v>
       </c>
       <c r="B197" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>470989</v>
+        <v>471330</v>
       </c>
       <c r="R197" t="n">
-        <v>6770629</v>
+        <v>6770712</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22129,22 +22134,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22170,51 +22175,56 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962443</t>
+          <t>https://artportalen.se/Sighting/129944452</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129962446</v>
+        <v>129945156</v>
       </c>
       <c r="B198" t="n">
-        <v>79327</v>
+        <v>57950</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>470993</v>
+        <v>471198</v>
       </c>
       <c r="R198" t="n">
-        <v>6770643</v>
+        <v>6770725</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22241,22 +22251,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22282,13 +22292,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962446</t>
+          <t>https://artportalen.se/Sighting/129945156</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129944452</v>
+        <v>129945440</v>
       </c>
       <c r="B199" t="n">
         <v>57950</v>
@@ -22319,7 +22329,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22328,10 +22338,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471330</v>
+        <v>471189</v>
       </c>
       <c r="R199" t="n">
-        <v>6770712</v>
+        <v>6770706</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22399,13 +22409,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944452</t>
+          <t>https://artportalen.se/Sighting/129945440</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129945156</v>
+        <v>129946321</v>
       </c>
       <c r="B200" t="n">
         <v>57950</v>
@@ -22436,7 +22446,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22445,10 +22455,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>471198</v>
+        <v>470871</v>
       </c>
       <c r="R200" t="n">
-        <v>6770725</v>
+        <v>6770635</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22516,13 +22526,13 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945156</t>
+          <t>https://artportalen.se/Sighting/129946321</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129945440</v>
+        <v>129946365</v>
       </c>
       <c r="B201" t="n">
         <v>57950</v>
@@ -22562,10 +22572,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>471189</v>
+        <v>470910</v>
       </c>
       <c r="R201" t="n">
-        <v>6770706</v>
+        <v>6770605</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22633,13 +22643,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945440</t>
+          <t>https://artportalen.se/Sighting/129946365</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129946321</v>
+        <v>129946391</v>
       </c>
       <c r="B202" t="n">
         <v>57950</v>
@@ -22670,7 +22680,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22679,10 +22689,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>470871</v>
+        <v>470921</v>
       </c>
       <c r="R202" t="n">
-        <v>6770635</v>
+        <v>6770579</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22750,13 +22760,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946321</t>
+          <t>https://artportalen.se/Sighting/129946391</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129946365</v>
+        <v>129946436</v>
       </c>
       <c r="B203" t="n">
         <v>57950</v>
@@ -22787,7 +22797,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22796,10 +22806,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>470910</v>
+        <v>470971</v>
       </c>
       <c r="R203" t="n">
-        <v>6770605</v>
+        <v>6770603</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22867,13 +22877,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946365</t>
+          <t>https://artportalen.se/Sighting/129946436</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129946391</v>
+        <v>129954441</v>
       </c>
       <c r="B204" t="n">
         <v>57950</v>
@@ -22913,10 +22923,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>470921</v>
+        <v>471052</v>
       </c>
       <c r="R204" t="n">
-        <v>6770579</v>
+        <v>6770696</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22943,22 +22953,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22984,13 +22994,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946391</t>
+          <t>https://artportalen.se/Sighting/129954441</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129946436</v>
+        <v>129957253</v>
       </c>
       <c r="B205" t="n">
         <v>57950</v>
@@ -23021,7 +23031,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -23030,10 +23040,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>470971</v>
+        <v>470916</v>
       </c>
       <c r="R205" t="n">
-        <v>6770603</v>
+        <v>6770721</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23060,22 +23070,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23101,13 +23111,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946436</t>
+          <t>https://artportalen.se/Sighting/129957253</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129954441</v>
+        <v>129958691</v>
       </c>
       <c r="B206" t="n">
         <v>57950</v>
@@ -23147,10 +23157,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>471052</v>
+        <v>470844</v>
       </c>
       <c r="R206" t="n">
-        <v>6770696</v>
+        <v>6770699</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23218,13 +23228,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954441</t>
+          <t>https://artportalen.se/Sighting/129958691</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129957253</v>
+        <v>129959434</v>
       </c>
       <c r="B207" t="n">
         <v>57950</v>
@@ -23264,10 +23274,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470916</v>
+        <v>470824</v>
       </c>
       <c r="R207" t="n">
-        <v>6770721</v>
+        <v>6770523</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23335,13 +23345,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957253</t>
+          <t>https://artportalen.se/Sighting/129959434</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129958691</v>
+        <v>129959567</v>
       </c>
       <c r="B208" t="n">
         <v>57950</v>
@@ -23381,10 +23391,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470844</v>
+        <v>470822</v>
       </c>
       <c r="R208" t="n">
-        <v>6770699</v>
+        <v>6770452</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23452,13 +23462,13 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958691</t>
+          <t>https://artportalen.se/Sighting/129959567</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129959434</v>
+        <v>129959730</v>
       </c>
       <c r="B209" t="n">
         <v>57950</v>
@@ -23489,7 +23499,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -23498,10 +23508,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>470824</v>
+        <v>470868</v>
       </c>
       <c r="R209" t="n">
-        <v>6770523</v>
+        <v>6770431</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23569,13 +23579,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959434</t>
+          <t>https://artportalen.se/Sighting/129959730</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129959567</v>
+        <v>129959870</v>
       </c>
       <c r="B210" t="n">
         <v>57950</v>
@@ -23606,7 +23616,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -23615,10 +23625,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>470822</v>
+        <v>470952</v>
       </c>
       <c r="R210" t="n">
-        <v>6770452</v>
+        <v>6770464</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23686,13 +23696,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959567</t>
+          <t>https://artportalen.se/Sighting/129959870</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129959730</v>
+        <v>129960642</v>
       </c>
       <c r="B211" t="n">
         <v>57950</v>
@@ -23732,10 +23742,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>470868</v>
+        <v>471025</v>
       </c>
       <c r="R211" t="n">
-        <v>6770431</v>
+        <v>6770488</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23803,13 +23813,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959730</t>
+          <t>https://artportalen.se/Sighting/129960642</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129959870</v>
+        <v>129962343</v>
       </c>
       <c r="B212" t="n">
         <v>57950</v>
@@ -23840,7 +23850,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -23849,10 +23859,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>470952</v>
+        <v>471017</v>
       </c>
       <c r="R212" t="n">
-        <v>6770464</v>
+        <v>6770613</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23920,13 +23930,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959870</t>
+          <t>https://artportalen.se/Sighting/129962343</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129960642</v>
+        <v>129962374</v>
       </c>
       <c r="B213" t="n">
         <v>57950</v>
@@ -23957,7 +23967,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23966,10 +23976,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>471025</v>
+        <v>470996</v>
       </c>
       <c r="R213" t="n">
-        <v>6770488</v>
+        <v>6770611</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24037,13 +24047,13 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960642</t>
+          <t>https://artportalen.se/Sighting/129962374</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129962343</v>
+        <v>129962430</v>
       </c>
       <c r="B214" t="n">
         <v>57950</v>
@@ -24074,7 +24084,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -24083,10 +24093,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471017</v>
+        <v>470989</v>
       </c>
       <c r="R214" t="n">
-        <v>6770613</v>
+        <v>6770629</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24154,44 +24164,48 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962343</t>
+          <t>https://artportalen.se/Sighting/129962430</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129962374</v>
+        <v>129944878</v>
       </c>
       <c r="B215" t="n">
-        <v>57950</v>
+        <v>58114</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -24200,13 +24214,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>470996</v>
+        <v>471258</v>
       </c>
       <c r="R215" t="n">
-        <v>6770611</v>
+        <v>6770712</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24230,22 +24244,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24271,16 +24285,16 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962374</t>
+          <t>https://artportalen.se/Sighting/129944878</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129962430</v>
+        <v>129944062</v>
       </c>
       <c r="B216" t="n">
-        <v>57950</v>
+        <v>8455</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24288,27 +24302,27 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -24317,10 +24331,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>470989</v>
+        <v>471432</v>
       </c>
       <c r="R216" t="n">
-        <v>6770629</v>
+        <v>6770716</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24347,22 +24361,22 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24388,48 +24402,44 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962430</t>
+          <t>https://artportalen.se/Sighting/129944062</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129944878</v>
+        <v>129944158</v>
       </c>
       <c r="B217" t="n">
-        <v>58114</v>
+        <v>8455</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="M217" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -24438,13 +24448,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>471258</v>
+        <v>471363</v>
       </c>
       <c r="R217" t="n">
-        <v>6770712</v>
+        <v>6770736</v>
       </c>
       <c r="S217" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -24509,13 +24519,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944878</t>
+          <t>https://artportalen.se/Sighting/129944158</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129944062</v>
+        <v>129944454</v>
       </c>
       <c r="B218" t="n">
         <v>8455</v>
@@ -24544,21 +24554,16 @@
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="M218" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>471432</v>
+        <v>471330</v>
       </c>
       <c r="R218" t="n">
-        <v>6770716</v>
+        <v>6770712</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24626,13 +24631,13 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944062</t>
+          <t>https://artportalen.se/Sighting/129944454</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129944158</v>
+        <v>129945161</v>
       </c>
       <c r="B219" t="n">
         <v>8455</v>
@@ -24672,10 +24677,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471363</v>
+        <v>471198</v>
       </c>
       <c r="R219" t="n">
-        <v>6770736</v>
+        <v>6770725</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24743,13 +24748,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944158</t>
+          <t>https://artportalen.se/Sighting/129945161</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129944454</v>
+        <v>129945444</v>
       </c>
       <c r="B220" t="n">
         <v>8455</v>
@@ -24778,16 +24783,21 @@
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>471330</v>
+        <v>471189</v>
       </c>
       <c r="R220" t="n">
-        <v>6770712</v>
+        <v>6770706</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24855,13 +24865,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944454</t>
+          <t>https://artportalen.se/Sighting/129945444</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129945161</v>
+        <v>129946047</v>
       </c>
       <c r="B221" t="n">
         <v>8455</v>
@@ -24890,21 +24900,16 @@
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>471198</v>
+        <v>471161</v>
       </c>
       <c r="R221" t="n">
-        <v>6770725</v>
+        <v>6770705</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24972,13 +24977,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945161</t>
+          <t>https://artportalen.se/Sighting/129946047</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129945444</v>
+        <v>129946334</v>
       </c>
       <c r="B222" t="n">
         <v>8455</v>
@@ -25018,10 +25023,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>471189</v>
+        <v>470871</v>
       </c>
       <c r="R222" t="n">
-        <v>6770706</v>
+        <v>6770635</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25089,13 +25094,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945444</t>
+          <t>https://artportalen.se/Sighting/129946334</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129946047</v>
+        <v>129946444</v>
       </c>
       <c r="B223" t="n">
         <v>8455</v>
@@ -25124,16 +25129,21 @@
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>471161</v>
+        <v>470971</v>
       </c>
       <c r="R223" t="n">
-        <v>6770705</v>
+        <v>6770603</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25201,13 +25211,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946047</t>
+          <t>https://artportalen.se/Sighting/129946444</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129946334</v>
+        <v>129954662</v>
       </c>
       <c r="B224" t="n">
         <v>8455</v>
@@ -25247,10 +25257,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470871</v>
+        <v>470941</v>
       </c>
       <c r="R224" t="n">
-        <v>6770635</v>
+        <v>6770708</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25277,22 +25287,22 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25318,13 +25328,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946334</t>
+          <t>https://artportalen.se/Sighting/129954662</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129946444</v>
+        <v>129958131</v>
       </c>
       <c r="B225" t="n">
         <v>8455</v>
@@ -25364,10 +25374,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470971</v>
+        <v>470869</v>
       </c>
       <c r="R225" t="n">
-        <v>6770603</v>
+        <v>6770702</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25394,22 +25404,22 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25435,13 +25445,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946444</t>
+          <t>https://artportalen.se/Sighting/129958131</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129954662</v>
+        <v>129958199</v>
       </c>
       <c r="B226" t="n">
         <v>8455</v>
@@ -25481,10 +25491,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>470941</v>
+        <v>470823</v>
       </c>
       <c r="R226" t="n">
-        <v>6770708</v>
+        <v>6770705</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25552,13 +25562,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954662</t>
+          <t>https://artportalen.se/Sighting/129958199</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129958131</v>
+        <v>129958686</v>
       </c>
       <c r="B227" t="n">
         <v>8455</v>
@@ -25598,10 +25608,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>470869</v>
+        <v>470844</v>
       </c>
       <c r="R227" t="n">
-        <v>6770702</v>
+        <v>6770699</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25669,13 +25679,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958131</t>
+          <t>https://artportalen.se/Sighting/129958686</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129958199</v>
+        <v>129959110</v>
       </c>
       <c r="B228" t="n">
         <v>8455</v>
@@ -25715,10 +25725,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470823</v>
+        <v>470926</v>
       </c>
       <c r="R228" t="n">
-        <v>6770705</v>
+        <v>6770613</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25786,13 +25796,13 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958199</t>
+          <t>https://artportalen.se/Sighting/129959110</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129958686</v>
+        <v>129959223</v>
       </c>
       <c r="B229" t="n">
         <v>8455</v>
@@ -25832,10 +25842,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>470844</v>
+        <v>470921</v>
       </c>
       <c r="R229" t="n">
-        <v>6770699</v>
+        <v>6770579</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25903,13 +25913,13 @@
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958686</t>
+          <t>https://artportalen.se/Sighting/129959223</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129959110</v>
+        <v>129959285</v>
       </c>
       <c r="B230" t="n">
         <v>8455</v>
@@ -25949,10 +25959,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>470926</v>
+        <v>470922</v>
       </c>
       <c r="R230" t="n">
-        <v>6770613</v>
+        <v>6770556</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26020,13 +26030,13 @@
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959110</t>
+          <t>https://artportalen.se/Sighting/129959285</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129959223</v>
+        <v>129959441</v>
       </c>
       <c r="B231" t="n">
         <v>8455</v>
@@ -26066,10 +26076,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>470921</v>
+        <v>470824</v>
       </c>
       <c r="R231" t="n">
-        <v>6770579</v>
+        <v>6770523</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26137,13 +26147,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959223</t>
+          <t>https://artportalen.se/Sighting/129959441</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129959285</v>
+        <v>129959579</v>
       </c>
       <c r="B232" t="n">
         <v>8455</v>
@@ -26183,10 +26193,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>470922</v>
+        <v>470822</v>
       </c>
       <c r="R232" t="n">
-        <v>6770556</v>
+        <v>6770452</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26254,13 +26264,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959285</t>
+          <t>https://artportalen.se/Sighting/129959579</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129959441</v>
+        <v>129959710</v>
       </c>
       <c r="B233" t="n">
         <v>8455</v>
@@ -26300,10 +26310,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>470824</v>
+        <v>470864</v>
       </c>
       <c r="R233" t="n">
-        <v>6770523</v>
+        <v>6770438</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26371,13 +26381,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959441</t>
+          <t>https://artportalen.se/Sighting/129959710</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129959579</v>
+        <v>129959735</v>
       </c>
       <c r="B234" t="n">
         <v>8455</v>
@@ -26417,10 +26427,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>470822</v>
+        <v>470868</v>
       </c>
       <c r="R234" t="n">
-        <v>6770452</v>
+        <v>6770431</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26488,13 +26498,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959579</t>
+          <t>https://artportalen.se/Sighting/129959735</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129959710</v>
+        <v>129959924</v>
       </c>
       <c r="B235" t="n">
         <v>8455</v>
@@ -26534,10 +26544,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>470864</v>
+        <v>470944</v>
       </c>
       <c r="R235" t="n">
-        <v>6770438</v>
+        <v>6770458</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26605,13 +26615,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959710</t>
+          <t>https://artportalen.se/Sighting/129959924</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129959735</v>
+        <v>129960514</v>
       </c>
       <c r="B236" t="n">
         <v>8455</v>
@@ -26651,13 +26661,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>470868</v>
+        <v>470976</v>
       </c>
       <c r="R236" t="n">
-        <v>6770431</v>
+        <v>6770536</v>
       </c>
       <c r="S236" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26722,13 +26732,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959735</t>
+          <t>https://artportalen.se/Sighting/129960514</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129959924</v>
+        <v>129960657</v>
       </c>
       <c r="B237" t="n">
         <v>8455</v>
@@ -26768,10 +26778,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>470944</v>
+        <v>471025</v>
       </c>
       <c r="R237" t="n">
-        <v>6770458</v>
+        <v>6770488</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26839,13 +26849,13 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959924</t>
+          <t>https://artportalen.se/Sighting/129960657</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129960514</v>
+        <v>129960746</v>
       </c>
       <c r="B238" t="n">
         <v>8455</v>
@@ -26885,13 +26895,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>470976</v>
+        <v>471053</v>
       </c>
       <c r="R238" t="n">
-        <v>6770536</v>
+        <v>6770528</v>
       </c>
       <c r="S238" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -26956,13 +26966,13 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960514</t>
+          <t>https://artportalen.se/Sighting/129960746</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129960657</v>
+        <v>129960827</v>
       </c>
       <c r="B239" t="n">
         <v>8455</v>
@@ -27002,10 +27012,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>471025</v>
+        <v>471078</v>
       </c>
       <c r="R239" t="n">
-        <v>6770488</v>
+        <v>6770561</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27073,13 +27083,13 @@
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960657</t>
+          <t>https://artportalen.se/Sighting/129960827</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129960746</v>
+        <v>129961109</v>
       </c>
       <c r="B240" t="n">
         <v>8455</v>
@@ -27119,10 +27129,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>471053</v>
+        <v>471175</v>
       </c>
       <c r="R240" t="n">
-        <v>6770528</v>
+        <v>6770631</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27190,13 +27200,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960746</t>
+          <t>https://artportalen.se/Sighting/129961109</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129960827</v>
+        <v>129962346</v>
       </c>
       <c r="B241" t="n">
         <v>8455</v>
@@ -27236,10 +27246,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>471078</v>
+        <v>471017</v>
       </c>
       <c r="R241" t="n">
-        <v>6770561</v>
+        <v>6770613</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27307,13 +27317,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960827</t>
+          <t>https://artportalen.se/Sighting/129962346</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129961109</v>
+        <v>129962376</v>
       </c>
       <c r="B242" t="n">
         <v>8455</v>
@@ -27353,10 +27363,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>471175</v>
+        <v>470996</v>
       </c>
       <c r="R242" t="n">
-        <v>6770631</v>
+        <v>6770611</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27424,13 +27434,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961109</t>
+          <t>https://artportalen.se/Sighting/129962376</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129962346</v>
+        <v>129962436</v>
       </c>
       <c r="B243" t="n">
         <v>8455</v>
@@ -27470,10 +27480,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>471017</v>
+        <v>470989</v>
       </c>
       <c r="R243" t="n">
-        <v>6770613</v>
+        <v>6770629</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27541,59 +27551,57 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962346</t>
+          <t>https://artportalen.se/Sighting/129962436</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129962376</v>
+        <v>129271581</v>
       </c>
       <c r="B244" t="n">
-        <v>8455</v>
+        <v>93228</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>106545</v>
+        <v>232140</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>470996</v>
+        <v>470835</v>
       </c>
       <c r="R244" t="n">
-        <v>6770611</v>
+        <v>6770662</v>
       </c>
       <c r="S244" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27617,22 +27625,12 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27641,76 +27639,72 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
+      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962376</t>
+          <t>https://artportalen.se/Sighting/129271581</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129962436</v>
+        <v>96714923</v>
       </c>
       <c r="B245" t="n">
-        <v>8455</v>
+        <v>91402</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>106545</v>
+        <v>256703</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>470989</v>
+        <v>470876</v>
       </c>
       <c r="R245" t="n">
-        <v>6770629</v>
+        <v>6770446</v>
       </c>
       <c r="S245" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27734,22 +27728,12 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27764,65 +27748,62 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962436</t>
+          <t>https://artportalen.se/Sighting/96714923</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>129271581</v>
+        <v>96714929</v>
       </c>
       <c r="B246" t="n">
-        <v>93228</v>
+        <v>91402</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>232140</v>
+        <v>256703</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>470835</v>
+        <v>471113</v>
       </c>
       <c r="R246" t="n">
-        <v>6770662</v>
+        <v>6770726</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -27849,12 +27830,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -27863,31 +27844,30 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129271581</t>
+          <t>https://artportalen.se/Sighting/96714929</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>96714923</v>
+        <v>96714933</v>
       </c>
       <c r="B247" t="n">
         <v>91402</v>
@@ -27922,10 +27902,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>470876</v>
+        <v>470806</v>
       </c>
       <c r="R247" t="n">
-        <v>6770446</v>
+        <v>6770695</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -27983,13 +27963,13 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714923</t>
+          <t>https://artportalen.se/Sighting/96714933</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>96714929</v>
+        <v>96714941</v>
       </c>
       <c r="B248" t="n">
         <v>91402</v>
@@ -28024,10 +28004,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>471113</v>
+        <v>471105</v>
       </c>
       <c r="R248" t="n">
-        <v>6770726</v>
+        <v>6770716</v>
       </c>
       <c r="S248" t="n">
         <v>25</v>
@@ -28085,13 +28065,13 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714929</t>
+          <t>https://artportalen.se/Sighting/96714941</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>96714933</v>
+        <v>96714946</v>
       </c>
       <c r="B249" t="n">
         <v>91402</v>
@@ -28126,10 +28106,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>470806</v>
+        <v>471072</v>
       </c>
       <c r="R249" t="n">
-        <v>6770695</v>
+        <v>6770716</v>
       </c>
       <c r="S249" t="n">
         <v>25</v>
@@ -28187,13 +28167,13 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714933</t>
+          <t>https://artportalen.se/Sighting/96714946</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>96714941</v>
+        <v>96714952</v>
       </c>
       <c r="B250" t="n">
         <v>91402</v>
@@ -28228,10 +28208,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>471105</v>
+        <v>470920</v>
       </c>
       <c r="R250" t="n">
-        <v>6770716</v>
+        <v>6770687</v>
       </c>
       <c r="S250" t="n">
         <v>25</v>
@@ -28289,13 +28269,13 @@
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714941</t>
+          <t>https://artportalen.se/Sighting/96714952</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>96714946</v>
+        <v>96714953</v>
       </c>
       <c r="B251" t="n">
         <v>91402</v>
@@ -28330,10 +28310,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>471072</v>
+        <v>471086</v>
       </c>
       <c r="R251" t="n">
-        <v>6770716</v>
+        <v>6770698</v>
       </c>
       <c r="S251" t="n">
         <v>25</v>
@@ -28391,13 +28371,13 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714946</t>
+          <t>https://artportalen.se/Sighting/96714953</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>96714952</v>
+        <v>96714960</v>
       </c>
       <c r="B252" t="n">
         <v>91402</v>
@@ -28432,10 +28412,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>470920</v>
+        <v>471091</v>
       </c>
       <c r="R252" t="n">
-        <v>6770687</v>
+        <v>6770723</v>
       </c>
       <c r="S252" t="n">
         <v>25</v>
@@ -28493,13 +28473,13 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714952</t>
+          <t>https://artportalen.se/Sighting/96714960</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>96714953</v>
+        <v>96714973</v>
       </c>
       <c r="B253" t="n">
         <v>91402</v>
@@ -28534,10 +28514,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>471086</v>
+        <v>471080</v>
       </c>
       <c r="R253" t="n">
-        <v>6770698</v>
+        <v>6770598</v>
       </c>
       <c r="S253" t="n">
         <v>25</v>
@@ -28595,13 +28575,13 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714953</t>
+          <t>https://artportalen.se/Sighting/96714973</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>96714960</v>
+        <v>96714981</v>
       </c>
       <c r="B254" t="n">
         <v>91402</v>
@@ -28636,10 +28616,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>471091</v>
+        <v>471483</v>
       </c>
       <c r="R254" t="n">
-        <v>6770723</v>
+        <v>6770715</v>
       </c>
       <c r="S254" t="n">
         <v>25</v>
@@ -28697,13 +28677,13 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714960</t>
+          <t>https://artportalen.se/Sighting/96714981</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>96714973</v>
+        <v>96715005</v>
       </c>
       <c r="B255" t="n">
         <v>91402</v>
@@ -28738,10 +28718,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>471080</v>
+        <v>470830</v>
       </c>
       <c r="R255" t="n">
-        <v>6770598</v>
+        <v>6770666</v>
       </c>
       <c r="S255" t="n">
         <v>25</v>
@@ -28799,13 +28779,13 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714973</t>
+          <t>https://artportalen.se/Sighting/96715005</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>96714981</v>
+        <v>96715010</v>
       </c>
       <c r="B256" t="n">
         <v>91402</v>
@@ -28840,10 +28820,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>471483</v>
+        <v>471253</v>
       </c>
       <c r="R256" t="n">
-        <v>6770715</v>
+        <v>6770676</v>
       </c>
       <c r="S256" t="n">
         <v>25</v>
@@ -28900,210 +28880,6 @@
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/96714981</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
-        <v>96715005</v>
-      </c>
-      <c r="B257" t="n">
-        <v>91402</v>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E257" t="n">
-        <v>256703</v>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>Tallfingersvamp</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>Ramaria eosanguinea</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr"/>
-      <c r="P257" t="inlineStr">
-        <is>
-          <t>Bonäsheden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q257" t="n">
-        <v>470830</v>
-      </c>
-      <c r="R257" t="n">
-        <v>6770666</v>
-      </c>
-      <c r="S257" t="n">
-        <v>25</v>
-      </c>
-      <c r="T257" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="AA257" t="inlineStr">
-        <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AD257" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE257" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG257" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT257" t="inlineStr"/>
-      <c r="AW257" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AX257" t="inlineStr">
-        <is>
-          <t>Andreas Öster, Maria Hindemo</t>
-        </is>
-      </c>
-      <c r="AY257" t="inlineStr"/>
-      <c r="AZ257" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/96715005</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
-        <v>96715010</v>
-      </c>
-      <c r="B258" t="n">
-        <v>91402</v>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E258" t="n">
-        <v>256703</v>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>Tallfingersvamp</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>Ramaria eosanguinea</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr"/>
-      <c r="P258" t="inlineStr">
-        <is>
-          <t>Bonäsheden, Dlr</t>
-        </is>
-      </c>
-      <c r="Q258" t="n">
-        <v>471253</v>
-      </c>
-      <c r="R258" t="n">
-        <v>6770676</v>
-      </c>
-      <c r="S258" t="n">
-        <v>25</v>
-      </c>
-      <c r="T258" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>Mora</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AD258" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE258" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG258" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT258" t="inlineStr"/>
-      <c r="AW258" t="inlineStr">
-        <is>
-          <t>Andreas Öster</t>
-        </is>
-      </c>
-      <c r="AX258" t="inlineStr">
-        <is>
-          <t>Andreas Öster, Maria Hindemo</t>
-        </is>
-      </c>
-      <c r="AY258" t="inlineStr"/>
-      <c r="AZ258" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96715010</t>
         </is>
@@ -29366,8 +29142,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7756,7 +7756,7 @@
         <v>136837813</v>
       </c>
       <c r="B69" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ256"/>
+  <dimension ref="A1:AZ258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6997,48 +6997,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>96714971</v>
+        <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93201</v>
+        <v>93441</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bengttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>470825</v>
+        <v>470909</v>
       </c>
       <c r="R62" t="n">
-        <v>6770664</v>
+        <v>6770448</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7062,12 +7062,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7082,49 +7092,49 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Uno Skog, Andreas Öster</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714971</t>
+          <t>https://artportalen.se/Sighting/136837910</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>96714979</v>
+        <v>96714971</v>
       </c>
       <c r="B63" t="n">
-        <v>92841</v>
+        <v>93201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7134,10 +7144,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>471064</v>
+        <v>470825</v>
       </c>
       <c r="R63" t="n">
-        <v>6770563</v>
+        <v>6770664</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7195,16 +7205,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714979</t>
+          <t>https://artportalen.se/Sighting/96714971</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129943849</v>
+        <v>96714979</v>
       </c>
       <c r="B64" t="n">
-        <v>91930</v>
+        <v>92841</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7212,41 +7222,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5442</v>
+        <v>4745</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>471451</v>
+        <v>471064</v>
       </c>
       <c r="R64" t="n">
-        <v>6770706</v>
+        <v>6770563</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7270,22 +7276,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7300,24 +7296,24 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943849</t>
+          <t>https://artportalen.se/Sighting/96714979</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129944262</v>
+        <v>129943849</v>
       </c>
       <c r="B65" t="n">
         <v>91930</v>
@@ -7356,10 +7352,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>471369</v>
+        <v>471451</v>
       </c>
       <c r="R65" t="n">
-        <v>6770686</v>
+        <v>6770706</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7427,13 +7423,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944262</t>
+          <t>https://artportalen.se/Sighting/129943849</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129959667</v>
+        <v>129944262</v>
       </c>
       <c r="B66" t="n">
         <v>91930</v>
@@ -7463,7 +7459,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7472,10 +7468,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>470864</v>
+        <v>471369</v>
       </c>
       <c r="R66" t="n">
-        <v>6770438</v>
+        <v>6770686</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7502,22 +7498,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7543,16 +7539,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959667</t>
+          <t>https://artportalen.se/Sighting/129944262</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>96714915</v>
+        <v>129959667</v>
       </c>
       <c r="B67" t="n">
-        <v>93235</v>
+        <v>91930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7560,37 +7556,41 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>471343</v>
+        <v>470864</v>
       </c>
       <c r="R67" t="n">
-        <v>6770659</v>
+        <v>6770438</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7614,12 +7614,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7634,24 +7644,24 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714915</t>
+          <t>https://artportalen.se/Sighting/129959667</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>96714991</v>
+        <v>96714915</v>
       </c>
       <c r="B68" t="n">
         <v>93235</v>
@@ -7686,10 +7696,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>470824</v>
+        <v>471343</v>
       </c>
       <c r="R68" t="n">
-        <v>6770660</v>
+        <v>6770659</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -7747,54 +7757,54 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714991</t>
+          <t>https://artportalen.se/Sighting/96714915</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136837813</v>
+        <v>96714991</v>
       </c>
       <c r="B69" t="n">
-        <v>93412</v>
+        <v>93235</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6055</v>
+        <v>5966</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bengttjärnen, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>470979</v>
+        <v>470824</v>
       </c>
       <c r="R69" t="n">
-        <v>6770615</v>
+        <v>6770660</v>
       </c>
       <c r="S69" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7818,12 +7828,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7838,27 +7848,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136837813</t>
+          <t>https://artportalen.se/Sighting/96714991</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>96714961</v>
+        <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>90691</v>
+        <v>93425</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7866,37 +7876,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6276</v>
+        <v>6055</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bengttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471372</v>
+        <v>470971</v>
       </c>
       <c r="R70" t="n">
-        <v>6770686</v>
+        <v>6770613</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7920,12 +7930,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7940,27 +7960,27 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714961</t>
+          <t>https://artportalen.se/Sighting/136836580</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>96715014</v>
+        <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>90691</v>
+        <v>93425</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7968,37 +7988,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6276</v>
+        <v>6055</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Bengttjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470841</v>
+        <v>470979</v>
       </c>
       <c r="R71" t="n">
-        <v>6770558</v>
+        <v>6770615</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8022,12 +8042,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8042,27 +8062,27 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715014</t>
+          <t>https://artportalen.se/Sighting/136837813</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>96715007</v>
+        <v>96714961</v>
       </c>
       <c r="B72" t="n">
-        <v>79327</v>
+        <v>90691</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8070,21 +8090,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8094,10 +8114,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471383</v>
+        <v>471372</v>
       </c>
       <c r="R72" t="n">
-        <v>6770715</v>
+        <v>6770686</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8155,16 +8175,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715007</t>
+          <t>https://artportalen.se/Sighting/96714961</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129943529</v>
+        <v>96715014</v>
       </c>
       <c r="B73" t="n">
-        <v>79327</v>
+        <v>90691</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8172,37 +8192,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471492</v>
+        <v>470841</v>
       </c>
       <c r="R73" t="n">
-        <v>6770712</v>
+        <v>6770558</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8226,22 +8246,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8256,24 +8266,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943529</t>
+          <t>https://artportalen.se/Sighting/96715014</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129943541</v>
+        <v>96715007</v>
       </c>
       <c r="B74" t="n">
         <v>79327</v>
@@ -8304,17 +8314,17 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svenlindor, Dlr</t>
+          <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471478</v>
+        <v>471383</v>
       </c>
       <c r="R74" t="n">
-        <v>6770707</v>
+        <v>6770715</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8338,22 +8348,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2021-09-28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8368,24 +8368,24 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Andreas Öster, Maria Hindemo</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943541</t>
+          <t>https://artportalen.se/Sighting/96715007</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129943580</v>
+        <v>129943529</v>
       </c>
       <c r="B75" t="n">
         <v>79327</v>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471468</v>
+        <v>471492</v>
       </c>
       <c r="R75" t="n">
-        <v>6770744</v>
+        <v>6770712</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8491,13 +8491,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943580</t>
+          <t>https://artportalen.se/Sighting/129943529</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129943763</v>
+        <v>129943541</v>
       </c>
       <c r="B76" t="n">
         <v>79327</v>
@@ -8532,10 +8532,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471466</v>
+        <v>471478</v>
       </c>
       <c r="R76" t="n">
-        <v>6770713</v>
+        <v>6770707</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8603,13 +8603,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943763</t>
+          <t>https://artportalen.se/Sighting/129943541</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129943809</v>
+        <v>129943580</v>
       </c>
       <c r="B77" t="n">
         <v>79327</v>
@@ -8644,10 +8644,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>471447</v>
+        <v>471468</v>
       </c>
       <c r="R77" t="n">
-        <v>6770716</v>
+        <v>6770744</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8715,13 +8715,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943809</t>
+          <t>https://artportalen.se/Sighting/129943580</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129943855</v>
+        <v>129943763</v>
       </c>
       <c r="B78" t="n">
         <v>79327</v>
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471451</v>
+        <v>471466</v>
       </c>
       <c r="R78" t="n">
-        <v>6770706</v>
+        <v>6770713</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8827,13 +8827,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943855</t>
+          <t>https://artportalen.se/Sighting/129943763</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129943914</v>
+        <v>129943809</v>
       </c>
       <c r="B79" t="n">
         <v>79327</v>
@@ -8868,10 +8868,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471432</v>
+        <v>471447</v>
       </c>
       <c r="R79" t="n">
-        <v>6770701</v>
+        <v>6770716</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8939,13 +8939,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943914</t>
+          <t>https://artportalen.se/Sighting/129943809</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129943999</v>
+        <v>129943855</v>
       </c>
       <c r="B80" t="n">
         <v>79327</v>
@@ -8980,10 +8980,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>471428</v>
+        <v>471451</v>
       </c>
       <c r="R80" t="n">
-        <v>6770747</v>
+        <v>6770706</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9051,13 +9051,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129943999</t>
+          <t>https://artportalen.se/Sighting/129943855</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129944026</v>
+        <v>129943914</v>
       </c>
       <c r="B81" t="n">
         <v>79327</v>
@@ -9092,10 +9092,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>471422</v>
+        <v>471432</v>
       </c>
       <c r="R81" t="n">
-        <v>6770745</v>
+        <v>6770701</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9163,13 +9163,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944026</t>
+          <t>https://artportalen.se/Sighting/129943914</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129944037</v>
+        <v>129943999</v>
       </c>
       <c r="B82" t="n">
         <v>79327</v>
@@ -9204,10 +9204,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471417</v>
+        <v>471428</v>
       </c>
       <c r="R82" t="n">
-        <v>6770738</v>
+        <v>6770747</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9275,13 +9275,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944037</t>
+          <t>https://artportalen.se/Sighting/129943999</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944164</v>
+        <v>129944026</v>
       </c>
       <c r="B83" t="n">
         <v>79327</v>
@@ -9316,10 +9316,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471363</v>
+        <v>471422</v>
       </c>
       <c r="R83" t="n">
-        <v>6770736</v>
+        <v>6770745</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9387,13 +9387,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944164</t>
+          <t>https://artportalen.se/Sighting/129944026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944178</v>
+        <v>129944037</v>
       </c>
       <c r="B84" t="n">
         <v>79327</v>
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471372</v>
+        <v>471417</v>
       </c>
       <c r="R84" t="n">
-        <v>6770719</v>
+        <v>6770738</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9499,13 +9499,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944178</t>
+          <t>https://artportalen.se/Sighting/129944037</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129944210</v>
+        <v>129944164</v>
       </c>
       <c r="B85" t="n">
         <v>79327</v>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471390</v>
+        <v>471363</v>
       </c>
       <c r="R85" t="n">
-        <v>6770705</v>
+        <v>6770736</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,13 +9611,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944210</t>
+          <t>https://artportalen.se/Sighting/129944164</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129944228</v>
+        <v>129944178</v>
       </c>
       <c r="B86" t="n">
         <v>79327</v>
@@ -9652,10 +9652,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471390</v>
+        <v>471372</v>
       </c>
       <c r="R86" t="n">
-        <v>6770693</v>
+        <v>6770719</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9723,13 +9723,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944228</t>
+          <t>https://artportalen.se/Sighting/129944178</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129944311</v>
+        <v>129944210</v>
       </c>
       <c r="B87" t="n">
         <v>79327</v>
@@ -9764,10 +9764,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471369</v>
+        <v>471390</v>
       </c>
       <c r="R87" t="n">
-        <v>6770686</v>
+        <v>6770705</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9835,13 +9835,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944311</t>
+          <t>https://artportalen.se/Sighting/129944210</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129944355</v>
+        <v>129944228</v>
       </c>
       <c r="B88" t="n">
         <v>79327</v>
@@ -9876,10 +9876,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471342</v>
+        <v>471390</v>
       </c>
       <c r="R88" t="n">
-        <v>6770682</v>
+        <v>6770693</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9947,13 +9947,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944355</t>
+          <t>https://artportalen.se/Sighting/129944228</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129944466</v>
+        <v>129944311</v>
       </c>
       <c r="B89" t="n">
         <v>79327</v>
@@ -9988,10 +9988,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>471322</v>
+        <v>471369</v>
       </c>
       <c r="R89" t="n">
-        <v>6770702</v>
+        <v>6770686</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10059,13 +10059,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944466</t>
+          <t>https://artportalen.se/Sighting/129944311</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129944473</v>
+        <v>129944355</v>
       </c>
       <c r="B90" t="n">
         <v>79327</v>
@@ -10100,10 +10100,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471328</v>
+        <v>471342</v>
       </c>
       <c r="R90" t="n">
-        <v>6770726</v>
+        <v>6770682</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10171,13 +10171,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944473</t>
+          <t>https://artportalen.se/Sighting/129944355</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129944488</v>
+        <v>129944466</v>
       </c>
       <c r="B91" t="n">
         <v>79327</v>
@@ -10212,10 +10212,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471318</v>
+        <v>471322</v>
       </c>
       <c r="R91" t="n">
-        <v>6770729</v>
+        <v>6770702</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10283,13 +10283,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944488</t>
+          <t>https://artportalen.se/Sighting/129944466</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129944495</v>
+        <v>129944473</v>
       </c>
       <c r="B92" t="n">
         <v>79327</v>
@@ -10324,10 +10324,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471288</v>
+        <v>471328</v>
       </c>
       <c r="R92" t="n">
-        <v>6770728</v>
+        <v>6770726</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10395,13 +10395,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944495</t>
+          <t>https://artportalen.se/Sighting/129944473</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129944523</v>
+        <v>129944488</v>
       </c>
       <c r="B93" t="n">
         <v>79327</v>
@@ -10436,10 +10436,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471303</v>
+        <v>471318</v>
       </c>
       <c r="R93" t="n">
-        <v>6770699</v>
+        <v>6770729</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10507,13 +10507,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944523</t>
+          <t>https://artportalen.se/Sighting/129944488</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129944544</v>
+        <v>129944495</v>
       </c>
       <c r="B94" t="n">
         <v>79327</v>
@@ -10548,10 +10548,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471330</v>
+        <v>471288</v>
       </c>
       <c r="R94" t="n">
-        <v>6770712</v>
+        <v>6770728</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10619,13 +10619,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944544</t>
+          <t>https://artportalen.se/Sighting/129944495</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129944592</v>
+        <v>129944523</v>
       </c>
       <c r="B95" t="n">
         <v>79327</v>
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471313</v>
+        <v>471303</v>
       </c>
       <c r="R95" t="n">
-        <v>6770688</v>
+        <v>6770699</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10731,13 +10731,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944592</t>
+          <t>https://artportalen.se/Sighting/129944523</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129944756</v>
+        <v>129944544</v>
       </c>
       <c r="B96" t="n">
         <v>79327</v>
@@ -10772,10 +10772,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471288</v>
+        <v>471330</v>
       </c>
       <c r="R96" t="n">
-        <v>6770685</v>
+        <v>6770712</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10843,13 +10843,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944756</t>
+          <t>https://artportalen.se/Sighting/129944544</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129944762</v>
+        <v>129944592</v>
       </c>
       <c r="B97" t="n">
         <v>79327</v>
@@ -10884,10 +10884,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471276</v>
+        <v>471313</v>
       </c>
       <c r="R97" t="n">
-        <v>6770703</v>
+        <v>6770688</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10955,13 +10955,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944762</t>
+          <t>https://artportalen.se/Sighting/129944592</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129944804</v>
+        <v>129944756</v>
       </c>
       <c r="B98" t="n">
         <v>79327</v>
@@ -10996,10 +10996,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471271</v>
+        <v>471288</v>
       </c>
       <c r="R98" t="n">
-        <v>6770733</v>
+        <v>6770685</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11067,13 +11067,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944804</t>
+          <t>https://artportalen.se/Sighting/129944756</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129944807</v>
+        <v>129944762</v>
       </c>
       <c r="B99" t="n">
         <v>79327</v>
@@ -11108,10 +11108,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471248</v>
+        <v>471276</v>
       </c>
       <c r="R99" t="n">
-        <v>6770737</v>
+        <v>6770703</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11179,13 +11179,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944807</t>
+          <t>https://artportalen.se/Sighting/129944762</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944809</v>
+        <v>129944804</v>
       </c>
       <c r="B100" t="n">
         <v>79327</v>
@@ -11220,10 +11220,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471247</v>
+        <v>471271</v>
       </c>
       <c r="R100" t="n">
-        <v>6770726</v>
+        <v>6770733</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11291,13 +11291,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944809</t>
+          <t>https://artportalen.se/Sighting/129944804</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129944917</v>
+        <v>129944807</v>
       </c>
       <c r="B101" t="n">
         <v>79327</v>
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471263</v>
+        <v>471248</v>
       </c>
       <c r="R101" t="n">
-        <v>6770694</v>
+        <v>6770737</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11403,13 +11403,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944917</t>
+          <t>https://artportalen.se/Sighting/129944807</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129944975</v>
+        <v>129944809</v>
       </c>
       <c r="B102" t="n">
         <v>79327</v>
@@ -11444,10 +11444,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471242</v>
+        <v>471247</v>
       </c>
       <c r="R102" t="n">
-        <v>6770682</v>
+        <v>6770726</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11515,13 +11515,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944975</t>
+          <t>https://artportalen.se/Sighting/129944809</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129945066</v>
+        <v>129944917</v>
       </c>
       <c r="B103" t="n">
         <v>79327</v>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471239</v>
+        <v>471263</v>
       </c>
       <c r="R103" t="n">
-        <v>6770732</v>
+        <v>6770694</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11627,13 +11627,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945066</t>
+          <t>https://artportalen.se/Sighting/129944917</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129945078</v>
+        <v>129944975</v>
       </c>
       <c r="B104" t="n">
         <v>79327</v>
@@ -11668,10 +11668,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471209</v>
+        <v>471242</v>
       </c>
       <c r="R104" t="n">
-        <v>6770731</v>
+        <v>6770682</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11739,13 +11739,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945078</t>
+          <t>https://artportalen.se/Sighting/129944975</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129945104</v>
+        <v>129945066</v>
       </c>
       <c r="B105" t="n">
         <v>79327</v>
@@ -11780,10 +11780,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471219</v>
+        <v>471239</v>
       </c>
       <c r="R105" t="n">
-        <v>6770720</v>
+        <v>6770732</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11851,13 +11851,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945104</t>
+          <t>https://artportalen.se/Sighting/129945066</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129945451</v>
+        <v>129945078</v>
       </c>
       <c r="B106" t="n">
         <v>79327</v>
@@ -11892,10 +11892,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471189</v>
+        <v>471209</v>
       </c>
       <c r="R106" t="n">
-        <v>6770706</v>
+        <v>6770731</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11963,13 +11963,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945451</t>
+          <t>https://artportalen.se/Sighting/129945078</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129945509</v>
+        <v>129945104</v>
       </c>
       <c r="B107" t="n">
         <v>79327</v>
@@ -12004,10 +12004,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471198</v>
+        <v>471219</v>
       </c>
       <c r="R107" t="n">
-        <v>6770689</v>
+        <v>6770720</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12052,11 +12052,6 @@
           <t>11:17</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12080,13 +12075,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945509</t>
+          <t>https://artportalen.se/Sighting/129945104</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129946029</v>
+        <v>129945451</v>
       </c>
       <c r="B108" t="n">
         <v>79327</v>
@@ -12121,10 +12116,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471185</v>
+        <v>471189</v>
       </c>
       <c r="R108" t="n">
-        <v>6770690</v>
+        <v>6770706</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12192,13 +12187,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946029</t>
+          <t>https://artportalen.se/Sighting/129945451</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129946053</v>
+        <v>129945509</v>
       </c>
       <c r="B109" t="n">
         <v>79327</v>
@@ -12233,10 +12228,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471161</v>
+        <v>471198</v>
       </c>
       <c r="R109" t="n">
-        <v>6770705</v>
+        <v>6770689</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12281,6 +12276,11 @@
           <t>11:17</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12304,13 +12304,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946053</t>
+          <t>https://artportalen.se/Sighting/129945509</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129946117</v>
+        <v>129946029</v>
       </c>
       <c r="B110" t="n">
         <v>79327</v>
@@ -12345,10 +12345,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471106</v>
+        <v>471185</v>
       </c>
       <c r="R110" t="n">
-        <v>6770711</v>
+        <v>6770690</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12416,13 +12416,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946117</t>
+          <t>https://artportalen.se/Sighting/129946029</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129946170</v>
+        <v>129946053</v>
       </c>
       <c r="B111" t="n">
         <v>79327</v>
@@ -12457,10 +12457,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>471030</v>
+        <v>471161</v>
       </c>
       <c r="R111" t="n">
-        <v>6770688</v>
+        <v>6770705</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12528,13 +12528,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946170</t>
+          <t>https://artportalen.se/Sighting/129946053</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129946182</v>
+        <v>129946117</v>
       </c>
       <c r="B112" t="n">
         <v>79327</v>
@@ -12569,10 +12569,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471000</v>
+        <v>471106</v>
       </c>
       <c r="R112" t="n">
-        <v>6770675</v>
+        <v>6770711</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12640,13 +12640,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946182</t>
+          <t>https://artportalen.se/Sighting/129946117</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129946197</v>
+        <v>129946170</v>
       </c>
       <c r="B113" t="n">
         <v>79327</v>
@@ -12681,10 +12681,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>470971</v>
+        <v>471030</v>
       </c>
       <c r="R113" t="n">
-        <v>6770676</v>
+        <v>6770688</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12752,13 +12752,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946197</t>
+          <t>https://artportalen.se/Sighting/129946170</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129946408</v>
+        <v>129946182</v>
       </c>
       <c r="B114" t="n">
         <v>79327</v>
@@ -12793,10 +12793,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>470921</v>
+        <v>471000</v>
       </c>
       <c r="R114" t="n">
-        <v>6770579</v>
+        <v>6770675</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12864,13 +12864,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946408</t>
+          <t>https://artportalen.se/Sighting/129946182</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129946586</v>
+        <v>129946197</v>
       </c>
       <c r="B115" t="n">
         <v>79327</v>
@@ -12905,10 +12905,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>471095</v>
+        <v>470971</v>
       </c>
       <c r="R115" t="n">
-        <v>6770660</v>
+        <v>6770676</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12976,13 +12976,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946586</t>
+          <t>https://artportalen.se/Sighting/129946197</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129946708</v>
+        <v>129946408</v>
       </c>
       <c r="B116" t="n">
         <v>79327</v>
@@ -13017,10 +13017,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>471171</v>
+        <v>470921</v>
       </c>
       <c r="R116" t="n">
-        <v>6770660</v>
+        <v>6770579</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13088,13 +13088,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946708</t>
+          <t>https://artportalen.se/Sighting/129946408</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129954408</v>
+        <v>129946586</v>
       </c>
       <c r="B117" t="n">
         <v>79327</v>
@@ -13129,10 +13129,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471019</v>
+        <v>471095</v>
       </c>
       <c r="R117" t="n">
-        <v>6770666</v>
+        <v>6770660</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13159,22 +13159,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13200,13 +13200,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954408</t>
+          <t>https://artportalen.se/Sighting/129946586</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129954413</v>
+        <v>129946708</v>
       </c>
       <c r="B118" t="n">
         <v>79327</v>
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>471028</v>
+        <v>471171</v>
       </c>
       <c r="R118" t="n">
-        <v>6770675</v>
+        <v>6770660</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13271,22 +13271,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13312,13 +13312,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954413</t>
+          <t>https://artportalen.se/Sighting/129946708</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129954442</v>
+        <v>129954408</v>
       </c>
       <c r="B119" t="n">
         <v>79327</v>
@@ -13353,10 +13353,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471053</v>
+        <v>471019</v>
       </c>
       <c r="R119" t="n">
-        <v>6770682</v>
+        <v>6770666</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13424,13 +13424,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954442</t>
+          <t>https://artportalen.se/Sighting/129954408</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129954452</v>
+        <v>129954413</v>
       </c>
       <c r="B120" t="n">
         <v>79327</v>
@@ -13465,10 +13465,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471058</v>
+        <v>471028</v>
       </c>
       <c r="R120" t="n">
-        <v>6770677</v>
+        <v>6770675</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13536,13 +13536,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954452</t>
+          <t>https://artportalen.se/Sighting/129954413</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129954531</v>
+        <v>129954442</v>
       </c>
       <c r="B121" t="n">
         <v>79327</v>
@@ -13577,10 +13577,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471106</v>
+        <v>471053</v>
       </c>
       <c r="R121" t="n">
-        <v>6770683</v>
+        <v>6770682</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13648,13 +13648,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954531</t>
+          <t>https://artportalen.se/Sighting/129954442</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129954534</v>
+        <v>129954452</v>
       </c>
       <c r="B122" t="n">
         <v>79327</v>
@@ -13689,10 +13689,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>471086</v>
+        <v>471058</v>
       </c>
       <c r="R122" t="n">
-        <v>6770684</v>
+        <v>6770677</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13760,13 +13760,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954534</t>
+          <t>https://artportalen.se/Sighting/129954452</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129954584</v>
+        <v>129954531</v>
       </c>
       <c r="B123" t="n">
         <v>79327</v>
@@ -13801,10 +13801,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471062</v>
+        <v>471106</v>
       </c>
       <c r="R123" t="n">
-        <v>6770731</v>
+        <v>6770683</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13872,13 +13872,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954584</t>
+          <t>https://artportalen.se/Sighting/129954531</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129954590</v>
+        <v>129954534</v>
       </c>
       <c r="B124" t="n">
         <v>79327</v>
@@ -13913,10 +13913,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471013</v>
+        <v>471086</v>
       </c>
       <c r="R124" t="n">
-        <v>6770715</v>
+        <v>6770684</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13984,13 +13984,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954590</t>
+          <t>https://artportalen.se/Sighting/129954534</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129954674</v>
+        <v>129954584</v>
       </c>
       <c r="B125" t="n">
         <v>79327</v>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470938</v>
+        <v>471062</v>
       </c>
       <c r="R125" t="n">
-        <v>6770693</v>
+        <v>6770731</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14096,13 +14096,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954674</t>
+          <t>https://artportalen.se/Sighting/129954584</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129955100</v>
+        <v>129954590</v>
       </c>
       <c r="B126" t="n">
         <v>79327</v>
@@ -14137,10 +14137,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470981</v>
+        <v>471013</v>
       </c>
       <c r="R126" t="n">
-        <v>6770691</v>
+        <v>6770715</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14208,13 +14208,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129955100</t>
+          <t>https://artportalen.se/Sighting/129954590</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129955313</v>
+        <v>129954674</v>
       </c>
       <c r="B127" t="n">
         <v>79327</v>
@@ -14249,10 +14249,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470992</v>
+        <v>470938</v>
       </c>
       <c r="R127" t="n">
-        <v>6770702</v>
+        <v>6770693</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14320,13 +14320,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129955313</t>
+          <t>https://artportalen.se/Sighting/129954674</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129956843</v>
+        <v>129955100</v>
       </c>
       <c r="B128" t="n">
         <v>79327</v>
@@ -14361,10 +14361,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470953</v>
+        <v>470981</v>
       </c>
       <c r="R128" t="n">
-        <v>6770692</v>
+        <v>6770691</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14432,13 +14432,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956843</t>
+          <t>https://artportalen.se/Sighting/129955100</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129956851</v>
+        <v>129955313</v>
       </c>
       <c r="B129" t="n">
         <v>79327</v>
@@ -14473,10 +14473,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470928</v>
+        <v>470992</v>
       </c>
       <c r="R129" t="n">
-        <v>6770695</v>
+        <v>6770702</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14544,13 +14544,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956851</t>
+          <t>https://artportalen.se/Sighting/129955313</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129956859</v>
+        <v>129956843</v>
       </c>
       <c r="B130" t="n">
         <v>79327</v>
@@ -14585,10 +14585,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470936</v>
+        <v>470953</v>
       </c>
       <c r="R130" t="n">
-        <v>6770721</v>
+        <v>6770692</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14656,13 +14656,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129956859</t>
+          <t>https://artportalen.se/Sighting/129956843</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129957713</v>
+        <v>129956851</v>
       </c>
       <c r="B131" t="n">
         <v>79327</v>
@@ -14697,10 +14697,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470904</v>
+        <v>470928</v>
       </c>
       <c r="R131" t="n">
-        <v>6770718</v>
+        <v>6770695</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14768,13 +14768,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957713</t>
+          <t>https://artportalen.se/Sighting/129956851</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129957969</v>
+        <v>129956859</v>
       </c>
       <c r="B132" t="n">
         <v>79327</v>
@@ -14809,10 +14809,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470911</v>
+        <v>470936</v>
       </c>
       <c r="R132" t="n">
-        <v>6770707</v>
+        <v>6770721</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14880,13 +14880,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957969</t>
+          <t>https://artportalen.se/Sighting/129956859</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129958010</v>
+        <v>129957713</v>
       </c>
       <c r="B133" t="n">
         <v>79327</v>
@@ -14921,10 +14921,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>470894</v>
+        <v>470904</v>
       </c>
       <c r="R133" t="n">
-        <v>6770713</v>
+        <v>6770718</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14992,13 +14992,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958010</t>
+          <t>https://artportalen.se/Sighting/129957713</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129958133</v>
+        <v>129957969</v>
       </c>
       <c r="B134" t="n">
         <v>79327</v>
@@ -15033,10 +15033,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>470869</v>
+        <v>470911</v>
       </c>
       <c r="R134" t="n">
-        <v>6770702</v>
+        <v>6770707</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15104,13 +15104,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958133</t>
+          <t>https://artportalen.se/Sighting/129957969</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129958151</v>
+        <v>129958010</v>
       </c>
       <c r="B135" t="n">
         <v>79327</v>
@@ -15145,10 +15145,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470842</v>
+        <v>470894</v>
       </c>
       <c r="R135" t="n">
-        <v>6770709</v>
+        <v>6770713</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15216,13 +15216,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958151</t>
+          <t>https://artportalen.se/Sighting/129958010</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129958214</v>
+        <v>129958133</v>
       </c>
       <c r="B136" t="n">
         <v>79327</v>
@@ -15257,10 +15257,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470823</v>
+        <v>470869</v>
       </c>
       <c r="R136" t="n">
-        <v>6770705</v>
+        <v>6770702</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15328,13 +15328,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958214</t>
+          <t>https://artportalen.se/Sighting/129958133</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129958228</v>
+        <v>129958151</v>
       </c>
       <c r="B137" t="n">
         <v>79327</v>
@@ -15369,10 +15369,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470813</v>
+        <v>470842</v>
       </c>
       <c r="R137" t="n">
-        <v>6770681</v>
+        <v>6770709</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15440,13 +15440,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958228</t>
+          <t>https://artportalen.se/Sighting/129958151</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129958464</v>
+        <v>129958214</v>
       </c>
       <c r="B138" t="n">
         <v>79327</v>
@@ -15481,10 +15481,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470822</v>
+        <v>470823</v>
       </c>
       <c r="R138" t="n">
-        <v>6770673</v>
+        <v>6770705</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15552,13 +15552,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958464</t>
+          <t>https://artportalen.se/Sighting/129958214</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129958466</v>
+        <v>129958228</v>
       </c>
       <c r="B139" t="n">
         <v>79327</v>
@@ -15593,10 +15593,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470812</v>
+        <v>470813</v>
       </c>
       <c r="R139" t="n">
-        <v>6770670</v>
+        <v>6770681</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15664,13 +15664,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958466</t>
+          <t>https://artportalen.se/Sighting/129958228</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129958499</v>
+        <v>129958464</v>
       </c>
       <c r="B140" t="n">
         <v>79327</v>
@@ -15705,10 +15705,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470850</v>
+        <v>470822</v>
       </c>
       <c r="R140" t="n">
-        <v>6770690</v>
+        <v>6770673</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15776,13 +15776,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958499</t>
+          <t>https://artportalen.se/Sighting/129958464</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129958545</v>
+        <v>129958466</v>
       </c>
       <c r="B141" t="n">
         <v>79327</v>
@@ -15817,10 +15817,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>470877</v>
+        <v>470812</v>
       </c>
       <c r="R141" t="n">
-        <v>6770687</v>
+        <v>6770670</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15888,13 +15888,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958545</t>
+          <t>https://artportalen.se/Sighting/129958466</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129958694</v>
+        <v>129958499</v>
       </c>
       <c r="B142" t="n">
         <v>79327</v>
@@ -15929,10 +15929,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>470844</v>
+        <v>470850</v>
       </c>
       <c r="R142" t="n">
-        <v>6770699</v>
+        <v>6770690</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16000,13 +16000,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958694</t>
+          <t>https://artportalen.se/Sighting/129958499</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129958706</v>
+        <v>129958545</v>
       </c>
       <c r="B143" t="n">
         <v>79327</v>
@@ -16041,10 +16041,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>470816</v>
+        <v>470877</v>
       </c>
       <c r="R143" t="n">
-        <v>6770646</v>
+        <v>6770687</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16112,13 +16112,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958706</t>
+          <t>https://artportalen.se/Sighting/129958545</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129958754</v>
+        <v>129958694</v>
       </c>
       <c r="B144" t="n">
         <v>79327</v>
@@ -16153,10 +16153,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>470817</v>
+        <v>470844</v>
       </c>
       <c r="R144" t="n">
-        <v>6770608</v>
+        <v>6770699</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16224,13 +16224,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958754</t>
+          <t>https://artportalen.se/Sighting/129958694</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129958775</v>
+        <v>129958706</v>
       </c>
       <c r="B145" t="n">
         <v>79327</v>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>470803</v>
+        <v>470816</v>
       </c>
       <c r="R145" t="n">
-        <v>6770595</v>
+        <v>6770646</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16336,13 +16336,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958775</t>
+          <t>https://artportalen.se/Sighting/129958706</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129958795</v>
+        <v>129958754</v>
       </c>
       <c r="B146" t="n">
         <v>79327</v>
@@ -16377,10 +16377,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>470822</v>
+        <v>470817</v>
       </c>
       <c r="R146" t="n">
-        <v>6770615</v>
+        <v>6770608</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16425,11 +16425,6 @@
           <t>09:55</t>
         </is>
       </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
-        </is>
-      </c>
       <c r="AD146" t="b">
         <v>0</v>
       </c>
@@ -16453,13 +16448,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958795</t>
+          <t>https://artportalen.se/Sighting/129958754</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129958800</v>
+        <v>129958775</v>
       </c>
       <c r="B147" t="n">
         <v>79327</v>
@@ -16494,10 +16489,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470858</v>
+        <v>470803</v>
       </c>
       <c r="R147" t="n">
-        <v>6770602</v>
+        <v>6770595</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16565,13 +16560,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958800</t>
+          <t>https://artportalen.se/Sighting/129958775</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129958828</v>
+        <v>129958795</v>
       </c>
       <c r="B148" t="n">
         <v>79327</v>
@@ -16606,10 +16601,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470871</v>
+        <v>470822</v>
       </c>
       <c r="R148" t="n">
-        <v>6770635</v>
+        <v>6770615</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16654,6 +16649,11 @@
           <t>09:55</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
+        </is>
+      </c>
       <c r="AD148" t="b">
         <v>0</v>
       </c>
@@ -16677,13 +16677,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958828</t>
+          <t>https://artportalen.se/Sighting/129958795</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129958841</v>
+        <v>129958800</v>
       </c>
       <c r="B149" t="n">
         <v>79327</v>
@@ -16718,10 +16718,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>470828</v>
+        <v>470858</v>
       </c>
       <c r="R149" t="n">
-        <v>6770636</v>
+        <v>6770602</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16789,13 +16789,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958841</t>
+          <t>https://artportalen.se/Sighting/129958800</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129958842</v>
+        <v>129958828</v>
       </c>
       <c r="B150" t="n">
         <v>79327</v>
@@ -16830,10 +16830,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>470820</v>
+        <v>470871</v>
       </c>
       <c r="R150" t="n">
-        <v>6770624</v>
+        <v>6770635</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16901,13 +16901,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958842</t>
+          <t>https://artportalen.se/Sighting/129958828</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129958895</v>
+        <v>129958841</v>
       </c>
       <c r="B151" t="n">
         <v>79327</v>
@@ -16942,10 +16942,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>470887</v>
+        <v>470828</v>
       </c>
       <c r="R151" t="n">
-        <v>6770658</v>
+        <v>6770636</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17013,13 +17013,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958895</t>
+          <t>https://artportalen.se/Sighting/129958841</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129958937</v>
+        <v>129958842</v>
       </c>
       <c r="B152" t="n">
         <v>79327</v>
@@ -17054,10 +17054,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>470897</v>
+        <v>470820</v>
       </c>
       <c r="R152" t="n">
-        <v>6770647</v>
+        <v>6770624</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17125,13 +17125,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958937</t>
+          <t>https://artportalen.se/Sighting/129958842</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129959037</v>
+        <v>129958895</v>
       </c>
       <c r="B153" t="n">
         <v>79327</v>
@@ -17166,10 +17166,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>470908</v>
+        <v>470887</v>
       </c>
       <c r="R153" t="n">
-        <v>6770622</v>
+        <v>6770658</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17237,13 +17237,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959037</t>
+          <t>https://artportalen.se/Sighting/129958895</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129959060</v>
+        <v>129958937</v>
       </c>
       <c r="B154" t="n">
         <v>79327</v>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>470926</v>
+        <v>470897</v>
       </c>
       <c r="R154" t="n">
-        <v>6770613</v>
+        <v>6770647</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17349,13 +17349,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959060</t>
+          <t>https://artportalen.se/Sighting/129958937</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129959250</v>
+        <v>129959037</v>
       </c>
       <c r="B155" t="n">
         <v>79327</v>
@@ -17390,10 +17390,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470943</v>
+        <v>470908</v>
       </c>
       <c r="R155" t="n">
-        <v>6770559</v>
+        <v>6770622</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17461,13 +17461,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959250</t>
+          <t>https://artportalen.se/Sighting/129959037</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129959256</v>
+        <v>129959060</v>
       </c>
       <c r="B156" t="n">
         <v>79327</v>
@@ -17502,10 +17502,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>470922</v>
+        <v>470926</v>
       </c>
       <c r="R156" t="n">
-        <v>6770556</v>
+        <v>6770613</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17573,13 +17573,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959256</t>
+          <t>https://artportalen.se/Sighting/129959060</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129959294</v>
+        <v>129959250</v>
       </c>
       <c r="B157" t="n">
         <v>79327</v>
@@ -17614,10 +17614,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>470904</v>
+        <v>470943</v>
       </c>
       <c r="R157" t="n">
-        <v>6770537</v>
+        <v>6770559</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17685,13 +17685,13 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959294</t>
+          <t>https://artportalen.se/Sighting/129959250</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129959303</v>
+        <v>129959256</v>
       </c>
       <c r="B158" t="n">
         <v>79327</v>
@@ -17726,10 +17726,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470879</v>
+        <v>470922</v>
       </c>
       <c r="R158" t="n">
-        <v>6770545</v>
+        <v>6770556</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17797,13 +17797,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959303</t>
+          <t>https://artportalen.se/Sighting/129959256</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129959375</v>
+        <v>129959294</v>
       </c>
       <c r="B159" t="n">
         <v>79327</v>
@@ -17838,10 +17838,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>470851</v>
+        <v>470904</v>
       </c>
       <c r="R159" t="n">
-        <v>6770520</v>
+        <v>6770537</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17909,13 +17909,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959375</t>
+          <t>https://artportalen.se/Sighting/129959294</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129959389</v>
+        <v>129959303</v>
       </c>
       <c r="B160" t="n">
         <v>79327</v>
@@ -17950,10 +17950,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>470824</v>
+        <v>470879</v>
       </c>
       <c r="R160" t="n">
-        <v>6770523</v>
+        <v>6770545</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18021,13 +18021,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959389</t>
+          <t>https://artportalen.se/Sighting/129959303</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129959479</v>
+        <v>129959375</v>
       </c>
       <c r="B161" t="n">
         <v>79327</v>
@@ -18062,10 +18062,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>470837</v>
+        <v>470851</v>
       </c>
       <c r="R161" t="n">
-        <v>6770498</v>
+        <v>6770520</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18133,13 +18133,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959479</t>
+          <t>https://artportalen.se/Sighting/129959375</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129959501</v>
+        <v>129959389</v>
       </c>
       <c r="B162" t="n">
         <v>79327</v>
@@ -18174,10 +18174,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>470807</v>
+        <v>470824</v>
       </c>
       <c r="R162" t="n">
-        <v>6770491</v>
+        <v>6770523</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18245,13 +18245,13 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959501</t>
+          <t>https://artportalen.se/Sighting/129959389</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129959519</v>
+        <v>129959479</v>
       </c>
       <c r="B163" t="n">
         <v>79327</v>
@@ -18286,10 +18286,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>470822</v>
+        <v>470837</v>
       </c>
       <c r="R163" t="n">
-        <v>6770452</v>
+        <v>6770498</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18357,13 +18357,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959519</t>
+          <t>https://artportalen.se/Sighting/129959479</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129959692</v>
+        <v>129959501</v>
       </c>
       <c r="B164" t="n">
         <v>79327</v>
@@ -18398,10 +18398,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>470864</v>
+        <v>470807</v>
       </c>
       <c r="R164" t="n">
-        <v>6770438</v>
+        <v>6770491</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18469,13 +18469,13 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959692</t>
+          <t>https://artportalen.se/Sighting/129959501</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129959740</v>
+        <v>129959519</v>
       </c>
       <c r="B165" t="n">
         <v>79327</v>
@@ -18510,10 +18510,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>470905</v>
+        <v>470822</v>
       </c>
       <c r="R165" t="n">
-        <v>6770435</v>
+        <v>6770452</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18581,13 +18581,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959740</t>
+          <t>https://artportalen.se/Sighting/129959519</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129959772</v>
+        <v>129959692</v>
       </c>
       <c r="B166" t="n">
         <v>79327</v>
@@ -18622,10 +18622,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470900</v>
+        <v>470864</v>
       </c>
       <c r="R166" t="n">
-        <v>6770473</v>
+        <v>6770438</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18693,13 +18693,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959772</t>
+          <t>https://artportalen.se/Sighting/129959692</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129959808</v>
+        <v>129959740</v>
       </c>
       <c r="B167" t="n">
         <v>79327</v>
@@ -18734,10 +18734,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470942</v>
+        <v>470905</v>
       </c>
       <c r="R167" t="n">
-        <v>6770455</v>
+        <v>6770435</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18805,13 +18805,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959808</t>
+          <t>https://artportalen.se/Sighting/129959740</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129959994</v>
+        <v>129959772</v>
       </c>
       <c r="B168" t="n">
         <v>79327</v>
@@ -18846,10 +18846,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>470954</v>
+        <v>470900</v>
       </c>
       <c r="R168" t="n">
-        <v>6770475</v>
+        <v>6770473</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18917,13 +18917,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959994</t>
+          <t>https://artportalen.se/Sighting/129959772</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129960002</v>
+        <v>129959808</v>
       </c>
       <c r="B169" t="n">
         <v>79327</v>
@@ -18958,10 +18958,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>470932</v>
+        <v>470942</v>
       </c>
       <c r="R169" t="n">
-        <v>6770480</v>
+        <v>6770455</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19029,13 +19029,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960002</t>
+          <t>https://artportalen.se/Sighting/129959808</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129960437</v>
+        <v>129959994</v>
       </c>
       <c r="B170" t="n">
         <v>79327</v>
@@ -19070,10 +19070,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>470948</v>
+        <v>470954</v>
       </c>
       <c r="R170" t="n">
-        <v>6770533</v>
+        <v>6770475</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19141,13 +19141,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960437</t>
+          <t>https://artportalen.se/Sighting/129959994</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129960691</v>
+        <v>129960002</v>
       </c>
       <c r="B171" t="n">
         <v>79327</v>
@@ -19182,10 +19182,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>471056</v>
+        <v>470932</v>
       </c>
       <c r="R171" t="n">
-        <v>6770494</v>
+        <v>6770480</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19253,13 +19253,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960691</t>
+          <t>https://artportalen.se/Sighting/129960002</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129960763</v>
+        <v>129960437</v>
       </c>
       <c r="B172" t="n">
         <v>79327</v>
@@ -19294,10 +19294,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>471062</v>
+        <v>470948</v>
       </c>
       <c r="R172" t="n">
-        <v>6770538</v>
+        <v>6770533</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19365,13 +19365,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960763</t>
+          <t>https://artportalen.se/Sighting/129960437</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129960790</v>
+        <v>129960691</v>
       </c>
       <c r="B173" t="n">
         <v>79327</v>
@@ -19406,10 +19406,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471073</v>
+        <v>471056</v>
       </c>
       <c r="R173" t="n">
-        <v>6770551</v>
+        <v>6770494</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19477,13 +19477,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960790</t>
+          <t>https://artportalen.se/Sighting/129960691</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129960823</v>
+        <v>129960763</v>
       </c>
       <c r="B174" t="n">
         <v>79327</v>
@@ -19518,10 +19518,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>471078</v>
+        <v>471062</v>
       </c>
       <c r="R174" t="n">
-        <v>6770561</v>
+        <v>6770538</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19566,11 +19566,6 @@
           <t>09:55</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
@@ -19594,13 +19589,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960823</t>
+          <t>https://artportalen.se/Sighting/129960763</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129960843</v>
+        <v>129960790</v>
       </c>
       <c r="B175" t="n">
         <v>79327</v>
@@ -19635,10 +19630,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471097</v>
+        <v>471073</v>
       </c>
       <c r="R175" t="n">
-        <v>6770561</v>
+        <v>6770551</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19706,13 +19701,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960843</t>
+          <t>https://artportalen.se/Sighting/129960790</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129960864</v>
+        <v>129960823</v>
       </c>
       <c r="B176" t="n">
         <v>79327</v>
@@ -19747,10 +19742,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471116</v>
+        <v>471078</v>
       </c>
       <c r="R176" t="n">
-        <v>6770565</v>
+        <v>6770561</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19795,6 +19790,11 @@
           <t>09:55</t>
         </is>
       </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
@@ -19818,13 +19818,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960864</t>
+          <t>https://artportalen.se/Sighting/129960823</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129960884</v>
+        <v>129960843</v>
       </c>
       <c r="B177" t="n">
         <v>79327</v>
@@ -19859,10 +19859,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>471129</v>
+        <v>471097</v>
       </c>
       <c r="R177" t="n">
-        <v>6770567</v>
+        <v>6770561</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19930,13 +19930,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960884</t>
+          <t>https://artportalen.se/Sighting/129960843</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129960891</v>
+        <v>129960864</v>
       </c>
       <c r="B178" t="n">
         <v>79327</v>
@@ -19971,10 +19971,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>471147</v>
+        <v>471116</v>
       </c>
       <c r="R178" t="n">
-        <v>6770575</v>
+        <v>6770565</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20042,13 +20042,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960891</t>
+          <t>https://artportalen.se/Sighting/129960864</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129960901</v>
+        <v>129960884</v>
       </c>
       <c r="B179" t="n">
         <v>79327</v>
@@ -20083,10 +20083,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>471185</v>
+        <v>471129</v>
       </c>
       <c r="R179" t="n">
-        <v>6770590</v>
+        <v>6770567</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20154,13 +20154,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960901</t>
+          <t>https://artportalen.se/Sighting/129960884</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129960929</v>
+        <v>129960891</v>
       </c>
       <c r="B180" t="n">
         <v>79327</v>
@@ -20195,10 +20195,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>471159</v>
+        <v>471147</v>
       </c>
       <c r="R180" t="n">
-        <v>6770613</v>
+        <v>6770575</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20266,13 +20266,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960929</t>
+          <t>https://artportalen.se/Sighting/129960891</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129961603</v>
+        <v>129960901</v>
       </c>
       <c r="B181" t="n">
         <v>79327</v>
@@ -20307,10 +20307,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471262</v>
+        <v>471185</v>
       </c>
       <c r="R181" t="n">
-        <v>6770622</v>
+        <v>6770590</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20378,13 +20378,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961603</t>
+          <t>https://artportalen.se/Sighting/129960901</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129961818</v>
+        <v>129960929</v>
       </c>
       <c r="B182" t="n">
         <v>79327</v>
@@ -20419,10 +20419,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471228</v>
+        <v>471159</v>
       </c>
       <c r="R182" t="n">
-        <v>6770667</v>
+        <v>6770613</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20490,13 +20490,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961818</t>
+          <t>https://artportalen.se/Sighting/129960929</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129961937</v>
+        <v>129961603</v>
       </c>
       <c r="B183" t="n">
         <v>79327</v>
@@ -20531,10 +20531,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>471216</v>
+        <v>471262</v>
       </c>
       <c r="R183" t="n">
-        <v>6770650</v>
+        <v>6770622</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20602,13 +20602,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961937</t>
+          <t>https://artportalen.se/Sighting/129961603</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129962073</v>
+        <v>129961818</v>
       </c>
       <c r="B184" t="n">
         <v>79327</v>
@@ -20643,10 +20643,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>471222</v>
+        <v>471228</v>
       </c>
       <c r="R184" t="n">
-        <v>6770635</v>
+        <v>6770667</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20714,13 +20714,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962073</t>
+          <t>https://artportalen.se/Sighting/129961818</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129962119</v>
+        <v>129961937</v>
       </c>
       <c r="B185" t="n">
         <v>79327</v>
@@ -20755,10 +20755,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>471156</v>
+        <v>471216</v>
       </c>
       <c r="R185" t="n">
-        <v>6770665</v>
+        <v>6770650</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20826,13 +20826,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962119</t>
+          <t>https://artportalen.se/Sighting/129961937</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129962224</v>
+        <v>129962073</v>
       </c>
       <c r="B186" t="n">
         <v>79327</v>
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>471098</v>
+        <v>471222</v>
       </c>
       <c r="R186" t="n">
-        <v>6770634</v>
+        <v>6770635</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20938,13 +20938,13 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962224</t>
+          <t>https://artportalen.se/Sighting/129962073</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129962243</v>
+        <v>129962119</v>
       </c>
       <c r="B187" t="n">
         <v>79327</v>
@@ -20979,10 +20979,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>471074</v>
+        <v>471156</v>
       </c>
       <c r="R187" t="n">
-        <v>6770617</v>
+        <v>6770665</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21050,13 +21050,13 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962243</t>
+          <t>https://artportalen.se/Sighting/129962119</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129962260</v>
+        <v>129962224</v>
       </c>
       <c r="B188" t="n">
         <v>79327</v>
@@ -21091,10 +21091,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>471044</v>
+        <v>471098</v>
       </c>
       <c r="R188" t="n">
-        <v>6770615</v>
+        <v>6770634</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21162,13 +21162,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962260</t>
+          <t>https://artportalen.se/Sighting/129962224</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129962290</v>
+        <v>129962243</v>
       </c>
       <c r="B189" t="n">
         <v>79327</v>
@@ -21203,10 +21203,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>471033</v>
+        <v>471074</v>
       </c>
       <c r="R189" t="n">
-        <v>6770614</v>
+        <v>6770617</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21274,13 +21274,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962290</t>
+          <t>https://artportalen.se/Sighting/129962243</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129962320</v>
+        <v>129962260</v>
       </c>
       <c r="B190" t="n">
         <v>79327</v>
@@ -21315,10 +21315,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>471024</v>
+        <v>471044</v>
       </c>
       <c r="R190" t="n">
-        <v>6770624</v>
+        <v>6770615</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21386,13 +21386,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962320</t>
+          <t>https://artportalen.se/Sighting/129962260</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129962351</v>
+        <v>129962290</v>
       </c>
       <c r="B191" t="n">
         <v>79327</v>
@@ -21427,10 +21427,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>471017</v>
+        <v>471033</v>
       </c>
       <c r="R191" t="n">
-        <v>6770613</v>
+        <v>6770614</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21498,13 +21498,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962351</t>
+          <t>https://artportalen.se/Sighting/129962290</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129962379</v>
+        <v>129962320</v>
       </c>
       <c r="B192" t="n">
         <v>79327</v>
@@ -21539,10 +21539,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>470996</v>
+        <v>471024</v>
       </c>
       <c r="R192" t="n">
-        <v>6770611</v>
+        <v>6770624</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21610,13 +21610,13 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962379</t>
+          <t>https://artportalen.se/Sighting/129962320</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129962390</v>
+        <v>129962351</v>
       </c>
       <c r="B193" t="n">
         <v>79327</v>
@@ -21651,10 +21651,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>471004</v>
+        <v>471017</v>
       </c>
       <c r="R193" t="n">
-        <v>6770581</v>
+        <v>6770613</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21722,13 +21722,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962390</t>
+          <t>https://artportalen.se/Sighting/129962351</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129962417</v>
+        <v>129962379</v>
       </c>
       <c r="B194" t="n">
         <v>79327</v>
@@ -21763,10 +21763,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>471002</v>
+        <v>470996</v>
       </c>
       <c r="R194" t="n">
-        <v>6770618</v>
+        <v>6770611</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21834,13 +21834,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962417</t>
+          <t>https://artportalen.se/Sighting/129962379</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129962443</v>
+        <v>129962390</v>
       </c>
       <c r="B195" t="n">
         <v>79327</v>
@@ -21875,10 +21875,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>470989</v>
+        <v>471004</v>
       </c>
       <c r="R195" t="n">
-        <v>6770629</v>
+        <v>6770581</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21946,13 +21946,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962443</t>
+          <t>https://artportalen.se/Sighting/129962390</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129962446</v>
+        <v>129962417</v>
       </c>
       <c r="B196" t="n">
         <v>79327</v>
@@ -21987,10 +21987,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>470993</v>
+        <v>471002</v>
       </c>
       <c r="R196" t="n">
-        <v>6770643</v>
+        <v>6770618</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22058,56 +22058,51 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962446</t>
+          <t>https://artportalen.se/Sighting/129962417</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129944452</v>
+        <v>129962443</v>
       </c>
       <c r="B197" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>471330</v>
+        <v>470989</v>
       </c>
       <c r="R197" t="n">
-        <v>6770712</v>
+        <v>6770629</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22134,22 +22129,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22175,56 +22170,51 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944452</t>
+          <t>https://artportalen.se/Sighting/129962443</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129945156</v>
+        <v>129962446</v>
       </c>
       <c r="B198" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>471198</v>
+        <v>470993</v>
       </c>
       <c r="R198" t="n">
-        <v>6770725</v>
+        <v>6770643</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22251,22 +22241,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22292,13 +22282,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945156</t>
+          <t>https://artportalen.se/Sighting/129962446</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129945440</v>
+        <v>129944452</v>
       </c>
       <c r="B199" t="n">
         <v>57950</v>
@@ -22329,7 +22319,7 @@
       <c r="I199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -22338,10 +22328,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471189</v>
+        <v>471330</v>
       </c>
       <c r="R199" t="n">
-        <v>6770706</v>
+        <v>6770712</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22409,13 +22399,13 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945440</t>
+          <t>https://artportalen.se/Sighting/129944452</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129946321</v>
+        <v>129945156</v>
       </c>
       <c r="B200" t="n">
         <v>57950</v>
@@ -22446,7 +22436,7 @@
       <c r="I200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22455,10 +22445,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>470871</v>
+        <v>471198</v>
       </c>
       <c r="R200" t="n">
-        <v>6770635</v>
+        <v>6770725</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22526,13 +22516,13 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946321</t>
+          <t>https://artportalen.se/Sighting/129945156</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129946365</v>
+        <v>129945440</v>
       </c>
       <c r="B201" t="n">
         <v>57950</v>
@@ -22572,10 +22562,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>470910</v>
+        <v>471189</v>
       </c>
       <c r="R201" t="n">
-        <v>6770605</v>
+        <v>6770706</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22643,13 +22633,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946365</t>
+          <t>https://artportalen.se/Sighting/129945440</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129946391</v>
+        <v>129946321</v>
       </c>
       <c r="B202" t="n">
         <v>57950</v>
@@ -22680,7 +22670,7 @@
       <c r="I202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22689,10 +22679,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>470921</v>
+        <v>470871</v>
       </c>
       <c r="R202" t="n">
-        <v>6770579</v>
+        <v>6770635</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22760,13 +22750,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946391</t>
+          <t>https://artportalen.se/Sighting/129946321</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129946436</v>
+        <v>129946365</v>
       </c>
       <c r="B203" t="n">
         <v>57950</v>
@@ -22797,7 +22787,7 @@
       <c r="I203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22806,10 +22796,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>470971</v>
+        <v>470910</v>
       </c>
       <c r="R203" t="n">
-        <v>6770603</v>
+        <v>6770605</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22877,13 +22867,13 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946436</t>
+          <t>https://artportalen.se/Sighting/129946365</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129954441</v>
+        <v>129946391</v>
       </c>
       <c r="B204" t="n">
         <v>57950</v>
@@ -22923,10 +22913,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>471052</v>
+        <v>470921</v>
       </c>
       <c r="R204" t="n">
-        <v>6770696</v>
+        <v>6770579</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22953,22 +22943,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22994,13 +22984,13 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954441</t>
+          <t>https://artportalen.se/Sighting/129946391</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129957253</v>
+        <v>129946436</v>
       </c>
       <c r="B205" t="n">
         <v>57950</v>
@@ -23031,7 +23021,7 @@
       <c r="I205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -23040,10 +23030,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>470916</v>
+        <v>470971</v>
       </c>
       <c r="R205" t="n">
-        <v>6770721</v>
+        <v>6770603</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23070,22 +23060,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23111,13 +23101,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129957253</t>
+          <t>https://artportalen.se/Sighting/129946436</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129958691</v>
+        <v>129954441</v>
       </c>
       <c r="B206" t="n">
         <v>57950</v>
@@ -23157,10 +23147,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470844</v>
+        <v>471052</v>
       </c>
       <c r="R206" t="n">
-        <v>6770699</v>
+        <v>6770696</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23228,13 +23218,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958691</t>
+          <t>https://artportalen.se/Sighting/129954441</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129959434</v>
+        <v>129957253</v>
       </c>
       <c r="B207" t="n">
         <v>57950</v>
@@ -23274,10 +23264,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470824</v>
+        <v>470916</v>
       </c>
       <c r="R207" t="n">
-        <v>6770523</v>
+        <v>6770721</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23345,13 +23335,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959434</t>
+          <t>https://artportalen.se/Sighting/129957253</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129959567</v>
+        <v>129958691</v>
       </c>
       <c r="B208" t="n">
         <v>57950</v>
@@ -23391,10 +23381,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470822</v>
+        <v>470844</v>
       </c>
       <c r="R208" t="n">
-        <v>6770452</v>
+        <v>6770699</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23462,13 +23452,13 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959567</t>
+          <t>https://artportalen.se/Sighting/129958691</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129959730</v>
+        <v>129959434</v>
       </c>
       <c r="B209" t="n">
         <v>57950</v>
@@ -23499,7 +23489,7 @@
       <c r="I209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -23508,10 +23498,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>470868</v>
+        <v>470824</v>
       </c>
       <c r="R209" t="n">
-        <v>6770431</v>
+        <v>6770523</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23579,13 +23569,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959730</t>
+          <t>https://artportalen.se/Sighting/129959434</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129959870</v>
+        <v>129959567</v>
       </c>
       <c r="B210" t="n">
         <v>57950</v>
@@ -23616,7 +23606,7 @@
       <c r="I210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -23625,10 +23615,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>470952</v>
+        <v>470822</v>
       </c>
       <c r="R210" t="n">
-        <v>6770464</v>
+        <v>6770452</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23696,13 +23686,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959870</t>
+          <t>https://artportalen.se/Sighting/129959567</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129960642</v>
+        <v>129959730</v>
       </c>
       <c r="B211" t="n">
         <v>57950</v>
@@ -23742,10 +23732,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>471025</v>
+        <v>470868</v>
       </c>
       <c r="R211" t="n">
-        <v>6770488</v>
+        <v>6770431</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23813,13 +23803,13 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960642</t>
+          <t>https://artportalen.se/Sighting/129959730</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129962343</v>
+        <v>129959870</v>
       </c>
       <c r="B212" t="n">
         <v>57950</v>
@@ -23850,7 +23840,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -23859,10 +23849,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>471017</v>
+        <v>470952</v>
       </c>
       <c r="R212" t="n">
-        <v>6770613</v>
+        <v>6770464</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23930,13 +23920,13 @@
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962343</t>
+          <t>https://artportalen.se/Sighting/129959870</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129962374</v>
+        <v>129960642</v>
       </c>
       <c r="B213" t="n">
         <v>57950</v>
@@ -23967,7 +23957,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23976,10 +23966,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>470996</v>
+        <v>471025</v>
       </c>
       <c r="R213" t="n">
-        <v>6770611</v>
+        <v>6770488</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -24047,13 +24037,13 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962374</t>
+          <t>https://artportalen.se/Sighting/129960642</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129962430</v>
+        <v>129962343</v>
       </c>
       <c r="B214" t="n">
         <v>57950</v>
@@ -24084,7 +24074,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -24093,10 +24083,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>470989</v>
+        <v>471017</v>
       </c>
       <c r="R214" t="n">
-        <v>6770629</v>
+        <v>6770613</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24164,48 +24154,44 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962430</t>
+          <t>https://artportalen.se/Sighting/129962343</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129944878</v>
+        <v>129962374</v>
       </c>
       <c r="B215" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -24214,13 +24200,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471258</v>
+        <v>470996</v>
       </c>
       <c r="R215" t="n">
-        <v>6770712</v>
+        <v>6770611</v>
       </c>
       <c r="S215" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -24244,22 +24230,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24285,16 +24271,16 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944878</t>
+          <t>https://artportalen.se/Sighting/129962374</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129944062</v>
+        <v>129962430</v>
       </c>
       <c r="B216" t="n">
-        <v>8455</v>
+        <v>57950</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24302,27 +24288,27 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -24331,10 +24317,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471432</v>
+        <v>470989</v>
       </c>
       <c r="R216" t="n">
-        <v>6770716</v>
+        <v>6770629</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24361,22 +24347,22 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24402,44 +24388,48 @@
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944062</t>
+          <t>https://artportalen.se/Sighting/129962430</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129944158</v>
+        <v>129944878</v>
       </c>
       <c r="B217" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -24448,13 +24438,13 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>471363</v>
+        <v>471258</v>
       </c>
       <c r="R217" t="n">
-        <v>6770736</v>
+        <v>6770712</v>
       </c>
       <c r="S217" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -24519,13 +24509,13 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944158</t>
+          <t>https://artportalen.se/Sighting/129944878</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129944454</v>
+        <v>129944062</v>
       </c>
       <c r="B218" t="n">
         <v>8455</v>
@@ -24554,16 +24544,21 @@
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>471330</v>
+        <v>471432</v>
       </c>
       <c r="R218" t="n">
-        <v>6770712</v>
+        <v>6770716</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24631,13 +24626,13 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129944454</t>
+          <t>https://artportalen.se/Sighting/129944062</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129945161</v>
+        <v>129944158</v>
       </c>
       <c r="B219" t="n">
         <v>8455</v>
@@ -24677,10 +24672,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471198</v>
+        <v>471363</v>
       </c>
       <c r="R219" t="n">
-        <v>6770725</v>
+        <v>6770736</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24748,13 +24743,13 @@
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945161</t>
+          <t>https://artportalen.se/Sighting/129944158</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129945444</v>
+        <v>129944454</v>
       </c>
       <c r="B220" t="n">
         <v>8455</v>
@@ -24783,21 +24778,16 @@
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>471189</v>
+        <v>471330</v>
       </c>
       <c r="R220" t="n">
-        <v>6770706</v>
+        <v>6770712</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24865,13 +24855,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129945444</t>
+          <t>https://artportalen.se/Sighting/129944454</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129946047</v>
+        <v>129945161</v>
       </c>
       <c r="B221" t="n">
         <v>8455</v>
@@ -24900,16 +24890,21 @@
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>471161</v>
+        <v>471198</v>
       </c>
       <c r="R221" t="n">
-        <v>6770705</v>
+        <v>6770725</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24977,13 +24972,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946047</t>
+          <t>https://artportalen.se/Sighting/129945161</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129946334</v>
+        <v>129945444</v>
       </c>
       <c r="B222" t="n">
         <v>8455</v>
@@ -25023,10 +25018,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470871</v>
+        <v>471189</v>
       </c>
       <c r="R222" t="n">
-        <v>6770635</v>
+        <v>6770706</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25094,13 +25089,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946334</t>
+          <t>https://artportalen.se/Sighting/129945444</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129946444</v>
+        <v>129946047</v>
       </c>
       <c r="B223" t="n">
         <v>8455</v>
@@ -25129,21 +25124,16 @@
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>470971</v>
+        <v>471161</v>
       </c>
       <c r="R223" t="n">
-        <v>6770603</v>
+        <v>6770705</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25211,13 +25201,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129946444</t>
+          <t>https://artportalen.se/Sighting/129946047</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129954662</v>
+        <v>129946334</v>
       </c>
       <c r="B224" t="n">
         <v>8455</v>
@@ -25257,10 +25247,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470941</v>
+        <v>470871</v>
       </c>
       <c r="R224" t="n">
-        <v>6770708</v>
+        <v>6770635</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25287,22 +25277,22 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25328,13 +25318,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129954662</t>
+          <t>https://artportalen.se/Sighting/129946334</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129958131</v>
+        <v>129946444</v>
       </c>
       <c r="B225" t="n">
         <v>8455</v>
@@ -25374,10 +25364,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470869</v>
+        <v>470971</v>
       </c>
       <c r="R225" t="n">
-        <v>6770702</v>
+        <v>6770603</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25404,22 +25394,22 @@
       </c>
       <c r="Y225" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25445,13 +25435,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958131</t>
+          <t>https://artportalen.se/Sighting/129946444</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129958199</v>
+        <v>129954662</v>
       </c>
       <c r="B226" t="n">
         <v>8455</v>
@@ -25491,10 +25481,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>470823</v>
+        <v>470941</v>
       </c>
       <c r="R226" t="n">
-        <v>6770705</v>
+        <v>6770708</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25562,13 +25552,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958199</t>
+          <t>https://artportalen.se/Sighting/129954662</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129958686</v>
+        <v>129958131</v>
       </c>
       <c r="B227" t="n">
         <v>8455</v>
@@ -25608,10 +25598,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>470844</v>
+        <v>470869</v>
       </c>
       <c r="R227" t="n">
-        <v>6770699</v>
+        <v>6770702</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25679,13 +25669,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129958686</t>
+          <t>https://artportalen.se/Sighting/129958131</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129959110</v>
+        <v>129958199</v>
       </c>
       <c r="B228" t="n">
         <v>8455</v>
@@ -25725,10 +25715,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470926</v>
+        <v>470823</v>
       </c>
       <c r="R228" t="n">
-        <v>6770613</v>
+        <v>6770705</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25796,13 +25786,13 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959110</t>
+          <t>https://artportalen.se/Sighting/129958199</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129959223</v>
+        <v>129958686</v>
       </c>
       <c r="B229" t="n">
         <v>8455</v>
@@ -25842,10 +25832,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>470921</v>
+        <v>470844</v>
       </c>
       <c r="R229" t="n">
-        <v>6770579</v>
+        <v>6770699</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25913,13 +25903,13 @@
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959223</t>
+          <t>https://artportalen.se/Sighting/129958686</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129959285</v>
+        <v>129959110</v>
       </c>
       <c r="B230" t="n">
         <v>8455</v>
@@ -25959,10 +25949,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>470922</v>
+        <v>470926</v>
       </c>
       <c r="R230" t="n">
-        <v>6770556</v>
+        <v>6770613</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -26030,13 +26020,13 @@
       <c r="AY230" t="inlineStr"/>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959285</t>
+          <t>https://artportalen.se/Sighting/129959110</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129959441</v>
+        <v>129959223</v>
       </c>
       <c r="B231" t="n">
         <v>8455</v>
@@ -26076,10 +26066,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>470824</v>
+        <v>470921</v>
       </c>
       <c r="R231" t="n">
-        <v>6770523</v>
+        <v>6770579</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -26147,13 +26137,13 @@
       <c r="AY231" t="inlineStr"/>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959441</t>
+          <t>https://artportalen.se/Sighting/129959223</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129959579</v>
+        <v>129959285</v>
       </c>
       <c r="B232" t="n">
         <v>8455</v>
@@ -26193,10 +26183,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>470822</v>
+        <v>470922</v>
       </c>
       <c r="R232" t="n">
-        <v>6770452</v>
+        <v>6770556</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26264,13 +26254,13 @@
       <c r="AY232" t="inlineStr"/>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959579</t>
+          <t>https://artportalen.se/Sighting/129959285</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129959710</v>
+        <v>129959441</v>
       </c>
       <c r="B233" t="n">
         <v>8455</v>
@@ -26310,10 +26300,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>470864</v>
+        <v>470824</v>
       </c>
       <c r="R233" t="n">
-        <v>6770438</v>
+        <v>6770523</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26381,13 +26371,13 @@
       <c r="AY233" t="inlineStr"/>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959710</t>
+          <t>https://artportalen.se/Sighting/129959441</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129959735</v>
+        <v>129959579</v>
       </c>
       <c r="B234" t="n">
         <v>8455</v>
@@ -26427,10 +26417,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>470868</v>
+        <v>470822</v>
       </c>
       <c r="R234" t="n">
-        <v>6770431</v>
+        <v>6770452</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26498,13 +26488,13 @@
       <c r="AY234" t="inlineStr"/>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959735</t>
+          <t>https://artportalen.se/Sighting/129959579</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>129959924</v>
+        <v>129959710</v>
       </c>
       <c r="B235" t="n">
         <v>8455</v>
@@ -26544,10 +26534,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>470944</v>
+        <v>470864</v>
       </c>
       <c r="R235" t="n">
-        <v>6770458</v>
+        <v>6770438</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26615,13 +26605,13 @@
       <c r="AY235" t="inlineStr"/>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129959924</t>
+          <t>https://artportalen.se/Sighting/129959710</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129960514</v>
+        <v>129959735</v>
       </c>
       <c r="B236" t="n">
         <v>8455</v>
@@ -26661,13 +26651,13 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>470976</v>
+        <v>470868</v>
       </c>
       <c r="R236" t="n">
-        <v>6770536</v>
+        <v>6770431</v>
       </c>
       <c r="S236" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -26732,13 +26722,13 @@
       <c r="AY236" t="inlineStr"/>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960514</t>
+          <t>https://artportalen.se/Sighting/129959735</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129960657</v>
+        <v>129959924</v>
       </c>
       <c r="B237" t="n">
         <v>8455</v>
@@ -26778,10 +26768,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>471025</v>
+        <v>470944</v>
       </c>
       <c r="R237" t="n">
-        <v>6770488</v>
+        <v>6770458</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26849,13 +26839,13 @@
       <c r="AY237" t="inlineStr"/>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960657</t>
+          <t>https://artportalen.se/Sighting/129959924</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129960746</v>
+        <v>129960514</v>
       </c>
       <c r="B238" t="n">
         <v>8455</v>
@@ -26895,13 +26885,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>471053</v>
+        <v>470976</v>
       </c>
       <c r="R238" t="n">
-        <v>6770528</v>
+        <v>6770536</v>
       </c>
       <c r="S238" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -26966,13 +26956,13 @@
       <c r="AY238" t="inlineStr"/>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960746</t>
+          <t>https://artportalen.se/Sighting/129960514</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129960827</v>
+        <v>129960657</v>
       </c>
       <c r="B239" t="n">
         <v>8455</v>
@@ -27012,10 +27002,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>471078</v>
+        <v>471025</v>
       </c>
       <c r="R239" t="n">
-        <v>6770561</v>
+        <v>6770488</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -27083,13 +27073,13 @@
       <c r="AY239" t="inlineStr"/>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129960827</t>
+          <t>https://artportalen.se/Sighting/129960657</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129961109</v>
+        <v>129960746</v>
       </c>
       <c r="B240" t="n">
         <v>8455</v>
@@ -27129,10 +27119,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>471175</v>
+        <v>471053</v>
       </c>
       <c r="R240" t="n">
-        <v>6770631</v>
+        <v>6770528</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -27200,13 +27190,13 @@
       <c r="AY240" t="inlineStr"/>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129961109</t>
+          <t>https://artportalen.se/Sighting/129960746</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129962346</v>
+        <v>129960827</v>
       </c>
       <c r="B241" t="n">
         <v>8455</v>
@@ -27246,10 +27236,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>471017</v>
+        <v>471078</v>
       </c>
       <c r="R241" t="n">
-        <v>6770613</v>
+        <v>6770561</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27317,13 +27307,13 @@
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962346</t>
+          <t>https://artportalen.se/Sighting/129960827</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129962376</v>
+        <v>129961109</v>
       </c>
       <c r="B242" t="n">
         <v>8455</v>
@@ -27363,10 +27353,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>470996</v>
+        <v>471175</v>
       </c>
       <c r="R242" t="n">
-        <v>6770611</v>
+        <v>6770631</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27434,13 +27424,13 @@
       <c r="AY242" t="inlineStr"/>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962376</t>
+          <t>https://artportalen.se/Sighting/129961109</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129962436</v>
+        <v>129962346</v>
       </c>
       <c r="B243" t="n">
         <v>8455</v>
@@ -27480,10 +27470,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>470989</v>
+        <v>471017</v>
       </c>
       <c r="R243" t="n">
-        <v>6770629</v>
+        <v>6770613</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27551,57 +27541,59 @@
       <c r="AY243" t="inlineStr"/>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129962436</t>
+          <t>https://artportalen.se/Sighting/129962346</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129271581</v>
+        <v>129962376</v>
       </c>
       <c r="B244" t="n">
-        <v>93228</v>
+        <v>8455</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>232140</v>
+        <v>106545</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
-      <c r="K244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>470835</v>
+        <v>470996</v>
       </c>
       <c r="R244" t="n">
-        <v>6770662</v>
+        <v>6770611</v>
       </c>
       <c r="S244" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -27625,12 +27617,22 @@
       </c>
       <c r="Y244" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27639,72 +27641,76 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
-      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
       <c r="AT244" t="inlineStr"/>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>Ville Pokela</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129271581</t>
+          <t>https://artportalen.se/Sighting/129962376</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>96714923</v>
+        <v>129962436</v>
       </c>
       <c r="B245" t="n">
-        <v>91402</v>
+        <v>8455</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>256703</v>
+        <v>106545</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>Bonäsheden, Dlr</t>
+          <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>470876</v>
+        <v>470989</v>
       </c>
       <c r="R245" t="n">
-        <v>6770446</v>
+        <v>6770629</v>
       </c>
       <c r="S245" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -27728,12 +27734,22 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27748,62 +27764,65 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714923</t>
+          <t>https://artportalen.se/Sighting/129962436</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>96714929</v>
+        <v>129271581</v>
       </c>
       <c r="B246" t="n">
-        <v>91402</v>
+        <v>93228</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>256703</v>
+        <v>232140</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Bonäsheden, Dlr</t>
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>471113</v>
+        <v>470835</v>
       </c>
       <c r="R246" t="n">
-        <v>6770726</v>
+        <v>6770662</v>
       </c>
       <c r="S246" t="n">
         <v>25</v>
@@ -27830,12 +27849,12 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -27844,30 +27863,31 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo</t>
+          <t>Ville Pokela</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714929</t>
+          <t>https://artportalen.se/Sighting/129271581</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>96714933</v>
+        <v>96714923</v>
       </c>
       <c r="B247" t="n">
         <v>91402</v>
@@ -27902,10 +27922,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>470806</v>
+        <v>470876</v>
       </c>
       <c r="R247" t="n">
-        <v>6770695</v>
+        <v>6770446</v>
       </c>
       <c r="S247" t="n">
         <v>25</v>
@@ -27963,13 +27983,13 @@
       <c r="AY247" t="inlineStr"/>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714933</t>
+          <t>https://artportalen.se/Sighting/96714923</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>96714941</v>
+        <v>96714929</v>
       </c>
       <c r="B248" t="n">
         <v>91402</v>
@@ -28004,10 +28024,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>471105</v>
+        <v>471113</v>
       </c>
       <c r="R248" t="n">
-        <v>6770716</v>
+        <v>6770726</v>
       </c>
       <c r="S248" t="n">
         <v>25</v>
@@ -28065,13 +28085,13 @@
       <c r="AY248" t="inlineStr"/>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714941</t>
+          <t>https://artportalen.se/Sighting/96714929</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>96714946</v>
+        <v>96714933</v>
       </c>
       <c r="B249" t="n">
         <v>91402</v>
@@ -28106,10 +28126,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>471072</v>
+        <v>470806</v>
       </c>
       <c r="R249" t="n">
-        <v>6770716</v>
+        <v>6770695</v>
       </c>
       <c r="S249" t="n">
         <v>25</v>
@@ -28167,13 +28187,13 @@
       <c r="AY249" t="inlineStr"/>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714946</t>
+          <t>https://artportalen.se/Sighting/96714933</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>96714952</v>
+        <v>96714941</v>
       </c>
       <c r="B250" t="n">
         <v>91402</v>
@@ -28208,10 +28228,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>470920</v>
+        <v>471105</v>
       </c>
       <c r="R250" t="n">
-        <v>6770687</v>
+        <v>6770716</v>
       </c>
       <c r="S250" t="n">
         <v>25</v>
@@ -28269,13 +28289,13 @@
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714952</t>
+          <t>https://artportalen.se/Sighting/96714941</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>96714953</v>
+        <v>96714946</v>
       </c>
       <c r="B251" t="n">
         <v>91402</v>
@@ -28310,10 +28330,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>471086</v>
+        <v>471072</v>
       </c>
       <c r="R251" t="n">
-        <v>6770698</v>
+        <v>6770716</v>
       </c>
       <c r="S251" t="n">
         <v>25</v>
@@ -28371,13 +28391,13 @@
       <c r="AY251" t="inlineStr"/>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714953</t>
+          <t>https://artportalen.se/Sighting/96714946</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>96714960</v>
+        <v>96714952</v>
       </c>
       <c r="B252" t="n">
         <v>91402</v>
@@ -28412,10 +28432,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>471091</v>
+        <v>470920</v>
       </c>
       <c r="R252" t="n">
-        <v>6770723</v>
+        <v>6770687</v>
       </c>
       <c r="S252" t="n">
         <v>25</v>
@@ -28473,13 +28493,13 @@
       <c r="AY252" t="inlineStr"/>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714960</t>
+          <t>https://artportalen.se/Sighting/96714952</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>96714973</v>
+        <v>96714953</v>
       </c>
       <c r="B253" t="n">
         <v>91402</v>
@@ -28514,10 +28534,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>471080</v>
+        <v>471086</v>
       </c>
       <c r="R253" t="n">
-        <v>6770598</v>
+        <v>6770698</v>
       </c>
       <c r="S253" t="n">
         <v>25</v>
@@ -28575,13 +28595,13 @@
       <c r="AY253" t="inlineStr"/>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714973</t>
+          <t>https://artportalen.se/Sighting/96714953</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>96714981</v>
+        <v>96714960</v>
       </c>
       <c r="B254" t="n">
         <v>91402</v>
@@ -28616,10 +28636,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>471483</v>
+        <v>471091</v>
       </c>
       <c r="R254" t="n">
-        <v>6770715</v>
+        <v>6770723</v>
       </c>
       <c r="S254" t="n">
         <v>25</v>
@@ -28677,13 +28697,13 @@
       <c r="AY254" t="inlineStr"/>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96714981</t>
+          <t>https://artportalen.se/Sighting/96714960</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>96715005</v>
+        <v>96714973</v>
       </c>
       <c r="B255" t="n">
         <v>91402</v>
@@ -28718,10 +28738,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>470830</v>
+        <v>471080</v>
       </c>
       <c r="R255" t="n">
-        <v>6770666</v>
+        <v>6770598</v>
       </c>
       <c r="S255" t="n">
         <v>25</v>
@@ -28779,13 +28799,13 @@
       <c r="AY255" t="inlineStr"/>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96715005</t>
+          <t>https://artportalen.se/Sighting/96714973</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>96715010</v>
+        <v>96714981</v>
       </c>
       <c r="B256" t="n">
         <v>91402</v>
@@ -28820,10 +28840,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>471253</v>
+        <v>471483</v>
       </c>
       <c r="R256" t="n">
-        <v>6770676</v>
+        <v>6770715</v>
       </c>
       <c r="S256" t="n">
         <v>25</v>
@@ -28880,6 +28900,210 @@
       </c>
       <c r="AY256" t="inlineStr"/>
       <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714981</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>96715005</v>
+      </c>
+      <c r="B257" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Bonäsheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>470830</v>
+      </c>
+      <c r="R257" t="n">
+        <v>6770666</v>
+      </c>
+      <c r="S257" t="n">
+        <v>25</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715005</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>96715010</v>
+      </c>
+      <c r="B258" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Bonäsheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>471253</v>
+      </c>
+      <c r="R258" t="n">
+        <v>6770676</v>
+      </c>
+      <c r="S258" t="n">
+        <v>25</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/96715010</t>
         </is>
@@ -29142,6 +29366,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8062,12 +8062,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Viktor Leo</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Viktor Leo</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>136837813</v>
       </c>
       <c r="B71" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93465</v>
+        <v>93466</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93466</v>
+        <v>93469</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93469</v>
+        <v>93470</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7000,7 +7000,7 @@
         <v>136837910</v>
       </c>
       <c r="B62" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>136836580</v>
       </c>
       <c r="B70" t="n">
-        <v>93470</v>
+        <v>93473</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
